--- a/Financial Analysis/GOOG.xlsx
+++ b/Financial Analysis/GOOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE59AD2E-C91E-4F8F-AFAD-541FA94E850B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A9ADDA-4C9C-475B-8D2E-EE8E672E2DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1C0874DB-3046-4806-9648-99CA4AF089C9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C0874DB-3046-4806-9648-99CA4AF089C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -919,14 +919,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>165.81</v>
+        <v>172.63</v>
       </c>
       <c r="E3" s="4">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45862</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>2021223.9000000001</v>
+        <v>2104359.6999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -992,7 +992,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>1898467.9000000001</v>
+        <v>1981603.6999999997</v>
       </c>
     </row>
   </sheetData>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="BI38" s="2">
         <f>Main!D3</f>
-        <v>165.81</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="BI39" s="10">
         <f>BI37/BI38-1</f>
-        <v>0.18618961424609415</v>
+        <v>0.13932746300263488</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">

--- a/Financial Analysis/GOOG.xlsx
+++ b/Financial Analysis/GOOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A9ADDA-4C9C-475B-8D2E-EE8E672E2DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EACB8E-A139-4162-8112-07BE11EDB7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C0874DB-3046-4806-9648-99CA4AF089C9}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
   <si>
     <t>GOOG</t>
   </si>
@@ -380,7 +380,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Q225 8K</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -496,14 +499,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -520,7 +523,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21206460" y="0"/>
+          <a:off x="21785580" y="0"/>
           <a:ext cx="0" cy="8862060"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -919,17 +922,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>172.63</v>
+        <v>249.85</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="4">
-        <v>45862</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -937,11 +940,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <f>5833+860+5497</f>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -950,7 +953,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>2104359.6999999997</v>
+        <v>3028681.6999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -958,11 +961,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <f>23466+72191+37982</f>
-        <v>133639</v>
+        <f>21036+74112+52574</f>
+        <v>147722</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -970,11 +973,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <f>10883</f>
-        <v>10883</v>
+        <f>23607</f>
+        <v>23607</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -983,7 +986,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>122756</v>
+        <v>124115</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -992,7 +995,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>1981603.6999999997</v>
+        <v>2904566.6999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1242,16 +1245,15 @@
         <v>50702</v>
       </c>
       <c r="AJ3" s="11">
-        <f>AF3*1.07</f>
-        <v>51904.630000000005</v>
+        <v>54190</v>
       </c>
       <c r="AK3" s="11">
-        <f t="shared" ref="AK3:AL3" si="0">AG3*1.07</f>
-        <v>52841.950000000004</v>
+        <f>AG3*1.1</f>
+        <v>54323.500000000007</v>
       </c>
       <c r="AL3" s="11">
-        <f t="shared" si="0"/>
-        <v>57816.380000000005</v>
+        <f>AH3*1.08</f>
+        <v>58356.72</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -1274,47 +1276,47 @@
       </c>
       <c r="AV3" s="1">
         <f>SUM(AI3:AL3)</f>
-        <v>213264.96000000002</v>
+        <v>217572.22</v>
       </c>
       <c r="AW3" s="1">
-        <f>AV3*1.05</f>
-        <v>223928.20800000004</v>
+        <f>AV3*1.07</f>
+        <v>232802.27540000001</v>
       </c>
       <c r="AX3" s="1">
-        <f>AW3*1.03</f>
-        <v>230646.05424000006</v>
+        <f>AW3*1.05</f>
+        <v>244442.38917000004</v>
       </c>
       <c r="AY3" s="1">
-        <f>AX3*1.03</f>
-        <v>237565.43586720005</v>
+        <f>AX3*1.04</f>
+        <v>254220.08473680005</v>
       </c>
       <c r="AZ3" s="1">
-        <f>AY3*1.02</f>
-        <v>242316.74458454407</v>
+        <f>AY3*1.03</f>
+        <v>261846.68727890405</v>
       </c>
       <c r="BA3" s="1">
-        <f t="shared" ref="BA3" si="1">AZ3*1.02</f>
-        <v>247163.07947623494</v>
+        <f t="shared" ref="BA3" si="0">AZ3*1.02</f>
+        <v>267083.62102448213</v>
       </c>
       <c r="BB3" s="1">
-        <f>BA3*1.01</f>
-        <v>249634.71027099728</v>
+        <f t="shared" ref="BB3" si="1">BA3*1.02</f>
+        <v>272425.29344497179</v>
       </c>
       <c r="BC3" s="1">
-        <f t="shared" ref="BC3:BF3" si="2">BB3*1.01</f>
-        <v>252131.05737370727</v>
+        <f t="shared" ref="BC3" si="2">BB3*1.02</f>
+        <v>277873.79931387125</v>
       </c>
       <c r="BD3" s="1">
-        <f t="shared" si="2"/>
-        <v>254652.36794744435</v>
+        <f t="shared" ref="BD3:BF3" si="3">BC3*1.01</f>
+        <v>280652.53730700997</v>
       </c>
       <c r="BE3" s="1">
-        <f t="shared" si="2"/>
-        <v>257198.8916269188</v>
+        <f t="shared" si="3"/>
+        <v>283459.06268008007</v>
       </c>
       <c r="BF3" s="1">
-        <f t="shared" si="2"/>
-        <v>259770.88054318799</v>
+        <f t="shared" si="3"/>
+        <v>286293.65330688085</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1355,7 +1357,7 @@
         <v>7952</v>
       </c>
       <c r="AD4" s="11">
-        <f t="shared" ref="AD4:AD9" si="3">AT4-AC4-AB4-AA4</f>
+        <f t="shared" ref="AD4:AD9" si="4">AT4-AC4-AB4-AA4</f>
         <v>9200</v>
       </c>
       <c r="AE4" s="11">
@@ -1374,16 +1376,15 @@
         <v>8927</v>
       </c>
       <c r="AJ4" s="11">
-        <f>AF4*1.08</f>
-        <v>9356.0400000000009</v>
+        <v>9796</v>
       </c>
       <c r="AK4" s="11">
-        <f>AG4*1.08</f>
-        <v>9634.68</v>
+        <f>AG4*1.11</f>
+        <v>9902.3100000000013</v>
       </c>
       <c r="AL4" s="11">
-        <f>AH4*1.05</f>
-        <v>10996.65</v>
+        <f>AH4*1.09</f>
+        <v>11415.570000000002</v>
       </c>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
@@ -1401,52 +1402,52 @@
         <v>31510</v>
       </c>
       <c r="AU4" s="1">
-        <f t="shared" ref="AU4:AU9" si="4">SUM(AE4:AH4)</f>
+        <f t="shared" ref="AU4:AU9" si="5">SUM(AE4:AH4)</f>
         <v>36147</v>
       </c>
       <c r="AV4" s="1">
-        <f t="shared" ref="AV4:AV9" si="5">SUM(AI4:AL4)</f>
-        <v>38914.370000000003</v>
+        <f t="shared" ref="AV4:AV9" si="6">SUM(AI4:AL4)</f>
+        <v>40040.880000000005</v>
       </c>
       <c r="AW4" s="1">
-        <f>AV4*1.06</f>
-        <v>41249.232200000006</v>
+        <f>AV4*1.07</f>
+        <v>42843.741600000008</v>
       </c>
       <c r="AX4" s="1">
         <f>AW4*1.05</f>
-        <v>43311.693810000012</v>
+        <v>44985.928680000012</v>
       </c>
       <c r="AY4" s="1">
         <f>AX4*1.04</f>
-        <v>45044.161562400011</v>
+        <v>46785.36582720001</v>
       </c>
       <c r="AZ4" s="1">
         <f>AY4*1.03</f>
-        <v>46395.486409272016</v>
+        <v>48188.926802016009</v>
       </c>
       <c r="BA4" s="1">
         <f>AZ4*1.03</f>
-        <v>47787.351001550182</v>
+        <v>49634.594606076491</v>
       </c>
       <c r="BB4" s="1">
         <f>BA4*1.02</f>
-        <v>48743.098021581187</v>
+        <v>50627.286498198024</v>
       </c>
       <c r="BC4" s="1">
-        <f t="shared" ref="BC4:BF4" si="6">BB4*1.02</f>
-        <v>49717.959982012813</v>
+        <f t="shared" ref="BC4:BF4" si="7">BB4*1.02</f>
+        <v>51639.832228161984</v>
       </c>
       <c r="BD4" s="1">
-        <f t="shared" si="6"/>
-        <v>50712.319181653067</v>
+        <f t="shared" si="7"/>
+        <v>52672.628872725225</v>
       </c>
       <c r="BE4" s="1">
-        <f t="shared" si="6"/>
-        <v>51726.565565286131</v>
+        <f t="shared" si="7"/>
+        <v>53726.081450179729</v>
       </c>
       <c r="BF4" s="1">
-        <f t="shared" si="6"/>
-        <v>52761.096876591851</v>
+        <f t="shared" si="7"/>
+        <v>54800.603079183325</v>
       </c>
     </row>
     <row r="5" spans="2:58" x14ac:dyDescent="0.3">
@@ -1487,7 +1488,7 @@
         <v>7669</v>
       </c>
       <c r="AD5" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8297</v>
       </c>
       <c r="AE5" s="11">
@@ -1506,15 +1507,14 @@
         <v>7256</v>
       </c>
       <c r="AJ5" s="11">
-        <f t="shared" ref="AJ5:AL5" si="7">AF5*0.98</f>
-        <v>7295.12</v>
+        <v>7354</v>
       </c>
       <c r="AK5" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AK5:AL5" si="8">AG5*0.98</f>
         <v>7397.04</v>
       </c>
       <c r="AL5" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7794.92</v>
       </c>
       <c r="AN5" s="1"/>
@@ -1533,52 +1533,52 @@
         <v>31312</v>
       </c>
       <c r="AU5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30359</v>
       </c>
       <c r="AV5" s="1">
-        <f t="shared" si="5"/>
-        <v>29743.08</v>
+        <f t="shared" si="6"/>
+        <v>29801.96</v>
       </c>
       <c r="AW5" s="1">
         <f>AV5*1.01</f>
-        <v>30040.510800000004</v>
+        <v>30099.979599999999</v>
       </c>
       <c r="AX5" s="1">
-        <f t="shared" ref="AX5:BF5" si="8">AW5*1.01</f>
-        <v>30340.915908000003</v>
+        <f t="shared" ref="AX5:BF5" si="9">AW5*1.01</f>
+        <v>30400.979395999999</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" si="8"/>
-        <v>30644.325067080004</v>
+        <f t="shared" si="9"/>
+        <v>30704.989189960001</v>
       </c>
       <c r="AZ5" s="1">
-        <f t="shared" si="8"/>
-        <v>30950.768317750804</v>
+        <f t="shared" si="9"/>
+        <v>31012.039081859602</v>
       </c>
       <c r="BA5" s="1">
-        <f t="shared" si="8"/>
-        <v>31260.276000928312</v>
+        <f t="shared" si="9"/>
+        <v>31322.159472678199</v>
       </c>
       <c r="BB5" s="1">
-        <f t="shared" si="8"/>
-        <v>31572.878760937594</v>
+        <f t="shared" si="9"/>
+        <v>31635.381067404982</v>
       </c>
       <c r="BC5" s="1">
-        <f t="shared" si="8"/>
-        <v>31888.60754854697</v>
+        <f t="shared" si="9"/>
+        <v>31951.734878079031</v>
       </c>
       <c r="BD5" s="1">
-        <f t="shared" si="8"/>
-        <v>32207.493624032439</v>
+        <f t="shared" si="9"/>
+        <v>32271.252226859822</v>
       </c>
       <c r="BE5" s="1">
-        <f t="shared" si="8"/>
-        <v>32529.568560272764</v>
+        <f t="shared" si="9"/>
+        <v>32593.964749128419</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" si="8"/>
-        <v>32854.864245875491</v>
+        <f t="shared" si="9"/>
+        <v>32919.904396619706</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1619,7 +1619,7 @@
         <v>8339</v>
       </c>
       <c r="AD6" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10794</v>
       </c>
       <c r="AE6" s="11">
@@ -1638,16 +1638,15 @@
         <v>10379</v>
       </c>
       <c r="AJ6" s="11">
-        <f>AF6*1.13</f>
-        <v>10522.56</v>
+        <v>11203</v>
       </c>
       <c r="AK6" s="11">
-        <f>AG6*1.03</f>
-        <v>10975.68</v>
+        <f>AG6*1.15</f>
+        <v>12254.4</v>
       </c>
       <c r="AL6" s="11">
-        <f>AH6*1.03</f>
-        <v>11981.99</v>
+        <f>AH6*1.13</f>
+        <v>13145.289999999999</v>
       </c>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
@@ -1665,52 +1664,52 @@
         <v>34688</v>
       </c>
       <c r="AU6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40340</v>
       </c>
       <c r="AV6" s="1">
-        <f t="shared" si="5"/>
-        <v>43859.229999999996</v>
+        <f t="shared" si="6"/>
+        <v>46981.69</v>
       </c>
       <c r="AW6" s="1">
-        <f>AV6*1.05</f>
-        <v>46052.191500000001</v>
+        <f>AV6*1.09</f>
+        <v>51210.042100000006</v>
       </c>
       <c r="AX6" s="1">
-        <f>AW6*1.04</f>
-        <v>47894.279160000006</v>
+        <f>AW6*1.05</f>
+        <v>53770.544205000006</v>
       </c>
       <c r="AY6" s="1">
-        <f>AX6*1.03</f>
-        <v>49331.107534800009</v>
+        <f>AX6*1.04</f>
+        <v>55921.365973200009</v>
       </c>
       <c r="AZ6" s="1">
         <f>AY6*1.03</f>
-        <v>50811.040760844007</v>
+        <v>57599.006952396012</v>
       </c>
       <c r="BA6" s="1">
-        <f t="shared" ref="BA6:BF6" si="9">AZ6*1.03</f>
-        <v>52335.371983669327</v>
+        <f t="shared" ref="BA6:BF6" si="10">AZ6*1.03</f>
+        <v>59326.977160967894</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="9"/>
-        <v>53905.433143179405</v>
+        <f t="shared" si="10"/>
+        <v>61106.786475796929</v>
       </c>
       <c r="BC6" s="1">
-        <f t="shared" si="9"/>
-        <v>55522.596137474786</v>
+        <f t="shared" si="10"/>
+        <v>62939.990070070839</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="9"/>
-        <v>57188.274021599034</v>
+        <f t="shared" si="10"/>
+        <v>64828.189772172962</v>
       </c>
       <c r="BE6" s="1">
-        <f t="shared" si="9"/>
-        <v>58903.922242247005</v>
+        <f t="shared" si="10"/>
+        <v>66773.035465338151</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="9"/>
-        <v>60671.039909514417</v>
+        <f t="shared" si="10"/>
+        <v>68776.226529298292</v>
       </c>
     </row>
     <row r="7" spans="2:58" x14ac:dyDescent="0.3">
@@ -1751,7 +1750,7 @@
         <v>8411</v>
       </c>
       <c r="AD7" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9192</v>
       </c>
       <c r="AE7" s="11">
@@ -1770,16 +1769,15 @@
         <v>12260</v>
       </c>
       <c r="AJ7" s="11">
-        <f t="shared" ref="AJ7:AL7" si="10">AF7*1.25</f>
-        <v>12933.75</v>
+        <v>13624</v>
       </c>
       <c r="AK7" s="11">
-        <f t="shared" si="10"/>
-        <v>14191.25</v>
+        <f>AG7*1.28</f>
+        <v>14531.84</v>
       </c>
       <c r="AL7" s="11">
-        <f t="shared" si="10"/>
-        <v>14943.75</v>
+        <f>AH7*1.26</f>
+        <v>15063.3</v>
       </c>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
@@ -1797,52 +1795,52 @@
         <v>33088</v>
       </c>
       <c r="AU7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>43229</v>
       </c>
       <c r="AV7" s="1">
-        <f t="shared" si="5"/>
-        <v>54328.75</v>
+        <f t="shared" si="6"/>
+        <v>55479.14</v>
       </c>
       <c r="AW7" s="1">
         <f>AV7*1.2</f>
-        <v>65194.5</v>
+        <v>66574.967999999993</v>
       </c>
       <c r="AX7" s="1">
         <f>AW7*1.15</f>
-        <v>74973.674999999988</v>
+        <v>76561.213199999984</v>
       </c>
       <c r="AY7" s="1">
         <f>AX7*1.1</f>
-        <v>82471.042499999996</v>
+        <v>84217.334519999989</v>
       </c>
       <c r="AZ7" s="1">
         <f>AY7*1.08</f>
-        <v>89068.725900000005</v>
+        <v>90954.721281599996</v>
       </c>
       <c r="BA7" s="1">
         <f>AZ7*1.06</f>
-        <v>94412.84945400001</v>
+        <v>96412.004558496003</v>
       </c>
       <c r="BB7" s="1">
         <f>BA7*1.05</f>
-        <v>99133.491926700008</v>
+        <v>101232.60478642081</v>
       </c>
       <c r="BC7" s="1">
         <f>BB7*1.03</f>
-        <v>102107.49668450101</v>
+        <v>104269.58293001344</v>
       </c>
       <c r="BD7" s="1">
         <f>BC7*1.02</f>
-        <v>104149.64661819102</v>
+        <v>106354.97458861371</v>
       </c>
       <c r="BE7" s="1">
         <f t="shared" ref="BE7:BF7" si="11">BD7*1.02</f>
-        <v>106232.63955055484</v>
+        <v>108482.07408038598</v>
       </c>
       <c r="BF7" s="1">
         <f t="shared" si="11"/>
-        <v>108357.29234156595</v>
+        <v>110651.7155619937</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -1883,7 +1881,7 @@
         <v>297</v>
       </c>
       <c r="AD8" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>657</v>
       </c>
       <c r="AE8" s="11">
@@ -1902,11 +1900,10 @@
         <v>450</v>
       </c>
       <c r="AJ8" s="11">
-        <f t="shared" ref="AJ8:AL8" si="12">AF8*1.1</f>
-        <v>401.50000000000006</v>
+        <v>373</v>
       </c>
       <c r="AK8" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="AK8:AL8" si="12">AG8*1.1</f>
         <v>426.8</v>
       </c>
       <c r="AL8" s="11">
@@ -1929,52 +1926,52 @@
         <v>1527</v>
       </c>
       <c r="AU8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1648</v>
       </c>
       <c r="AV8" s="1">
-        <f t="shared" si="5"/>
-        <v>1718.3</v>
+        <f t="shared" si="6"/>
+        <v>1689.8</v>
       </c>
       <c r="AW8" s="1">
         <f>AV8*1.25</f>
-        <v>2147.875</v>
+        <v>2112.25</v>
       </c>
       <c r="AX8" s="1">
         <f>AW8*1.2</f>
-        <v>2577.4499999999998</v>
+        <v>2534.6999999999998</v>
       </c>
       <c r="AY8" s="1">
         <f>AX8*1.15</f>
-        <v>2964.0674999999997</v>
+        <v>2914.9049999999997</v>
       </c>
       <c r="AZ8" s="1">
         <f>AY8*1.1</f>
-        <v>3260.4742499999998</v>
+        <v>3206.3955000000001</v>
       </c>
       <c r="BA8" s="1">
         <f>AZ8*1.05</f>
-        <v>3423.4979625000001</v>
+        <v>3366.715275</v>
       </c>
       <c r="BB8" s="1">
         <f t="shared" ref="BB8:BF8" si="13">BA8*1.05</f>
-        <v>3594.6728606250003</v>
+        <v>3535.0510387500003</v>
       </c>
       <c r="BC8" s="1">
         <f t="shared" si="13"/>
-        <v>3774.4065036562506</v>
+        <v>3711.8035906875007</v>
       </c>
       <c r="BD8" s="1">
         <f t="shared" si="13"/>
-        <v>3963.1268288390634</v>
+        <v>3897.3937702218759</v>
       </c>
       <c r="BE8" s="1">
         <f t="shared" si="13"/>
-        <v>4161.2831702810163</v>
+        <v>4092.2634587329699</v>
       </c>
       <c r="BF8" s="1">
         <f t="shared" si="13"/>
-        <v>4369.3473287950674</v>
+        <v>4296.8766316696183</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2015,7 +2012,7 @@
         <v>-1</v>
       </c>
       <c r="AD9" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="AE9" s="11">
@@ -2034,7 +2031,7 @@
         <v>260</v>
       </c>
       <c r="AJ9" s="11">
-        <v>50</v>
+        <v>-112</v>
       </c>
       <c r="AK9" s="11">
         <v>50</v>
@@ -2058,52 +2055,52 @@
         <v>236</v>
       </c>
       <c r="AU9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>211</v>
       </c>
       <c r="AV9" s="1">
-        <f t="shared" si="5"/>
-        <v>410</v>
+        <f t="shared" si="6"/>
+        <v>248</v>
       </c>
       <c r="AW9" s="1">
         <f t="shared" ref="AW9:BF9" si="14">AV9*1.02</f>
-        <v>418.2</v>
+        <v>252.96</v>
       </c>
       <c r="AX9" s="1">
         <f t="shared" si="14"/>
-        <v>426.56400000000002</v>
+        <v>258.01920000000001</v>
       </c>
       <c r="AY9" s="1">
         <f t="shared" si="14"/>
-        <v>435.09528</v>
+        <v>263.17958400000003</v>
       </c>
       <c r="AZ9" s="1">
         <f t="shared" si="14"/>
-        <v>443.79718560000003</v>
+        <v>268.44317568000002</v>
       </c>
       <c r="BA9" s="1">
         <f t="shared" si="14"/>
-        <v>452.67312931200001</v>
+        <v>273.81203919360001</v>
       </c>
       <c r="BB9" s="1">
         <f t="shared" si="14"/>
-        <v>461.72659189824003</v>
+        <v>279.28827997747203</v>
       </c>
       <c r="BC9" s="1">
         <f t="shared" si="14"/>
-        <v>470.96112373620485</v>
+        <v>284.87404557702149</v>
       </c>
       <c r="BD9" s="1">
         <f t="shared" si="14"/>
-        <v>480.38034621092896</v>
+        <v>290.57152648856191</v>
       </c>
       <c r="BE9" s="1">
         <f t="shared" si="14"/>
-        <v>489.98795313514756</v>
+        <v>296.38295701833317</v>
       </c>
       <c r="BF9" s="1">
         <f t="shared" si="14"/>
-        <v>499.78771219785051</v>
+        <v>302.31061615869982</v>
       </c>
     </row>
     <row r="10" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2218,15 +2215,15 @@
       </c>
       <c r="AJ10" s="9">
         <f t="shared" ref="AJ10:AL10" si="15">SUM(AJ3:AJ9)</f>
-        <v>92463.6</v>
+        <v>96428</v>
       </c>
       <c r="AK10" s="9">
         <f t="shared" si="15"/>
-        <v>95517.400000000009</v>
+        <v>98885.89</v>
       </c>
       <c r="AL10" s="9">
         <f t="shared" si="15"/>
-        <v>104023.69</v>
+        <v>106265.8</v>
       </c>
       <c r="AN10" s="9">
         <f>SUM(C10:F10)</f>
@@ -2262,47 +2259,47 @@
       </c>
       <c r="AV10" s="9">
         <f>SUM(AV3:AV9)</f>
-        <v>382238.69</v>
+        <v>391813.69</v>
       </c>
       <c r="AW10" s="9">
         <f t="shared" ref="AW10:BF10" si="16">SUM(AW3:AW9)</f>
-        <v>409030.71750000009</v>
+        <v>425896.21670000005</v>
       </c>
       <c r="AX10" s="9">
         <f t="shared" si="16"/>
-        <v>430170.63211800007</v>
+        <v>452953.77385100001</v>
       </c>
       <c r="AY10" s="9">
         <f t="shared" si="16"/>
-        <v>448455.23531148006</v>
+        <v>475027.2248311601</v>
       </c>
       <c r="AZ10" s="9">
         <f t="shared" si="16"/>
-        <v>463247.03740801098</v>
+        <v>493076.22007245565</v>
       </c>
       <c r="BA10" s="9">
         <f t="shared" si="16"/>
-        <v>476835.09900819481</v>
+        <v>507419.88413689431</v>
       </c>
       <c r="BB10" s="9">
         <f t="shared" si="16"/>
-        <v>487046.0115759187</v>
+        <v>520841.69159152004</v>
       </c>
       <c r="BC10" s="9">
         <f t="shared" si="16"/>
-        <v>495613.08535363537</v>
+        <v>532671.61705646105</v>
       </c>
       <c r="BD10" s="9">
         <f t="shared" si="16"/>
-        <v>503353.60856796987</v>
+        <v>540967.54806409206</v>
       </c>
       <c r="BE10" s="9">
         <f t="shared" si="16"/>
-        <v>511242.85866869579</v>
+        <v>549422.86484086374</v>
       </c>
       <c r="BF10" s="9">
         <f t="shared" si="16"/>
-        <v>519284.30895772867</v>
+        <v>558041.29012180411</v>
       </c>
     </row>
     <row r="11" spans="2:58" x14ac:dyDescent="0.3">
@@ -2409,16 +2406,15 @@
         <v>36361</v>
       </c>
       <c r="AJ11" s="1">
-        <f t="shared" ref="AJ11:AL11" si="17">AJ10-AJ12</f>
-        <v>36985.440000000002</v>
+        <v>39039</v>
       </c>
       <c r="AK11" s="1">
-        <f t="shared" si="17"/>
-        <v>38206.960000000006</v>
+        <f t="shared" ref="AK11:AL11" si="17">AK10-AK12</f>
+        <v>39554.356</v>
       </c>
       <c r="AL11" s="1">
         <f t="shared" si="17"/>
-        <v>41609.476000000002</v>
+        <v>42506.320000000007</v>
       </c>
       <c r="AN11" s="1">
         <f>SUM(C11:F11)</f>
@@ -2454,47 +2450,47 @@
       </c>
       <c r="AV11" s="1">
         <f>SUM(AI11:AL11)</f>
-        <v>153162.87600000002</v>
+        <v>157460.67600000001</v>
       </c>
       <c r="AW11" s="1">
         <f t="shared" ref="AW11:BA11" si="18">AW10-AW12</f>
-        <v>163612.28700000004</v>
+        <v>170358.48668000003</v>
       </c>
       <c r="AX11" s="1">
         <f t="shared" si="18"/>
-        <v>172068.25284720003</v>
+        <v>181181.5095404</v>
       </c>
       <c r="AY11" s="1">
         <f t="shared" si="18"/>
-        <v>179382.09412459203</v>
+        <v>190010.88993246405</v>
       </c>
       <c r="AZ11" s="1">
         <f t="shared" si="18"/>
-        <v>185298.81496320438</v>
+        <v>197230.48802898225</v>
       </c>
       <c r="BA11" s="1">
         <f t="shared" si="18"/>
-        <v>190734.03960327792</v>
+        <v>202967.95365475776</v>
       </c>
       <c r="BB11" s="1">
         <f t="shared" ref="BB11:BF11" si="19">BB10-BB12</f>
-        <v>194818.40463036747</v>
+        <v>208336.67663660803</v>
       </c>
       <c r="BC11" s="1">
         <f t="shared" si="19"/>
-        <v>198245.23414145416</v>
+        <v>213068.64682258444</v>
       </c>
       <c r="BD11" s="1">
         <f t="shared" si="19"/>
-        <v>201341.44342718797</v>
+        <v>216387.01922563685</v>
       </c>
       <c r="BE11" s="1">
         <f t="shared" si="19"/>
-        <v>204497.14346747834</v>
+        <v>219769.14593634551</v>
       </c>
       <c r="BF11" s="1">
         <f t="shared" si="19"/>
-        <v>207713.72358309146</v>
+        <v>223216.51604872168</v>
       </c>
     </row>
     <row r="12" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2614,7 +2610,7 @@
         <v>48735</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" ref="AE12:AI12" si="28">AE10-AE11</f>
+        <f t="shared" ref="AE12:AJ12" si="28">AE10-AE11</f>
         <v>46827</v>
       </c>
       <c r="AF12" s="9">
@@ -2634,16 +2630,16 @@
         <v>53873</v>
       </c>
       <c r="AJ12" s="9">
-        <f>AJ10*0.6</f>
-        <v>55478.16</v>
+        <f t="shared" si="28"/>
+        <v>57389</v>
       </c>
       <c r="AK12" s="9">
         <f t="shared" ref="AK12:AL12" si="29">AK10*0.6</f>
-        <v>57310.44</v>
+        <v>59331.534</v>
       </c>
       <c r="AL12" s="9">
         <f t="shared" si="29"/>
-        <v>62414.214</v>
+        <v>63759.479999999996</v>
       </c>
       <c r="AN12" s="9">
         <f t="shared" ref="AN12:AV12" si="30">AN10-AN11</f>
@@ -2679,47 +2675,47 @@
       </c>
       <c r="AV12" s="9">
         <f t="shared" si="30"/>
-        <v>229075.81399999998</v>
+        <v>234353.014</v>
       </c>
       <c r="AW12" s="9">
         <f>AW10*0.6</f>
-        <v>245418.43050000005</v>
+        <v>255537.73002000002</v>
       </c>
       <c r="AX12" s="9">
         <f t="shared" ref="AX12:BF12" si="31">AX10*0.6</f>
-        <v>258102.37927080004</v>
+        <v>271772.2643106</v>
       </c>
       <c r="AY12" s="9">
         <f t="shared" si="31"/>
-        <v>269073.14118688804</v>
+        <v>285016.33489869605</v>
       </c>
       <c r="AZ12" s="9">
         <f t="shared" si="31"/>
-        <v>277948.2224448066</v>
+        <v>295845.7320434734</v>
       </c>
       <c r="BA12" s="9">
         <f t="shared" si="31"/>
-        <v>286101.05940491689</v>
+        <v>304451.93048213655</v>
       </c>
       <c r="BB12" s="9">
         <f t="shared" si="31"/>
-        <v>292227.60694555123</v>
+        <v>312505.01495491201</v>
       </c>
       <c r="BC12" s="9">
         <f t="shared" si="31"/>
-        <v>297367.85121218121</v>
+        <v>319602.97023387661</v>
       </c>
       <c r="BD12" s="9">
         <f t="shared" si="31"/>
-        <v>302012.1651407819</v>
+        <v>324580.52883845521</v>
       </c>
       <c r="BE12" s="9">
         <f t="shared" si="31"/>
-        <v>306745.71520121745</v>
+        <v>329653.71890451823</v>
       </c>
       <c r="BF12" s="9">
         <f t="shared" si="31"/>
-        <v>311570.58537463722</v>
+        <v>334824.77407308243</v>
       </c>
     </row>
     <row r="13" spans="2:58" x14ac:dyDescent="0.3">
@@ -2826,16 +2822,15 @@
         <v>13556</v>
       </c>
       <c r="AJ13" s="1">
-        <f>AF13*1.15</f>
-        <v>13638.999999999998</v>
+        <v>13808</v>
       </c>
       <c r="AK13" s="1">
-        <f t="shared" ref="AK13" si="32">AG13*1.12</f>
-        <v>13940.640000000001</v>
+        <f>AG13*1.14</f>
+        <v>14189.579999999998</v>
       </c>
       <c r="AL13" s="1">
-        <f>AH13*1.1</f>
-        <v>14427.6</v>
+        <f>AH13*1.12</f>
+        <v>14689.920000000002</v>
       </c>
       <c r="AN13" s="1">
         <f>SUM(C13:F13)</f>
@@ -2871,47 +2866,47 @@
       </c>
       <c r="AV13" s="1">
         <f>SUM(AI13:AL13)</f>
-        <v>55563.24</v>
+        <v>56243.5</v>
       </c>
       <c r="AW13" s="1">
         <f>AV13*1.07</f>
-        <v>59452.666799999999</v>
+        <v>60180.545000000006</v>
       </c>
       <c r="AX13" s="1">
         <f>AW13*1.04</f>
-        <v>61830.773472000001</v>
+        <v>62587.766800000005</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" ref="AY13" si="33">AX13*1.03</f>
-        <v>63685.696676160005</v>
+        <f t="shared" ref="AY13" si="32">AX13*1.03</f>
+        <v>64465.399804000008</v>
       </c>
       <c r="AZ13" s="1">
         <f>AY13*1.03</f>
-        <v>65596.267576444807</v>
+        <v>66399.361798120008</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" ref="BA13:BB13" si="34">AZ13*1.02</f>
-        <v>66908.192927973709</v>
+        <f t="shared" ref="BA13:BB13" si="33">AZ13*1.02</f>
+        <v>67727.349034082406</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="34"/>
-        <v>68246.356786533186</v>
+        <f t="shared" si="33"/>
+        <v>69081.896014764061</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" ref="BC13" si="35">BB13*1.02</f>
-        <v>69611.283922263858</v>
+        <f t="shared" ref="BC13" si="34">BB13*1.02</f>
+        <v>70463.533935059342</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" ref="BD13" si="36">BC13*1.02</f>
-        <v>71003.509600709134</v>
+        <f t="shared" ref="BD13" si="35">BC13*1.02</f>
+        <v>71872.804613760527</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" ref="BE13" si="37">BD13*1.02</f>
-        <v>72423.579792723322</v>
+        <f t="shared" ref="BE13" si="36">BD13*1.02</f>
+        <v>73310.26070603574</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" ref="BF13" si="38">BE13*1.02</f>
-        <v>73872.051388577791</v>
+        <f t="shared" ref="BF13" si="37">BE13*1.02</f>
+        <v>74776.46592015645</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3018,16 +3013,15 @@
         <v>6172</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" ref="AJ14:AL14" si="39">AJ10*0.08</f>
-        <v>7397.0880000000006</v>
+        <v>7101</v>
       </c>
       <c r="AK14" s="1">
-        <f t="shared" si="39"/>
-        <v>7641.3920000000007</v>
+        <f>AK10*0.075</f>
+        <v>7416.44175</v>
       </c>
       <c r="AL14" s="1">
-        <f t="shared" si="39"/>
-        <v>8321.8952000000008</v>
+        <f>AL10*0.075</f>
+        <v>7969.9349999999995</v>
       </c>
       <c r="AN14" s="1">
         <f>SUM(C14:F14)</f>
@@ -3063,47 +3057,47 @@
       </c>
       <c r="AV14" s="1">
         <f>SUM(AI14:AL14)</f>
-        <v>29532.375200000002</v>
+        <v>28659.376749999996</v>
       </c>
       <c r="AW14" s="1">
-        <f>AW10*0.075</f>
-        <v>30677.303812500006</v>
+        <f>AW10*0.07</f>
+        <v>29812.735169000007</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" ref="AX14:BF14" si="40">AX10*0.075</f>
-        <v>32262.797408850005</v>
+        <f t="shared" ref="AX14:BF14" si="38">AX10*0.07</f>
+        <v>31706.764169570004</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="40"/>
-        <v>33634.142648361005</v>
+        <f t="shared" si="38"/>
+        <v>33251.905738181209</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="40"/>
-        <v>34743.527805600825</v>
+        <f t="shared" si="38"/>
+        <v>34515.335405071899</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="40"/>
-        <v>35762.632425614611</v>
+        <f t="shared" si="38"/>
+        <v>35519.391889582606</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="40"/>
-        <v>36528.450868193904</v>
+        <f t="shared" si="38"/>
+        <v>36458.918411406405</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="40"/>
-        <v>37170.981401522651</v>
+        <f t="shared" si="38"/>
+        <v>37287.013193952276</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="40"/>
-        <v>37751.520642597738</v>
+        <f t="shared" si="38"/>
+        <v>37867.728364486451</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="40"/>
-        <v>38343.214400152181</v>
+        <f t="shared" si="38"/>
+        <v>38459.600538860468</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="40"/>
-        <v>38946.323171829652</v>
+        <f t="shared" si="38"/>
+        <v>39062.890308526294</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3211,16 +3205,15 @@
         <v>3539</v>
       </c>
       <c r="AJ15" s="1">
-        <f>AF15*1.15</f>
-        <v>3631.7</v>
+        <v>5209</v>
       </c>
       <c r="AK15" s="1">
-        <f>AG15*1.05</f>
-        <v>3778.9500000000003</v>
+        <f>AG15*1.5</f>
+        <v>5398.5</v>
       </c>
       <c r="AL15" s="1">
-        <f>AH15*1.05</f>
-        <v>4625.25</v>
+        <f>AH15*1.45</f>
+        <v>6387.25</v>
       </c>
       <c r="AN15" s="1">
         <f>SUM(C15:F15)</f>
@@ -3256,47 +3249,47 @@
       </c>
       <c r="AV15" s="1">
         <f>SUM(AI15:AL15)</f>
-        <v>15574.9</v>
+        <v>20533.75</v>
       </c>
       <c r="AW15" s="1">
         <f>AV15*1.05</f>
-        <v>16353.645</v>
+        <v>21560.4375</v>
       </c>
       <c r="AX15" s="1">
         <f>AW15*1.03</f>
-        <v>16844.254349999999</v>
+        <v>22207.250625000001</v>
       </c>
       <c r="AY15" s="1">
-        <f t="shared" ref="AY15:BB15" si="41">AX15*1.02</f>
-        <v>17181.139436999998</v>
+        <f t="shared" ref="AY15:BB15" si="39">AX15*1.02</f>
+        <v>22651.395637500002</v>
       </c>
       <c r="AZ15" s="1">
-        <f t="shared" si="41"/>
-        <v>17524.76222574</v>
+        <f t="shared" si="39"/>
+        <v>23104.423550250001</v>
       </c>
       <c r="BA15" s="1">
-        <f t="shared" si="41"/>
-        <v>17875.257470254801</v>
+        <f t="shared" si="39"/>
+        <v>23566.512021255003</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="41"/>
-        <v>18232.762619659898</v>
+        <f t="shared" si="39"/>
+        <v>24037.842261680104</v>
       </c>
       <c r="BC15" s="1">
-        <f t="shared" ref="BC15" si="42">BB15*1.02</f>
-        <v>18597.417872053094</v>
+        <f t="shared" ref="BC15" si="40">BB15*1.02</f>
+        <v>24518.599106913705</v>
       </c>
       <c r="BD15" s="1">
-        <f t="shared" ref="BD15" si="43">BC15*1.02</f>
-        <v>18969.366229494157</v>
+        <f t="shared" ref="BD15" si="41">BC15*1.02</f>
+        <v>25008.971089051978</v>
       </c>
       <c r="BE15" s="1">
-        <f t="shared" ref="BE15" si="44">BD15*1.02</f>
-        <v>19348.75355408404</v>
+        <f t="shared" ref="BE15" si="42">BD15*1.02</f>
+        <v>25509.150510833017</v>
       </c>
       <c r="BF15" s="1">
-        <f t="shared" ref="BF15" si="45">BE15*1.02</f>
-        <v>19735.728625165721</v>
+        <f t="shared" ref="BF15" si="43">BE15*1.02</f>
+        <v>26019.333521049677</v>
       </c>
     </row>
     <row r="16" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3304,148 +3297,148 @@
         <v>28</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:P16" si="46">C12-C13-C14-C15</f>
+        <f t="shared" ref="C16:P16" si="44">C12-C13-C14-C15</f>
         <v>6568</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="44"/>
+        <v>6868</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="44"/>
+        <v>7782</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="44"/>
+        <v>7573</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="44"/>
+        <v>7633</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="44"/>
+        <v>8116</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="44"/>
+        <v>8625</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="44"/>
+        <v>8221</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="44"/>
+        <v>6608</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="44"/>
+        <v>9180</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="44"/>
+        <v>9177</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="44"/>
+        <v>9266</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="44"/>
+        <v>7977</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="44"/>
+        <v>6383</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" ref="Q16" si="45">Q12-Q13-Q14-Q15</f>
+        <v>11213</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" ref="R16:V16" si="46">R12-R13-R14-R15</f>
+        <v>15651</v>
+      </c>
+      <c r="S16" s="9">
         <f t="shared" si="46"/>
-        <v>6868</v>
-      </c>
-      <c r="E16" s="9">
+        <v>16437</v>
+      </c>
+      <c r="T16" s="9">
         <f t="shared" si="46"/>
-        <v>7782</v>
-      </c>
-      <c r="F16" s="9">
+        <v>16437</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" ref="U16" si="47">U12-U13-U14-U15</f>
+        <v>21031</v>
+      </c>
+      <c r="V16" s="9">
         <f t="shared" si="46"/>
-        <v>7573</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="46"/>
-        <v>7633</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="46"/>
-        <v>8116</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="46"/>
-        <v>8625</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="46"/>
-        <v>8221</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="46"/>
-        <v>6608</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="46"/>
-        <v>9180</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="46"/>
-        <v>9177</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="46"/>
-        <v>9266</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="46"/>
-        <v>7977</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="46"/>
-        <v>6383</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" ref="Q16" si="47">Q12-Q13-Q14-Q15</f>
-        <v>11213</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" ref="R16:V16" si="48">R12-R13-R14-R15</f>
-        <v>15651</v>
-      </c>
-      <c r="S16" s="9">
+        <v>21885</v>
+      </c>
+      <c r="W16" s="9">
+        <f t="shared" ref="W16:X16" si="48">W12-W13-W14-W15</f>
+        <v>20094</v>
+      </c>
+      <c r="X16" s="9">
         <f t="shared" si="48"/>
-        <v>16437</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" si="48"/>
-        <v>16437</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" ref="U16" si="49">U12-U13-U14-U15</f>
-        <v>21031</v>
-      </c>
-      <c r="V16" s="9">
-        <f t="shared" si="48"/>
-        <v>21885</v>
-      </c>
-      <c r="W16" s="9">
-        <f t="shared" ref="W16:X16" si="50">W12-W13-W14-W15</f>
-        <v>20094</v>
-      </c>
-      <c r="X16" s="9">
-        <f t="shared" si="50"/>
         <v>19453</v>
       </c>
       <c r="Y16" s="9">
-        <f t="shared" ref="Y16" si="51">Y12-Y13-Y14-Y15</f>
+        <f t="shared" ref="Y16" si="49">Y12-Y13-Y14-Y15</f>
         <v>17135</v>
       </c>
       <c r="Z16" s="9">
-        <f t="shared" ref="Z16" si="52">Z12-Z13-Z14-Z15</f>
+        <f t="shared" ref="Z16" si="50">Z12-Z13-Z14-Z15</f>
         <v>18160</v>
       </c>
       <c r="AA16" s="9">
-        <f t="shared" ref="AA16:AB16" si="53">AA12-AA13-AA14-AA15</f>
+        <f t="shared" ref="AA16:AB16" si="51">AA12-AA13-AA14-AA15</f>
         <v>17415</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>21838</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" ref="AC16" si="54">AC12-AC13-AC14-AC15</f>
+        <f t="shared" ref="AC16" si="52">AC12-AC13-AC14-AC15</f>
         <v>21343</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" ref="AD16" si="55">AD12-AD13-AD14-AD15</f>
+        <f t="shared" ref="AD16" si="53">AD12-AD13-AD14-AD15</f>
         <v>23697</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" ref="AE16:AL16" si="56">AE12-AE13-AE14-AE15</f>
+        <f t="shared" ref="AE16:AL16" si="54">AE12-AE13-AE14-AE15</f>
         <v>25472</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>27425</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>28521</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>30972</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>30606</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="56"/>
-        <v>30810.371999999999</v>
+        <f t="shared" si="54"/>
+        <v>31271</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="56"/>
-        <v>31949.458000000002</v>
+        <f t="shared" si="54"/>
+        <v>32327.01225</v>
       </c>
       <c r="AL16" s="9">
-        <f t="shared" si="56"/>
-        <v>35039.468800000002</v>
+        <f t="shared" si="54"/>
+        <v>34712.375</v>
       </c>
       <c r="AN16" s="9">
         <f>AN12-AN13-AN14-AN15</f>
@@ -3464,64 +3457,64 @@
         <v>41224</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" ref="AR16:BA16" si="57">AR12-AR13-AR14-AR15</f>
+        <f t="shared" ref="AR16:BA16" si="55">AR12-AR13-AR14-AR15</f>
         <v>75790</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>74842</v>
       </c>
       <c r="AT16" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>84293</v>
       </c>
       <c r="AU16" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>112390</v>
       </c>
       <c r="AV16" s="9">
-        <f t="shared" si="57"/>
-        <v>128405.29879999999</v>
+        <f t="shared" si="55"/>
+        <v>128916.38725</v>
       </c>
       <c r="AW16" s="9">
-        <f t="shared" si="57"/>
-        <v>138934.81488750005</v>
+        <f t="shared" si="55"/>
+        <v>143984.01235099998</v>
       </c>
       <c r="AX16" s="9">
-        <f t="shared" si="57"/>
-        <v>147164.55403995002</v>
+        <f t="shared" si="55"/>
+        <v>155270.48271602998</v>
       </c>
       <c r="AY16" s="9">
-        <f t="shared" si="57"/>
-        <v>154572.16242536702</v>
+        <f t="shared" si="55"/>
+        <v>164647.63371901482</v>
       </c>
       <c r="AZ16" s="9">
-        <f t="shared" si="57"/>
-        <v>160083.66483702097</v>
+        <f t="shared" si="55"/>
+        <v>171826.61129003146</v>
       </c>
       <c r="BA16" s="9">
-        <f t="shared" si="57"/>
-        <v>165554.97658107377</v>
+        <f t="shared" si="55"/>
+        <v>177638.67753721654</v>
       </c>
       <c r="BB16" s="9">
-        <f t="shared" ref="BB16:BF16" si="58">BB12-BB13-BB14-BB15</f>
-        <v>169220.03667116424</v>
+        <f t="shared" ref="BB16:BF16" si="56">BB12-BB13-BB14-BB15</f>
+        <v>182926.35826706144</v>
       </c>
       <c r="BC16" s="9">
-        <f t="shared" si="58"/>
-        <v>171988.1680163416</v>
+        <f t="shared" si="56"/>
+        <v>187333.82399795132</v>
       </c>
       <c r="BD16" s="9">
-        <f t="shared" si="58"/>
-        <v>174287.76866798085</v>
+        <f t="shared" si="56"/>
+        <v>189831.02477115626</v>
       </c>
       <c r="BE16" s="9">
-        <f t="shared" si="58"/>
-        <v>176630.1674542579</v>
+        <f t="shared" si="56"/>
+        <v>192374.70714878902</v>
       </c>
       <c r="BF16" s="9">
-        <f t="shared" si="58"/>
-        <v>179016.48218906403</v>
+        <f t="shared" si="56"/>
+        <v>194966.08432335002</v>
       </c>
     </row>
     <row r="17" spans="2:193" x14ac:dyDescent="0.3">
@@ -3628,15 +3621,14 @@
         <v>-11183</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" ref="AJ17:AL17" si="59">AF17*1.03</f>
-        <v>-129.78</v>
+        <v>-2662</v>
       </c>
       <c r="AK17" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="AK17:AL17" si="57">AG17*1.03</f>
         <v>-3280.55</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>-1309.1300000000001</v>
       </c>
       <c r="AN17" s="1">
@@ -3673,46 +3665,46 @@
       </c>
       <c r="AV17" s="1">
         <f>SUM(AI17:AL17)</f>
-        <v>-15902.460000000003</v>
+        <v>-18434.68</v>
       </c>
       <c r="AW17" s="1">
         <f>AU17*1.01</f>
         <v>-7499.25</v>
       </c>
       <c r="AX17" s="1">
-        <f t="shared" ref="AX17:BF17" si="60">AW17*1.01</f>
+        <f t="shared" ref="AX17:BF17" si="58">AW17*1.01</f>
         <v>-7574.2425000000003</v>
       </c>
       <c r="AY17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-7649.9849250000007</v>
       </c>
       <c r="AZ17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-7726.4847742500006</v>
       </c>
       <c r="BA17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-7803.7496219925006</v>
       </c>
       <c r="BB17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-7881.7871182124254</v>
       </c>
       <c r="BC17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-7960.6049893945501</v>
       </c>
       <c r="BD17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-8040.2110392884961</v>
       </c>
       <c r="BE17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-8120.6131496813814</v>
       </c>
       <c r="BF17" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-8201.8192811781955</v>
       </c>
     </row>
@@ -3721,148 +3713,148 @@
         <v>29</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:P18" si="61">C16-C17</f>
+        <f t="shared" ref="C18:P18" si="59">C16-C17</f>
         <v>6819</v>
       </c>
       <c r="D18" s="9">
+        <f t="shared" si="59"/>
+        <v>7113</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="59"/>
+        <v>7979</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="59"/>
+        <v>7927</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="59"/>
+        <v>10543</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="59"/>
+        <v>9286</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="59"/>
+        <v>10083</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="59"/>
+        <v>10072</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="59"/>
+        <v>8146</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="59"/>
+        <v>12147</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="59"/>
+        <v>8628</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="59"/>
+        <v>10704</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="59"/>
+        <v>7757</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="59"/>
+        <v>8277</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" ref="Q18" si="60">Q16-Q17</f>
+        <v>13629</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" ref="R18:V18" si="61">R16-R17</f>
+        <v>18689</v>
+      </c>
+      <c r="S18" s="9">
         <f t="shared" si="61"/>
-        <v>7113</v>
-      </c>
-      <c r="E18" s="9">
+        <v>21283</v>
+      </c>
+      <c r="T18" s="9">
         <f t="shared" si="61"/>
-        <v>7979</v>
-      </c>
-      <c r="F18" s="9">
+        <v>21283</v>
+      </c>
+      <c r="U18" s="9">
+        <f t="shared" ref="U18" si="62">U16-U17</f>
+        <v>23064</v>
+      </c>
+      <c r="V18" s="9">
         <f t="shared" si="61"/>
-        <v>7927</v>
-      </c>
-      <c r="G18" s="9">
-        <f t="shared" si="61"/>
-        <v>10543</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="61"/>
-        <v>9286</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="61"/>
-        <v>10083</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="61"/>
-        <v>10072</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="61"/>
-        <v>8146</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="61"/>
-        <v>12147</v>
-      </c>
-      <c r="M18" s="9">
-        <f t="shared" si="61"/>
-        <v>8628</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="61"/>
-        <v>10704</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="61"/>
-        <v>7757</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="61"/>
-        <v>8277</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" ref="Q18" si="62">Q16-Q17</f>
-        <v>13629</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" ref="R18:V18" si="63">R16-R17</f>
-        <v>18689</v>
-      </c>
-      <c r="S18" s="9">
+        <v>24402</v>
+      </c>
+      <c r="W18" s="9">
+        <f t="shared" ref="W18:X18" si="63">W16-W17</f>
+        <v>18934</v>
+      </c>
+      <c r="X18" s="9">
         <f t="shared" si="63"/>
-        <v>21283</v>
-      </c>
-      <c r="T18" s="9">
-        <f t="shared" si="63"/>
-        <v>21283</v>
-      </c>
-      <c r="U18" s="9">
-        <f t="shared" ref="U18" si="64">U16-U17</f>
-        <v>23064</v>
-      </c>
-      <c r="V18" s="9">
-        <f t="shared" si="63"/>
-        <v>24402</v>
-      </c>
-      <c r="W18" s="9">
-        <f t="shared" ref="W18:X18" si="65">W16-W17</f>
-        <v>18934</v>
-      </c>
-      <c r="X18" s="9">
-        <f t="shared" si="65"/>
         <v>19014</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="66">Y16-Y17</f>
+        <f t="shared" ref="Y18" si="64">Y16-Y17</f>
         <v>16233</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="67">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="65">Z16-Z17</f>
         <v>17147</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18:AB18" si="68">AA16-AA17</f>
+        <f t="shared" ref="AA18:AB18" si="66">AA16-AA17</f>
         <v>18205</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>21903</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="69">AC16-AC17</f>
+        <f t="shared" ref="AC18" si="67">AC16-AC17</f>
         <v>21197</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="70">AD16-AD17</f>
+        <f t="shared" ref="AD18" si="68">AD16-AD17</f>
         <v>24412</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18:AL18" si="71">AE16-AE17</f>
+        <f t="shared" ref="AE18:AL18" si="69">AE16-AE17</f>
         <v>28315</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>27551</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>31706</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>32243</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>41789</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="71"/>
-        <v>30940.151999999998</v>
+        <f t="shared" si="69"/>
+        <v>33933</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="71"/>
-        <v>35230.008000000002</v>
+        <f t="shared" si="69"/>
+        <v>35607.562250000003</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="71"/>
-        <v>36348.5988</v>
+        <f t="shared" si="69"/>
+        <v>36021.504999999997</v>
       </c>
       <c r="AN18" s="9">
         <f>AN16-AN17</f>
@@ -3881,64 +3873,64 @@
         <v>48352</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" ref="AR18:BA18" si="72">AR16-AR17</f>
+        <f t="shared" ref="AR18:BA18" si="70">AR16-AR17</f>
         <v>90032</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>71328</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>85717</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>119815</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" si="72"/>
-        <v>144307.75879999998</v>
+        <f t="shared" si="70"/>
+        <v>147351.06724999999</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="72"/>
-        <v>146434.06488750005</v>
+        <f t="shared" si="70"/>
+        <v>151483.26235099998</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" si="72"/>
-        <v>154738.79653995001</v>
+        <f t="shared" si="70"/>
+        <v>162844.72521602997</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" si="72"/>
-        <v>162222.14735036701</v>
+        <f t="shared" si="70"/>
+        <v>172297.61864401482</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" si="72"/>
-        <v>167810.14961127099</v>
+        <f t="shared" si="70"/>
+        <v>179553.09606428148</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="72"/>
-        <v>173358.72620306627</v>
+        <f t="shared" si="70"/>
+        <v>185442.42715920904</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="73">BB16-BB17</f>
-        <v>177101.82378937668</v>
+        <f t="shared" ref="BB18:BF18" si="71">BB16-BB17</f>
+        <v>190808.14538527388</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="73"/>
-        <v>179948.77300573615</v>
+        <f t="shared" si="71"/>
+        <v>195294.42898734586</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="73"/>
-        <v>182327.97970726935</v>
+        <f t="shared" si="71"/>
+        <v>197871.23581044475</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="73"/>
-        <v>184750.78060393929</v>
+        <f t="shared" si="71"/>
+        <v>200495.32029847041</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" si="73"/>
-        <v>187218.30147024224</v>
+        <f t="shared" si="71"/>
+        <v>203167.90360452823</v>
       </c>
     </row>
     <row r="19" spans="2:193" x14ac:dyDescent="0.3">
@@ -4046,16 +4038,15 @@
         <v>7249</v>
       </c>
       <c r="AJ19" s="1">
-        <f t="shared" ref="AJ19:AL19" si="74">AJ18*0.15</f>
-        <v>4641.0227999999997</v>
+        <v>5737</v>
       </c>
       <c r="AK19" s="1">
-        <f t="shared" si="74"/>
-        <v>5284.5011999999997</v>
+        <f t="shared" ref="AK19:AL19" si="72">AK18*0.15</f>
+        <v>5341.1343375000006</v>
       </c>
       <c r="AL19" s="1">
-        <f t="shared" si="74"/>
-        <v>5452.28982</v>
+        <f t="shared" si="72"/>
+        <v>5403.2257499999996</v>
       </c>
       <c r="AN19" s="1">
         <f>SUM(C19:F19)-10200</f>
@@ -4091,47 +4082,47 @@
       </c>
       <c r="AV19" s="1">
         <f>SUM(AI19:AL19)</f>
-        <v>22626.813819999996</v>
+        <v>23730.360087499997</v>
       </c>
       <c r="AW19" s="1">
-        <f t="shared" ref="AW19:BA19" si="75">AW18*0.16</f>
-        <v>23429.450382000006</v>
+        <f t="shared" ref="AW19:BA19" si="73">AW18*0.16</f>
+        <v>24237.321976159998</v>
       </c>
       <c r="AX19" s="1">
-        <f t="shared" si="75"/>
-        <v>24758.207446392003</v>
+        <f t="shared" si="73"/>
+        <v>26055.156034564796</v>
       </c>
       <c r="AY19" s="1">
-        <f t="shared" si="75"/>
-        <v>25955.543576058724</v>
+        <f t="shared" si="73"/>
+        <v>27567.618983042372</v>
       </c>
       <c r="AZ19" s="1">
-        <f t="shared" si="75"/>
-        <v>26849.623937803357</v>
+        <f t="shared" si="73"/>
+        <v>28728.495370285036</v>
       </c>
       <c r="BA19" s="1">
-        <f t="shared" si="75"/>
-        <v>27737.396192490603</v>
+        <f t="shared" si="73"/>
+        <v>29670.788345473447</v>
       </c>
       <c r="BB19" s="1">
-        <f t="shared" ref="BB19:BF19" si="76">BB18*0.16</f>
-        <v>28336.291806300269</v>
+        <f t="shared" ref="BB19:BF19" si="74">BB18*0.16</f>
+        <v>30529.303261643821</v>
       </c>
       <c r="BC19" s="1">
-        <f t="shared" si="76"/>
-        <v>28791.803680917783</v>
+        <f t="shared" si="74"/>
+        <v>31247.10863797534</v>
       </c>
       <c r="BD19" s="1">
-        <f t="shared" si="76"/>
-        <v>29172.476753163097</v>
+        <f t="shared" si="74"/>
+        <v>31659.39772967116</v>
       </c>
       <c r="BE19" s="1">
-        <f t="shared" si="76"/>
-        <v>29560.124896630288</v>
+        <f t="shared" si="74"/>
+        <v>32079.251247755266</v>
       </c>
       <c r="BF19" s="1">
-        <f t="shared" si="76"/>
-        <v>29954.92823523876</v>
+        <f t="shared" si="74"/>
+        <v>32506.864576724518</v>
       </c>
     </row>
     <row r="20" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4139,148 +4130,148 @@
         <v>31</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:P20" si="77">C18-C19</f>
+        <f t="shared" ref="C20:P20" si="75">C18-C19</f>
         <v>5426</v>
       </c>
       <c r="D20" s="9">
+        <f t="shared" si="75"/>
+        <v>6260</v>
+      </c>
+      <c r="E20" s="9">
+        <f t="shared" si="75"/>
+        <v>6732</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="75"/>
+        <v>-3111</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="75"/>
+        <v>9401</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="75"/>
+        <v>8266</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="75"/>
+        <v>9192</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="75"/>
+        <v>8948</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="75"/>
+        <v>6657</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="75"/>
+        <v>9947</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="75"/>
+        <v>7068</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="75"/>
+        <v>10671</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" si="75"/>
+        <v>6836</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" si="75"/>
+        <v>6959</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" ref="Q20" si="76">Q18-Q19</f>
+        <v>11517</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" ref="R20:V20" si="77">R18-R19</f>
+        <v>15227</v>
+      </c>
+      <c r="S20" s="9">
         <f t="shared" si="77"/>
-        <v>6260</v>
-      </c>
-      <c r="E20" s="9">
+        <v>17930</v>
+      </c>
+      <c r="T20" s="9">
         <f t="shared" si="77"/>
-        <v>6732</v>
-      </c>
-      <c r="F20" s="9">
+        <v>17930</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" ref="U20" si="78">U18-U19</f>
+        <v>18936</v>
+      </c>
+      <c r="V20" s="9">
         <f t="shared" si="77"/>
-        <v>-3111</v>
-      </c>
-      <c r="G20" s="9">
-        <f t="shared" si="77"/>
-        <v>9401</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="77"/>
-        <v>8266</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="77"/>
-        <v>9192</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="77"/>
-        <v>8948</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" si="77"/>
-        <v>6657</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="77"/>
-        <v>9947</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="77"/>
-        <v>7068</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="77"/>
-        <v>10671</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" si="77"/>
-        <v>6836</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" si="77"/>
-        <v>6959</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" ref="Q20" si="78">Q18-Q19</f>
-        <v>11517</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" ref="R20:V20" si="79">R18-R19</f>
-        <v>15227</v>
-      </c>
-      <c r="S20" s="9">
+        <v>20642</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" ref="W20:X20" si="79">W18-W19</f>
+        <v>16436</v>
+      </c>
+      <c r="X20" s="9">
         <f t="shared" si="79"/>
-        <v>17930</v>
-      </c>
-      <c r="T20" s="9">
-        <f t="shared" si="79"/>
-        <v>17930</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" ref="U20" si="80">U18-U19</f>
-        <v>18936</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="79"/>
-        <v>20642</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" ref="W20:X20" si="81">W18-W19</f>
-        <v>16436</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="81"/>
         <v>16002</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="82">Y18-Y19</f>
+        <f t="shared" ref="Y20" si="80">Y18-Y19</f>
         <v>13910</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="83">Z18-Z19</f>
+        <f t="shared" ref="Z20" si="81">Z18-Z19</f>
         <v>13624</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20:AB20" si="84">AA18-AA19</f>
+        <f t="shared" ref="AA20:AB20" si="82">AA18-AA19</f>
         <v>15051</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>18368</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="85">AC18-AC19</f>
+        <f t="shared" ref="AC20" si="83">AC18-AC19</f>
         <v>19689</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="86">AD18-AD19</f>
+        <f t="shared" ref="AD20" si="84">AD18-AD19</f>
         <v>20687</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="87">AE18-AE19</f>
+        <f t="shared" ref="AE20:AH20" si="85">AE18-AE19</f>
         <v>23662</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>23619</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>26301</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>26536</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20:AL20" si="88">AI18-AI19</f>
+        <f t="shared" ref="AI20:AL20" si="86">AI18-AI19</f>
         <v>34540</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="88"/>
-        <v>26299.129199999999</v>
+        <f t="shared" si="86"/>
+        <v>28196</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="88"/>
-        <v>29945.506800000003</v>
+        <f t="shared" si="86"/>
+        <v>30266.427912500003</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="88"/>
-        <v>30896.308980000002</v>
+        <f t="shared" si="86"/>
+        <v>30618.27925</v>
       </c>
       <c r="AN20" s="9">
         <f>AN18-AN19</f>
@@ -4299,604 +4290,604 @@
         <v>40539</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" ref="AR20:BA20" si="89">AR18-AR19</f>
+        <f t="shared" ref="AR20:BA20" si="87">AR18-AR19</f>
         <v>75438</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>59972</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>73795</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>100118</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" si="89"/>
-        <v>121680.94497999999</v>
+        <f t="shared" si="87"/>
+        <v>123620.7071625</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="89"/>
-        <v>123004.61450550004</v>
+        <f t="shared" si="87"/>
+        <v>127245.94037483999</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" si="89"/>
-        <v>129980.58909355801</v>
+        <f t="shared" si="87"/>
+        <v>136789.56918146517</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="89"/>
-        <v>136266.60377430829</v>
+        <f t="shared" si="87"/>
+        <v>144729.99966097245</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="89"/>
-        <v>140960.52567346764</v>
+        <f t="shared" si="87"/>
+        <v>150824.60069399644</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="89"/>
-        <v>145621.33001057565</v>
+        <f t="shared" si="87"/>
+        <v>155771.6388137356</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" ref="BB20:BF20" si="90">BB18-BB19</f>
-        <v>148765.53198307642</v>
+        <f t="shared" ref="BB20:BF20" si="88">BB18-BB19</f>
+        <v>160278.84212363005</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" si="90"/>
-        <v>151156.96932481838</v>
+        <f t="shared" si="88"/>
+        <v>164047.32034937054</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" si="90"/>
-        <v>153155.50295410625</v>
+        <f t="shared" si="88"/>
+        <v>166211.8380807736</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" si="90"/>
-        <v>155190.65570730899</v>
+        <f t="shared" si="88"/>
+        <v>168416.06905071513</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" si="90"/>
-        <v>157263.37323500347</v>
+        <f t="shared" si="88"/>
+        <v>170661.03902780369</v>
       </c>
       <c r="BG20" s="6">
         <f>BF20*(1+$BI$32)</f>
-        <v>155690.73950265342</v>
+        <v>168954.42863752565</v>
       </c>
       <c r="BH20" s="6">
-        <f t="shared" ref="BH20:DS20" si="91">BG20*(1+$BI$32)</f>
-        <v>154133.83210762689</v>
+        <f t="shared" ref="BH20:DS20" si="89">BG20*(1+$BI$32)</f>
+        <v>167264.88435115039</v>
       </c>
       <c r="BI20" s="6">
+        <f t="shared" si="89"/>
+        <v>165592.23550763889</v>
+      </c>
+      <c r="BJ20" s="6">
+        <f t="shared" si="89"/>
+        <v>163936.31315256251</v>
+      </c>
+      <c r="BK20" s="6">
+        <f t="shared" si="89"/>
+        <v>162296.95002103687</v>
+      </c>
+      <c r="BL20" s="6">
+        <f t="shared" si="89"/>
+        <v>160673.9805208265</v>
+      </c>
+      <c r="BM20" s="6">
+        <f t="shared" si="89"/>
+        <v>159067.24071561825</v>
+      </c>
+      <c r="BN20" s="6">
+        <f t="shared" si="89"/>
+        <v>157476.56830846207</v>
+      </c>
+      <c r="BO20" s="6">
+        <f t="shared" si="89"/>
+        <v>155901.80262537746</v>
+      </c>
+      <c r="BP20" s="6">
+        <f t="shared" si="89"/>
+        <v>154342.7845991237</v>
+      </c>
+      <c r="BQ20" s="6">
+        <f t="shared" si="89"/>
+        <v>152799.35675313245</v>
+      </c>
+      <c r="BR20" s="6">
+        <f t="shared" si="89"/>
+        <v>151271.36318560113</v>
+      </c>
+      <c r="BS20" s="6">
+        <f t="shared" si="89"/>
+        <v>149758.64955374511</v>
+      </c>
+      <c r="BT20" s="6">
+        <f t="shared" si="89"/>
+        <v>148261.06305820766</v>
+      </c>
+      <c r="BU20" s="6">
+        <f t="shared" si="89"/>
+        <v>146778.45242762557</v>
+      </c>
+      <c r="BV20" s="6">
+        <f t="shared" si="89"/>
+        <v>145310.6679033493</v>
+      </c>
+      <c r="BW20" s="6">
+        <f t="shared" si="89"/>
+        <v>143857.56122431581</v>
+      </c>
+      <c r="BX20" s="6">
+        <f t="shared" si="89"/>
+        <v>142418.98561207266</v>
+      </c>
+      <c r="BY20" s="6">
+        <f t="shared" si="89"/>
+        <v>140994.79575595193</v>
+      </c>
+      <c r="BZ20" s="6">
+        <f t="shared" si="89"/>
+        <v>139584.84779839241</v>
+      </c>
+      <c r="CA20" s="6">
+        <f t="shared" si="89"/>
+        <v>138188.99932040847</v>
+      </c>
+      <c r="CB20" s="6">
+        <f t="shared" si="89"/>
+        <v>136807.10932720438</v>
+      </c>
+      <c r="CC20" s="6">
+        <f t="shared" si="89"/>
+        <v>135439.03823393234</v>
+      </c>
+      <c r="CD20" s="6">
+        <f t="shared" si="89"/>
+        <v>134084.64785159301</v>
+      </c>
+      <c r="CE20" s="6">
+        <f t="shared" si="89"/>
+        <v>132743.80137307706</v>
+      </c>
+      <c r="CF20" s="6">
+        <f t="shared" si="89"/>
+        <v>131416.36335934629</v>
+      </c>
+      <c r="CG20" s="6">
+        <f t="shared" si="89"/>
+        <v>130102.19972575283</v>
+      </c>
+      <c r="CH20" s="6">
+        <f t="shared" si="89"/>
+        <v>128801.1777284953</v>
+      </c>
+      <c r="CI20" s="6">
+        <f t="shared" si="89"/>
+        <v>127513.16595121035</v>
+      </c>
+      <c r="CJ20" s="6">
+        <f t="shared" si="89"/>
+        <v>126238.03429169825</v>
+      </c>
+      <c r="CK20" s="6">
+        <f t="shared" si="89"/>
+        <v>124975.65394878127</v>
+      </c>
+      <c r="CL20" s="6">
+        <f t="shared" si="89"/>
+        <v>123725.89740929345</v>
+      </c>
+      <c r="CM20" s="6">
+        <f t="shared" si="89"/>
+        <v>122488.63843520051</v>
+      </c>
+      <c r="CN20" s="6">
+        <f t="shared" si="89"/>
+        <v>121263.7520508485</v>
+      </c>
+      <c r="CO20" s="6">
+        <f t="shared" si="89"/>
+        <v>120051.11453034001</v>
+      </c>
+      <c r="CP20" s="6">
+        <f t="shared" si="89"/>
+        <v>118850.60338503661</v>
+      </c>
+      <c r="CQ20" s="6">
+        <f t="shared" si="89"/>
+        <v>117662.09735118624</v>
+      </c>
+      <c r="CR20" s="6">
+        <f t="shared" si="89"/>
+        <v>116485.47637767438</v>
+      </c>
+      <c r="CS20" s="6">
+        <f t="shared" si="89"/>
+        <v>115320.62161389763</v>
+      </c>
+      <c r="CT20" s="6">
+        <f t="shared" si="89"/>
+        <v>114167.41539775865</v>
+      </c>
+      <c r="CU20" s="6">
+        <f t="shared" si="89"/>
+        <v>113025.74124378107</v>
+      </c>
+      <c r="CV20" s="6">
+        <f t="shared" si="89"/>
+        <v>111895.48383134326</v>
+      </c>
+      <c r="CW20" s="6">
+        <f t="shared" si="89"/>
+        <v>110776.52899302982</v>
+      </c>
+      <c r="CX20" s="6">
+        <f t="shared" si="89"/>
+        <v>109668.76370309952</v>
+      </c>
+      <c r="CY20" s="6">
+        <f t="shared" si="89"/>
+        <v>108572.07606606853</v>
+      </c>
+      <c r="CZ20" s="6">
+        <f t="shared" si="89"/>
+        <v>107486.35530540785</v>
+      </c>
+      <c r="DA20" s="6">
+        <f t="shared" si="89"/>
+        <v>106411.49175235377</v>
+      </c>
+      <c r="DB20" s="6">
+        <f t="shared" si="89"/>
+        <v>105347.37683483024</v>
+      </c>
+      <c r="DC20" s="6">
+        <f t="shared" si="89"/>
+        <v>104293.90306648194</v>
+      </c>
+      <c r="DD20" s="6">
+        <f t="shared" si="89"/>
+        <v>103250.96403581712</v>
+      </c>
+      <c r="DE20" s="6">
+        <f t="shared" si="89"/>
+        <v>102218.45439545895</v>
+      </c>
+      <c r="DF20" s="6">
+        <f t="shared" si="89"/>
+        <v>101196.26985150436</v>
+      </c>
+      <c r="DG20" s="6">
+        <f t="shared" si="89"/>
+        <v>100184.30715298932</v>
+      </c>
+      <c r="DH20" s="6">
+        <f t="shared" si="89"/>
+        <v>99182.464081459431</v>
+      </c>
+      <c r="DI20" s="6">
+        <f t="shared" si="89"/>
+        <v>98190.639440644838</v>
+      </c>
+      <c r="DJ20" s="6">
+        <f t="shared" si="89"/>
+        <v>97208.733046238383</v>
+      </c>
+      <c r="DK20" s="6">
+        <f t="shared" si="89"/>
+        <v>96236.645715776001</v>
+      </c>
+      <c r="DL20" s="6">
+        <f t="shared" si="89"/>
+        <v>95274.279258618248</v>
+      </c>
+      <c r="DM20" s="6">
+        <f t="shared" si="89"/>
+        <v>94321.536466032063</v>
+      </c>
+      <c r="DN20" s="6">
+        <f t="shared" si="89"/>
+        <v>93378.321101371737</v>
+      </c>
+      <c r="DO20" s="6">
+        <f t="shared" si="89"/>
+        <v>92444.537890358013</v>
+      </c>
+      <c r="DP20" s="6">
+        <f t="shared" si="89"/>
+        <v>91520.092511454437</v>
+      </c>
+      <c r="DQ20" s="6">
+        <f t="shared" si="89"/>
+        <v>90604.891586339887</v>
+      </c>
+      <c r="DR20" s="6">
+        <f t="shared" si="89"/>
+        <v>89698.842670476486</v>
+      </c>
+      <c r="DS20" s="6">
+        <f t="shared" si="89"/>
+        <v>88801.854243771726</v>
+      </c>
+      <c r="DT20" s="6">
+        <f t="shared" ref="DT20:GE20" si="90">DS20*(1+$BI$32)</f>
+        <v>87913.835701334014</v>
+      </c>
+      <c r="DU20" s="6">
+        <f t="shared" si="90"/>
+        <v>87034.697344320666</v>
+      </c>
+      <c r="DV20" s="6">
+        <f t="shared" si="90"/>
+        <v>86164.350370877451</v>
+      </c>
+      <c r="DW20" s="6">
+        <f t="shared" si="90"/>
+        <v>85302.706867168672</v>
+      </c>
+      <c r="DX20" s="6">
+        <f t="shared" si="90"/>
+        <v>84449.679798496989</v>
+      </c>
+      <c r="DY20" s="6">
+        <f t="shared" si="90"/>
+        <v>83605.183000512014</v>
+      </c>
+      <c r="DZ20" s="6">
+        <f t="shared" si="90"/>
+        <v>82769.131170506895</v>
+      </c>
+      <c r="EA20" s="6">
+        <f t="shared" si="90"/>
+        <v>81941.439858801823</v>
+      </c>
+      <c r="EB20" s="6">
+        <f t="shared" si="90"/>
+        <v>81122.025460213801</v>
+      </c>
+      <c r="EC20" s="6">
+        <f t="shared" si="90"/>
+        <v>80310.805205611658</v>
+      </c>
+      <c r="ED20" s="6">
+        <f t="shared" si="90"/>
+        <v>79507.697153555535</v>
+      </c>
+      <c r="EE20" s="6">
+        <f t="shared" si="90"/>
+        <v>78712.620182019979</v>
+      </c>
+      <c r="EF20" s="6">
+        <f t="shared" si="90"/>
+        <v>77925.493980199783</v>
+      </c>
+      <c r="EG20" s="6">
+        <f t="shared" si="90"/>
+        <v>77146.239040397777</v>
+      </c>
+      <c r="EH20" s="6">
+        <f t="shared" si="90"/>
+        <v>76374.776649993801</v>
+      </c>
+      <c r="EI20" s="6">
+        <f t="shared" si="90"/>
+        <v>75611.028883493869</v>
+      </c>
+      <c r="EJ20" s="6">
+        <f t="shared" si="90"/>
+        <v>74854.918594658928</v>
+      </c>
+      <c r="EK20" s="6">
+        <f t="shared" si="90"/>
+        <v>74106.369408712344</v>
+      </c>
+      <c r="EL20" s="6">
+        <f t="shared" si="90"/>
+        <v>73365.305714625225</v>
+      </c>
+      <c r="EM20" s="6">
+        <f t="shared" si="90"/>
+        <v>72631.652657478975</v>
+      </c>
+      <c r="EN20" s="6">
+        <f t="shared" si="90"/>
+        <v>71905.336130904179</v>
+      </c>
+      <c r="EO20" s="6">
+        <f t="shared" si="90"/>
+        <v>71186.282769595142</v>
+      </c>
+      <c r="EP20" s="6">
+        <f t="shared" si="90"/>
+        <v>70474.419941899192</v>
+      </c>
+      <c r="EQ20" s="6">
+        <f t="shared" si="90"/>
+        <v>69769.675742480205</v>
+      </c>
+      <c r="ER20" s="6">
+        <f t="shared" si="90"/>
+        <v>69071.978985055408</v>
+      </c>
+      <c r="ES20" s="6">
+        <f t="shared" si="90"/>
+        <v>68381.259195204853</v>
+      </c>
+      <c r="ET20" s="6">
+        <f t="shared" si="90"/>
+        <v>67697.4466032528</v>
+      </c>
+      <c r="EU20" s="6">
+        <f t="shared" si="90"/>
+        <v>67020.472137220277</v>
+      </c>
+      <c r="EV20" s="6">
+        <f t="shared" si="90"/>
+        <v>66350.26741584808</v>
+      </c>
+      <c r="EW20" s="6">
+        <f t="shared" si="90"/>
+        <v>65686.764741689592</v>
+      </c>
+      <c r="EX20" s="6">
+        <f t="shared" si="90"/>
+        <v>65029.897094272696</v>
+      </c>
+      <c r="EY20" s="6">
+        <f t="shared" si="90"/>
+        <v>64379.598123329968</v>
+      </c>
+      <c r="EZ20" s="6">
+        <f t="shared" si="90"/>
+        <v>63735.802142096669</v>
+      </c>
+      <c r="FA20" s="6">
+        <f t="shared" si="90"/>
+        <v>63098.444120675704</v>
+      </c>
+      <c r="FB20" s="6">
+        <f t="shared" si="90"/>
+        <v>62467.45967946895</v>
+      </c>
+      <c r="FC20" s="6">
+        <f t="shared" si="90"/>
+        <v>61842.785082674258</v>
+      </c>
+      <c r="FD20" s="6">
+        <f t="shared" si="90"/>
+        <v>61224.357231847513</v>
+      </c>
+      <c r="FE20" s="6">
+        <f t="shared" si="90"/>
+        <v>60612.113659529037</v>
+      </c>
+      <c r="FF20" s="6">
+        <f t="shared" si="90"/>
+        <v>60005.992522933746</v>
+      </c>
+      <c r="FG20" s="6">
+        <f t="shared" si="90"/>
+        <v>59405.932597704406</v>
+      </c>
+      <c r="FH20" s="6">
+        <f t="shared" si="90"/>
+        <v>58811.87327172736</v>
+      </c>
+      <c r="FI20" s="6">
+        <f t="shared" si="90"/>
+        <v>58223.754539010086</v>
+      </c>
+      <c r="FJ20" s="6">
+        <f t="shared" si="90"/>
+        <v>57641.516993619982</v>
+      </c>
+      <c r="FK20" s="6">
+        <f t="shared" si="90"/>
+        <v>57065.101823683784</v>
+      </c>
+      <c r="FL20" s="6">
+        <f t="shared" si="90"/>
+        <v>56494.450805446948</v>
+      </c>
+      <c r="FM20" s="6">
+        <f t="shared" si="90"/>
+        <v>55929.50629739248</v>
+      </c>
+      <c r="FN20" s="6">
+        <f t="shared" si="90"/>
+        <v>55370.211234418552</v>
+      </c>
+      <c r="FO20" s="6">
+        <f t="shared" si="90"/>
+        <v>54816.509122074363</v>
+      </c>
+      <c r="FP20" s="6">
+        <f t="shared" si="90"/>
+        <v>54268.344030853623</v>
+      </c>
+      <c r="FQ20" s="6">
+        <f t="shared" si="90"/>
+        <v>53725.660590545085</v>
+      </c>
+      <c r="FR20" s="6">
+        <f t="shared" si="90"/>
+        <v>53188.403984639634</v>
+      </c>
+      <c r="FS20" s="6">
+        <f t="shared" si="90"/>
+        <v>52656.519944793239</v>
+      </c>
+      <c r="FT20" s="6">
+        <f t="shared" si="90"/>
+        <v>52129.954745345305</v>
+      </c>
+      <c r="FU20" s="6">
+        <f t="shared" si="90"/>
+        <v>51608.655197891851</v>
+      </c>
+      <c r="FV20" s="6">
+        <f t="shared" si="90"/>
+        <v>51092.568645912928</v>
+      </c>
+      <c r="FW20" s="6">
+        <f t="shared" si="90"/>
+        <v>50581.642959453799</v>
+      </c>
+      <c r="FX20" s="6">
+        <f t="shared" si="90"/>
+        <v>50075.82652985926</v>
+      </c>
+      <c r="FY20" s="6">
+        <f t="shared" si="90"/>
+        <v>49575.068264560665</v>
+      </c>
+      <c r="FZ20" s="6">
+        <f t="shared" si="90"/>
+        <v>49079.317581915057</v>
+      </c>
+      <c r="GA20" s="6">
+        <f t="shared" si="90"/>
+        <v>48588.524406095908</v>
+      </c>
+      <c r="GB20" s="6">
+        <f t="shared" si="90"/>
+        <v>48102.639162034946</v>
+      </c>
+      <c r="GC20" s="6">
+        <f t="shared" si="90"/>
+        <v>47621.612770414598</v>
+      </c>
+      <c r="GD20" s="6">
+        <f t="shared" si="90"/>
+        <v>47145.396642710453</v>
+      </c>
+      <c r="GE20" s="6">
+        <f t="shared" si="90"/>
+        <v>46673.942676283346</v>
+      </c>
+      <c r="GF20" s="6">
+        <f t="shared" ref="GF20:GK20" si="91">GE20*(1+$BI$32)</f>
+        <v>46207.203249520513</v>
+      </c>
+      <c r="GG20" s="6">
         <f t="shared" si="91"/>
-        <v>152592.49378655062</v>
-      </c>
-      <c r="BJ20" s="6">
+        <v>45745.131217025308</v>
+      </c>
+      <c r="GH20" s="6">
         <f t="shared" si="91"/>
-        <v>151066.56884868513</v>
-      </c>
-      <c r="BK20" s="6">
+        <v>45287.679904855053</v>
+      </c>
+      <c r="GI20" s="6">
         <f t="shared" si="91"/>
-        <v>149555.90316019827</v>
-      </c>
-      <c r="BL20" s="6">
+        <v>44834.803105806503</v>
+      </c>
+      <c r="GJ20" s="6">
         <f t="shared" si="91"/>
-        <v>148060.34412859628</v>
-      </c>
-      <c r="BM20" s="6">
+        <v>44386.455074748439</v>
+      </c>
+      <c r="GK20" s="6">
         <f t="shared" si="91"/>
-        <v>146579.74068731032</v>
-      </c>
-      <c r="BN20" s="6">
-        <f t="shared" si="91"/>
-        <v>145113.9432804372</v>
-      </c>
-      <c r="BO20" s="6">
-        <f t="shared" si="91"/>
-        <v>143662.80384763284</v>
-      </c>
-      <c r="BP20" s="6">
-        <f t="shared" si="91"/>
-        <v>142226.1758091565</v>
-      </c>
-      <c r="BQ20" s="6">
-        <f t="shared" si="91"/>
-        <v>140803.91405106493</v>
-      </c>
-      <c r="BR20" s="6">
-        <f t="shared" si="91"/>
-        <v>139395.87491055427</v>
-      </c>
-      <c r="BS20" s="6">
-        <f t="shared" si="91"/>
-        <v>138001.91616144872</v>
-      </c>
-      <c r="BT20" s="6">
-        <f t="shared" si="91"/>
-        <v>136621.89699983422</v>
-      </c>
-      <c r="BU20" s="6">
-        <f t="shared" si="91"/>
-        <v>135255.67802983586</v>
-      </c>
-      <c r="BV20" s="6">
-        <f t="shared" si="91"/>
-        <v>133903.12124953751</v>
-      </c>
-      <c r="BW20" s="6">
-        <f t="shared" si="91"/>
-        <v>132564.09003704213</v>
-      </c>
-      <c r="BX20" s="6">
-        <f t="shared" si="91"/>
-        <v>131238.4491366717</v>
-      </c>
-      <c r="BY20" s="6">
-        <f t="shared" si="91"/>
-        <v>129926.06464530498</v>
-      </c>
-      <c r="BZ20" s="6">
-        <f t="shared" si="91"/>
-        <v>128626.80399885193</v>
-      </c>
-      <c r="CA20" s="6">
-        <f t="shared" si="91"/>
-        <v>127340.53595886342</v>
-      </c>
-      <c r="CB20" s="6">
-        <f t="shared" si="91"/>
-        <v>126067.13059927478</v>
-      </c>
-      <c r="CC20" s="6">
-        <f t="shared" si="91"/>
-        <v>124806.45929328204</v>
-      </c>
-      <c r="CD20" s="6">
-        <f t="shared" si="91"/>
-        <v>123558.39470034922</v>
-      </c>
-      <c r="CE20" s="6">
-        <f t="shared" si="91"/>
-        <v>122322.81075334572</v>
-      </c>
-      <c r="CF20" s="6">
-        <f t="shared" si="91"/>
-        <v>121099.58264581226</v>
-      </c>
-      <c r="CG20" s="6">
-        <f t="shared" si="91"/>
-        <v>119888.58681935414</v>
-      </c>
-      <c r="CH20" s="6">
-        <f t="shared" si="91"/>
-        <v>118689.7009511606</v>
-      </c>
-      <c r="CI20" s="6">
-        <f t="shared" si="91"/>
-        <v>117502.80394164899</v>
-      </c>
-      <c r="CJ20" s="6">
-        <f t="shared" si="91"/>
-        <v>116327.7759022325</v>
-      </c>
-      <c r="CK20" s="6">
-        <f t="shared" si="91"/>
-        <v>115164.49814321018</v>
-      </c>
-      <c r="CL20" s="6">
-        <f t="shared" si="91"/>
-        <v>114012.85316177807</v>
-      </c>
-      <c r="CM20" s="6">
-        <f t="shared" si="91"/>
-        <v>112872.72463016029</v>
-      </c>
-      <c r="CN20" s="6">
-        <f t="shared" si="91"/>
-        <v>111743.99738385869</v>
-      </c>
-      <c r="CO20" s="6">
-        <f t="shared" si="91"/>
-        <v>110626.5574100201</v>
-      </c>
-      <c r="CP20" s="6">
-        <f t="shared" si="91"/>
-        <v>109520.2918359199</v>
-      </c>
-      <c r="CQ20" s="6">
-        <f t="shared" si="91"/>
-        <v>108425.0889175607</v>
-      </c>
-      <c r="CR20" s="6">
-        <f t="shared" si="91"/>
-        <v>107340.83802838509</v>
-      </c>
-      <c r="CS20" s="6">
-        <f t="shared" si="91"/>
-        <v>106267.42964810123</v>
-      </c>
-      <c r="CT20" s="6">
-        <f t="shared" si="91"/>
-        <v>105204.75535162022</v>
-      </c>
-      <c r="CU20" s="6">
-        <f t="shared" si="91"/>
-        <v>104152.70779810402</v>
-      </c>
-      <c r="CV20" s="6">
-        <f t="shared" si="91"/>
-        <v>103111.18072012298</v>
-      </c>
-      <c r="CW20" s="6">
-        <f t="shared" si="91"/>
-        <v>102080.06891292175</v>
-      </c>
-      <c r="CX20" s="6">
-        <f t="shared" si="91"/>
-        <v>101059.26822379253</v>
-      </c>
-      <c r="CY20" s="6">
-        <f t="shared" si="91"/>
-        <v>100048.67554155461</v>
-      </c>
-      <c r="CZ20" s="6">
-        <f t="shared" si="91"/>
-        <v>99048.188786139057</v>
-      </c>
-      <c r="DA20" s="6">
-        <f t="shared" si="91"/>
-        <v>98057.706898277669</v>
-      </c>
-      <c r="DB20" s="6">
-        <f t="shared" si="91"/>
-        <v>97077.129829294892</v>
-      </c>
-      <c r="DC20" s="6">
-        <f t="shared" si="91"/>
-        <v>96106.358531001941</v>
-      </c>
-      <c r="DD20" s="6">
-        <f t="shared" si="91"/>
-        <v>95145.294945691916</v>
-      </c>
-      <c r="DE20" s="6">
-        <f t="shared" si="91"/>
-        <v>94193.841996235002</v>
-      </c>
-      <c r="DF20" s="6">
-        <f t="shared" si="91"/>
-        <v>93251.903576272656</v>
-      </c>
-      <c r="DG20" s="6">
-        <f t="shared" si="91"/>
-        <v>92319.384540509927</v>
-      </c>
-      <c r="DH20" s="6">
-        <f t="shared" si="91"/>
-        <v>91396.19069510483</v>
-      </c>
-      <c r="DI20" s="6">
-        <f t="shared" si="91"/>
-        <v>90482.228788153778</v>
-      </c>
-      <c r="DJ20" s="6">
-        <f t="shared" si="91"/>
-        <v>89577.406500272235</v>
-      </c>
-      <c r="DK20" s="6">
-        <f t="shared" si="91"/>
-        <v>88681.632435269508</v>
-      </c>
-      <c r="DL20" s="6">
-        <f t="shared" si="91"/>
-        <v>87794.816110916814</v>
-      </c>
-      <c r="DM20" s="6">
-        <f t="shared" si="91"/>
-        <v>86916.867949807638</v>
-      </c>
-      <c r="DN20" s="6">
-        <f t="shared" si="91"/>
-        <v>86047.69927030956</v>
-      </c>
-      <c r="DO20" s="6">
-        <f t="shared" si="91"/>
-        <v>85187.222277606459</v>
-      </c>
-      <c r="DP20" s="6">
-        <f t="shared" si="91"/>
-        <v>84335.3500548304</v>
-      </c>
-      <c r="DQ20" s="6">
-        <f t="shared" si="91"/>
-        <v>83491.996554282101</v>
-      </c>
-      <c r="DR20" s="6">
-        <f t="shared" si="91"/>
-        <v>82657.076588739277</v>
-      </c>
-      <c r="DS20" s="6">
-        <f t="shared" si="91"/>
-        <v>81830.50582285189</v>
-      </c>
-      <c r="DT20" s="6">
-        <f t="shared" ref="DT20:GE20" si="92">DS20*(1+$BI$32)</f>
-        <v>81012.200764623369</v>
-      </c>
-      <c r="DU20" s="6">
-        <f t="shared" si="92"/>
-        <v>80202.078756977135</v>
-      </c>
-      <c r="DV20" s="6">
-        <f t="shared" si="92"/>
-        <v>79400.057969407368</v>
-      </c>
-      <c r="DW20" s="6">
-        <f t="shared" si="92"/>
-        <v>78606.0573897133</v>
-      </c>
-      <c r="DX20" s="6">
-        <f t="shared" si="92"/>
-        <v>77819.996815816165</v>
-      </c>
-      <c r="DY20" s="6">
-        <f t="shared" si="92"/>
-        <v>77041.796847657999</v>
-      </c>
-      <c r="DZ20" s="6">
-        <f t="shared" si="92"/>
-        <v>76271.378879181415</v>
-      </c>
-      <c r="EA20" s="6">
-        <f t="shared" si="92"/>
-        <v>75508.665090389593</v>
-      </c>
-      <c r="EB20" s="6">
-        <f t="shared" si="92"/>
-        <v>74753.578439485704</v>
-      </c>
-      <c r="EC20" s="6">
-        <f t="shared" si="92"/>
-        <v>74006.042655090845</v>
-      </c>
-      <c r="ED20" s="6">
-        <f t="shared" si="92"/>
-        <v>73265.982228539942</v>
-      </c>
-      <c r="EE20" s="6">
-        <f t="shared" si="92"/>
-        <v>72533.322406254549</v>
-      </c>
-      <c r="EF20" s="6">
-        <f t="shared" si="92"/>
-        <v>71807.989182192003</v>
-      </c>
-      <c r="EG20" s="6">
-        <f t="shared" si="92"/>
-        <v>71089.90929037008</v>
-      </c>
-      <c r="EH20" s="6">
-        <f t="shared" si="92"/>
-        <v>70379.010197466385</v>
-      </c>
-      <c r="EI20" s="6">
-        <f t="shared" si="92"/>
-        <v>69675.220095491721</v>
-      </c>
-      <c r="EJ20" s="6">
-        <f t="shared" si="92"/>
-        <v>68978.467894536807</v>
-      </c>
-      <c r="EK20" s="6">
-        <f t="shared" si="92"/>
-        <v>68288.683215591445</v>
-      </c>
-      <c r="EL20" s="6">
-        <f t="shared" si="92"/>
-        <v>67605.796383435532</v>
-      </c>
-      <c r="EM20" s="6">
-        <f t="shared" si="92"/>
-        <v>66929.73841960117</v>
-      </c>
-      <c r="EN20" s="6">
-        <f t="shared" si="92"/>
-        <v>66260.441035405151</v>
-      </c>
-      <c r="EO20" s="6">
-        <f t="shared" si="92"/>
-        <v>65597.836625051103</v>
-      </c>
-      <c r="EP20" s="6">
-        <f t="shared" si="92"/>
-        <v>64941.858258800588</v>
-      </c>
-      <c r="EQ20" s="6">
-        <f t="shared" si="92"/>
-        <v>64292.439676212583</v>
-      </c>
-      <c r="ER20" s="6">
-        <f t="shared" si="92"/>
-        <v>63649.515279450454</v>
-      </c>
-      <c r="ES20" s="6">
-        <f t="shared" si="92"/>
-        <v>63013.020126655945</v>
-      </c>
-      <c r="ET20" s="6">
-        <f t="shared" si="92"/>
-        <v>62382.889925389383</v>
-      </c>
-      <c r="EU20" s="6">
-        <f t="shared" si="92"/>
-        <v>61759.061026135489</v>
-      </c>
-      <c r="EV20" s="6">
-        <f t="shared" si="92"/>
-        <v>61141.47041587413</v>
-      </c>
-      <c r="EW20" s="6">
-        <f t="shared" si="92"/>
-        <v>60530.055711715388</v>
-      </c>
-      <c r="EX20" s="6">
-        <f t="shared" si="92"/>
-        <v>59924.755154598235</v>
-      </c>
-      <c r="EY20" s="6">
-        <f t="shared" si="92"/>
-        <v>59325.507603052254</v>
-      </c>
-      <c r="EZ20" s="6">
-        <f t="shared" si="92"/>
-        <v>58732.25252702173</v>
-      </c>
-      <c r="FA20" s="6">
-        <f t="shared" si="92"/>
-        <v>58144.930001751512</v>
-      </c>
-      <c r="FB20" s="6">
-        <f t="shared" si="92"/>
-        <v>57563.480701733999</v>
-      </c>
-      <c r="FC20" s="6">
-        <f t="shared" si="92"/>
-        <v>56987.845894716658</v>
-      </c>
-      <c r="FD20" s="6">
-        <f t="shared" si="92"/>
-        <v>56417.967435769489</v>
-      </c>
-      <c r="FE20" s="6">
-        <f t="shared" si="92"/>
-        <v>55853.787761411797</v>
-      </c>
-      <c r="FF20" s="6">
-        <f t="shared" si="92"/>
-        <v>55295.249883797682</v>
-      </c>
-      <c r="FG20" s="6">
-        <f t="shared" si="92"/>
-        <v>54742.297384959704</v>
-      </c>
-      <c r="FH20" s="6">
-        <f t="shared" si="92"/>
-        <v>54194.874411110104</v>
-      </c>
-      <c r="FI20" s="6">
-        <f t="shared" si="92"/>
-        <v>53652.925666998999</v>
-      </c>
-      <c r="FJ20" s="6">
-        <f t="shared" si="92"/>
-        <v>53116.396410329005</v>
-      </c>
-      <c r="FK20" s="6">
-        <f t="shared" si="92"/>
-        <v>52585.232446225717</v>
-      </c>
-      <c r="FL20" s="6">
-        <f t="shared" si="92"/>
-        <v>52059.380121763461</v>
-      </c>
-      <c r="FM20" s="6">
-        <f t="shared" si="92"/>
-        <v>51538.786320545827</v>
-      </c>
-      <c r="FN20" s="6">
-        <f t="shared" si="92"/>
-        <v>51023.398457340365</v>
-      </c>
-      <c r="FO20" s="6">
-        <f t="shared" si="92"/>
-        <v>50513.164472766963</v>
-      </c>
-      <c r="FP20" s="6">
-        <f t="shared" si="92"/>
-        <v>50008.032828039293</v>
-      </c>
-      <c r="FQ20" s="6">
-        <f t="shared" si="92"/>
-        <v>49507.952499758903</v>
-      </c>
-      <c r="FR20" s="6">
-        <f t="shared" si="92"/>
-        <v>49012.872974761311</v>
-      </c>
-      <c r="FS20" s="6">
-        <f t="shared" si="92"/>
-        <v>48522.744245013695</v>
-      </c>
-      <c r="FT20" s="6">
-        <f t="shared" si="92"/>
-        <v>48037.516802563558</v>
-      </c>
-      <c r="FU20" s="6">
-        <f t="shared" si="92"/>
-        <v>47557.141634537918</v>
-      </c>
-      <c r="FV20" s="6">
-        <f t="shared" si="92"/>
-        <v>47081.570218192537</v>
-      </c>
-      <c r="FW20" s="6">
-        <f t="shared" si="92"/>
-        <v>46610.754516010609</v>
-      </c>
-      <c r="FX20" s="6">
-        <f t="shared" si="92"/>
-        <v>46144.646970850503</v>
-      </c>
-      <c r="FY20" s="6">
-        <f t="shared" si="92"/>
-        <v>45683.200501141997</v>
-      </c>
-      <c r="FZ20" s="6">
-        <f t="shared" si="92"/>
-        <v>45226.368496130577</v>
-      </c>
-      <c r="GA20" s="6">
-        <f t="shared" si="92"/>
-        <v>44774.104811169273</v>
-      </c>
-      <c r="GB20" s="6">
-        <f t="shared" si="92"/>
-        <v>44326.363763057576</v>
-      </c>
-      <c r="GC20" s="6">
-        <f t="shared" si="92"/>
-        <v>43883.100125427001</v>
-      </c>
-      <c r="GD20" s="6">
-        <f t="shared" si="92"/>
-        <v>43444.26912417273</v>
-      </c>
-      <c r="GE20" s="6">
-        <f t="shared" si="92"/>
-        <v>43009.826432931004</v>
-      </c>
-      <c r="GF20" s="6">
-        <f t="shared" ref="GF20:GK20" si="93">GE20*(1+$BI$32)</f>
-        <v>42579.728168601694</v>
-      </c>
-      <c r="GG20" s="6">
-        <f t="shared" si="93"/>
-        <v>42153.930886915674</v>
-      </c>
-      <c r="GH20" s="6">
-        <f t="shared" si="93"/>
-        <v>41732.391578046518</v>
-      </c>
-      <c r="GI20" s="6">
-        <f t="shared" si="93"/>
-        <v>41315.067662266054</v>
-      </c>
-      <c r="GJ20" s="6">
-        <f t="shared" si="93"/>
-        <v>40901.916985643395</v>
-      </c>
-      <c r="GK20" s="6">
-        <f t="shared" si="93"/>
-        <v>40492.897815786957</v>
+        <v>43942.590524000952</v>
       </c>
     </row>
     <row r="21" spans="2:193" x14ac:dyDescent="0.3">
@@ -5003,20 +4994,20 @@
         <v>12190</v>
       </c>
       <c r="AI21" s="1">
-        <f t="shared" ref="AI21:AL21" si="94">5833+860+5497</f>
+        <f t="shared" ref="AI21" si="92">5833+860+5497</f>
         <v>12190</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" si="94"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AK21" s="1">
-        <f t="shared" si="94"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AL21" s="1">
-        <f t="shared" si="94"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AN21" s="1">
         <v>680</v>
@@ -5040,52 +5031,52 @@
         <v>12488</v>
       </c>
       <c r="AU21" s="1">
-        <f t="shared" ref="AU21:BF21" si="95">5833+860+5497</f>
+        <f t="shared" ref="AU21" si="93">5833+860+5497</f>
         <v>12190</v>
       </c>
       <c r="AV21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AW21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AX21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AY21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="AZ21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BA21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BB21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BC21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BD21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BE21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
       <c r="BF21" s="1">
-        <f t="shared" si="95"/>
-        <v>12190</v>
+        <f>12122</f>
+        <v>12122</v>
       </c>
     </row>
     <row r="22" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -5093,224 +5084,224 @@
         <v>32</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:P22" si="96">C20/C21</f>
+        <f t="shared" ref="C22:P22" si="94">C20/C21</f>
         <v>7.9794117647058824</v>
       </c>
       <c r="D22" s="7">
+        <f t="shared" si="94"/>
+        <v>9.2058823529411757</v>
+      </c>
+      <c r="E22" s="7">
+        <f t="shared" si="94"/>
+        <v>9.9</v>
+      </c>
+      <c r="F22" s="7">
+        <f t="shared" si="94"/>
+        <v>-4.5750000000000002</v>
+      </c>
+      <c r="G22" s="7">
+        <f t="shared" si="94"/>
+        <v>13.824999999999999</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="94"/>
+        <v>12.155882352941177</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="94"/>
+        <v>13.517647058823529</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="94"/>
+        <v>13.158823529411764</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="94"/>
+        <v>9.7897058823529406</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="94"/>
+        <v>14.627941176470589</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" si="94"/>
+        <v>10.394117647058824</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="94"/>
+        <v>15.69264705882353</v>
+      </c>
+      <c r="O22" s="7">
+        <f t="shared" si="94"/>
+        <v>10.052941176470588</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" si="94"/>
+        <v>10.233823529411765</v>
+      </c>
+      <c r="Q22" s="7">
+        <f t="shared" ref="Q22" si="95">Q20/Q21</f>
+        <v>17.036982248520712</v>
+      </c>
+      <c r="R22" s="7">
+        <f t="shared" ref="R22:V22" si="96">R20/R21</f>
+        <v>22.132267441860463</v>
+      </c>
+      <c r="S22" s="7">
         <f t="shared" si="96"/>
-        <v>9.2058823529411757</v>
-      </c>
-      <c r="E22" s="7">
+        <v>26.061046511627907</v>
+      </c>
+      <c r="T22" s="7">
         <f t="shared" si="96"/>
-        <v>9.9</v>
-      </c>
-      <c r="F22" s="7">
+        <v>1.352901229910209</v>
+      </c>
+      <c r="U22" s="7">
+        <f t="shared" ref="U22" si="97">U20/U21</f>
+        <v>1.4288085716441561</v>
+      </c>
+      <c r="V22" s="7">
         <f t="shared" si="96"/>
-        <v>-4.5750000000000002</v>
-      </c>
-      <c r="G22" s="7">
-        <f t="shared" si="96"/>
-        <v>13.824999999999999</v>
-      </c>
-      <c r="H22" s="7">
-        <f t="shared" si="96"/>
-        <v>12.155882352941177</v>
-      </c>
-      <c r="I22" s="7">
-        <f t="shared" si="96"/>
-        <v>13.517647058823529</v>
-      </c>
-      <c r="J22" s="7">
-        <f t="shared" si="96"/>
-        <v>13.158823529411764</v>
-      </c>
-      <c r="K22" s="7">
-        <f t="shared" si="96"/>
-        <v>9.7897058823529406</v>
-      </c>
-      <c r="L22" s="7">
-        <f t="shared" si="96"/>
-        <v>14.627941176470589</v>
-      </c>
-      <c r="M22" s="7">
-        <f t="shared" si="96"/>
-        <v>10.394117647058824</v>
-      </c>
-      <c r="N22" s="7">
-        <f t="shared" si="96"/>
-        <v>15.69264705882353</v>
-      </c>
-      <c r="O22" s="7">
-        <f t="shared" si="96"/>
-        <v>10.052941176470588</v>
-      </c>
-      <c r="P22" s="7">
-        <f t="shared" si="96"/>
-        <v>10.233823529411765</v>
-      </c>
-      <c r="Q22" s="7">
-        <f t="shared" ref="Q22" si="97">Q20/Q21</f>
-        <v>17.036982248520712</v>
-      </c>
-      <c r="R22" s="7">
-        <f t="shared" ref="R22:V22" si="98">R20/R21</f>
-        <v>22.132267441860463</v>
-      </c>
-      <c r="S22" s="7">
+        <v>1.5575341432128575</v>
+      </c>
+      <c r="W22" s="7">
+        <f t="shared" ref="W22:X22" si="98">W20/W21</f>
+        <v>1.2744049003644258</v>
+      </c>
+      <c r="X22" s="7">
         <f t="shared" si="98"/>
-        <v>26.061046511627907</v>
-      </c>
-      <c r="T22" s="7">
-        <f t="shared" si="98"/>
-        <v>1.352901229910209</v>
-      </c>
-      <c r="U22" s="7">
-        <f t="shared" ref="U22" si="99">U20/U21</f>
-        <v>1.4288085716441561</v>
-      </c>
-      <c r="V22" s="7">
-        <f t="shared" si="98"/>
-        <v>1.5575341432128575</v>
-      </c>
-      <c r="W22" s="7">
-        <f t="shared" ref="W22:X22" si="100">W20/W21</f>
-        <v>1.2744049003644258</v>
-      </c>
-      <c r="X22" s="7">
-        <f t="shared" si="100"/>
         <v>1.2407536636427077</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" ref="Y22" si="101">Y20/Y21</f>
+        <f t="shared" ref="Y22" si="99">Y20/Y21</f>
         <v>1.0785453981546096</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" ref="Z22" si="102">Z20/Z21</f>
+        <f t="shared" ref="Z22" si="100">Z20/Z21</f>
         <v>1.0563696983794681</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AB22" si="103">AA20/AA21</f>
+        <f t="shared" ref="AA22:AB22" si="101">AA20/AA21</f>
         <v>1.1670155850197721</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>1.4242071799643328</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" ref="AC22" si="104">AC20/AC21</f>
+        <f t="shared" ref="AC22" si="102">AC20/AC21</f>
         <v>1.5266341009537101</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" ref="AD22" si="105">AD20/AD21</f>
+        <f t="shared" ref="AD22" si="103">AD20/AD21</f>
         <v>1.6565502882767458</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" ref="AE22:AH22" si="106">AE20/AE21</f>
+        <f t="shared" ref="AE22:AH22" si="104">AE20/AE21</f>
         <v>1.8947789878283152</v>
       </c>
       <c r="AF22" s="7">
+        <f t="shared" si="104"/>
+        <v>1.9186839967506093</v>
+      </c>
+      <c r="AG22" s="7">
+        <f t="shared" si="104"/>
+        <v>2.1485989706723307</v>
+      </c>
+      <c r="AH22" s="7">
+        <f t="shared" si="104"/>
+        <v>2.1768662838392125</v>
+      </c>
+      <c r="AI22" s="7">
+        <f t="shared" ref="AI22:AL22" si="105">AI20/AI21</f>
+        <v>2.8334700574241181</v>
+      </c>
+      <c r="AJ22" s="7">
+        <f t="shared" si="105"/>
+        <v>2.3260188087774294</v>
+      </c>
+      <c r="AK22" s="7">
+        <f t="shared" si="105"/>
+        <v>2.4968180096106254</v>
+      </c>
+      <c r="AL22" s="7">
+        <f t="shared" si="105"/>
+        <v>2.5258438582742122</v>
+      </c>
+      <c r="AN22" s="7">
+        <f t="shared" ref="AN22:AQ22" si="106">AN20/AN21</f>
+        <v>37.510294117647057</v>
+      </c>
+      <c r="AO22" s="7">
         <f t="shared" si="106"/>
-        <v>1.9186839967506093</v>
-      </c>
-      <c r="AG22" s="7">
+        <v>52.65735294117647</v>
+      </c>
+      <c r="AP22" s="7">
         <f t="shared" si="106"/>
-        <v>2.1485989706723307</v>
-      </c>
-      <c r="AH22" s="7">
+        <v>53.361764705882351</v>
+      </c>
+      <c r="AQ22" s="7">
         <f t="shared" si="106"/>
-        <v>2.1768662838392125</v>
-      </c>
-      <c r="AI22" s="7">
-        <f t="shared" ref="AI22:AL22" si="107">AI20/AI21</f>
-        <v>2.8334700574241181</v>
-      </c>
-      <c r="AJ22" s="7">
-        <f t="shared" si="107"/>
-        <v>2.1574347169811321</v>
-      </c>
-      <c r="AK22" s="7">
-        <f t="shared" si="107"/>
-        <v>2.4565633141919609</v>
-      </c>
-      <c r="AL22" s="7">
-        <f t="shared" si="107"/>
-        <v>2.534561852337982</v>
-      </c>
-      <c r="AN22" s="7">
-        <f t="shared" ref="AN22:AQ22" si="108">AN20/AN21</f>
-        <v>37.510294117647057</v>
-      </c>
-      <c r="AO22" s="7">
-        <f t="shared" si="108"/>
-        <v>52.65735294117647</v>
-      </c>
-      <c r="AP22" s="7">
-        <f t="shared" si="108"/>
-        <v>53.361764705882351</v>
-      </c>
-      <c r="AQ22" s="7">
-        <f t="shared" si="108"/>
         <v>59.968934911242606</v>
       </c>
       <c r="AR22" s="7">
-        <f t="shared" ref="AR22" si="109">AR20/AR21</f>
+        <f t="shared" ref="AR22" si="107">AR20/AR21</f>
         <v>109.64825581395348</v>
       </c>
       <c r="AS22" s="7">
-        <f t="shared" ref="AS22" si="110">AS20/AS21</f>
+        <f t="shared" ref="AS22" si="108">AS20/AS21</f>
         <v>4.650073660541211</v>
       </c>
       <c r="AT22" s="7">
-        <f t="shared" ref="AT22" si="111">AT20/AT21</f>
+        <f t="shared" ref="AT22" si="109">AT20/AT21</f>
         <v>5.909272901985906</v>
       </c>
       <c r="AU22" s="7">
-        <f t="shared" ref="AU22" si="112">AU20/AU21</f>
+        <f t="shared" ref="AU22" si="110">AU20/AU21</f>
         <v>8.2131255127153402</v>
       </c>
       <c r="AV22" s="7">
-        <f t="shared" ref="AV22" si="113">AV20/AV21</f>
-        <v>9.9820299409351918</v>
+        <f t="shared" ref="AV22" si="111">AV20/AV21</f>
+        <v>10.198045467950832</v>
       </c>
       <c r="AW22" s="7">
-        <f t="shared" ref="AW22" si="114">AW20/AW21</f>
-        <v>10.090616448359315</v>
+        <f t="shared" ref="AW22" si="112">AW20/AW21</f>
+        <v>10.497107768919319</v>
       </c>
       <c r="AX22" s="7">
-        <f t="shared" ref="AX22" si="115">AX20/AX21</f>
-        <v>10.662886718093356</v>
+        <f t="shared" ref="AX22" si="113">AX20/AX21</f>
+        <v>11.284405971082755</v>
       </c>
       <c r="AY22" s="7">
-        <f t="shared" ref="AY22" si="116">AY20/AY21</f>
-        <v>11.178556503224634</v>
+        <f t="shared" ref="AY22" si="114">AY20/AY21</f>
+        <v>11.939448907851217</v>
       </c>
       <c r="AZ22" s="7">
-        <f t="shared" ref="AZ22" si="117">AZ20/AZ21</f>
-        <v>11.563619825551077</v>
+        <f t="shared" ref="AZ22" si="115">AZ20/AZ21</f>
+        <v>12.442220812901867</v>
       </c>
       <c r="BA22" s="7">
-        <f t="shared" ref="BA22:BB22" si="118">BA20/BA21</f>
-        <v>11.945966366741235</v>
+        <f t="shared" ref="BA22:BB22" si="116">BA20/BA21</f>
+        <v>12.85032493101267</v>
       </c>
       <c r="BB22" s="7">
-        <f t="shared" si="118"/>
-        <v>12.203899260301593</v>
+        <f t="shared" si="116"/>
+        <v>13.222145035772154</v>
       </c>
       <c r="BC22" s="7">
-        <f t="shared" ref="BC22:BF22" si="119">BC20/BC21</f>
-        <v>12.40007951803268</v>
+        <f t="shared" ref="BC22:BF22" si="117">BC20/BC21</f>
+        <v>13.533024282244723</v>
       </c>
       <c r="BD22" s="7">
-        <f t="shared" si="119"/>
-        <v>12.564028134053014</v>
+        <f t="shared" si="117"/>
+        <v>13.711585388613562</v>
       </c>
       <c r="BE22" s="7">
-        <f t="shared" si="119"/>
-        <v>12.730980779926906</v>
+        <f t="shared" si="117"/>
+        <v>13.893422624213425</v>
       </c>
       <c r="BF22" s="7">
-        <f t="shared" si="119"/>
-        <v>12.901015031583549</v>
+        <f t="shared" si="117"/>
+        <v>14.078620609454191</v>
       </c>
     </row>
     <row r="24" spans="2:193" x14ac:dyDescent="0.3">
@@ -5323,39 +5314,39 @@
         <v>0.14363586808394668</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24:AH24" si="120">AF3/AB3-1</f>
+        <f t="shared" ref="AF24:AH24" si="118">AF3/AB3-1</f>
         <v>0.13796096462419061</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>0.12172352700676869</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>0.12523948354852155</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" ref="AI24:AI29" si="121">AI3/AE3-1</f>
+        <f t="shared" ref="AI24:AI29" si="119">AI3/AE3-1</f>
         <v>9.8492070370049367E-2</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24:AJ29" si="122">AJ3/AF3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AJ24:AJ29" si="120">AJ3/AF3-1</f>
+        <v>0.11711228844132027</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" ref="AK24:AK29" si="123">AK3/AG3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AK24:AK29" si="121">AK3/AG3-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AL24" s="8">
-        <f t="shared" ref="AL24:AL29" si="124">AL3/AH3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AL24:AL29" si="122">AL3/AH3-1</f>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AR24" s="8">
-        <f t="shared" ref="AR24:AS24" si="125">AR3/AQ3-1</f>
+        <f t="shared" ref="AR24:AS24" si="123">AR3/AQ3-1</f>
         <v>0.43136783840402826</v>
       </c>
       <c r="AS24" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>9.0627118985438182E-2</v>
       </c>
       <c r="AT24" s="8">
@@ -5363,51 +5354,51 @@
         <v>7.7457679285934056E-2</v>
       </c>
       <c r="AU24" s="8">
-        <f t="shared" ref="AU24:BF29" si="126">AU3/AT3-1</f>
+        <f t="shared" ref="AU24:BF29" si="124">AU3/AT3-1</f>
         <v>0.13169516605440124</v>
       </c>
       <c r="AV24" s="8">
-        <f t="shared" si="126"/>
-        <v>7.6639001635669723E-2</v>
+        <f t="shared" si="124"/>
+        <v>9.8383615032006544E-2</v>
       </c>
       <c r="AW24" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AX24" s="8">
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AX24" s="8">
-        <f t="shared" si="126"/>
+      <c r="AY24" s="8">
+        <f t="shared" si="124"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AZ24" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AY24" s="8">
-        <f t="shared" si="126"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AZ24" s="8">
-        <f t="shared" si="126"/>
+      <c r="BA24" s="8">
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA24" s="8">
-        <f t="shared" si="126"/>
+      <c r="BB24" s="8">
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB24" s="8">
-        <f t="shared" si="126"/>
+      <c r="BC24" s="8">
+        <f t="shared" si="124"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BD24" s="8">
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC24" s="8">
-        <f t="shared" si="126"/>
+      <c r="BE24" s="8">
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD24" s="8">
-        <f t="shared" si="126"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BE24" s="8">
-        <f t="shared" si="126"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BF24" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5416,95 +5407,95 @@
         <v>81</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AH25" si="127">AE4/AA4-1</f>
+        <f t="shared" ref="AE25:AH25" si="125">AE4/AA4-1</f>
         <v>0.20872553414014638</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>0.13020221787345077</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>0.12185613682092544</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>0.1383695652173913</v>
       </c>
       <c r="AI25" s="8">
+        <f t="shared" si="119"/>
+        <v>0.10346106304079106</v>
+      </c>
+      <c r="AJ25" s="8">
+        <f t="shared" si="120"/>
+        <v>0.1307861018123051</v>
+      </c>
+      <c r="AK25" s="8">
         <f t="shared" si="121"/>
-        <v>0.10346106304079106</v>
-      </c>
-      <c r="AJ25" s="8">
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="AL25" s="8">
         <f t="shared" si="122"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AK25" s="8">
-        <f t="shared" si="123"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AL25" s="8">
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AR25" s="8">
+        <f t="shared" ref="AR25:AS25" si="126">AR4/AQ4-1</f>
+        <v>0.45888124620675708</v>
+      </c>
+      <c r="AS25" s="8">
+        <f t="shared" si="126"/>
+        <v>1.3797885248743258E-2</v>
+      </c>
+      <c r="AT25" s="8">
+        <f t="shared" ref="AT25" si="127">AT4/AS4-1</f>
+        <v>7.7522825975447018E-2</v>
+      </c>
+      <c r="AU25" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14715963186290071</v>
+      </c>
+      <c r="AV25" s="8">
+        <f t="shared" si="124"/>
+        <v>0.10772346252801079</v>
+      </c>
+      <c r="AW25" s="8">
+        <f t="shared" si="124"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AX25" s="8">
         <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AR25" s="8">
-        <f t="shared" ref="AR25:AS25" si="128">AR4/AQ4-1</f>
-        <v>0.45888124620675708</v>
-      </c>
-      <c r="AS25" s="8">
-        <f t="shared" si="128"/>
-        <v>1.3797885248743258E-2</v>
-      </c>
-      <c r="AT25" s="8">
-        <f t="shared" ref="AT25" si="129">AT4/AS4-1</f>
-        <v>7.7522825975447018E-2</v>
-      </c>
-      <c r="AU25" s="8">
-        <f t="shared" si="126"/>
-        <v>0.14715963186290071</v>
-      </c>
-      <c r="AV25" s="8">
-        <f t="shared" si="126"/>
-        <v>7.655877389548249E-2</v>
-      </c>
-      <c r="AW25" s="8">
-        <f t="shared" si="126"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AX25" s="8">
-        <f t="shared" si="126"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AY25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AZ25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF25" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5513,95 +5504,95 @@
         <v>82</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AH26" si="130">AE5/AA5-1</f>
+        <f t="shared" ref="AE26:AH26" si="128">AE5/AA5-1</f>
         <v>-1.1072572038420492E-2</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>-5.1719745222929991E-2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>-1.5777806754466051E-2</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>-4.1340243461492121E-2</v>
       </c>
       <c r="AI26" s="8">
+        <f t="shared" si="119"/>
+        <v>-2.1179009847565045E-2</v>
+      </c>
+      <c r="AJ26" s="8">
+        <f t="shared" si="120"/>
+        <v>-1.2090274046211769E-2</v>
+      </c>
+      <c r="AK26" s="8">
         <f t="shared" si="121"/>
-        <v>-2.1179009847565045E-2</v>
-      </c>
-      <c r="AJ26" s="8">
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="AL26" s="8">
         <f t="shared" si="122"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AK26" s="8">
-        <f t="shared" si="123"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="AL26" s="8">
+      <c r="AR26" s="8">
+        <f t="shared" ref="AR26:AS26" si="129">AR5/AQ5-1</f>
+        <v>0.37293200519705505</v>
+      </c>
+      <c r="AS26" s="8">
+        <f t="shared" si="129"/>
+        <v>3.4036781174095365E-2</v>
+      </c>
+      <c r="AT26" s="8">
+        <f t="shared" ref="AT26" si="130">AT5/AS5-1</f>
+        <v>-4.4783404514948111E-2</v>
+      </c>
+      <c r="AU26" s="8">
         <f t="shared" si="124"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="AR26" s="8">
-        <f t="shared" ref="AR26:AS26" si="131">AR5/AQ5-1</f>
-        <v>0.37293200519705505</v>
-      </c>
-      <c r="AS26" s="8">
-        <f t="shared" si="131"/>
-        <v>3.4036781174095365E-2</v>
-      </c>
-      <c r="AT26" s="8">
-        <f t="shared" ref="AT26" si="132">AT5/AS5-1</f>
-        <v>-4.4783404514948111E-2</v>
-      </c>
-      <c r="AU26" s="8">
-        <f t="shared" si="126"/>
         <v>-3.0435615738375055E-2</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" si="126"/>
-        <v>-2.028788827036454E-2</v>
+        <f t="shared" si="124"/>
+        <v>-1.834843044896084E-2</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF26" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5610,95 +5601,95 @@
         <v>83</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AH27" si="133">AE6/AA6-1</f>
+        <f t="shared" ref="AE27:AH27" si="131">AE6/AA6-1</f>
         <v>0.17887494941319293</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>0.14369933677229185</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>0.2778510612783307</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>7.772836761163604E-2</v>
       </c>
       <c r="AI27" s="8">
+        <f t="shared" si="119"/>
+        <v>0.18766449250486317</v>
+      </c>
+      <c r="AJ27" s="8">
+        <f t="shared" si="120"/>
+        <v>0.20307130584192445</v>
+      </c>
+      <c r="AK27" s="8">
         <f t="shared" si="121"/>
-        <v>0.18766449250486317</v>
-      </c>
-      <c r="AJ27" s="8">
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AL27" s="8">
         <f t="shared" si="122"/>
         <v>0.12999999999999989</v>
       </c>
-      <c r="AK27" s="8">
-        <f t="shared" si="123"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AL27" s="8">
+      <c r="AR27" s="8">
+        <f t="shared" ref="AR27:AS27" si="132">AR6/AQ6-1</f>
+        <v>0.29114273870388274</v>
+      </c>
+      <c r="AS27" s="8">
+        <f t="shared" si="132"/>
+        <v>3.6494006849315141E-2</v>
+      </c>
+      <c r="AT27" s="8">
+        <f t="shared" ref="AT27" si="133">AT6/AS6-1</f>
+        <v>0.19387368783341929</v>
+      </c>
+      <c r="AU27" s="8">
+        <f t="shared" si="124"/>
+        <v>0.16293819188191883</v>
+      </c>
+      <c r="AV27" s="8">
+        <f t="shared" si="124"/>
+        <v>0.16464278631631135</v>
+      </c>
+      <c r="AW27" s="8">
+        <f t="shared" si="124"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="AX27" s="8">
+        <f t="shared" si="124"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AY27" s="8">
+        <f t="shared" si="124"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AZ27" s="8">
         <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR27" s="8">
-        <f t="shared" ref="AR27:AS27" si="134">AR6/AQ6-1</f>
-        <v>0.29114273870388274</v>
-      </c>
-      <c r="AS27" s="8">
-        <f t="shared" si="134"/>
-        <v>3.6494006849315141E-2</v>
-      </c>
-      <c r="AT27" s="8">
-        <f t="shared" ref="AT27" si="135">AT6/AS6-1</f>
-        <v>0.19387368783341929</v>
-      </c>
-      <c r="AU27" s="8">
-        <f t="shared" si="126"/>
-        <v>0.16293819188191883</v>
-      </c>
-      <c r="AV27" s="8">
-        <f t="shared" si="126"/>
-        <v>8.7239216658403507E-2</v>
-      </c>
-      <c r="AW27" s="8">
-        <f t="shared" si="126"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AX27" s="8">
-        <f t="shared" si="126"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AY27" s="8">
-        <f t="shared" si="126"/>
+      <c r="BA27" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ27" s="8">
-        <f t="shared" si="126"/>
+      <c r="BB27" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA27" s="8">
-        <f t="shared" si="126"/>
+      <c r="BC27" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB27" s="8">
-        <f t="shared" si="126"/>
+      <c r="BD27" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC27" s="8">
-        <f t="shared" si="126"/>
+      <c r="BE27" s="8">
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BD27" s="8">
-        <f t="shared" si="126"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BE27" s="8">
-        <f t="shared" si="126"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="BF27" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -5707,95 +5698,95 @@
         <v>84</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" ref="AE28:AH28" si="136">AE7/AA7-1</f>
+        <f t="shared" ref="AE28:AH28" si="134">AE7/AA7-1</f>
         <v>0.28441105446740012</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.28838251774374291</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.34978004993460954</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.3005874673629243</v>
       </c>
       <c r="AI28" s="8">
+        <f t="shared" si="119"/>
+        <v>0.28055149362857734</v>
+      </c>
+      <c r="AJ28" s="8">
+        <f t="shared" si="120"/>
+        <v>0.31671015753358467</v>
+      </c>
+      <c r="AK28" s="8">
         <f t="shared" si="121"/>
-        <v>0.28055149362857734</v>
-      </c>
-      <c r="AJ28" s="8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AL28" s="8">
         <f t="shared" si="122"/>
-        <v>0.25</v>
-      </c>
-      <c r="AK28" s="8">
-        <f t="shared" si="123"/>
-        <v>0.25</v>
-      </c>
-      <c r="AL28" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="AR28" s="8">
+        <f t="shared" ref="AR28:AS28" si="135">AR7/AQ7-1</f>
+        <v>0.47070985527222597</v>
+      </c>
+      <c r="AS28" s="8">
+        <f t="shared" si="135"/>
+        <v>0.36832239925023424</v>
+      </c>
+      <c r="AT28" s="8">
+        <f t="shared" ref="AT28" si="136">AT7/AS7-1</f>
+        <v>0.25905631659056327</v>
+      </c>
+      <c r="AU28" s="8">
         <f t="shared" si="124"/>
-        <v>0.25</v>
-      </c>
-      <c r="AR28" s="8">
-        <f t="shared" ref="AR28:AS28" si="137">AR7/AQ7-1</f>
-        <v>0.47070985527222597</v>
-      </c>
-      <c r="AS28" s="8">
-        <f t="shared" si="137"/>
-        <v>0.36832239925023424</v>
-      </c>
-      <c r="AT28" s="8">
-        <f t="shared" ref="AT28" si="138">AT7/AS7-1</f>
-        <v>0.25905631659056327</v>
-      </c>
-      <c r="AU28" s="8">
-        <f t="shared" si="126"/>
         <v>0.30648573500967125</v>
       </c>
       <c r="AV28" s="8">
-        <f t="shared" si="126"/>
-        <v>0.25676629114714666</v>
+        <f t="shared" si="124"/>
+        <v>0.28337782507113274</v>
       </c>
       <c r="AW28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AX28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AY28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AZ28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="BA28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BB28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF28" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5804,95 +5795,95 @@
         <v>85</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" ref="AE29:AH29" si="139">AE8/AA8-1</f>
+        <f t="shared" ref="AE29:AH29" si="137">AE8/AA8-1</f>
         <v>0.71875</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>0.2807017543859649</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>0.30639730639730645</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>-0.39117199391171997</v>
       </c>
       <c r="AI29" s="8">
+        <f t="shared" si="119"/>
+        <v>-9.0909090909090939E-2</v>
+      </c>
+      <c r="AJ29" s="8">
+        <f t="shared" si="120"/>
+        <v>2.1917808219177992E-2</v>
+      </c>
+      <c r="AK29" s="8">
         <f t="shared" si="121"/>
-        <v>-9.0909090909090939E-2</v>
-      </c>
-      <c r="AJ29" s="8">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AL29" s="8">
         <f t="shared" si="122"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AK29" s="8">
-        <f t="shared" si="123"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AL29" s="8">
+      <c r="AR29" s="8">
+        <f t="shared" ref="AR29:AS29" si="138">AR8/AQ8-1</f>
+        <v>0.14611872146118721</v>
+      </c>
+      <c r="AS29" s="8">
+        <f t="shared" si="138"/>
+        <v>0.41832669322709171</v>
+      </c>
+      <c r="AT29" s="8">
+        <f t="shared" ref="AT29" si="139">AT8/AS8-1</f>
+        <v>0.4297752808988764</v>
+      </c>
+      <c r="AU29" s="8">
+        <f t="shared" si="124"/>
+        <v>7.9240340537000575E-2</v>
+      </c>
+      <c r="AV29" s="8">
+        <f t="shared" si="124"/>
+        <v>2.5364077669902896E-2</v>
+      </c>
+      <c r="AW29" s="8">
+        <f t="shared" si="124"/>
+        <v>0.25</v>
+      </c>
+      <c r="AX29" s="8">
+        <f t="shared" si="124"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AY29" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AZ29" s="8">
         <f t="shared" si="124"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AR29" s="8">
-        <f t="shared" ref="AR29:AS29" si="140">AR8/AQ8-1</f>
-        <v>0.14611872146118721</v>
-      </c>
-      <c r="AS29" s="8">
-        <f t="shared" si="140"/>
-        <v>0.41832669322709171</v>
-      </c>
-      <c r="AT29" s="8">
-        <f t="shared" ref="AT29" si="141">AT8/AS8-1</f>
-        <v>0.4297752808988764</v>
-      </c>
-      <c r="AU29" s="8">
-        <f t="shared" si="126"/>
-        <v>7.9240340537000575E-2</v>
-      </c>
-      <c r="AV29" s="8">
-        <f t="shared" si="126"/>
-        <v>4.2657766990291224E-2</v>
-      </c>
-      <c r="AW29" s="8">
-        <f t="shared" si="126"/>
-        <v>0.25</v>
-      </c>
-      <c r="AX29" s="8">
-        <f t="shared" si="126"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AY29" s="8">
-        <f t="shared" si="126"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AZ29" s="8">
-        <f t="shared" si="126"/>
-        <v>0.10000000000000009</v>
-      </c>
       <c r="BA29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BD29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BE29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BF29" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -5905,39 +5896,39 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="8">
-        <f t="shared" ref="G30" si="142">G10/C10-1</f>
+        <f t="shared" ref="G30" si="140">G10/C10-1</f>
         <v>0.25842424242424245</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" ref="H30" si="143">H10/D10-1</f>
+        <f t="shared" ref="H30" si="141">H10/D10-1</f>
         <v>0.25555555555555554</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" ref="I30" si="144">I10/E10-1</f>
+        <f t="shared" ref="I30" si="142">I10/E10-1</f>
         <v>0.21489269768111763</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" ref="J30" si="145">J10/F10-1</f>
+        <f t="shared" ref="J30" si="143">J10/F10-1</f>
         <v>0.21854058078927774</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" ref="K30:O30" si="146">K10/G10-1</f>
+        <f t="shared" ref="K30:O30" si="144">K10/G10-1</f>
         <v>0.16673088036987083</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.19251615273907574</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.2003260225251926</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.17310825949689379</v>
       </c>
       <c r="O30" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.13263986350752632</v>
       </c>
       <c r="P30" s="8">
@@ -5945,164 +5936,164 @@
         <v>-1.6613599013968749E-2</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" ref="Q30:R30" si="147">Q10/M10-1</f>
+        <f t="shared" ref="Q30:R30" si="145">Q10/M10-1</f>
         <v>0.14010222474628997</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.23489962018448174</v>
       </c>
       <c r="S30" s="8">
-        <f t="shared" ref="S30" si="148">S10/O10-1</f>
+        <f t="shared" ref="S30" si="146">S10/O10-1</f>
         <v>0.34391020189994892</v>
       </c>
       <c r="T30" s="8">
-        <f t="shared" ref="T30" si="149">T10/P10-1</f>
+        <f t="shared" ref="T30" si="147">T10/P10-1</f>
         <v>0.44434289892158652</v>
       </c>
       <c r="U30" s="8">
-        <f t="shared" ref="U30" si="150">U10/Q10-1</f>
+        <f t="shared" ref="U30" si="148">U10/Q10-1</f>
         <v>0.41030472353973102</v>
       </c>
       <c r="V30" s="8">
-        <f t="shared" ref="V30" si="151">V10/R10-1</f>
+        <f t="shared" ref="V30" si="149">V10/R10-1</f>
         <v>0.32386024113325607</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" ref="W30" si="152">W10/S10-1</f>
+        <f t="shared" ref="W30" si="150">W10/S10-1</f>
         <v>0.22954405756228069</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" ref="X30" si="153">X10/T10-1</f>
+        <f t="shared" ref="X30" si="151">X10/T10-1</f>
         <v>0.25980764363452291</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" ref="Y30" si="154">Y10/U10-1</f>
+        <f t="shared" ref="Y30" si="152">Y10/U10-1</f>
         <v>6.1027672840074931E-2</v>
       </c>
       <c r="Z30" s="8">
-        <f t="shared" ref="Z30" si="155">Z10/V10-1</f>
+        <f t="shared" ref="Z30" si="153">Z10/V10-1</f>
         <v>9.5984069034185104E-3</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" ref="AA30" si="156">AA10/W10-1</f>
+        <f t="shared" ref="AA30" si="154">AA10/W10-1</f>
         <v>2.6113422828660138E-2</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" ref="AB30" si="157">AB10/X10-1</f>
+        <f t="shared" ref="AB30" si="155">AB10/X10-1</f>
         <v>7.0589079428858392E-2</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" ref="AC30" si="158">AC10/Y10-1</f>
+        <f t="shared" ref="AC30" si="156">AC10/Y10-1</f>
         <v>0.11001273664100042</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" ref="AD30" si="159">AD10/Z10-1</f>
+        <f t="shared" ref="AD30" si="157">AD10/Z10-1</f>
         <v>0.13494108983799702</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" ref="AE30" si="160">AE10/AA10-1</f>
+        <f t="shared" ref="AE30" si="158">AE10/AA10-1</f>
         <v>0.15406880937710454</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" ref="AF30" si="161">AF10/AB10-1</f>
+        <f t="shared" ref="AF30" si="159">AF10/AB10-1</f>
         <v>0.13589083695244231</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" ref="AG30" si="162">AG10/AC10-1</f>
+        <f t="shared" ref="AG30" si="160">AG10/AC10-1</f>
         <v>0.15092642092498654</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" ref="AH30" si="163">AH10/AD10-1</f>
+        <f t="shared" ref="AH30" si="161">AH10/AD10-1</f>
         <v>0.11770362646275045</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" ref="AI30" si="164">AI10/AE10-1</f>
+        <f t="shared" ref="AI30" si="162">AI10/AE10-1</f>
         <v>0.12037646357665222</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" ref="AJ30" si="165">AJ10/AF10-1</f>
-        <v>9.1118925680300222E-2</v>
+        <f t="shared" ref="AJ30" si="163">AJ10/AF10-1</f>
+        <v>0.13790092280097244</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" ref="AK30" si="166">AK10/AG10-1</f>
-        <v>8.2129424026827547E-2</v>
+        <f t="shared" ref="AK30" si="164">AK10/AG10-1</f>
+        <v>0.1202914986178456</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" ref="AL30" si="167">AL10/AH10-1</f>
-        <v>7.8312100260187201E-2</v>
+        <f t="shared" ref="AL30" si="165">AL10/AH10-1</f>
+        <v>0.10155386704537217</v>
       </c>
       <c r="AO30" s="8">
         <f>AO10/AN10-1</f>
         <v>0.23522985807663144</v>
       </c>
       <c r="AP30" s="8">
-        <f t="shared" ref="AP30:BB30" si="168">AP10/AO10-1</f>
+        <f t="shared" ref="AP30:BB30" si="166">AP10/AO10-1</f>
         <v>0.18300089899794614</v>
       </c>
       <c r="AQ30" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>0.12770532012826141</v>
       </c>
       <c r="AR30" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>0.37552800407610931</v>
       </c>
       <c r="AS30" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>0.12651799690127485</v>
       </c>
       <c r="AT30" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>8.6827702272695095E-2</v>
       </c>
       <c r="AU30" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="166"/>
         <v>0.13866243322901561</v>
       </c>
       <c r="AV30" s="8">
-        <f t="shared" si="168"/>
-        <v>9.2054380060454077E-2</v>
+        <f t="shared" si="166"/>
+        <v>0.11941011605117446</v>
       </c>
       <c r="AW30" s="8">
-        <f t="shared" si="168"/>
-        <v>7.0092400902692642E-2</v>
+        <f t="shared" si="166"/>
+        <v>8.6986564200959959E-2</v>
       </c>
       <c r="AX30" s="8">
-        <f t="shared" si="168"/>
-        <v>5.1682951215026973E-2</v>
+        <f t="shared" si="166"/>
+        <v>6.3530869939751655E-2</v>
       </c>
       <c r="AY30" s="8">
-        <f t="shared" si="168"/>
-        <v>4.2505466036705908E-2</v>
+        <f t="shared" si="166"/>
+        <v>4.8732237712674875E-2</v>
       </c>
       <c r="AZ30" s="8">
-        <f t="shared" si="168"/>
-        <v>3.2983898797071864E-2</v>
+        <f t="shared" si="166"/>
+        <v>3.7995706978080523E-2</v>
       </c>
       <c r="BA30" s="8">
-        <f t="shared" si="168"/>
-        <v>2.9332214785900534E-2</v>
+        <f t="shared" si="166"/>
+        <v>2.9090155802546924E-2</v>
       </c>
       <c r="BB30" s="8">
-        <f t="shared" si="168"/>
-        <v>2.1413928188093401E-2</v>
+        <f t="shared" si="166"/>
+        <v>2.6451086908932941E-2</v>
       </c>
       <c r="BC30" s="8">
-        <f t="shared" ref="BC30" si="169">BC10/BB10-1</f>
-        <v>1.7589865380472913E-2</v>
+        <f t="shared" ref="BC30" si="167">BC10/BB10-1</f>
+        <v>2.2713092396257073E-2</v>
       </c>
       <c r="BD30" s="8">
-        <f t="shared" ref="BD30" si="170">BD10/BC10-1</f>
-        <v>1.5618076768113109E-2</v>
+        <f t="shared" ref="BD30" si="168">BD10/BC10-1</f>
+        <v>1.557419382221692E-2</v>
       </c>
       <c r="BE30" s="8">
-        <f t="shared" ref="BE30" si="171">BE10/BD10-1</f>
-        <v>1.5673375468928663E-2</v>
+        <f t="shared" ref="BE30" si="169">BE10/BD10-1</f>
+        <v>1.5629988909741321E-2</v>
       </c>
       <c r="BF30" s="8">
-        <f t="shared" ref="BF30" si="172">BF10/BE10-1</f>
-        <v>1.5729217831958131E-2</v>
+        <f t="shared" ref="BF30" si="170">BF10/BE10-1</f>
+        <v>1.5686324382289119E-2</v>
       </c>
     </row>
     <row r="31" spans="2:193" x14ac:dyDescent="0.3">
@@ -6110,55 +6101,55 @@
         <v>34</v>
       </c>
       <c r="C31" s="8">
-        <f t="shared" ref="C31:F31" si="173">C12/C10</f>
+        <f t="shared" ref="C31:F31" si="171">C12/C10</f>
         <v>0.60424242424242425</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.60119184928873515</v>
       </c>
       <c r="E31" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.59858850640933314</v>
       </c>
       <c r="F31" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.55736535120377262</v>
       </c>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:O31" si="174">G12/G10</f>
+        <f t="shared" ref="G31:O31" si="172">G12/G10</f>
         <v>0.56761702947408976</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.57488440456869894</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.57673384706579722</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.54379264690905382</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.55937147417375277</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.55587510271158591</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.56621151139534309</v>
       </c>
       <c r="N31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.54378730330982095</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.53881289632887097</v>
       </c>
       <c r="P31" s="8">
@@ -6166,167 +6157,167 @@
         <v>0.51554952085019712</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" ref="Q31:R31" si="175">Q12/Q10</f>
+        <f t="shared" ref="Q31:R31" si="173">Q12/Q10</f>
         <v>0.54265479825872265</v>
       </c>
       <c r="R31" s="8">
+        <f t="shared" si="173"/>
+        <v>0.54163590987380927</v>
+      </c>
+      <c r="S31" s="8">
+        <f t="shared" ref="S31:V31" si="174">S12/S10</f>
+        <v>0.56425136493473627</v>
+      </c>
+      <c r="T31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.56425136493473627</v>
+      </c>
+      <c r="U31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.57583156730857832</v>
+      </c>
+      <c r="V31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.56205774975107869</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" ref="W31:AE31" si="175">W12/W10</f>
+        <v>0.5647909896928438</v>
+      </c>
+      <c r="X31" s="8">
         <f t="shared" si="175"/>
-        <v>0.54163590987380927</v>
-      </c>
-      <c r="S31" s="8">
-        <f t="shared" ref="S31:V31" si="176">S12/S10</f>
-        <v>0.56425136493473627</v>
-      </c>
-      <c r="T31" s="8">
+        <v>0.56799885197675248</v>
+      </c>
+      <c r="Y31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.54903606785156023</v>
+      </c>
+      <c r="Z31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.53526719966337055</v>
+      </c>
+      <c r="AA31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.56135096794531936</v>
+      </c>
+      <c r="AB31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.5721945204010509</v>
+      </c>
+      <c r="AC31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.56672708069836886</v>
+      </c>
+      <c r="AD31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.56465067778936395</v>
+      </c>
+      <c r="AE31" s="8">
+        <f t="shared" si="175"/>
+        <v>0.58142018152696207</v>
+      </c>
+      <c r="AF31" s="8">
+        <f t="shared" ref="AF31:AH31" si="176">AF12/AF10</f>
+        <v>0.58099879634655782</v>
+      </c>
+      <c r="AG31" s="8">
         <f t="shared" si="176"/>
-        <v>0.56425136493473627</v>
-      </c>
-      <c r="U31" s="8">
+        <v>0.58678116644763678</v>
+      </c>
+      <c r="AH31" s="8">
         <f t="shared" si="176"/>
-        <v>0.57583156730857832</v>
-      </c>
-      <c r="V31" s="8">
-        <f t="shared" si="176"/>
-        <v>0.56205774975107869</v>
-      </c>
-      <c r="W31" s="8">
-        <f t="shared" ref="W31:AE31" si="177">W12/W10</f>
-        <v>0.5647909896928438</v>
-      </c>
-      <c r="X31" s="8">
+        <v>0.5790046543449191</v>
+      </c>
+      <c r="AI31" s="8">
+        <f t="shared" ref="AI31:AL31" si="177">AI12/AI10</f>
+        <v>0.5970365937451515</v>
+      </c>
+      <c r="AJ31" s="8">
         <f t="shared" si="177"/>
-        <v>0.56799885197675248</v>
-      </c>
-      <c r="Y31" s="8">
+        <v>0.59514871199236741</v>
+      </c>
+      <c r="AK31" s="8">
         <f t="shared" si="177"/>
-        <v>0.54903606785156023</v>
-      </c>
-      <c r="Z31" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AL31" s="8">
         <f t="shared" si="177"/>
-        <v>0.53526719966337055</v>
-      </c>
-      <c r="AA31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.56135096794531936</v>
-      </c>
-      <c r="AB31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.5721945204010509</v>
-      </c>
-      <c r="AC31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.56672708069836886</v>
-      </c>
-      <c r="AD31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.56465067778936395</v>
-      </c>
-      <c r="AE31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.58142018152696207</v>
-      </c>
-      <c r="AF31" s="8">
-        <f t="shared" ref="AF31:AH31" si="178">AF12/AF10</f>
-        <v>0.58099879634655782</v>
-      </c>
-      <c r="AG31" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="AN31" s="8">
+        <f t="shared" ref="AN31:BA31" si="178">AN12/AN10</f>
+        <v>0.58846737207034772</v>
+      </c>
+      <c r="AO31" s="8">
         <f t="shared" si="178"/>
-        <v>0.58678116644763678</v>
-      </c>
-      <c r="AH31" s="8">
+        <v>0.5647607422945643</v>
+      </c>
+      <c r="AP31" s="8">
         <f t="shared" si="178"/>
-        <v>0.5790046543449191</v>
-      </c>
-      <c r="AI31" s="8">
-        <f t="shared" ref="AI31:AL31" si="179">AI12/AI10</f>
-        <v>0.5970365937451515</v>
-      </c>
-      <c r="AJ31" s="8">
+        <v>0.5558054331910266</v>
+      </c>
+      <c r="AQ31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.53578374706207854</v>
+      </c>
+      <c r="AR31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.56659669973832105</v>
+      </c>
+      <c r="AS31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.55379442503783116</v>
+      </c>
+      <c r="AT31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.56625047984020505</v>
+      </c>
+      <c r="AU31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.58200435406179107</v>
+      </c>
+      <c r="AV31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.59812359797841674</v>
+      </c>
+      <c r="AW31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.6</v>
+      </c>
+      <c r="AX31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.6</v>
+      </c>
+      <c r="AY31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.6</v>
+      </c>
+      <c r="AZ31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.6</v>
+      </c>
+      <c r="BA31" s="8">
+        <f t="shared" si="178"/>
+        <v>0.6</v>
+      </c>
+      <c r="BB31" s="8">
+        <f t="shared" ref="BB31:BF31" si="179">BB12/BB10</f>
+        <v>0.6</v>
+      </c>
+      <c r="BC31" s="8">
         <f t="shared" si="179"/>
         <v>0.6</v>
       </c>
-      <c r="AK31" s="8">
+      <c r="BD31" s="8">
         <f t="shared" si="179"/>
         <v>0.6</v>
       </c>
-      <c r="AL31" s="8">
+      <c r="BE31" s="8">
         <f t="shared" si="179"/>
         <v>0.6</v>
       </c>
-      <c r="AN31" s="8">
-        <f t="shared" ref="AN31:BA31" si="180">AN12/AN10</f>
-        <v>0.58846737207034772</v>
-      </c>
-      <c r="AO31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.5647607422945643</v>
-      </c>
-      <c r="AP31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.5558054331910266</v>
-      </c>
-      <c r="AQ31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.53578374706207854</v>
-      </c>
-      <c r="AR31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.56659669973832105</v>
-      </c>
-      <c r="AS31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.55379442503783116</v>
-      </c>
-      <c r="AT31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.56625047984020505</v>
-      </c>
-      <c r="AU31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.58200435406179107</v>
-      </c>
-      <c r="AV31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.59930043711692293</v>
-      </c>
-      <c r="AW31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.6</v>
-      </c>
-      <c r="AX31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.6</v>
-      </c>
-      <c r="AY31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.6</v>
-      </c>
-      <c r="AZ31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.6</v>
-      </c>
-      <c r="BA31" s="8">
-        <f t="shared" si="180"/>
-        <v>0.6</v>
-      </c>
-      <c r="BB31" s="8">
-        <f t="shared" ref="BB31:BF31" si="181">BB12/BB10</f>
-        <v>0.6</v>
-      </c>
-      <c r="BC31" s="8">
-        <f t="shared" si="181"/>
-        <v>0.6</v>
-      </c>
-      <c r="BD31" s="8">
-        <f t="shared" si="181"/>
-        <v>0.6</v>
-      </c>
-      <c r="BE31" s="8">
-        <f t="shared" si="181"/>
-        <v>0.6</v>
-      </c>
       <c r="BF31" s="8">
-        <f t="shared" si="181"/>
+        <f t="shared" si="179"/>
         <v>0.6</v>
       </c>
     </row>
@@ -6335,19 +6326,19 @@
         <v>35</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:F32" si="182">C16/C10</f>
+        <f t="shared" ref="C32:F32" si="180">C16/C10</f>
         <v>0.26537373737373737</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="182"/>
+        <f t="shared" si="180"/>
         <v>0.26405228758169935</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="182"/>
+        <f t="shared" si="180"/>
         <v>0.28021028373901774</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="182"/>
+        <f t="shared" si="180"/>
         <v>0.23495284189625218</v>
       </c>
       <c r="G32" s="8">
@@ -6355,204 +6346,204 @@
         <v>0.24507159827907277</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" ref="H32:R32" si="183">H16/H10</f>
+        <f t="shared" ref="H32:R32" si="181">H16/H10</f>
         <v>0.24852252197078728</v>
       </c>
       <c r="I32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.25563129816241847</v>
+      </c>
+      <c r="J32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.20931357572054179</v>
+      </c>
+      <c r="K32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.18184319876716476</v>
+      </c>
+      <c r="L32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.23572308956450289</v>
+      </c>
+      <c r="M32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.22659818760957059</v>
+      </c>
+      <c r="N32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.20110689093868692</v>
+      </c>
+      <c r="O32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.1938093734055735</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.1666710186176463</v>
+      </c>
+      <c r="Q32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.24284755159941956</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.27507118000632713</v>
+      </c>
+      <c r="S32" s="8">
+        <f t="shared" ref="S32:V32" si="182">S16/S10</f>
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="T32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="U32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.32296753585798088</v>
+      </c>
+      <c r="V32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.29054098904746101</v>
+      </c>
+      <c r="W32" s="8">
+        <f t="shared" ref="W32:AE32" si="183">W16/W10</f>
+        <v>0.29545220626075192</v>
+      </c>
+      <c r="X32" s="8">
         <f t="shared" si="183"/>
-        <v>0.25563129816241847</v>
-      </c>
-      <c r="J32" s="8">
+        <v>0.279156202913109</v>
+      </c>
+      <c r="Y32" s="8">
         <f t="shared" si="183"/>
-        <v>0.20931357572054179</v>
-      </c>
-      <c r="K32" s="8">
+        <v>0.24800266311584554</v>
+      </c>
+      <c r="Z32" s="8">
         <f t="shared" si="183"/>
-        <v>0.18184319876716476</v>
-      </c>
-      <c r="L32" s="8">
+        <v>0.23879654954765411</v>
+      </c>
+      <c r="AA32" s="8">
         <f t="shared" si="183"/>
-        <v>0.23572308956450289</v>
-      </c>
-      <c r="M32" s="8">
+        <v>0.24954504420594092</v>
+      </c>
+      <c r="AB32" s="8">
         <f t="shared" si="183"/>
-        <v>0.22659818760957059</v>
-      </c>
-      <c r="N32" s="8">
+        <v>0.29271888906761029</v>
+      </c>
+      <c r="AC32" s="8">
         <f t="shared" si="183"/>
-        <v>0.20110689093868692</v>
-      </c>
-      <c r="O32" s="8">
+        <v>0.27829136948613303</v>
+      </c>
+      <c r="AD32" s="8">
         <f t="shared" si="183"/>
-        <v>0.1938093734055735</v>
-      </c>
-      <c r="P32" s="8">
+        <v>0.27455683003128256</v>
+      </c>
+      <c r="AE32" s="8">
         <f t="shared" si="183"/>
-        <v>0.1666710186176463</v>
-      </c>
-      <c r="Q32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.24284755159941956</v>
-      </c>
-      <c r="R32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.27507118000632713</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" ref="S32:V32" si="184">S16/S10</f>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="T32" s="8">
+        <v>0.31626913669154072</v>
+      </c>
+      <c r="AF32" s="8">
+        <f t="shared" ref="AF32:AH32" si="184">AF16/AF10</f>
+        <v>0.32362936914398999</v>
+      </c>
+      <c r="AG32" s="8">
         <f t="shared" si="184"/>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="U32" s="8">
+        <v>0.32311823084243441</v>
+      </c>
+      <c r="AH32" s="8">
         <f t="shared" si="184"/>
-        <v>0.32296753585798088</v>
-      </c>
-      <c r="V32" s="8">
-        <f t="shared" si="184"/>
-        <v>0.29054098904746101</v>
-      </c>
-      <c r="W32" s="8">
-        <f t="shared" ref="W32:AE32" si="185">W16/W10</f>
-        <v>0.29545220626075192</v>
-      </c>
-      <c r="X32" s="8">
+        <v>0.32105650519856122</v>
+      </c>
+      <c r="AI32" s="8">
+        <f t="shared" ref="AI32:AL32" si="185">AI16/AI10</f>
+        <v>0.33918478622248821</v>
+      </c>
+      <c r="AJ32" s="8">
         <f t="shared" si="185"/>
-        <v>0.279156202913109</v>
-      </c>
-      <c r="Y32" s="8">
+        <v>0.32429377359273243</v>
+      </c>
+      <c r="AK32" s="8">
         <f t="shared" si="185"/>
-        <v>0.24800266311584554</v>
-      </c>
-      <c r="Z32" s="8">
+        <v>0.32691228495794494</v>
+      </c>
+      <c r="AL32" s="8">
         <f t="shared" si="185"/>
-        <v>0.23879654954765411</v>
-      </c>
-      <c r="AA32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.24954504420594092</v>
-      </c>
-      <c r="AB32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.29271888906761029</v>
-      </c>
-      <c r="AC32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.27829136948613303</v>
-      </c>
-      <c r="AD32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.27455683003128256</v>
-      </c>
-      <c r="AE32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.31626913669154072</v>
-      </c>
-      <c r="AF32" s="8">
-        <f t="shared" ref="AF32:AH32" si="186">AF16/AF10</f>
-        <v>0.32362936914398999</v>
-      </c>
-      <c r="AG32" s="8">
+        <v>0.32665613019428641</v>
+      </c>
+      <c r="AN32" s="8">
+        <f t="shared" ref="AN32:BA32" si="186">AN16/AN10</f>
+        <v>0.25993102452060235</v>
+      </c>
+      <c r="AO32" s="8">
         <f t="shared" si="186"/>
-        <v>0.32311823084243441</v>
-      </c>
-      <c r="AH32" s="8">
+        <v>0.23823445574079624</v>
+      </c>
+      <c r="AP32" s="8">
         <f t="shared" si="186"/>
-        <v>0.32105650519856122</v>
-      </c>
-      <c r="AI32" s="8">
-        <f t="shared" ref="AI32:AL32" si="187">AI16/AI10</f>
-        <v>0.33918478622248821</v>
-      </c>
-      <c r="AJ32" s="8">
+        <v>0.22349357766423447</v>
+      </c>
+      <c r="AQ32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.22585151785763202</v>
+      </c>
+      <c r="AR32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.30186680261758625</v>
+      </c>
+      <c r="AS32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.26461270842467011</v>
+      </c>
+      <c r="AT32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.27421810445226646</v>
+      </c>
+      <c r="AU32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.32109777211457696</v>
+      </c>
+      <c r="AV32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.32902471388888938</v>
+      </c>
+      <c r="AW32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.33807300160269294</v>
+      </c>
+      <c r="AX32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.34279542787760608</v>
+      </c>
+      <c r="AY32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.3466067313879449</v>
+      </c>
+      <c r="AZ32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.34847880367214262</v>
+      </c>
+      <c r="BA32" s="8">
+        <f t="shared" si="186"/>
+        <v>0.35008221611057772</v>
+      </c>
+      <c r="BB32" s="8">
+        <f t="shared" ref="BB32:BF32" si="187">BB16/BB10</f>
+        <v>0.35121297165766235</v>
+      </c>
+      <c r="BC32" s="8">
         <f t="shared" si="187"/>
-        <v>0.33321622779126053</v>
-      </c>
-      <c r="AK32" s="8">
+        <v>0.35168726472260053</v>
+      </c>
+      <c r="BD32" s="8">
         <f t="shared" si="187"/>
-        <v>0.33448835500128771</v>
-      </c>
-      <c r="AL32" s="8">
+        <v>0.35091018943832414</v>
+      </c>
+      <c r="BE32" s="8">
         <f t="shared" si="187"/>
-        <v>0.33684124068277144</v>
-      </c>
-      <c r="AN32" s="8">
-        <f t="shared" ref="AN32:BA32" si="188">AN16/AN10</f>
-        <v>0.25993102452060235</v>
-      </c>
-      <c r="AO32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.23823445574079624</v>
-      </c>
-      <c r="AP32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.22349357766423447</v>
-      </c>
-      <c r="AQ32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.22585151785763202</v>
-      </c>
-      <c r="AR32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.30186680261758625</v>
-      </c>
-      <c r="AS32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.26461270842467011</v>
-      </c>
-      <c r="AT32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.27421810445226646</v>
-      </c>
-      <c r="AU32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.32109777211457696</v>
-      </c>
-      <c r="AV32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.33592962240426261</v>
-      </c>
-      <c r="AW32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.33966841350368759</v>
-      </c>
-      <c r="AX32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.34210739425740555</v>
-      </c>
-      <c r="AY32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.34467690474837925</v>
-      </c>
-      <c r="AZ32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.34556867483218279</v>
-      </c>
-      <c r="BA32" s="8">
-        <f t="shared" si="188"/>
-        <v>0.3471954495913242</v>
-      </c>
-      <c r="BB32" s="8">
-        <f t="shared" ref="BB32:BF32" si="189">BB16/BB10</f>
-        <v>0.34744158179968365</v>
-      </c>
-      <c r="BC32" s="8">
-        <f t="shared" si="189"/>
-        <v>0.34702103939330553</v>
-      </c>
-      <c r="BD32" s="8">
-        <f t="shared" si="189"/>
-        <v>0.34625314232637727</v>
-      </c>
-      <c r="BE32" s="8">
-        <f t="shared" si="189"/>
-        <v>0.34549170606355745</v>
+        <v>0.3501396091415106</v>
       </c>
       <c r="BF32" s="8">
-        <f t="shared" si="189"/>
-        <v>0.34473693716718201</v>
+        <f t="shared" si="187"/>
+        <v>0.34937573218066825</v>
       </c>
       <c r="BH32" t="s">
         <v>44</v>
@@ -6570,211 +6561,211 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33" si="190">G13/C13-1</f>
+        <f t="shared" ref="G33" si="188">G13/C13-1</f>
         <v>0.27828513444951808</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" ref="H33" si="191">H13/D13-1</f>
+        <f t="shared" ref="H33" si="189">H13/D13-1</f>
         <v>0.22579098753595406</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" ref="I33" si="192">I13/E13-1</f>
+        <f t="shared" ref="I33" si="190">I13/E13-1</f>
         <v>0.24423305588585009</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" ref="J33" si="193">J13/F13-1</f>
+        <f t="shared" ref="J33" si="191">J13/F13-1</f>
         <v>0.4013005109150023</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" ref="K33" si="194">K13/G13-1</f>
+        <f t="shared" ref="K33" si="192">K13/G13-1</f>
         <v>0.19646755308592967</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" ref="L33" si="195">L13/H13-1</f>
+        <f t="shared" ref="L33" si="193">L13/H13-1</f>
         <v>0.21490027375831056</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" ref="M33" si="196">M13/I13-1</f>
+        <f t="shared" ref="M33" si="194">M13/I13-1</f>
         <v>0.25267584097859319</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" ref="N33" si="197">N13/J13-1</f>
+        <f t="shared" ref="N33" si="195">N13/J13-1</f>
         <v>0.19688432217434548</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" ref="O33" si="198">O13/K13-1</f>
+        <f t="shared" ref="O33" si="196">O13/K13-1</f>
         <v>0.1311992038480676</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" ref="P33" si="199">P13/L13-1</f>
+        <f t="shared" ref="P33" si="197">P13/L13-1</f>
         <v>0.10655078062127799</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" ref="Q33" si="200">Q13/M13-1</f>
+        <f t="shared" ref="Q33" si="198">Q13/M13-1</f>
         <v>4.607873054623135E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" ref="R33" si="201">R13/N13-1</f>
+        <f t="shared" ref="R33" si="199">R13/N13-1</f>
         <v>-2.7693159789532018E-2</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" ref="S33" si="202">S13/O13-1</f>
+        <f t="shared" ref="S33" si="200">S13/O13-1</f>
         <v>9.7507331378299034E-2</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" ref="T33" si="203">T13/P13-1</f>
+        <f t="shared" ref="T33" si="201">T13/P13-1</f>
         <v>8.8727272727272766E-2</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" ref="U33" si="204">U13/Q13-1</f>
+        <f t="shared" ref="U33" si="202">U13/Q13-1</f>
         <v>0.12222870478413062</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" ref="V33" si="205">V13/R13-1</f>
+        <f t="shared" ref="V33" si="203">V13/R13-1</f>
         <v>0.24010253489034472</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="206">W13/S13-1</f>
+        <f t="shared" ref="W33" si="204">W13/S13-1</f>
         <v>0.21830327321309295</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" ref="X33" si="207">X13/T13-1</f>
+        <f t="shared" ref="X33" si="205">X13/T13-1</f>
         <v>0.31476285905143619</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" ref="Y33" si="208">Y13/U13-1</f>
+        <f t="shared" ref="Y33" si="206">Y13/U13-1</f>
         <v>0.33519625682349874</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" ref="Z33" si="209">Z13/V13-1</f>
+        <f t="shared" ref="Z33" si="207">Z13/V13-1</f>
         <v>0.17903077629765729</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33" si="210">AA13/W13-1</f>
+        <f t="shared" ref="AA33" si="208">AA13/W13-1</f>
         <v>0.25759403443360007</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" ref="AB33" si="211">AB13/X13-1</f>
+        <f t="shared" ref="AB33" si="209">AB13/X13-1</f>
         <v>7.590692002845234E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" ref="AC33" si="212">AC13/Y13-1</f>
+        <f t="shared" ref="AC33" si="210">AC13/Y13-1</f>
         <v>9.5882410201499013E-2</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" ref="AD33" si="213">AD13/Z13-1</f>
+        <f t="shared" ref="AD33" si="211">AD13/Z13-1</f>
         <v>0.17979935716372841</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33" si="214">AE13/AA13-1</f>
+        <f t="shared" ref="AE33" si="212">AE13/AA13-1</f>
         <v>3.7931635856295776E-2</v>
       </c>
       <c r="AF33" s="8">
-        <f t="shared" ref="AF33" si="215">AF13/AB13-1</f>
+        <f t="shared" ref="AF33" si="213">AF13/AB13-1</f>
         <v>0.12013600302228933</v>
       </c>
       <c r="AG33" s="8">
-        <f t="shared" ref="AG33" si="216">AG13/AC13-1</f>
+        <f t="shared" ref="AG33" si="214">AG13/AC13-1</f>
         <v>0.10561378575235381</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" ref="AH33" si="217">AH13/AD13-1</f>
+        <f t="shared" ref="AH33" si="215">AH13/AD13-1</f>
         <v>8.2803599438619591E-2</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33" si="218">AI13/AE13-1</f>
+        <f t="shared" ref="AI33" si="216">AI13/AE13-1</f>
         <v>0.13887255313786451</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33" si="219">AJ13/AF13-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AJ33" si="217">AJ13/AF13-1</f>
+        <v>0.16424957841483989</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" ref="AK33" si="220">AK13/AG13-1</f>
+        <f t="shared" ref="AK33" si="218">AK13/AG13-1</f>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AL33" s="8">
+        <f t="shared" ref="AL33" si="219">AL13/AH13-1</f>
         <v>0.12000000000000011</v>
-      </c>
-      <c r="AL33" s="8">
-        <f t="shared" ref="AL33" si="221">AL13/AH13-1</f>
-        <v>0.10000000000000009</v>
       </c>
       <c r="AN33" s="8"/>
       <c r="AO33" s="8">
-        <f t="shared" ref="AO33:BB35" si="222">AO13/AN13-1</f>
+        <f t="shared" ref="AO33:BB35" si="220">AO13/AN13-1</f>
         <v>0.28836090225563904</v>
       </c>
       <c r="AP33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.21471590643820915</v>
       </c>
       <c r="AQ33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>5.9766315627642452E-2</v>
       </c>
       <c r="AR33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.13777971203713779</v>
       </c>
       <c r="AS33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.25908453397934461</v>
       </c>
       <c r="AT33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.15005063291139242</v>
       </c>
       <c r="AU33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>8.583001298787063E-2</v>
       </c>
       <c r="AV33" s="8">
-        <f t="shared" si="222"/>
-        <v>0.1264493370636175</v>
+        <f t="shared" si="220"/>
+        <v>0.1402404411466569</v>
       </c>
       <c r="AW33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AX33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AY33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB33" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="8">
-        <f t="shared" ref="BC33" si="223">BC13/BB13-1</f>
+        <f t="shared" ref="BC33" si="221">BC13/BB13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="8">
-        <f t="shared" ref="BD33" si="224">BD13/BC13-1</f>
+        <f t="shared" ref="BD33" si="222">BD13/BC13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE33" s="8">
-        <f t="shared" ref="BE33" si="225">BE13/BD13-1</f>
+        <f t="shared" ref="BE33" si="223">BE13/BD13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF33" s="8">
-        <f t="shared" ref="BF33" si="226">BF13/BE13-1</f>
+        <f t="shared" ref="BF33" si="224">BF13/BE13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH33" t="s">
         <v>45</v>
       </c>
       <c r="BI33" s="8">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="34" spans="2:61" x14ac:dyDescent="0.3">
@@ -6782,19 +6773,19 @@
         <v>36</v>
       </c>
       <c r="C34" s="8">
-        <f t="shared" ref="C34:F34" si="227">C14/C10</f>
+        <f t="shared" ref="C34:F34" si="225">C14/C10</f>
         <v>0.10682828282828283</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>0.11138023836985775</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>0.10953478323491286</v>
       </c>
       <c r="F34" s="8">
-        <f t="shared" si="227"/>
+        <f t="shared" si="225"/>
         <v>0.13371804417969718</v>
       </c>
       <c r="G34" s="8">
@@ -6802,211 +6793,211 @@
         <v>0.11571309317408335</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" ref="H34:R34" si="228">H14/H10</f>
+        <f t="shared" ref="H34:R34" si="226">H14/H10</f>
         <v>0.11574853783262394</v>
       </c>
       <c r="I34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.11407824540604623</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.12985029025358999</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.10746030435620132</v>
+      </c>
+      <c r="L34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.10815529991783072</v>
+      </c>
+      <c r="M34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.11380527914269488</v>
+      </c>
+      <c r="N34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.1245360824742268</v>
+      </c>
+      <c r="O34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.10933210233484779</v>
+      </c>
+      <c r="P34" s="8">
+        <f t="shared" si="226"/>
+        <v>0.10186176462908322</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="226"/>
+        <v>9.1633638706603432E-2</v>
+      </c>
+      <c r="R34" s="8">
+        <f t="shared" si="226"/>
+        <v>9.3395198425252207E-2</v>
+      </c>
+      <c r="S34" s="8">
+        <f t="shared" ref="S34:V34" si="227">S14/S10</f>
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="T34" s="8">
+        <f t="shared" si="227"/>
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="U34" s="8">
+        <f t="shared" si="227"/>
+        <v>8.4707761294880057E-2</v>
+      </c>
+      <c r="V34" s="8">
+        <f t="shared" si="227"/>
+        <v>0.10094922004646532</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" ref="W34:AE34" si="228">W14/W10</f>
+        <v>8.5647909896928442E-2</v>
+      </c>
+      <c r="X34" s="8">
         <f t="shared" si="228"/>
-        <v>0.11407824540604623</v>
-      </c>
-      <c r="J34" s="8">
+        <v>9.514242663413934E-2</v>
+      </c>
+      <c r="Y34" s="8">
         <f t="shared" si="228"/>
-        <v>0.12985029025358999</v>
-      </c>
-      <c r="K34" s="8">
+        <v>0.10028657442250911</v>
+      </c>
+      <c r="Z34" s="8">
         <f t="shared" si="228"/>
-        <v>0.10746030435620132</v>
-      </c>
-      <c r="L34" s="8">
+        <v>9.4453503050704823E-2</v>
+      </c>
+      <c r="AA34" s="8">
         <f t="shared" si="228"/>
-        <v>0.10815529991783072</v>
-      </c>
-      <c r="M34" s="8">
+        <v>9.3613423703555104E-2</v>
+      </c>
+      <c r="AB34" s="8">
         <f t="shared" si="228"/>
-        <v>0.11380527914269488</v>
-      </c>
-      <c r="N34" s="8">
+        <v>9.0893249691705535E-2</v>
+      </c>
+      <c r="AC34" s="8">
         <f t="shared" si="228"/>
-        <v>0.1245360824742268</v>
-      </c>
-      <c r="O34" s="8">
+        <v>8.9760473576467215E-2</v>
+      </c>
+      <c r="AD34" s="8">
         <f t="shared" si="228"/>
-        <v>0.10933210233484779</v>
-      </c>
-      <c r="P34" s="8">
+        <v>8.9433437608620089E-2</v>
+      </c>
+      <c r="AE34" s="8">
         <f t="shared" si="228"/>
-        <v>0.10186176462908322</v>
-      </c>
-      <c r="Q34" s="8">
-        <f t="shared" si="228"/>
-        <v>9.1633638706603432E-2</v>
-      </c>
-      <c r="R34" s="8">
-        <f t="shared" si="228"/>
-        <v>9.3395198425252207E-2</v>
-      </c>
-      <c r="S34" s="8">
-        <f t="shared" ref="S34:V34" si="229">S14/S10</f>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="T34" s="8">
+        <v>7.9787432175716114E-2</v>
+      </c>
+      <c r="AF34" s="8">
+        <f t="shared" ref="AF34:AH34" si="229">AF14/AF10</f>
+        <v>8.0149158622642852E-2</v>
+      </c>
+      <c r="AG34" s="8">
         <f t="shared" si="229"/>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="U34" s="8">
+        <v>8.1875651425205059E-2</v>
+      </c>
+      <c r="AH34" s="8">
         <f t="shared" si="229"/>
-        <v>8.4707761294880057E-2</v>
-      </c>
-      <c r="V34" s="8">
-        <f t="shared" si="229"/>
-        <v>0.10094922004646532</v>
-      </c>
-      <c r="W34" s="8">
-        <f t="shared" ref="W34:AE34" si="230">W14/W10</f>
-        <v>8.5647909896928442E-2</v>
-      </c>
-      <c r="X34" s="8">
+        <v>7.6325037058536938E-2</v>
+      </c>
+      <c r="AI34" s="8">
+        <f t="shared" ref="AI34:AL34" si="230">AI14/AI10</f>
+        <v>6.8399937939136027E-2</v>
+      </c>
+      <c r="AJ34" s="8">
         <f t="shared" si="230"/>
-        <v>9.514242663413934E-2</v>
-      </c>
-      <c r="Y34" s="8">
+        <v>7.3640436387771194E-2</v>
+      </c>
+      <c r="AK34" s="8">
         <f t="shared" si="230"/>
-        <v>0.10028657442250911</v>
-      </c>
-      <c r="Z34" s="8">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="AL34" s="8">
         <f t="shared" si="230"/>
-        <v>9.4453503050704823E-2</v>
-      </c>
-      <c r="AA34" s="8">
-        <f t="shared" si="230"/>
-        <v>9.3613423703555104E-2</v>
-      </c>
-      <c r="AB34" s="8">
-        <f t="shared" si="230"/>
-        <v>9.0893249691705535E-2</v>
-      </c>
-      <c r="AC34" s="8">
-        <f t="shared" si="230"/>
-        <v>8.9760473576467215E-2</v>
-      </c>
-      <c r="AD34" s="8">
-        <f t="shared" si="230"/>
-        <v>8.9433437608620089E-2</v>
-      </c>
-      <c r="AE34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.9787432175716114E-2</v>
-      </c>
-      <c r="AF34" s="8">
-        <f t="shared" ref="AF34:AH34" si="231">AF14/AF10</f>
-        <v>8.0149158622642852E-2</v>
-      </c>
-      <c r="AG34" s="8">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="AN34" s="8">
+        <f t="shared" ref="AN34:BA34" si="231">AN14/AN10</f>
+        <v>0.11640063558556932</v>
+      </c>
+      <c r="AO34" s="8">
         <f t="shared" si="231"/>
-        <v>8.1875651425205059E-2</v>
-      </c>
-      <c r="AH34" s="8">
+        <v>0.1193766947573071</v>
+      </c>
+      <c r="AP34" s="8">
         <f t="shared" si="231"/>
-        <v>7.6325037058536938E-2</v>
-      </c>
-      <c r="AI34" s="8">
-        <f t="shared" ref="AI34:AL34" si="232">AI14/AI10</f>
-        <v>6.8399937939136027E-2</v>
-      </c>
-      <c r="AJ34" s="8">
+        <v>0.11407600536275848</v>
+      </c>
+      <c r="AQ34" s="8">
+        <f t="shared" si="231"/>
+        <v>9.8319700647027566E-2</v>
+      </c>
+      <c r="AR34" s="8">
+        <f t="shared" si="231"/>
+        <v>8.823002258325334E-2</v>
+      </c>
+      <c r="AS34" s="8">
+        <f t="shared" si="231"/>
+        <v>9.3930758460733427E-2</v>
+      </c>
+      <c r="AT34" s="8">
+        <f t="shared" si="231"/>
+        <v>9.0818298340240869E-2</v>
+      </c>
+      <c r="AU34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.94473427080893E-2</v>
+      </c>
+      <c r="AV34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.3145419574287968E-2</v>
+      </c>
+      <c r="AW34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AX34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AY34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AZ34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BA34" s="8">
+        <f t="shared" si="231"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BB34" s="8">
+        <f t="shared" ref="BB34:BF34" si="232">BB14/BB10</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BC34" s="8">
         <f t="shared" si="232"/>
-        <v>0.08</v>
-      </c>
-      <c r="AK34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BD34" s="8">
         <f t="shared" si="232"/>
-        <v>0.08</v>
-      </c>
-      <c r="AL34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BE34" s="8">
         <f t="shared" si="232"/>
-        <v>0.08</v>
-      </c>
-      <c r="AN34" s="8">
-        <f t="shared" ref="AN34:BA34" si="233">AN14/AN10</f>
-        <v>0.11640063558556932</v>
-      </c>
-      <c r="AO34" s="8">
-        <f t="shared" si="233"/>
-        <v>0.1193766947573071</v>
-      </c>
-      <c r="AP34" s="8">
-        <f t="shared" si="233"/>
-        <v>0.11407600536275848</v>
-      </c>
-      <c r="AQ34" s="8">
-        <f t="shared" si="233"/>
-        <v>9.8319700647027566E-2</v>
-      </c>
-      <c r="AR34" s="8">
-        <f t="shared" si="233"/>
-        <v>8.823002258325334E-2</v>
-      </c>
-      <c r="AS34" s="8">
-        <f t="shared" si="233"/>
-        <v>9.3930758460733427E-2</v>
-      </c>
-      <c r="AT34" s="8">
-        <f t="shared" si="233"/>
-        <v>9.0818298340240869E-2</v>
-      </c>
-      <c r="AU34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.94473427080893E-2</v>
-      </c>
-      <c r="AV34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.7261606353872761E-2</v>
-      </c>
-      <c r="AW34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AX34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AY34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AZ34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="BA34" s="8">
-        <f t="shared" si="233"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="BB34" s="8">
-        <f t="shared" ref="BB34:BF34" si="234">BB14/BB10</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="BC34" s="8">
-        <f t="shared" si="234"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="BD34" s="8">
-        <f t="shared" si="234"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="BE34" s="8">
-        <f t="shared" si="234"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="BF34" s="8">
-        <f t="shared" si="234"/>
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="232"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="BH34" t="s">
         <v>46</v>
       </c>
       <c r="BI34" s="1">
         <f>NPV(BI33,AV20:GK20)</f>
-        <v>2274798.798245986</v>
+        <v>2885873.2308964119</v>
       </c>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.3">
@@ -7018,204 +7009,204 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
-        <f t="shared" ref="G35" si="235">G15/C15-1</f>
+        <f t="shared" ref="G35" si="233">G15/C15-1</f>
         <v>-0.22098833981121602</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" ref="H35" si="236">H15/D15-1</f>
+        <f t="shared" ref="H35" si="234">H15/D15-1</f>
         <v>3.7647058823529367E-2</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35" si="237">I15/E15-1</f>
+        <f t="shared" ref="I35" si="235">I15/E15-1</f>
         <v>9.9059561128526541E-2</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" ref="J35" si="238">J15/F15-1</f>
+        <f t="shared" ref="J35" si="236">J15/F15-1</f>
         <v>0.12781531531531543</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" ref="K35" si="239">K15/G15-1</f>
+        <f t="shared" ref="K35" si="237">K15/G15-1</f>
         <v>1.6977904490377762</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" ref="L35" si="240">L15/H15-1</f>
+        <f t="shared" ref="L35" si="238">L15/H15-1</f>
         <v>0.15816326530612246</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" ref="M35" si="241">M15/I15-1</f>
+        <f t="shared" ref="M35" si="239">M15/I15-1</f>
         <v>0.47803764974329721</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" ref="N35" si="242">N15/J15-1</f>
+        <f t="shared" ref="N35" si="240">N15/J15-1</f>
         <v>0.41238142785821275</v>
       </c>
       <c r="O35" s="8">
-        <f t="shared" ref="O35" si="243">O15/K15-1</f>
+        <f t="shared" ref="O35" si="241">O15/K15-1</f>
         <v>-0.23910171730515195</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" ref="P35" si="244">P15/L15-1</f>
+        <f t="shared" ref="P35" si="242">P15/L15-1</f>
         <v>0.26529613313754274</v>
       </c>
       <c r="Q35" s="8">
-        <f t="shared" ref="Q35" si="245">Q15/M15-1</f>
+        <f t="shared" ref="Q35" si="243">Q15/M15-1</f>
         <v>6.3681976071015001E-2</v>
       </c>
       <c r="R35" s="8">
-        <f t="shared" ref="R35" si="246">R15/N15-1</f>
+        <f t="shared" ref="R35" si="244">R15/N15-1</f>
         <v>7.0696359137500941E-4</v>
       </c>
       <c r="S35" s="8">
-        <f t="shared" ref="S35" si="247">S15/O15-1</f>
+        <f t="shared" ref="S35" si="245">S15/O15-1</f>
         <v>-3.7152777777777812E-2</v>
       </c>
       <c r="T35" s="8">
-        <f t="shared" ref="T35" si="248">T15/P15-1</f>
+        <f t="shared" ref="T35" si="246">T15/P15-1</f>
         <v>7.2727272727272751E-2</v>
       </c>
       <c r="U35" s="8">
-        <f t="shared" ref="U35" si="249">U15/Q15-1</f>
+        <f t="shared" ref="U35" si="247">U15/Q15-1</f>
         <v>0.1814223512336719</v>
       </c>
       <c r="V35" s="8">
-        <f t="shared" ref="V35" si="250">V15/R15-1</f>
+        <f t="shared" ref="V35" si="248">V15/R15-1</f>
         <v>0.46238078417520301</v>
       </c>
       <c r="W35" s="8">
-        <f t="shared" ref="W35" si="251">W15/S15-1</f>
+        <f t="shared" ref="W35" si="249">W15/S15-1</f>
         <v>0.21673278038225741</v>
       </c>
       <c r="X35" s="8">
-        <f t="shared" ref="X35" si="252">X15/T15-1</f>
+        <f t="shared" ref="X35" si="250">X15/T15-1</f>
         <v>0.31878831590335377</v>
       </c>
       <c r="Y35" s="8">
-        <f t="shared" ref="Y35" si="253">Y15/U15-1</f>
+        <f t="shared" ref="Y35" si="251">Y15/U15-1</f>
         <v>0.10472972972972983</v>
       </c>
       <c r="Z35" s="8">
-        <f t="shared" ref="Z35" si="254">Z15/V15-1</f>
+        <f t="shared" ref="Z35" si="252">Z15/V15-1</f>
         <v>0.23091787439613531</v>
       </c>
       <c r="AA35" s="8">
-        <f t="shared" ref="AA35" si="255">AA15/W15-1</f>
+        <f t="shared" ref="AA35" si="253">AA15/W15-1</f>
         <v>0.11410788381742742</v>
       </c>
       <c r="AB35" s="8">
-        <f t="shared" ref="AB35" si="256">AB15/X15-1</f>
+        <f t="shared" ref="AB35" si="254">AB15/X15-1</f>
         <v>-4.8126879956248314E-2</v>
       </c>
       <c r="AC35" s="8">
-        <f t="shared" ref="AC35" si="257">AC15/Y15-1</f>
+        <f t="shared" ref="AC35" si="255">AC15/Y15-1</f>
         <v>0.10619961078676665</v>
       </c>
       <c r="AD35" s="8">
-        <f t="shared" ref="AD35" si="258">AD15/Z15-1</f>
+        <f t="shared" ref="AD35" si="256">AD15/Z15-1</f>
         <v>2.1585557299842906E-2</v>
       </c>
       <c r="AE35" s="8">
-        <f t="shared" ref="AE35" si="259">AE15/AA15-1</f>
+        <f t="shared" ref="AE35" si="257">AE15/AA15-1</f>
         <v>-0.19499866985900505</v>
       </c>
       <c r="AF35" s="8">
-        <f t="shared" ref="AF35" si="260">AF15/AB15-1</f>
+        <f t="shared" ref="AF35" si="258">AF15/AB15-1</f>
         <v>-9.2789428325193879E-2</v>
       </c>
       <c r="AG35" s="8">
-        <f t="shared" ref="AG35" si="261">AG15/AC15-1</f>
+        <f t="shared" ref="AG35" si="259">AG15/AC15-1</f>
         <v>-9.5501382256848455E-2</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" ref="AH35" si="262">AH15/AD15-1</f>
+        <f t="shared" ref="AH35" si="260">AH15/AD15-1</f>
         <v>-0.153860929696504</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" ref="AI35" si="263">AI15/AE15-1</f>
+        <f t="shared" ref="AI35" si="261">AI15/AE15-1</f>
         <v>0.16953073364177129</v>
       </c>
       <c r="AJ35" s="8">
-        <f t="shared" ref="AJ35" si="264">AJ15/AF15-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AJ35" si="262">AJ15/AF15-1</f>
+        <v>0.64946168461051301</v>
       </c>
       <c r="AK35" s="8">
-        <f t="shared" ref="AK35" si="265">AK15/AG15-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AK35" si="263">AK15/AG15-1</f>
+        <v>0.5</v>
       </c>
       <c r="AL35" s="8">
-        <f t="shared" ref="AL35" si="266">AL15/AH15-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AL35" si="264">AL15/AH15-1</f>
+        <v>0.44999999999999996</v>
       </c>
       <c r="AN35" s="8"/>
       <c r="AO35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>7.4214202561118103E-3</v>
       </c>
       <c r="AP35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.3440704896721074</v>
       </c>
       <c r="AQ35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.18774852229983874</v>
       </c>
       <c r="AR35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.17100977198697076</v>
       </c>
       <c r="AS35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>0.21495904806057786</v>
       </c>
       <c r="AT35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>4.4581531416942211E-2</v>
       </c>
       <c r="AU35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>-0.13619482496194824</v>
       </c>
       <c r="AV35" s="8">
-        <f t="shared" si="222"/>
-        <v>9.7751621088243645E-2</v>
+        <f t="shared" si="220"/>
+        <v>0.44726177051029037</v>
       </c>
       <c r="AW35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AX35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB35" s="8">
-        <f t="shared" si="222"/>
+        <f t="shared" si="220"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC35" s="8">
-        <f t="shared" ref="BC35" si="267">BC15/BB15-1</f>
+        <f t="shared" ref="BC35" si="265">BC15/BB15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD35" s="8">
-        <f t="shared" ref="BD35" si="268">BD15/BC15-1</f>
+        <f t="shared" ref="BD35" si="266">BD15/BC15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE35" s="8">
-        <f t="shared" ref="BE35" si="269">BE15/BD15-1</f>
+        <f t="shared" ref="BE35" si="267">BE15/BD15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF35" s="8">
-        <f t="shared" ref="BF35" si="270">BF15/BE15-1</f>
+        <f t="shared" ref="BF35" si="268">BF15/BE15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH35" t="s">
@@ -7223,7 +7214,7 @@
       </c>
       <c r="BI35" s="1">
         <f>Main!D8</f>
-        <v>122756</v>
+        <v>124115</v>
       </c>
     </row>
     <row r="36" spans="2:61" x14ac:dyDescent="0.3">
@@ -7231,19 +7222,19 @@
         <v>37</v>
       </c>
       <c r="C36" s="8">
-        <f t="shared" ref="C36:F36" si="271">C19/C18</f>
+        <f t="shared" ref="C36:F36" si="269">C19/C18</f>
         <v>0.20428215280832968</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="271"/>
+        <f t="shared" si="269"/>
         <v>0.11992127091241389</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="271"/>
+        <f t="shared" si="269"/>
         <v>0.15628524877804237</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="271"/>
+        <f t="shared" si="269"/>
         <v>1.3924561624826541</v>
       </c>
       <c r="G36" s="8">
@@ -7251,203 +7242,203 @@
         <v>0.10831831546998008</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" ref="H36:R36" si="272">H19/H18</f>
+        <f t="shared" ref="H36:R36" si="270">H19/H18</f>
         <v>0.1098427740684902</v>
       </c>
       <c r="I36" s="8">
+        <f t="shared" si="270"/>
+        <v>8.8366557572151144E-2</v>
+      </c>
+      <c r="J36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.11159650516282764</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.18278909894426712</v>
+      </c>
+      <c r="L36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.18111467852144564</v>
+      </c>
+      <c r="M36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.1808066759388039</v>
+      </c>
+      <c r="N36" s="8">
+        <f t="shared" si="270"/>
+        <v>3.0829596412556052E-3</v>
+      </c>
+      <c r="O36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.11873146835116669</v>
+      </c>
+      <c r="P36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.15923643832306392</v>
+      </c>
+      <c r="Q36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.15496368038740921</v>
+      </c>
+      <c r="R36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.18524265610787094</v>
+      </c>
+      <c r="S36" s="8">
+        <f t="shared" ref="S36:V36" si="271">S19/S18</f>
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="T36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="U36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.17898022892819979</v>
+      </c>
+      <c r="V36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.15408573067781328</v>
+      </c>
+      <c r="W36" s="8">
+        <f t="shared" ref="W36:AE36" si="272">W19/W18</f>
+        <v>0.13193197422625963</v>
+      </c>
+      <c r="X36" s="8">
         <f t="shared" si="272"/>
-        <v>8.8366557572151144E-2</v>
-      </c>
-      <c r="J36" s="8">
+        <v>0.15840959293152415</v>
+      </c>
+      <c r="Y36" s="8">
         <f t="shared" si="272"/>
-        <v>0.11159650516282764</v>
-      </c>
-      <c r="K36" s="8">
+        <v>0.14310355448777182</v>
+      </c>
+      <c r="Z36" s="8">
         <f t="shared" si="272"/>
-        <v>0.18278909894426712</v>
-      </c>
-      <c r="L36" s="8">
+        <v>0.20545868081880211</v>
+      </c>
+      <c r="AA36" s="8">
         <f t="shared" si="272"/>
-        <v>0.18111467852144564</v>
-      </c>
-      <c r="M36" s="8">
+        <v>0.17324910738808019</v>
+      </c>
+      <c r="AB36" s="8">
         <f t="shared" si="272"/>
-        <v>0.1808066759388039</v>
-      </c>
-      <c r="N36" s="8">
+        <v>0.16139341642697347</v>
+      </c>
+      <c r="AC36" s="8">
         <f t="shared" si="272"/>
-        <v>3.0829596412556052E-3</v>
-      </c>
-      <c r="O36" s="8">
+        <v>7.1142142756050381E-2</v>
+      </c>
+      <c r="AD36" s="8">
         <f t="shared" si="272"/>
-        <v>0.11873146835116669</v>
-      </c>
-      <c r="P36" s="8">
+        <v>0.15258889070948714</v>
+      </c>
+      <c r="AE36" s="8">
         <f t="shared" si="272"/>
-        <v>0.15923643832306392</v>
-      </c>
-      <c r="Q36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.15496368038740921</v>
-      </c>
-      <c r="R36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.18524265610787094</v>
-      </c>
-      <c r="S36" s="8">
-        <f t="shared" ref="S36:V36" si="273">S19/S18</f>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="T36" s="8">
+        <v>0.16432986049796927</v>
+      </c>
+      <c r="AF36" s="8">
+        <f t="shared" ref="AF36:AH36" si="273">AF19/AF18</f>
+        <v>0.14271714275343908</v>
+      </c>
+      <c r="AG36" s="8">
         <f t="shared" si="273"/>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="U36" s="8">
+        <v>0.17047246577934777</v>
+      </c>
+      <c r="AH36" s="8">
         <f t="shared" si="273"/>
-        <v>0.17898022892819979</v>
-      </c>
-      <c r="V36" s="8">
-        <f t="shared" si="273"/>
-        <v>0.15408573067781328</v>
-      </c>
-      <c r="W36" s="8">
-        <f t="shared" ref="W36:AE36" si="274">W19/W18</f>
-        <v>0.13193197422625963</v>
-      </c>
-      <c r="X36" s="8">
+        <v>0.17699965884067859</v>
+      </c>
+      <c r="AI36" s="8">
+        <f t="shared" ref="AI36:AL36" si="274">AI19/AI18</f>
+        <v>0.173466701763622</v>
+      </c>
+      <c r="AJ36" s="8">
         <f t="shared" si="274"/>
-        <v>0.15840959293152415</v>
-      </c>
-      <c r="Y36" s="8">
+        <v>0.16906845843279403</v>
+      </c>
+      <c r="AK36" s="8">
         <f t="shared" si="274"/>
-        <v>0.14310355448777182</v>
-      </c>
-      <c r="Z36" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="AL36" s="8">
         <f t="shared" si="274"/>
-        <v>0.20545868081880211</v>
-      </c>
-      <c r="AA36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.17324910738808019</v>
-      </c>
-      <c r="AB36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16139341642697347</v>
-      </c>
-      <c r="AC36" s="8">
-        <f t="shared" si="274"/>
-        <v>7.1142142756050381E-2</v>
-      </c>
-      <c r="AD36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.15258889070948714</v>
-      </c>
-      <c r="AE36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16432986049796927</v>
-      </c>
-      <c r="AF36" s="8">
-        <f t="shared" ref="AF36:AH36" si="275">AF19/AF18</f>
-        <v>0.14271714275343908</v>
-      </c>
-      <c r="AG36" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="AN36" s="8">
+        <f t="shared" ref="AN36:BA36" si="275">AN19/AN18</f>
+        <v>0.14515047925464172</v>
+      </c>
+      <c r="AO36" s="8">
         <f t="shared" si="275"/>
-        <v>0.17047246577934777</v>
-      </c>
-      <c r="AH36" s="8">
+        <v>0.10446678671468587</v>
+      </c>
+      <c r="AP36" s="8">
         <f t="shared" si="275"/>
-        <v>0.17699965884067859</v>
-      </c>
-      <c r="AI36" s="8">
-        <f t="shared" ref="AI36:AL36" si="276">AI19/AI18</f>
-        <v>0.173466701763622</v>
-      </c>
-      <c r="AJ36" s="8">
+        <v>0.12706889915319478</v>
+      </c>
+      <c r="AQ36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16158587028457974</v>
+      </c>
+      <c r="AR36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16209792073929269</v>
+      </c>
+      <c r="AS36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.1592081650964558</v>
+      </c>
+      <c r="AT36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.13908559562280529</v>
+      </c>
+      <c r="AU36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16439510912657013</v>
+      </c>
+      <c r="AV36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16104640794517217</v>
+      </c>
+      <c r="AW36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16</v>
+      </c>
+      <c r="AX36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16</v>
+      </c>
+      <c r="AY36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16</v>
+      </c>
+      <c r="AZ36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16</v>
+      </c>
+      <c r="BA36" s="8">
+        <f t="shared" si="275"/>
+        <v>0.16</v>
+      </c>
+      <c r="BB36" s="8">
+        <f t="shared" ref="BB36:BF36" si="276">BB19/BB18</f>
+        <v>0.16</v>
+      </c>
+      <c r="BC36" s="8">
         <f t="shared" si="276"/>
-        <v>0.15</v>
-      </c>
-      <c r="AK36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BD36" s="8">
         <f t="shared" si="276"/>
-        <v>0.15</v>
-      </c>
-      <c r="AL36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BE36" s="8">
         <f t="shared" si="276"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN36" s="8">
-        <f t="shared" ref="AN36:BA36" si="277">AN19/AN18</f>
-        <v>0.14515047925464172</v>
-      </c>
-      <c r="AO36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.10446678671468587</v>
-      </c>
-      <c r="AP36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.12706889915319478</v>
-      </c>
-      <c r="AQ36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16158587028457974</v>
-      </c>
-      <c r="AR36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16209792073929269</v>
-      </c>
-      <c r="AS36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.1592081650964558</v>
-      </c>
-      <c r="AT36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.13908559562280529</v>
-      </c>
-      <c r="AU36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16439510912657013</v>
-      </c>
-      <c r="AV36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.15679554590934441</v>
-      </c>
-      <c r="AW36" s="8">
-        <f t="shared" si="277"/>
         <v>0.16</v>
       </c>
-      <c r="AX36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16</v>
-      </c>
-      <c r="AY36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16</v>
-      </c>
-      <c r="AZ36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16</v>
-      </c>
-      <c r="BA36" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB36" s="8">
-        <f t="shared" ref="BB36:BF36" si="278">BB19/BB18</f>
-        <v>0.16</v>
-      </c>
-      <c r="BC36" s="8">
-        <f t="shared" si="278"/>
-        <v>0.16</v>
-      </c>
-      <c r="BD36" s="8">
-        <f t="shared" si="278"/>
-        <v>0.16</v>
-      </c>
-      <c r="BE36" s="8">
-        <f t="shared" si="278"/>
-        <v>0.16</v>
-      </c>
       <c r="BF36" s="8">
-        <f t="shared" si="278"/>
+        <f t="shared" si="276"/>
         <v>0.16</v>
       </c>
       <c r="BH36" t="s">
@@ -7455,7 +7446,7 @@
       </c>
       <c r="BI36" s="1">
         <f>BI34+BI35</f>
-        <v>2397554.798245986</v>
+        <v>3009988.2308964119</v>
       </c>
     </row>
     <row r="37" spans="2:61" x14ac:dyDescent="0.3">
@@ -7467,227 +7458,227 @@
         <v>0.21923232323232322</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" ref="D37:V37" si="279">D20/D10</f>
+        <f t="shared" ref="D37:V37" si="277">D20/D10</f>
         <v>0.24067666282199154</v>
       </c>
       <c r="E37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.24240241970329829</v>
+      </c>
+      <c r="F37" s="8">
+        <f t="shared" si="277"/>
+        <v>-9.6518987341772153E-2</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.30183651191164196</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.25311571791652632</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.2724362774155305</v>
+      </c>
+      <c r="J37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.22782360729198492</v>
+      </c>
+      <c r="K37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.18319161231734502</v>
+      </c>
+      <c r="L37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.25541803615447822</v>
+      </c>
+      <c r="M37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.17452282772414135</v>
+      </c>
+      <c r="N37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.23160065111231687</v>
+      </c>
+      <c r="O37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.16608761145800433</v>
+      </c>
+      <c r="P37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.1817113612032274</v>
+      </c>
+      <c r="Q37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.24943148593333767</v>
+      </c>
+      <c r="R37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.26761924847973567</v>
+      </c>
+      <c r="S37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="T37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="U37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.29079517184188702</v>
+      </c>
+      <c r="V37" s="8">
+        <f t="shared" si="277"/>
+        <v>0.2740391636242947</v>
+      </c>
+      <c r="W37" s="8">
+        <f t="shared" ref="W37:AE37" si="278">W20/W10</f>
+        <v>0.24166678919586537</v>
+      </c>
+      <c r="X37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.22963335007533903</v>
+      </c>
+      <c r="Y37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.20132576854049672</v>
+      </c>
+      <c r="Z37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.17915001051967178</v>
+      </c>
+      <c r="AA37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.21567054035851949</v>
+      </c>
+      <c r="AB37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.2462066377137955</v>
+      </c>
+      <c r="AC37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.25672486406842865</v>
+      </c>
+      <c r="AD37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.23968253968253969</v>
+      </c>
+      <c r="AE37" s="8">
+        <f t="shared" si="278"/>
+        <v>0.29379555246526529</v>
+      </c>
+      <c r="AF37" s="8">
+        <f t="shared" ref="AF37:AH37" si="279">AF20/AF10</f>
+        <v>0.27871657501593072</v>
+      </c>
+      <c r="AG37" s="8">
         <f t="shared" si="279"/>
-        <v>0.24240241970329829</v>
-      </c>
-      <c r="F37" s="8">
+        <v>0.29796755336022113</v>
+      </c>
+      <c r="AH37" s="8">
         <f t="shared" si="279"/>
-        <v>-9.6518987341772153E-2</v>
-      </c>
-      <c r="G37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.30183651191164196</v>
-      </c>
-      <c r="H37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.25311571791652632</v>
-      </c>
-      <c r="I37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.2724362774155305</v>
-      </c>
-      <c r="J37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.22782360729198492</v>
-      </c>
-      <c r="K37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.18319161231734502</v>
-      </c>
-      <c r="L37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.25541803615447822</v>
-      </c>
-      <c r="M37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.17452282772414135</v>
-      </c>
-      <c r="N37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.23160065111231687</v>
-      </c>
-      <c r="O37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.16608761145800433</v>
-      </c>
-      <c r="P37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.1817113612032274</v>
-      </c>
-      <c r="Q37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.24943148593333767</v>
-      </c>
-      <c r="R37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.26761924847973567</v>
-      </c>
-      <c r="S37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="T37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="U37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.29079517184188702</v>
-      </c>
-      <c r="V37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.2740391636242947</v>
-      </c>
-      <c r="W37" s="8">
-        <f t="shared" ref="W37:AE37" si="280">W20/W10</f>
-        <v>0.24166678919586537</v>
-      </c>
-      <c r="X37" s="8">
+        <v>0.27507282132083882</v>
+      </c>
+      <c r="AI37" s="8">
+        <f t="shared" ref="AI37:AL37" si="280">AI20/AI10</f>
+        <v>0.38278254316554733</v>
+      </c>
+      <c r="AJ37" s="8">
         <f t="shared" si="280"/>
-        <v>0.22963335007533903</v>
-      </c>
-      <c r="Y37" s="8">
+        <v>0.29240469573153027</v>
+      </c>
+      <c r="AK37" s="8">
         <f t="shared" si="280"/>
-        <v>0.20132576854049672</v>
-      </c>
-      <c r="Z37" s="8">
+        <v>0.30607428332292913</v>
+      </c>
+      <c r="AL37" s="8">
         <f t="shared" si="280"/>
-        <v>0.17915001051967178</v>
-      </c>
-      <c r="AA37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.21567054035851949</v>
-      </c>
-      <c r="AB37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.2462066377137955</v>
-      </c>
-      <c r="AC37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.25672486406842865</v>
-      </c>
-      <c r="AD37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.23968253968253969</v>
-      </c>
-      <c r="AE37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.29379555246526529</v>
-      </c>
-      <c r="AF37" s="8">
-        <f t="shared" ref="AF37:AH37" si="281">AF20/AF10</f>
-        <v>0.27871657501593072</v>
-      </c>
-      <c r="AG37" s="8">
+        <v>0.28812919349404981</v>
+      </c>
+      <c r="AN37" s="8">
+        <f t="shared" ref="AN37:BA37" si="281">AN20/AN10</f>
+        <v>0.23028240222454949</v>
+      </c>
+      <c r="AO37" s="8">
         <f t="shared" si="281"/>
-        <v>0.29796755336022113</v>
-      </c>
-      <c r="AH37" s="8">
+        <v>0.26171072731126527</v>
+      </c>
+      <c r="AP37" s="8">
         <f t="shared" si="281"/>
-        <v>0.27507282132083882</v>
-      </c>
-      <c r="AI37" s="8">
-        <f t="shared" ref="AI37:AL37" si="282">AI20/AI10</f>
-        <v>0.38278254316554733</v>
-      </c>
-      <c r="AJ37" s="8">
+        <v>0.22418554650092365</v>
+      </c>
+      <c r="AQ37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.22209864841913798</v>
+      </c>
+      <c r="AR37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.30046480875927528</v>
+      </c>
+      <c r="AS37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.21203807153261961</v>
+      </c>
+      <c r="AT37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.24006649446638517</v>
+      </c>
+      <c r="AU37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.28603671811164</v>
+      </c>
+      <c r="AV37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.3155089021072745</v>
+      </c>
+      <c r="AW37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.29877217825691943</v>
+      </c>
+      <c r="AX37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.30199454575349749</v>
+      </c>
+      <c r="AY37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.30467727341820067</v>
+      </c>
+      <c r="AZ37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.30588496170396001</v>
+      </c>
+      <c r="BA37" s="8">
+        <f t="shared" si="281"/>
+        <v>0.30698765200874695</v>
+      </c>
+      <c r="BB37" s="8">
+        <f t="shared" ref="BB37:BF37" si="282">BB20/BB10</f>
+        <v>0.30773043846369302</v>
+      </c>
+      <c r="BC37" s="8">
         <f t="shared" si="282"/>
-        <v>0.2844268360738712</v>
-      </c>
-      <c r="AK37" s="8">
+        <v>0.30797083061398067</v>
+      </c>
+      <c r="BD37" s="8">
         <f t="shared" si="282"/>
-        <v>0.31350839532901859</v>
-      </c>
-      <c r="AL37" s="8">
+        <v>0.30724918467952417</v>
+      </c>
+      <c r="BE37" s="8">
         <f t="shared" si="282"/>
-        <v>0.29701223807769173</v>
-      </c>
-      <c r="AN37" s="8">
-        <f t="shared" ref="AN37:BA37" si="283">AN20/AN10</f>
-        <v>0.23028240222454949</v>
-      </c>
-      <c r="AO37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.26171072731126527</v>
-      </c>
-      <c r="AP37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.22418554650092365</v>
-      </c>
-      <c r="AQ37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.22209864841913798</v>
-      </c>
-      <c r="AR37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.30046480875927528</v>
-      </c>
-      <c r="AS37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.21203807153261961</v>
-      </c>
-      <c r="AT37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.24006649446638517</v>
-      </c>
-      <c r="AU37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.28603671811164</v>
-      </c>
-      <c r="AV37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.31833759418754803</v>
-      </c>
-      <c r="AW37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.30072219332891548</v>
-      </c>
-      <c r="AX37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.30216053674696941</v>
-      </c>
-      <c r="AY37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.30385776114234153</v>
-      </c>
-      <c r="AZ37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.3042880240792879</v>
-      </c>
-      <c r="BA37" s="8">
-        <f t="shared" si="283"/>
-        <v>0.30539138229015522</v>
-      </c>
-      <c r="BB37" s="8">
-        <f t="shared" ref="BB37:BF37" si="284">BB20/BB10</f>
-        <v>0.30544451334632777</v>
-      </c>
-      <c r="BC37" s="8">
-        <f t="shared" si="284"/>
-        <v>0.30498986768471453</v>
-      </c>
-      <c r="BD37" s="8">
-        <f t="shared" si="284"/>
-        <v>0.30427019961142299</v>
-      </c>
-      <c r="BE37" s="8">
-        <f t="shared" si="284"/>
-        <v>0.30355564498530874</v>
+        <v>0.306532690625272</v>
       </c>
       <c r="BF37" s="8">
-        <f t="shared" si="284"/>
-        <v>0.30284638014703652</v>
+        <f t="shared" si="282"/>
+        <v>0.30582152620024472</v>
       </c>
       <c r="BH37" t="s">
         <v>49</v>
       </c>
       <c r="BI37" s="2">
         <f>BI36/BA21</f>
-        <v>196.68209993814486</v>
+        <v>248.30788903616664</v>
       </c>
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.3">
@@ -7696,7 +7687,7 @@
       </c>
       <c r="BI38" s="2">
         <f>Main!D3</f>
-        <v>172.63</v>
+        <v>249.85</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -7705,7 +7696,7 @@
       </c>
       <c r="BI39" s="10">
         <f>BI37/BI38-1</f>
-        <v>0.13932746300263488</v>
+        <v>-6.1721471436195774E-3</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">
@@ -7713,7 +7704,7 @@
         <v>52</v>
       </c>
       <c r="BI40" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/GOOG.xlsx
+++ b/Financial Analysis/GOOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EACB8E-A139-4162-8112-07BE11EDB7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA209DE-0E65-475A-95AC-9D48A73C9F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C0874DB-3046-4806-9648-99CA4AF089C9}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
   <si>
     <t>GOOG</t>
   </si>
@@ -380,10 +380,13 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q225 8K</t>
-  </si>
-  <si>
-    <t>Fairly valued</t>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>Q325 8K</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -499,14 +502,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -523,7 +526,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21785580" y="0"/>
+          <a:off x="23027640" y="0"/>
           <a:ext cx="0" cy="8862060"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -922,17 +925,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>249.85</v>
+        <v>296.3</v>
       </c>
       <c r="E3" s="4">
-        <v>45918</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45960</v>
       </c>
       <c r="G3" s="4">
-        <v>45958</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -940,11 +943,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -953,7 +955,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>3028681.6999999997</v>
+        <v>3581081.8000000003</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -961,11 +963,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <f>21036+74112+52574</f>
-        <v>147722</v>
+        <f>23466+72191+37982</f>
+        <v>133639</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -973,11 +975,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <f>23607</f>
-        <v>23607</v>
+        <f>10883</f>
+        <v>10883</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -986,7 +988,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>124115</v>
+        <v>122756</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -995,7 +997,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>2904566.6999999997</v>
+        <v>3458325.8000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1248,12 +1250,11 @@
         <v>54190</v>
       </c>
       <c r="AK3" s="11">
-        <f>AG3*1.1</f>
-        <v>54323.500000000007</v>
+        <v>56567</v>
       </c>
       <c r="AL3" s="11">
-        <f>AH3*1.08</f>
-        <v>58356.72</v>
+        <f>AH3*1.12</f>
+        <v>60518.080000000009</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -1276,47 +1277,47 @@
       </c>
       <c r="AV3" s="1">
         <f>SUM(AI3:AL3)</f>
-        <v>217572.22</v>
+        <v>221977.08000000002</v>
       </c>
       <c r="AW3" s="1">
-        <f>AV3*1.07</f>
-        <v>232802.27540000001</v>
+        <f>AV3*1.09</f>
+        <v>241955.01720000003</v>
       </c>
       <c r="AX3" s="1">
-        <f>AW3*1.05</f>
-        <v>244442.38917000004</v>
+        <f>AW3*1.06</f>
+        <v>256472.31823200005</v>
       </c>
       <c r="AY3" s="1">
         <f>AX3*1.04</f>
-        <v>254220.08473680005</v>
+        <v>266731.21096128004</v>
       </c>
       <c r="AZ3" s="1">
         <f>AY3*1.03</f>
-        <v>261846.68727890405</v>
+        <v>274733.14729011845</v>
       </c>
       <c r="BA3" s="1">
         <f t="shared" ref="BA3" si="0">AZ3*1.02</f>
-        <v>267083.62102448213</v>
+        <v>280227.81023592083</v>
       </c>
       <c r="BB3" s="1">
         <f t="shared" ref="BB3" si="1">BA3*1.02</f>
-        <v>272425.29344497179</v>
+        <v>285832.36644063925</v>
       </c>
       <c r="BC3" s="1">
         <f t="shared" ref="BC3" si="2">BB3*1.02</f>
-        <v>277873.79931387125</v>
+        <v>291549.01376945205</v>
       </c>
       <c r="BD3" s="1">
         <f t="shared" ref="BD3:BF3" si="3">BC3*1.01</f>
-        <v>280652.53730700997</v>
+        <v>294464.50390714657</v>
       </c>
       <c r="BE3" s="1">
         <f t="shared" si="3"/>
-        <v>283459.06268008007</v>
+        <v>297409.14894621802</v>
       </c>
       <c r="BF3" s="1">
         <f t="shared" si="3"/>
-        <v>286293.65330688085</v>
+        <v>300383.2404356802</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1379,12 +1380,11 @@
         <v>9796</v>
       </c>
       <c r="AK4" s="11">
-        <f>AG4*1.11</f>
-        <v>9902.3100000000013</v>
+        <v>10261</v>
       </c>
       <c r="AL4" s="11">
-        <f>AH4*1.09</f>
-        <v>11415.570000000002</v>
+        <f>AH4*1.12</f>
+        <v>11729.76</v>
       </c>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
@@ -1407,47 +1407,47 @@
       </c>
       <c r="AV4" s="1">
         <f t="shared" ref="AV4:AV9" si="6">SUM(AI4:AL4)</f>
-        <v>40040.880000000005</v>
+        <v>40713.760000000002</v>
       </c>
       <c r="AW4" s="1">
-        <f>AV4*1.07</f>
-        <v>42843.741600000008</v>
+        <f>AV4*1.08</f>
+        <v>43970.860800000002</v>
       </c>
       <c r="AX4" s="1">
-        <f>AW4*1.05</f>
-        <v>44985.928680000012</v>
+        <f>AW4*1.06</f>
+        <v>46609.112448000007</v>
       </c>
       <c r="AY4" s="1">
         <f>AX4*1.04</f>
-        <v>46785.36582720001</v>
+        <v>48473.476945920011</v>
       </c>
       <c r="AZ4" s="1">
         <f>AY4*1.03</f>
-        <v>48188.926802016009</v>
+        <v>49927.681254297611</v>
       </c>
       <c r="BA4" s="1">
         <f>AZ4*1.03</f>
-        <v>49634.594606076491</v>
+        <v>51425.511691926542</v>
       </c>
       <c r="BB4" s="1">
         <f>BA4*1.02</f>
-        <v>50627.286498198024</v>
+        <v>52454.021925765075</v>
       </c>
       <c r="BC4" s="1">
         <f t="shared" ref="BC4:BF4" si="7">BB4*1.02</f>
-        <v>51639.832228161984</v>
+        <v>53503.102364280378</v>
       </c>
       <c r="BD4" s="1">
         <f t="shared" si="7"/>
-        <v>52672.628872725225</v>
+        <v>54573.164411565987</v>
       </c>
       <c r="BE4" s="1">
         <f t="shared" si="7"/>
-        <v>53726.081450179729</v>
+        <v>55664.627699797311</v>
       </c>
       <c r="BF4" s="1">
         <f t="shared" si="7"/>
-        <v>54800.603079183325</v>
+        <v>56777.920253793258</v>
       </c>
     </row>
     <row r="5" spans="2:58" x14ac:dyDescent="0.3">
@@ -1510,11 +1510,10 @@
         <v>7354</v>
       </c>
       <c r="AK5" s="11">
-        <f t="shared" ref="AK5:AL5" si="8">AG5*0.98</f>
-        <v>7397.04</v>
+        <v>7354</v>
       </c>
       <c r="AL5" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="AL5" si="8">AH5*0.98</f>
         <v>7794.92</v>
       </c>
       <c r="AN5" s="1"/>
@@ -1538,47 +1537,47 @@
       </c>
       <c r="AV5" s="1">
         <f t="shared" si="6"/>
-        <v>29801.96</v>
+        <v>29758.92</v>
       </c>
       <c r="AW5" s="1">
         <f>AV5*1.01</f>
-        <v>30099.979599999999</v>
+        <v>30056.509199999997</v>
       </c>
       <c r="AX5" s="1">
         <f t="shared" ref="AX5:BF5" si="9">AW5*1.01</f>
-        <v>30400.979395999999</v>
+        <v>30357.074291999998</v>
       </c>
       <c r="AY5" s="1">
         <f t="shared" si="9"/>
-        <v>30704.989189960001</v>
+        <v>30660.645034919999</v>
       </c>
       <c r="AZ5" s="1">
         <f t="shared" si="9"/>
-        <v>31012.039081859602</v>
+        <v>30967.2514852692</v>
       </c>
       <c r="BA5" s="1">
         <f t="shared" si="9"/>
-        <v>31322.159472678199</v>
+        <v>31276.924000121893</v>
       </c>
       <c r="BB5" s="1">
         <f t="shared" si="9"/>
-        <v>31635.381067404982</v>
+        <v>31589.693240123113</v>
       </c>
       <c r="BC5" s="1">
         <f t="shared" si="9"/>
-        <v>31951.734878079031</v>
+        <v>31905.590172524346</v>
       </c>
       <c r="BD5" s="1">
         <f t="shared" si="9"/>
-        <v>32271.252226859822</v>
+        <v>32224.646074249591</v>
       </c>
       <c r="BE5" s="1">
         <f t="shared" si="9"/>
-        <v>32593.964749128419</v>
+        <v>32546.892534992086</v>
       </c>
       <c r="BF5" s="1">
         <f t="shared" si="9"/>
-        <v>32919.904396619706</v>
+        <v>32872.361460342006</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1641,12 +1640,11 @@
         <v>11203</v>
       </c>
       <c r="AK6" s="11">
-        <f>AG6*1.15</f>
-        <v>12254.4</v>
+        <v>12870</v>
       </c>
       <c r="AL6" s="11">
-        <f>AH6*1.13</f>
-        <v>13145.289999999999</v>
+        <f>AH6*1.19</f>
+        <v>13843.269999999999</v>
       </c>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
@@ -1669,47 +1667,47 @@
       </c>
       <c r="AV6" s="1">
         <f t="shared" si="6"/>
-        <v>46981.69</v>
+        <v>48295.27</v>
       </c>
       <c r="AW6" s="1">
-        <f>AV6*1.09</f>
-        <v>51210.042100000006</v>
+        <f>AV6*1.12</f>
+        <v>54090.702400000002</v>
       </c>
       <c r="AX6" s="1">
-        <f>AW6*1.05</f>
-        <v>53770.544205000006</v>
+        <f>AW6*1.08</f>
+        <v>58417.958592000003</v>
       </c>
       <c r="AY6" s="1">
-        <f>AX6*1.04</f>
-        <v>55921.365973200009</v>
+        <f>AX6*1.06</f>
+        <v>61923.036107520005</v>
       </c>
       <c r="AZ6" s="1">
-        <f>AY6*1.03</f>
-        <v>57599.006952396012</v>
+        <f>AY6*1.05</f>
+        <v>65019.187912896006</v>
       </c>
       <c r="BA6" s="1">
-        <f t="shared" ref="BA6:BF6" si="10">AZ6*1.03</f>
-        <v>59326.977160967894</v>
+        <f>AZ6*1.04</f>
+        <v>67619.955429411842</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="10"/>
-        <v>61106.786475796929</v>
+        <f t="shared" ref="BB6:BF6" si="10">BA6*1.03</f>
+        <v>69648.554092294202</v>
       </c>
       <c r="BC6" s="1">
         <f t="shared" si="10"/>
-        <v>62939.990070070839</v>
+        <v>71738.010715063036</v>
       </c>
       <c r="BD6" s="1">
         <f t="shared" si="10"/>
-        <v>64828.189772172962</v>
+        <v>73890.15103651493</v>
       </c>
       <c r="BE6" s="1">
         <f t="shared" si="10"/>
-        <v>66773.035465338151</v>
+        <v>76106.855567610386</v>
       </c>
       <c r="BF6" s="1">
         <f t="shared" si="10"/>
-        <v>68776.226529298292</v>
+        <v>78390.061234638706</v>
       </c>
     </row>
     <row r="7" spans="2:58" x14ac:dyDescent="0.3">
@@ -1772,12 +1770,11 @@
         <v>13624</v>
       </c>
       <c r="AK7" s="11">
-        <f>AG7*1.28</f>
-        <v>14531.84</v>
+        <v>15157</v>
       </c>
       <c r="AL7" s="11">
-        <f>AH7*1.26</f>
-        <v>15063.3</v>
+        <f>AH7*1.32</f>
+        <v>15780.6</v>
       </c>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
@@ -1800,47 +1797,47 @@
       </c>
       <c r="AV7" s="1">
         <f t="shared" si="6"/>
-        <v>55479.14</v>
+        <v>56821.599999999999</v>
       </c>
       <c r="AW7" s="1">
         <f>AV7*1.2</f>
-        <v>66574.967999999993</v>
+        <v>68185.919999999998</v>
       </c>
       <c r="AX7" s="1">
         <f>AW7*1.15</f>
-        <v>76561.213199999984</v>
+        <v>78413.80799999999</v>
       </c>
       <c r="AY7" s="1">
         <f>AX7*1.1</f>
-        <v>84217.334519999989</v>
+        <v>86255.188799999989</v>
       </c>
       <c r="AZ7" s="1">
         <f>AY7*1.08</f>
-        <v>90954.721281599996</v>
+        <v>93155.603903999989</v>
       </c>
       <c r="BA7" s="1">
         <f>AZ7*1.06</f>
-        <v>96412.004558496003</v>
+        <v>98744.940138239996</v>
       </c>
       <c r="BB7" s="1">
         <f>BA7*1.05</f>
-        <v>101232.60478642081</v>
+        <v>103682.187145152</v>
       </c>
       <c r="BC7" s="1">
         <f>BB7*1.03</f>
-        <v>104269.58293001344</v>
+        <v>106792.65275950656</v>
       </c>
       <c r="BD7" s="1">
         <f>BC7*1.02</f>
-        <v>106354.97458861371</v>
+        <v>108928.50581469669</v>
       </c>
       <c r="BE7" s="1">
         <f t="shared" ref="BE7:BF7" si="11">BD7*1.02</f>
-        <v>108482.07408038598</v>
+        <v>111107.07593099063</v>
       </c>
       <c r="BF7" s="1">
         <f t="shared" si="11"/>
-        <v>110651.7155619937</v>
+        <v>113329.21744961044</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -1903,12 +1900,11 @@
         <v>373</v>
       </c>
       <c r="AK8" s="11">
-        <f t="shared" ref="AK8:AL8" si="12">AG8*1.1</f>
-        <v>426.8</v>
+        <v>344</v>
       </c>
       <c r="AL8" s="11">
-        <f t="shared" si="12"/>
-        <v>440.00000000000006</v>
+        <f>AH8*1.05</f>
+        <v>420</v>
       </c>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
@@ -1931,47 +1927,47 @@
       </c>
       <c r="AV8" s="1">
         <f t="shared" si="6"/>
-        <v>1689.8</v>
+        <v>1587</v>
       </c>
       <c r="AW8" s="1">
         <f>AV8*1.25</f>
-        <v>2112.25</v>
+        <v>1983.75</v>
       </c>
       <c r="AX8" s="1">
         <f>AW8*1.2</f>
-        <v>2534.6999999999998</v>
+        <v>2380.5</v>
       </c>
       <c r="AY8" s="1">
         <f>AX8*1.15</f>
-        <v>2914.9049999999997</v>
+        <v>2737.5749999999998</v>
       </c>
       <c r="AZ8" s="1">
         <f>AY8*1.1</f>
-        <v>3206.3955000000001</v>
+        <v>3011.3325</v>
       </c>
       <c r="BA8" s="1">
         <f>AZ8*1.05</f>
-        <v>3366.715275</v>
+        <v>3161.8991249999999</v>
       </c>
       <c r="BB8" s="1">
-        <f t="shared" ref="BB8:BF8" si="13">BA8*1.05</f>
-        <v>3535.0510387500003</v>
+        <f t="shared" ref="BB8:BF8" si="12">BA8*1.05</f>
+        <v>3319.9940812499999</v>
       </c>
       <c r="BC8" s="1">
-        <f t="shared" si="13"/>
-        <v>3711.8035906875007</v>
+        <f t="shared" si="12"/>
+        <v>3485.9937853125002</v>
       </c>
       <c r="BD8" s="1">
-        <f t="shared" si="13"/>
-        <v>3897.3937702218759</v>
+        <f t="shared" si="12"/>
+        <v>3660.2934745781254</v>
       </c>
       <c r="BE8" s="1">
-        <f t="shared" si="13"/>
-        <v>4092.2634587329699</v>
+        <f t="shared" si="12"/>
+        <v>3843.3081483070318</v>
       </c>
       <c r="BF8" s="1">
-        <f t="shared" si="13"/>
-        <v>4296.8766316696183</v>
+        <f t="shared" si="12"/>
+        <v>4035.4735557223835</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2034,7 +2030,7 @@
         <v>-112</v>
       </c>
       <c r="AK9" s="11">
-        <v>50</v>
+        <v>-207</v>
       </c>
       <c r="AL9" s="11">
         <v>50</v>
@@ -2060,47 +2056,47 @@
       </c>
       <c r="AV9" s="1">
         <f t="shared" si="6"/>
-        <v>248</v>
+        <v>-9</v>
       </c>
       <c r="AW9" s="1">
-        <f t="shared" ref="AW9:BF9" si="14">AV9*1.02</f>
-        <v>252.96</v>
+        <f t="shared" ref="AW9:BF9" si="13">AV9*1.02</f>
+        <v>-9.18</v>
       </c>
       <c r="AX9" s="1">
-        <f t="shared" si="14"/>
-        <v>258.01920000000001</v>
+        <f t="shared" si="13"/>
+        <v>-9.3635999999999999</v>
       </c>
       <c r="AY9" s="1">
-        <f t="shared" si="14"/>
-        <v>263.17958400000003</v>
+        <f t="shared" si="13"/>
+        <v>-9.550872</v>
       </c>
       <c r="AZ9" s="1">
-        <f t="shared" si="14"/>
-        <v>268.44317568000002</v>
+        <f t="shared" si="13"/>
+        <v>-9.7418894399999996</v>
       </c>
       <c r="BA9" s="1">
-        <f t="shared" si="14"/>
-        <v>273.81203919360001</v>
+        <f t="shared" si="13"/>
+        <v>-9.9367272288000006</v>
       </c>
       <c r="BB9" s="1">
-        <f t="shared" si="14"/>
-        <v>279.28827997747203</v>
+        <f t="shared" si="13"/>
+        <v>-10.135461773376001</v>
       </c>
       <c r="BC9" s="1">
-        <f t="shared" si="14"/>
-        <v>284.87404557702149</v>
+        <f t="shared" si="13"/>
+        <v>-10.338171008843521</v>
       </c>
       <c r="BD9" s="1">
-        <f t="shared" si="14"/>
-        <v>290.57152648856191</v>
+        <f t="shared" si="13"/>
+        <v>-10.54493442902039</v>
       </c>
       <c r="BE9" s="1">
-        <f t="shared" si="14"/>
-        <v>296.38295701833317</v>
+        <f t="shared" si="13"/>
+        <v>-10.755833117600798</v>
       </c>
       <c r="BF9" s="1">
-        <f t="shared" si="14"/>
-        <v>302.31061615869982</v>
+        <f t="shared" si="13"/>
+        <v>-10.970949779952814</v>
       </c>
     </row>
     <row r="10" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2214,16 +2210,16 @@
         <v>90234</v>
       </c>
       <c r="AJ10" s="9">
-        <f t="shared" ref="AJ10:AL10" si="15">SUM(AJ3:AJ9)</f>
+        <f t="shared" ref="AJ10:AL10" si="14">SUM(AJ3:AJ9)</f>
         <v>96428</v>
       </c>
       <c r="AK10" s="9">
-        <f t="shared" si="15"/>
-        <v>98885.89</v>
+        <f t="shared" si="14"/>
+        <v>102346</v>
       </c>
       <c r="AL10" s="9">
-        <f t="shared" si="15"/>
-        <v>106265.8</v>
+        <f t="shared" si="14"/>
+        <v>110136.63000000002</v>
       </c>
       <c r="AN10" s="9">
         <f>SUM(C10:F10)</f>
@@ -2259,47 +2255,47 @@
       </c>
       <c r="AV10" s="9">
         <f>SUM(AV3:AV9)</f>
-        <v>391813.69</v>
+        <v>399144.63</v>
       </c>
       <c r="AW10" s="9">
-        <f t="shared" ref="AW10:BF10" si="16">SUM(AW3:AW9)</f>
-        <v>425896.21670000005</v>
+        <f t="shared" ref="AW10:BF10" si="15">SUM(AW3:AW9)</f>
+        <v>440233.5796</v>
       </c>
       <c r="AX10" s="9">
-        <f t="shared" si="16"/>
-        <v>452953.77385100001</v>
+        <f t="shared" si="15"/>
+        <v>472641.40796400007</v>
       </c>
       <c r="AY10" s="9">
-        <f t="shared" si="16"/>
-        <v>475027.2248311601</v>
+        <f t="shared" si="15"/>
+        <v>496771.5819776401</v>
       </c>
       <c r="AZ10" s="9">
-        <f t="shared" si="16"/>
-        <v>493076.22007245565</v>
+        <f t="shared" si="15"/>
+        <v>516804.46245714126</v>
       </c>
       <c r="BA10" s="9">
-        <f t="shared" si="16"/>
-        <v>507419.88413689431</v>
+        <f t="shared" si="15"/>
+        <v>532447.10389339225</v>
       </c>
       <c r="BB10" s="9">
-        <f t="shared" si="16"/>
-        <v>520841.69159152004</v>
+        <f t="shared" si="15"/>
+        <v>546516.68146345031</v>
       </c>
       <c r="BC10" s="9">
-        <f t="shared" si="16"/>
-        <v>532671.61705646105</v>
+        <f t="shared" si="15"/>
+        <v>558964.02539513004</v>
       </c>
       <c r="BD10" s="9">
-        <f t="shared" si="16"/>
-        <v>540967.54806409206</v>
+        <f t="shared" si="15"/>
+        <v>567730.71978432289</v>
       </c>
       <c r="BE10" s="9">
-        <f t="shared" si="16"/>
-        <v>549422.86484086374</v>
+        <f t="shared" si="15"/>
+        <v>576667.1529947978</v>
       </c>
       <c r="BF10" s="9">
-        <f t="shared" si="16"/>
-        <v>558041.29012180411</v>
+        <f t="shared" si="15"/>
+        <v>585777.30344000703</v>
       </c>
     </row>
     <row r="11" spans="2:58" x14ac:dyDescent="0.3">
@@ -2409,12 +2405,11 @@
         <v>39039</v>
       </c>
       <c r="AK11" s="1">
-        <f t="shared" ref="AK11:AL11" si="17">AK10-AK12</f>
-        <v>39554.356</v>
+        <v>41369</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" si="17"/>
-        <v>42506.320000000007</v>
+        <f t="shared" ref="AL11" si="16">AL10-AL12</f>
+        <v>44054.652000000016</v>
       </c>
       <c r="AN11" s="1">
         <f>SUM(C11:F11)</f>
@@ -2450,47 +2445,47 @@
       </c>
       <c r="AV11" s="1">
         <f>SUM(AI11:AL11)</f>
-        <v>157460.67600000001</v>
+        <v>160823.652</v>
       </c>
       <c r="AW11" s="1">
-        <f t="shared" ref="AW11:BA11" si="18">AW10-AW12</f>
-        <v>170358.48668000003</v>
+        <f t="shared" ref="AW11:BA11" si="17">AW10-AW12</f>
+        <v>176093.43184000003</v>
       </c>
       <c r="AX11" s="1">
+        <f t="shared" si="17"/>
+        <v>189056.56318560004</v>
+      </c>
+      <c r="AY11" s="1">
+        <f t="shared" si="17"/>
+        <v>198708.63279105606</v>
+      </c>
+      <c r="AZ11" s="1">
+        <f t="shared" si="17"/>
+        <v>206721.78498285654</v>
+      </c>
+      <c r="BA11" s="1">
+        <f t="shared" si="17"/>
+        <v>212978.84155735694</v>
+      </c>
+      <c r="BB11" s="1">
+        <f t="shared" ref="BB11:BF11" si="18">BB10-BB12</f>
+        <v>218606.67258538015</v>
+      </c>
+      <c r="BC11" s="1">
         <f t="shared" si="18"/>
-        <v>181181.5095404</v>
-      </c>
-      <c r="AY11" s="1">
+        <v>223585.610158052</v>
+      </c>
+      <c r="BD11" s="1">
         <f t="shared" si="18"/>
-        <v>190010.88993246405</v>
-      </c>
-      <c r="AZ11" s="1">
+        <v>227092.28791372915</v>
+      </c>
+      <c r="BE11" s="1">
         <f t="shared" si="18"/>
-        <v>197230.48802898225</v>
-      </c>
-      <c r="BA11" s="1">
+        <v>230666.86119791912</v>
+      </c>
+      <c r="BF11" s="1">
         <f t="shared" si="18"/>
-        <v>202967.95365475776</v>
-      </c>
-      <c r="BB11" s="1">
-        <f t="shared" ref="BB11:BF11" si="19">BB10-BB12</f>
-        <v>208336.67663660803</v>
-      </c>
-      <c r="BC11" s="1">
-        <f t="shared" si="19"/>
-        <v>213068.64682258444</v>
-      </c>
-      <c r="BD11" s="1">
-        <f t="shared" si="19"/>
-        <v>216387.01922563685</v>
-      </c>
-      <c r="BE11" s="1">
-        <f t="shared" si="19"/>
-        <v>219769.14593634551</v>
-      </c>
-      <c r="BF11" s="1">
-        <f t="shared" si="19"/>
-        <v>223216.51604872168</v>
+        <v>234310.92137600284</v>
       </c>
     </row>
     <row r="12" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2498,224 +2493,224 @@
         <v>24</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" ref="C12:T12" si="20">C10-C11</f>
+        <f t="shared" ref="C12:T12" si="19">C10-C11</f>
         <v>14955</v>
       </c>
       <c r="D12" s="9">
+        <f t="shared" si="19"/>
+        <v>15637</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="19"/>
+        <v>16624</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="19"/>
+        <v>17965</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" si="19"/>
+        <v>17679</v>
+      </c>
+      <c r="H12" s="9">
+        <f t="shared" si="19"/>
+        <v>18774</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="19"/>
+        <v>19459</v>
+      </c>
+      <c r="J12" s="9">
+        <f t="shared" si="19"/>
+        <v>21358</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="19"/>
+        <v>20327</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="19"/>
+        <v>21648</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="19"/>
+        <v>22931</v>
+      </c>
+      <c r="N12" s="9">
+        <f t="shared" si="19"/>
+        <v>25055</v>
+      </c>
+      <c r="O12" s="9">
+        <f t="shared" si="19"/>
+        <v>22177</v>
+      </c>
+      <c r="P12" s="9">
+        <f t="shared" si="19"/>
+        <v>19744</v>
+      </c>
+      <c r="Q12" s="9">
+        <f t="shared" si="19"/>
+        <v>25056</v>
+      </c>
+      <c r="R12" s="9">
+        <f t="shared" si="19"/>
+        <v>30818</v>
+      </c>
+      <c r="S12" s="9">
+        <f t="shared" si="19"/>
+        <v>31211</v>
+      </c>
+      <c r="T12" s="9">
+        <f t="shared" si="19"/>
+        <v>31211</v>
+      </c>
+      <c r="U12" s="9">
+        <f t="shared" ref="U12:V12" si="20">U10-U11</f>
+        <v>37497</v>
+      </c>
+      <c r="V12" s="9">
         <f t="shared" si="20"/>
-        <v>15637</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="20"/>
-        <v>16624</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="20"/>
-        <v>17965</v>
-      </c>
-      <c r="G12" s="9">
-        <f t="shared" si="20"/>
-        <v>17679</v>
-      </c>
-      <c r="H12" s="9">
-        <f t="shared" si="20"/>
-        <v>18774</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="20"/>
-        <v>19459</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="20"/>
-        <v>21358</v>
-      </c>
-      <c r="K12" s="9">
-        <f t="shared" si="20"/>
-        <v>20327</v>
-      </c>
-      <c r="L12" s="9">
-        <f t="shared" si="20"/>
-        <v>21648</v>
-      </c>
-      <c r="M12" s="9">
-        <f t="shared" si="20"/>
-        <v>22931</v>
-      </c>
-      <c r="N12" s="9">
-        <f t="shared" si="20"/>
-        <v>25055</v>
-      </c>
-      <c r="O12" s="9">
-        <f t="shared" si="20"/>
-        <v>22177</v>
-      </c>
-      <c r="P12" s="9">
-        <f t="shared" si="20"/>
-        <v>19744</v>
-      </c>
-      <c r="Q12" s="9">
-        <f t="shared" si="20"/>
-        <v>25056</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" si="20"/>
-        <v>30818</v>
-      </c>
-      <c r="S12" s="9">
-        <f t="shared" si="20"/>
-        <v>31211</v>
-      </c>
-      <c r="T12" s="9">
-        <f t="shared" si="20"/>
-        <v>31211</v>
-      </c>
-      <c r="U12" s="9">
-        <f t="shared" ref="U12:V12" si="21">U10-U11</f>
-        <v>37497</v>
-      </c>
-      <c r="V12" s="9">
+        <v>42337</v>
+      </c>
+      <c r="W12" s="9">
+        <f t="shared" ref="W12:X12" si="21">W10-W11</f>
+        <v>38412</v>
+      </c>
+      <c r="X12" s="9">
         <f t="shared" si="21"/>
-        <v>42337</v>
-      </c>
-      <c r="W12" s="9">
-        <f t="shared" ref="W12:X12" si="22">W10-W11</f>
-        <v>38412</v>
-      </c>
-      <c r="X12" s="9">
-        <f t="shared" si="22"/>
         <v>39581</v>
       </c>
       <c r="Y12" s="9">
-        <f t="shared" ref="Y12" si="23">Y10-Y11</f>
+        <f t="shared" ref="Y12" si="22">Y10-Y11</f>
         <v>37934</v>
       </c>
       <c r="Z12" s="9">
-        <f t="shared" ref="Z12" si="24">Z10-Z11</f>
+        <f t="shared" ref="Z12" si="23">Z10-Z11</f>
         <v>40706</v>
       </c>
       <c r="AA12" s="9">
-        <f t="shared" ref="AA12:AB12" si="25">AA10-AA11</f>
+        <f t="shared" ref="AA12:AB12" si="24">AA10-AA11</f>
         <v>39175</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>42688</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" ref="AC12" si="26">AC10-AC11</f>
+        <f t="shared" ref="AC12" si="25">AC10-AC11</f>
         <v>43464</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" ref="AD12" si="27">AD10-AD11</f>
+        <f t="shared" ref="AD12" si="26">AD10-AD11</f>
         <v>48735</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" ref="AE12:AJ12" si="28">AE10-AE11</f>
+        <f t="shared" ref="AE12:AK12" si="27">AE10-AE11</f>
         <v>46827</v>
       </c>
       <c r="AF12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>49235</v>
       </c>
       <c r="AG12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>51794</v>
       </c>
       <c r="AH12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>55856</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>53873</v>
       </c>
       <c r="AJ12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>57389</v>
       </c>
       <c r="AK12" s="9">
-        <f t="shared" ref="AK12:AL12" si="29">AK10*0.6</f>
-        <v>59331.534</v>
+        <f t="shared" si="27"/>
+        <v>60977</v>
       </c>
       <c r="AL12" s="9">
+        <f t="shared" ref="AL12" si="28">AL10*0.6</f>
+        <v>66081.978000000003</v>
+      </c>
+      <c r="AN12" s="9">
+        <f t="shared" ref="AN12:AV12" si="29">AN10-AN11</f>
+        <v>65181</v>
+      </c>
+      <c r="AO12" s="9">
         <f t="shared" si="29"/>
-        <v>63759.479999999996</v>
-      </c>
-      <c r="AN12" s="9">
-        <f t="shared" ref="AN12:AV12" si="30">AN10-AN11</f>
-        <v>65181</v>
-      </c>
-      <c r="AO12" s="9">
-        <f t="shared" si="30"/>
         <v>77270</v>
       </c>
       <c r="AP12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>89961</v>
       </c>
       <c r="AQ12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>97795</v>
       </c>
       <c r="AR12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>142256</v>
       </c>
       <c r="AS12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>156633</v>
       </c>
       <c r="AT12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>174062</v>
       </c>
       <c r="AU12" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>203712</v>
       </c>
       <c r="AV12" s="9">
-        <f t="shared" si="30"/>
-        <v>234353.014</v>
+        <f t="shared" si="29"/>
+        <v>238320.978</v>
       </c>
       <c r="AW12" s="9">
         <f>AW10*0.6</f>
-        <v>255537.73002000002</v>
+        <v>264140.14775999996</v>
       </c>
       <c r="AX12" s="9">
-        <f t="shared" ref="AX12:BF12" si="31">AX10*0.6</f>
-        <v>271772.2643106</v>
+        <f t="shared" ref="AX12:BF12" si="30">AX10*0.6</f>
+        <v>283584.84477840003</v>
       </c>
       <c r="AY12" s="9">
-        <f t="shared" si="31"/>
-        <v>285016.33489869605</v>
+        <f t="shared" si="30"/>
+        <v>298062.94918658404</v>
       </c>
       <c r="AZ12" s="9">
-        <f t="shared" si="31"/>
-        <v>295845.7320434734</v>
+        <f t="shared" si="30"/>
+        <v>310082.67747428472</v>
       </c>
       <c r="BA12" s="9">
-        <f t="shared" si="31"/>
-        <v>304451.93048213655</v>
+        <f t="shared" si="30"/>
+        <v>319468.26233603532</v>
       </c>
       <c r="BB12" s="9">
-        <f t="shared" si="31"/>
-        <v>312505.01495491201</v>
+        <f t="shared" si="30"/>
+        <v>327910.00887807016</v>
       </c>
       <c r="BC12" s="9">
-        <f t="shared" si="31"/>
-        <v>319602.97023387661</v>
+        <f t="shared" si="30"/>
+        <v>335378.41523707804</v>
       </c>
       <c r="BD12" s="9">
-        <f t="shared" si="31"/>
-        <v>324580.52883845521</v>
+        <f t="shared" si="30"/>
+        <v>340638.43187059375</v>
       </c>
       <c r="BE12" s="9">
-        <f t="shared" si="31"/>
-        <v>329653.71890451823</v>
+        <f t="shared" si="30"/>
+        <v>346000.29179687868</v>
       </c>
       <c r="BF12" s="9">
-        <f t="shared" si="31"/>
-        <v>334824.77407308243</v>
+        <f t="shared" si="30"/>
+        <v>351466.3820640042</v>
       </c>
     </row>
     <row r="13" spans="2:58" x14ac:dyDescent="0.3">
@@ -2825,12 +2820,11 @@
         <v>13808</v>
       </c>
       <c r="AK13" s="1">
-        <f>AG13*1.14</f>
-        <v>14189.579999999998</v>
+        <v>15151</v>
       </c>
       <c r="AL13" s="1">
-        <f>AH13*1.12</f>
-        <v>14689.920000000002</v>
+        <f>AH13*1.25</f>
+        <v>16395</v>
       </c>
       <c r="AN13" s="1">
         <f>SUM(C13:F13)</f>
@@ -2866,47 +2860,47 @@
       </c>
       <c r="AV13" s="1">
         <f>SUM(AI13:AL13)</f>
-        <v>56243.5</v>
+        <v>58910</v>
       </c>
       <c r="AW13" s="1">
-        <f>AV13*1.07</f>
-        <v>60180.545000000006</v>
+        <f>AV13*1.09</f>
+        <v>64211.9</v>
       </c>
       <c r="AX13" s="1">
         <f>AW13*1.04</f>
-        <v>62587.766800000005</v>
+        <v>66780.376000000004</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" ref="AY13" si="32">AX13*1.03</f>
-        <v>64465.399804000008</v>
+        <f t="shared" ref="AY13" si="31">AX13*1.03</f>
+        <v>68783.787280000004</v>
       </c>
       <c r="AZ13" s="1">
         <f>AY13*1.03</f>
-        <v>66399.361798120008</v>
+        <v>70847.300898400004</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" ref="BA13:BB13" si="33">AZ13*1.02</f>
-        <v>67727.349034082406</v>
+        <f t="shared" ref="BA13:BB13" si="32">AZ13*1.02</f>
+        <v>72264.246916368007</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="33"/>
-        <v>69081.896014764061</v>
+        <f t="shared" si="32"/>
+        <v>73709.531854695364</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" ref="BC13" si="34">BB13*1.02</f>
-        <v>70463.533935059342</v>
+        <f t="shared" ref="BC13" si="33">BB13*1.02</f>
+        <v>75183.722491789274</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" ref="BD13" si="35">BC13*1.02</f>
-        <v>71872.804613760527</v>
+        <f t="shared" ref="BD13" si="34">BC13*1.02</f>
+        <v>76687.396941625062</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" ref="BE13" si="36">BD13*1.02</f>
-        <v>73310.26070603574</v>
+        <f t="shared" ref="BE13" si="35">BD13*1.02</f>
+        <v>78221.144880457563</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" ref="BF13" si="37">BE13*1.02</f>
-        <v>74776.46592015645</v>
+        <f t="shared" ref="BF13" si="36">BE13*1.02</f>
+        <v>79785.567778066717</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3016,12 +3010,11 @@
         <v>7101</v>
       </c>
       <c r="AK14" s="1">
-        <f>AK10*0.075</f>
-        <v>7416.44175</v>
+        <v>7205</v>
       </c>
       <c r="AL14" s="1">
         <f>AL10*0.075</f>
-        <v>7969.9349999999995</v>
+        <v>8260.2472500000003</v>
       </c>
       <c r="AN14" s="1">
         <f>SUM(C14:F14)</f>
@@ -3057,47 +3050,47 @@
       </c>
       <c r="AV14" s="1">
         <f>SUM(AI14:AL14)</f>
-        <v>28659.376749999996</v>
+        <v>28738.24725</v>
       </c>
       <c r="AW14" s="1">
         <f>AW10*0.07</f>
-        <v>29812.735169000007</v>
+        <v>30816.350572000003</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" ref="AX14:BF14" si="38">AX10*0.07</f>
-        <v>31706.764169570004</v>
+        <f t="shared" ref="AX14:BF14" si="37">AX10*0.07</f>
+        <v>33084.89855748001</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="38"/>
-        <v>33251.905738181209</v>
+        <f t="shared" si="37"/>
+        <v>34774.010738434808</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="38"/>
-        <v>34515.335405071899</v>
+        <f t="shared" si="37"/>
+        <v>36176.312371999891</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="38"/>
-        <v>35519.391889582606</v>
+        <f t="shared" si="37"/>
+        <v>37271.297272537464</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="38"/>
-        <v>36458.918411406405</v>
+        <f t="shared" si="37"/>
+        <v>38256.167702441526</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="38"/>
-        <v>37287.013193952276</v>
+        <f t="shared" si="37"/>
+        <v>39127.481777659108</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="38"/>
-        <v>37867.728364486451</v>
+        <f t="shared" si="37"/>
+        <v>39741.150384902605</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="38"/>
-        <v>38459.600538860468</v>
+        <f t="shared" si="37"/>
+        <v>40366.70070963585</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="38"/>
-        <v>39062.890308526294</v>
+        <f t="shared" si="37"/>
+        <v>41004.411240800495</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3208,8 +3201,7 @@
         <v>5209</v>
       </c>
       <c r="AK15" s="1">
-        <f>AG15*1.5</f>
-        <v>5398.5</v>
+        <v>7393</v>
       </c>
       <c r="AL15" s="1">
         <f>AH15*1.45</f>
@@ -3249,47 +3241,47 @@
       </c>
       <c r="AV15" s="1">
         <f>SUM(AI15:AL15)</f>
-        <v>20533.75</v>
+        <v>22528.25</v>
       </c>
       <c r="AW15" s="1">
-        <f>AV15*1.05</f>
-        <v>21560.4375</v>
+        <f>AV15*1.15</f>
+        <v>25907.487499999999</v>
       </c>
       <c r="AX15" s="1">
-        <f>AW15*1.03</f>
-        <v>22207.250625000001</v>
+        <f>AW15*1.07</f>
+        <v>27721.011624999999</v>
       </c>
       <c r="AY15" s="1">
-        <f t="shared" ref="AY15:BB15" si="39">AX15*1.02</f>
-        <v>22651.395637500002</v>
+        <f>AX15*1.03</f>
+        <v>28552.64197375</v>
       </c>
       <c r="AZ15" s="1">
-        <f t="shared" si="39"/>
-        <v>23104.423550250001</v>
+        <f t="shared" ref="AZ15:BB15" si="38">AY15*1.02</f>
+        <v>29123.694813225</v>
       </c>
       <c r="BA15" s="1">
-        <f t="shared" si="39"/>
-        <v>23566.512021255003</v>
+        <f t="shared" si="38"/>
+        <v>29706.168709489499</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="39"/>
-        <v>24037.842261680104</v>
+        <f t="shared" si="38"/>
+        <v>30300.292083679291</v>
       </c>
       <c r="BC15" s="1">
-        <f t="shared" ref="BC15" si="40">BB15*1.02</f>
-        <v>24518.599106913705</v>
+        <f t="shared" ref="BC15" si="39">BB15*1.02</f>
+        <v>30906.297925352876</v>
       </c>
       <c r="BD15" s="1">
-        <f t="shared" ref="BD15" si="41">BC15*1.02</f>
-        <v>25008.971089051978</v>
+        <f t="shared" ref="BD15" si="40">BC15*1.02</f>
+        <v>31524.423883859934</v>
       </c>
       <c r="BE15" s="1">
-        <f t="shared" ref="BE15" si="42">BD15*1.02</f>
-        <v>25509.150510833017</v>
+        <f t="shared" ref="BE15" si="41">BD15*1.02</f>
+        <v>32154.912361537132</v>
       </c>
       <c r="BF15" s="1">
-        <f t="shared" ref="BF15" si="43">BE15*1.02</f>
-        <v>26019.333521049677</v>
+        <f t="shared" ref="BF15" si="42">BE15*1.02</f>
+        <v>32798.010608767872</v>
       </c>
     </row>
     <row r="16" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3297,148 +3289,148 @@
         <v>28</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:P16" si="44">C12-C13-C14-C15</f>
+        <f t="shared" ref="C16:P16" si="43">C12-C13-C14-C15</f>
         <v>6568</v>
       </c>
       <c r="D16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>6868</v>
       </c>
       <c r="E16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7782</v>
       </c>
       <c r="F16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7573</v>
       </c>
       <c r="G16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7633</v>
       </c>
       <c r="H16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8116</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8625</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8221</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>6608</v>
       </c>
       <c r="L16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9180</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9177</v>
       </c>
       <c r="N16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9266</v>
       </c>
       <c r="O16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7977</v>
       </c>
       <c r="P16" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>6383</v>
       </c>
       <c r="Q16" s="9">
-        <f t="shared" ref="Q16" si="45">Q12-Q13-Q14-Q15</f>
+        <f t="shared" ref="Q16" si="44">Q12-Q13-Q14-Q15</f>
         <v>11213</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" ref="R16:V16" si="46">R12-R13-R14-R15</f>
+        <f t="shared" ref="R16:V16" si="45">R12-R13-R14-R15</f>
         <v>15651</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>16437</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>16437</v>
       </c>
       <c r="U16" s="9">
-        <f t="shared" ref="U16" si="47">U12-U13-U14-U15</f>
+        <f t="shared" ref="U16" si="46">U12-U13-U14-U15</f>
         <v>21031</v>
       </c>
       <c r="V16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>21885</v>
       </c>
       <c r="W16" s="9">
-        <f t="shared" ref="W16:X16" si="48">W12-W13-W14-W15</f>
+        <f t="shared" ref="W16:X16" si="47">W12-W13-W14-W15</f>
         <v>20094</v>
       </c>
       <c r="X16" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>19453</v>
       </c>
       <c r="Y16" s="9">
-        <f t="shared" ref="Y16" si="49">Y12-Y13-Y14-Y15</f>
+        <f t="shared" ref="Y16" si="48">Y12-Y13-Y14-Y15</f>
         <v>17135</v>
       </c>
       <c r="Z16" s="9">
-        <f t="shared" ref="Z16" si="50">Z12-Z13-Z14-Z15</f>
+        <f t="shared" ref="Z16" si="49">Z12-Z13-Z14-Z15</f>
         <v>18160</v>
       </c>
       <c r="AA16" s="9">
-        <f t="shared" ref="AA16:AB16" si="51">AA12-AA13-AA14-AA15</f>
+        <f t="shared" ref="AA16:AB16" si="50">AA12-AA13-AA14-AA15</f>
         <v>17415</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>21838</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" ref="AC16" si="52">AC12-AC13-AC14-AC15</f>
+        <f t="shared" ref="AC16" si="51">AC12-AC13-AC14-AC15</f>
         <v>21343</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" ref="AD16" si="53">AD12-AD13-AD14-AD15</f>
+        <f t="shared" ref="AD16" si="52">AD12-AD13-AD14-AD15</f>
         <v>23697</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" ref="AE16:AL16" si="54">AE12-AE13-AE14-AE15</f>
+        <f t="shared" ref="AE16:AL16" si="53">AE12-AE13-AE14-AE15</f>
         <v>25472</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>27425</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>28521</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>30972</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>30606</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>31271</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="54"/>
-        <v>32327.01225</v>
+        <f t="shared" si="53"/>
+        <v>31228</v>
       </c>
       <c r="AL16" s="9">
-        <f t="shared" si="54"/>
-        <v>34712.375</v>
+        <f t="shared" si="53"/>
+        <v>35039.480750000002</v>
       </c>
       <c r="AN16" s="9">
         <f>AN12-AN13-AN14-AN15</f>
@@ -3457,64 +3449,64 @@
         <v>41224</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" ref="AR16:BA16" si="55">AR12-AR13-AR14-AR15</f>
+        <f t="shared" ref="AR16:BA16" si="54">AR12-AR13-AR14-AR15</f>
         <v>75790</v>
       </c>
       <c r="AS16" s="9">
+        <f t="shared" si="54"/>
+        <v>74842</v>
+      </c>
+      <c r="AT16" s="9">
+        <f t="shared" si="54"/>
+        <v>84293</v>
+      </c>
+      <c r="AU16" s="9">
+        <f t="shared" si="54"/>
+        <v>112390</v>
+      </c>
+      <c r="AV16" s="9">
+        <f t="shared" si="54"/>
+        <v>128144.48074999999</v>
+      </c>
+      <c r="AW16" s="9">
+        <f t="shared" si="54"/>
+        <v>143204.40968799999</v>
+      </c>
+      <c r="AX16" s="9">
+        <f t="shared" si="54"/>
+        <v>155998.55859592004</v>
+      </c>
+      <c r="AY16" s="9">
+        <f t="shared" si="54"/>
+        <v>165952.50919439926</v>
+      </c>
+      <c r="AZ16" s="9">
+        <f t="shared" si="54"/>
+        <v>173935.36939065979</v>
+      </c>
+      <c r="BA16" s="9">
+        <f t="shared" si="54"/>
+        <v>180226.54943764035</v>
+      </c>
+      <c r="BB16" s="9">
+        <f t="shared" ref="BB16:BF16" si="55">BB12-BB13-BB14-BB15</f>
+        <v>185644.01723725401</v>
+      </c>
+      <c r="BC16" s="9">
         <f t="shared" si="55"/>
-        <v>74842</v>
-      </c>
-      <c r="AT16" s="9">
+        <v>190160.91304227681</v>
+      </c>
+      <c r="BD16" s="9">
         <f t="shared" si="55"/>
-        <v>84293</v>
-      </c>
-      <c r="AU16" s="9">
+        <v>192685.46066020615</v>
+      </c>
+      <c r="BE16" s="9">
         <f t="shared" si="55"/>
-        <v>112390</v>
-      </c>
-      <c r="AV16" s="9">
+        <v>195257.53384524814</v>
+      </c>
+      <c r="BF16" s="9">
         <f t="shared" si="55"/>
-        <v>128916.38725</v>
-      </c>
-      <c r="AW16" s="9">
-        <f t="shared" si="55"/>
-        <v>143984.01235099998</v>
-      </c>
-      <c r="AX16" s="9">
-        <f t="shared" si="55"/>
-        <v>155270.48271602998</v>
-      </c>
-      <c r="AY16" s="9">
-        <f t="shared" si="55"/>
-        <v>164647.63371901482</v>
-      </c>
-      <c r="AZ16" s="9">
-        <f t="shared" si="55"/>
-        <v>171826.61129003146</v>
-      </c>
-      <c r="BA16" s="9">
-        <f t="shared" si="55"/>
-        <v>177638.67753721654</v>
-      </c>
-      <c r="BB16" s="9">
-        <f t="shared" ref="BB16:BF16" si="56">BB12-BB13-BB14-BB15</f>
-        <v>182926.35826706144</v>
-      </c>
-      <c r="BC16" s="9">
-        <f t="shared" si="56"/>
-        <v>187333.82399795132</v>
-      </c>
-      <c r="BD16" s="9">
-        <f t="shared" si="56"/>
-        <v>189831.02477115626</v>
-      </c>
-      <c r="BE16" s="9">
-        <f t="shared" si="56"/>
-        <v>192374.70714878902</v>
-      </c>
-      <c r="BF16" s="9">
-        <f t="shared" si="56"/>
-        <v>194966.08432335002</v>
+        <v>197878.39243636909</v>
       </c>
     </row>
     <row r="17" spans="2:193" x14ac:dyDescent="0.3">
@@ -3624,11 +3616,10 @@
         <v>-2662</v>
       </c>
       <c r="AK17" s="1">
-        <f t="shared" ref="AK17:AL17" si="57">AG17*1.03</f>
-        <v>-3280.55</v>
+        <v>-12759</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="AL17" si="56">AH17*1.03</f>
         <v>-1309.1300000000001</v>
       </c>
       <c r="AN17" s="1">
@@ -3665,46 +3656,46 @@
       </c>
       <c r="AV17" s="1">
         <f>SUM(AI17:AL17)</f>
-        <v>-18434.68</v>
+        <v>-27913.13</v>
       </c>
       <c r="AW17" s="1">
         <f>AU17*1.01</f>
         <v>-7499.25</v>
       </c>
       <c r="AX17" s="1">
-        <f t="shared" ref="AX17:BF17" si="58">AW17*1.01</f>
+        <f t="shared" ref="AX17:BF17" si="57">AW17*1.01</f>
         <v>-7574.2425000000003</v>
       </c>
       <c r="AY17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7649.9849250000007</v>
       </c>
       <c r="AZ17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7726.4847742500006</v>
       </c>
       <c r="BA17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7803.7496219925006</v>
       </c>
       <c r="BB17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7881.7871182124254</v>
       </c>
       <c r="BC17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-7960.6049893945501</v>
       </c>
       <c r="BD17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-8040.2110392884961</v>
       </c>
       <c r="BE17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-8120.6131496813814</v>
       </c>
       <c r="BF17" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>-8201.8192811781955</v>
       </c>
     </row>
@@ -3713,148 +3704,148 @@
         <v>29</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:P18" si="59">C16-C17</f>
+        <f t="shared" ref="C18:P18" si="58">C16-C17</f>
         <v>6819</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>7113</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>7979</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>7927</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>10543</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>9286</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>10083</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>10072</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>8146</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>12147</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>8628</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>10704</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>7757</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>8277</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18" si="60">Q16-Q17</f>
+        <f t="shared" ref="Q18" si="59">Q16-Q17</f>
         <v>13629</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" ref="R18:V18" si="61">R16-R17</f>
+        <f t="shared" ref="R18:V18" si="60">R16-R17</f>
         <v>18689</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>21283</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>21283</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="62">U16-U17</f>
+        <f t="shared" ref="U18" si="61">U16-U17</f>
         <v>23064</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>24402</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:X18" si="63">W16-W17</f>
+        <f t="shared" ref="W18:X18" si="62">W16-W17</f>
         <v>18934</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>19014</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="64">Y16-Y17</f>
+        <f t="shared" ref="Y18" si="63">Y16-Y17</f>
         <v>16233</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="65">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="64">Z16-Z17</f>
         <v>17147</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18:AB18" si="66">AA16-AA17</f>
+        <f t="shared" ref="AA18:AB18" si="65">AA16-AA17</f>
         <v>18205</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>21903</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="67">AC16-AC17</f>
+        <f t="shared" ref="AC18" si="66">AC16-AC17</f>
         <v>21197</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="68">AD16-AD17</f>
+        <f t="shared" ref="AD18" si="67">AD16-AD17</f>
         <v>24412</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18:AL18" si="69">AE16-AE17</f>
+        <f t="shared" ref="AE18:AL18" si="68">AE16-AE17</f>
         <v>28315</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>27551</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>31706</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>32243</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>41789</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>33933</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="69"/>
-        <v>35607.562250000003</v>
+        <f t="shared" si="68"/>
+        <v>43987</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="69"/>
-        <v>36021.504999999997</v>
+        <f t="shared" si="68"/>
+        <v>36348.61075</v>
       </c>
       <c r="AN18" s="9">
         <f>AN16-AN17</f>
@@ -3873,64 +3864,64 @@
         <v>48352</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" ref="AR18:BA18" si="70">AR16-AR17</f>
+        <f t="shared" ref="AR18:BA18" si="69">AR16-AR17</f>
         <v>90032</v>
       </c>
       <c r="AS18" s="9">
+        <f t="shared" si="69"/>
+        <v>71328</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="69"/>
+        <v>85717</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" si="69"/>
+        <v>119815</v>
+      </c>
+      <c r="AV18" s="9">
+        <f t="shared" si="69"/>
+        <v>156057.61074999999</v>
+      </c>
+      <c r="AW18" s="9">
+        <f t="shared" si="69"/>
+        <v>150703.65968799999</v>
+      </c>
+      <c r="AX18" s="9">
+        <f t="shared" si="69"/>
+        <v>163572.80109592003</v>
+      </c>
+      <c r="AY18" s="9">
+        <f t="shared" si="69"/>
+        <v>173602.49411939926</v>
+      </c>
+      <c r="AZ18" s="9">
+        <f t="shared" si="69"/>
+        <v>181661.8541649098</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="69"/>
+        <v>188030.29905963285</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" ref="BB18:BF18" si="70">BB16-BB17</f>
+        <v>193525.80435546645</v>
+      </c>
+      <c r="BC18" s="9">
         <f t="shared" si="70"/>
-        <v>71328</v>
-      </c>
-      <c r="AT18" s="9">
+        <v>198121.51803167135</v>
+      </c>
+      <c r="BD18" s="9">
         <f t="shared" si="70"/>
-        <v>85717</v>
-      </c>
-      <c r="AU18" s="9">
+        <v>200725.67169949465</v>
+      </c>
+      <c r="BE18" s="9">
         <f t="shared" si="70"/>
-        <v>119815</v>
-      </c>
-      <c r="AV18" s="9">
+        <v>203378.14699492953</v>
+      </c>
+      <c r="BF18" s="9">
         <f t="shared" si="70"/>
-        <v>147351.06724999999</v>
-      </c>
-      <c r="AW18" s="9">
-        <f t="shared" si="70"/>
-        <v>151483.26235099998</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="70"/>
-        <v>162844.72521602997</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="70"/>
-        <v>172297.61864401482</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="70"/>
-        <v>179553.09606428148</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="70"/>
-        <v>185442.42715920904</v>
-      </c>
-      <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="71">BB16-BB17</f>
-        <v>190808.14538527388</v>
-      </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="71"/>
-        <v>195294.42898734586</v>
-      </c>
-      <c r="BD18" s="9">
-        <f t="shared" si="71"/>
-        <v>197871.23581044475</v>
-      </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="71"/>
-        <v>200495.32029847041</v>
-      </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="71"/>
-        <v>203167.90360452823</v>
+        <v>206080.2117175473</v>
       </c>
     </row>
     <row r="19" spans="2:193" x14ac:dyDescent="0.3">
@@ -4041,12 +4032,11 @@
         <v>5737</v>
       </c>
       <c r="AK19" s="1">
-        <f t="shared" ref="AK19:AL19" si="72">AK18*0.15</f>
-        <v>5341.1343375000006</v>
+        <v>9008</v>
       </c>
       <c r="AL19" s="1">
-        <f t="shared" si="72"/>
-        <v>5403.2257499999996</v>
+        <f t="shared" ref="AL19" si="71">AL18*0.15</f>
+        <v>5452.2916125000002</v>
       </c>
       <c r="AN19" s="1">
         <f>SUM(C19:F19)-10200</f>
@@ -4082,47 +4072,47 @@
       </c>
       <c r="AV19" s="1">
         <f>SUM(AI19:AL19)</f>
-        <v>23730.360087499997</v>
+        <v>27446.291612500001</v>
       </c>
       <c r="AW19" s="1">
-        <f t="shared" ref="AW19:BA19" si="73">AW18*0.16</f>
-        <v>24237.321976159998</v>
+        <f t="shared" ref="AW19:BA19" si="72">AW18*0.16</f>
+        <v>24112.585550079999</v>
       </c>
       <c r="AX19" s="1">
+        <f t="shared" si="72"/>
+        <v>26171.648175347207</v>
+      </c>
+      <c r="AY19" s="1">
+        <f t="shared" si="72"/>
+        <v>27776.399059103882</v>
+      </c>
+      <c r="AZ19" s="1">
+        <f t="shared" si="72"/>
+        <v>29065.896666385568</v>
+      </c>
+      <c r="BA19" s="1">
+        <f t="shared" si="72"/>
+        <v>30084.847849541256</v>
+      </c>
+      <c r="BB19" s="1">
+        <f t="shared" ref="BB19:BF19" si="73">BB18*0.16</f>
+        <v>30964.128696874632</v>
+      </c>
+      <c r="BC19" s="1">
         <f t="shared" si="73"/>
-        <v>26055.156034564796</v>
-      </c>
-      <c r="AY19" s="1">
+        <v>31699.442885067416</v>
+      </c>
+      <c r="BD19" s="1">
         <f t="shared" si="73"/>
-        <v>27567.618983042372</v>
-      </c>
-      <c r="AZ19" s="1">
+        <v>32116.107471919146</v>
+      </c>
+      <c r="BE19" s="1">
         <f t="shared" si="73"/>
-        <v>28728.495370285036</v>
-      </c>
-      <c r="BA19" s="1">
+        <v>32540.503519188725</v>
+      </c>
+      <c r="BF19" s="1">
         <f t="shared" si="73"/>
-        <v>29670.788345473447</v>
-      </c>
-      <c r="BB19" s="1">
-        <f t="shared" ref="BB19:BF19" si="74">BB18*0.16</f>
-        <v>30529.303261643821</v>
-      </c>
-      <c r="BC19" s="1">
-        <f t="shared" si="74"/>
-        <v>31247.10863797534</v>
-      </c>
-      <c r="BD19" s="1">
-        <f t="shared" si="74"/>
-        <v>31659.39772967116</v>
-      </c>
-      <c r="BE19" s="1">
-        <f t="shared" si="74"/>
-        <v>32079.251247755266</v>
-      </c>
-      <c r="BF19" s="1">
-        <f t="shared" si="74"/>
-        <v>32506.864576724518</v>
+        <v>32972.833874807569</v>
       </c>
     </row>
     <row r="20" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4130,148 +4120,148 @@
         <v>31</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:P20" si="75">C18-C19</f>
+        <f t="shared" ref="C20:P20" si="74">C18-C19</f>
         <v>5426</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6260</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6732</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-3111</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>9401</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>8266</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>9192</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>8948</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6657</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>9947</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>7068</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>10671</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6836</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>6959</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20" si="76">Q18-Q19</f>
+        <f t="shared" ref="Q20" si="75">Q18-Q19</f>
         <v>11517</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" ref="R20:V20" si="77">R18-R19</f>
+        <f t="shared" ref="R20:V20" si="76">R18-R19</f>
         <v>15227</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>17930</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>17930</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="78">U18-U19</f>
+        <f t="shared" ref="U20" si="77">U18-U19</f>
         <v>18936</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>20642</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20:X20" si="79">W18-W19</f>
+        <f t="shared" ref="W20:X20" si="78">W18-W19</f>
         <v>16436</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>16002</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="80">Y18-Y19</f>
+        <f t="shared" ref="Y20" si="79">Y18-Y19</f>
         <v>13910</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="81">Z18-Z19</f>
+        <f t="shared" ref="Z20" si="80">Z18-Z19</f>
         <v>13624</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20:AB20" si="82">AA18-AA19</f>
+        <f t="shared" ref="AA20:AB20" si="81">AA18-AA19</f>
         <v>15051</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>18368</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="83">AC18-AC19</f>
+        <f t="shared" ref="AC20" si="82">AC18-AC19</f>
         <v>19689</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="84">AD18-AD19</f>
+        <f t="shared" ref="AD20" si="83">AD18-AD19</f>
         <v>20687</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="85">AE18-AE19</f>
+        <f t="shared" ref="AE20:AH20" si="84">AE18-AE19</f>
         <v>23662</v>
       </c>
       <c r="AF20" s="9">
+        <f t="shared" si="84"/>
+        <v>23619</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="84"/>
+        <v>26301</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="84"/>
+        <v>26536</v>
+      </c>
+      <c r="AI20" s="9">
+        <f t="shared" ref="AI20:AL20" si="85">AI18-AI19</f>
+        <v>34540</v>
+      </c>
+      <c r="AJ20" s="9">
         <f t="shared" si="85"/>
-        <v>23619</v>
-      </c>
-      <c r="AG20" s="9">
+        <v>28196</v>
+      </c>
+      <c r="AK20" s="9">
         <f t="shared" si="85"/>
-        <v>26301</v>
-      </c>
-      <c r="AH20" s="9">
+        <v>34979</v>
+      </c>
+      <c r="AL20" s="9">
         <f t="shared" si="85"/>
-        <v>26536</v>
-      </c>
-      <c r="AI20" s="9">
-        <f t="shared" ref="AI20:AL20" si="86">AI18-AI19</f>
-        <v>34540</v>
-      </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="86"/>
-        <v>28196</v>
-      </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="86"/>
-        <v>30266.427912500003</v>
-      </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="86"/>
-        <v>30618.27925</v>
+        <v>30896.319137499999</v>
       </c>
       <c r="AN20" s="9">
         <f>AN18-AN19</f>
@@ -4290,604 +4280,604 @@
         <v>40539</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" ref="AR20:BA20" si="87">AR18-AR19</f>
+        <f t="shared" ref="AR20:BA20" si="86">AR18-AR19</f>
         <v>75438</v>
       </c>
       <c r="AS20" s="9">
+        <f t="shared" si="86"/>
+        <v>59972</v>
+      </c>
+      <c r="AT20" s="9">
+        <f t="shared" si="86"/>
+        <v>73795</v>
+      </c>
+      <c r="AU20" s="9">
+        <f t="shared" si="86"/>
+        <v>100118</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" si="86"/>
+        <v>128611.31913749999</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" si="86"/>
+        <v>126591.07413791999</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" si="86"/>
+        <v>137401.15292057281</v>
+      </c>
+      <c r="AY20" s="9">
+        <f t="shared" si="86"/>
+        <v>145826.09506029537</v>
+      </c>
+      <c r="AZ20" s="9">
+        <f t="shared" si="86"/>
+        <v>152595.95749852422</v>
+      </c>
+      <c r="BA20" s="9">
+        <f t="shared" si="86"/>
+        <v>157945.45121009159</v>
+      </c>
+      <c r="BB20" s="9">
+        <f t="shared" ref="BB20:BF20" si="87">BB18-BB19</f>
+        <v>162561.67565859182</v>
+      </c>
+      <c r="BC20" s="9">
         <f t="shared" si="87"/>
-        <v>59972</v>
-      </c>
-      <c r="AT20" s="9">
+        <v>166422.07514660392</v>
+      </c>
+      <c r="BD20" s="9">
         <f t="shared" si="87"/>
-        <v>73795</v>
-      </c>
-      <c r="AU20" s="9">
+        <v>168609.56422757549</v>
+      </c>
+      <c r="BE20" s="9">
         <f t="shared" si="87"/>
-        <v>100118</v>
-      </c>
-      <c r="AV20" s="9">
+        <v>170837.6434757408</v>
+      </c>
+      <c r="BF20" s="9">
         <f t="shared" si="87"/>
-        <v>123620.7071625</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="87"/>
-        <v>127245.94037483999</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" si="87"/>
-        <v>136789.56918146517</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="87"/>
-        <v>144729.99966097245</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="87"/>
-        <v>150824.60069399644</v>
-      </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="87"/>
-        <v>155771.6388137356</v>
-      </c>
-      <c r="BB20" s="9">
-        <f t="shared" ref="BB20:BF20" si="88">BB18-BB19</f>
-        <v>160278.84212363005</v>
-      </c>
-      <c r="BC20" s="9">
-        <f t="shared" si="88"/>
-        <v>164047.32034937054</v>
-      </c>
-      <c r="BD20" s="9">
-        <f t="shared" si="88"/>
-        <v>166211.8380807736</v>
-      </c>
-      <c r="BE20" s="9">
-        <f t="shared" si="88"/>
-        <v>168416.06905071513</v>
-      </c>
-      <c r="BF20" s="9">
-        <f t="shared" si="88"/>
-        <v>170661.03902780369</v>
+        <v>173107.37784273972</v>
       </c>
       <c r="BG20" s="6">
         <f>BF20*(1+$BI$32)</f>
-        <v>168954.42863752565</v>
+        <v>171376.30406431231</v>
       </c>
       <c r="BH20" s="6">
-        <f t="shared" ref="BH20:DS20" si="89">BG20*(1+$BI$32)</f>
-        <v>167264.88435115039</v>
+        <f t="shared" ref="BH20:DS20" si="88">BG20*(1+$BI$32)</f>
+        <v>169662.54102366918</v>
       </c>
       <c r="BI20" s="6">
+        <f t="shared" si="88"/>
+        <v>167965.9156134325</v>
+      </c>
+      <c r="BJ20" s="6">
+        <f t="shared" si="88"/>
+        <v>166286.25645729818</v>
+      </c>
+      <c r="BK20" s="6">
+        <f t="shared" si="88"/>
+        <v>164623.3938927252</v>
+      </c>
+      <c r="BL20" s="6">
+        <f t="shared" si="88"/>
+        <v>162977.15995379793</v>
+      </c>
+      <c r="BM20" s="6">
+        <f t="shared" si="88"/>
+        <v>161347.38835425995</v>
+      </c>
+      <c r="BN20" s="6">
+        <f t="shared" si="88"/>
+        <v>159733.91447071734</v>
+      </c>
+      <c r="BO20" s="6">
+        <f t="shared" si="88"/>
+        <v>158136.57532601018</v>
+      </c>
+      <c r="BP20" s="6">
+        <f t="shared" si="88"/>
+        <v>156555.20957275009</v>
+      </c>
+      <c r="BQ20" s="6">
+        <f t="shared" si="88"/>
+        <v>154989.65747702259</v>
+      </c>
+      <c r="BR20" s="6">
+        <f t="shared" si="88"/>
+        <v>153439.76090225237</v>
+      </c>
+      <c r="BS20" s="6">
+        <f t="shared" si="88"/>
+        <v>151905.36329322984</v>
+      </c>
+      <c r="BT20" s="6">
+        <f t="shared" si="88"/>
+        <v>150386.30966029753</v>
+      </c>
+      <c r="BU20" s="6">
+        <f t="shared" si="88"/>
+        <v>148882.44656369454</v>
+      </c>
+      <c r="BV20" s="6">
+        <f t="shared" si="88"/>
+        <v>147393.62209805759</v>
+      </c>
+      <c r="BW20" s="6">
+        <f t="shared" si="88"/>
+        <v>145919.68587707702</v>
+      </c>
+      <c r="BX20" s="6">
+        <f t="shared" si="88"/>
+        <v>144460.48901830625</v>
+      </c>
+      <c r="BY20" s="6">
+        <f t="shared" si="88"/>
+        <v>143015.8841281232</v>
+      </c>
+      <c r="BZ20" s="6">
+        <f t="shared" si="88"/>
+        <v>141585.72528684197</v>
+      </c>
+      <c r="CA20" s="6">
+        <f t="shared" si="88"/>
+        <v>140169.86803397356</v>
+      </c>
+      <c r="CB20" s="6">
+        <f t="shared" si="88"/>
+        <v>138768.16935363383</v>
+      </c>
+      <c r="CC20" s="6">
+        <f t="shared" si="88"/>
+        <v>137380.48766009748</v>
+      </c>
+      <c r="CD20" s="6">
+        <f t="shared" si="88"/>
+        <v>136006.68278349651</v>
+      </c>
+      <c r="CE20" s="6">
+        <f t="shared" si="88"/>
+        <v>134646.61595566155</v>
+      </c>
+      <c r="CF20" s="6">
+        <f t="shared" si="88"/>
+        <v>133300.14979610493</v>
+      </c>
+      <c r="CG20" s="6">
+        <f t="shared" si="88"/>
+        <v>131967.14829814387</v>
+      </c>
+      <c r="CH20" s="6">
+        <f t="shared" si="88"/>
+        <v>130647.47681516243</v>
+      </c>
+      <c r="CI20" s="6">
+        <f t="shared" si="88"/>
+        <v>129341.0020470108</v>
+      </c>
+      <c r="CJ20" s="6">
+        <f t="shared" si="88"/>
+        <v>128047.59202654069</v>
+      </c>
+      <c r="CK20" s="6">
+        <f t="shared" si="88"/>
+        <v>126767.11610627528</v>
+      </c>
+      <c r="CL20" s="6">
+        <f t="shared" si="88"/>
+        <v>125499.44494521253</v>
+      </c>
+      <c r="CM20" s="6">
+        <f t="shared" si="88"/>
+        <v>124244.45049576039</v>
+      </c>
+      <c r="CN20" s="6">
+        <f t="shared" si="88"/>
+        <v>123002.00599080279</v>
+      </c>
+      <c r="CO20" s="6">
+        <f t="shared" si="88"/>
+        <v>121771.98593089476</v>
+      </c>
+      <c r="CP20" s="6">
+        <f t="shared" si="88"/>
+        <v>120554.26607158582</v>
+      </c>
+      <c r="CQ20" s="6">
+        <f t="shared" si="88"/>
+        <v>119348.72341086996</v>
+      </c>
+      <c r="CR20" s="6">
+        <f t="shared" si="88"/>
+        <v>118155.23617676126</v>
+      </c>
+      <c r="CS20" s="6">
+        <f t="shared" si="88"/>
+        <v>116973.68381499365</v>
+      </c>
+      <c r="CT20" s="6">
+        <f t="shared" si="88"/>
+        <v>115803.94697684371</v>
+      </c>
+      <c r="CU20" s="6">
+        <f t="shared" si="88"/>
+        <v>114645.90750707527</v>
+      </c>
+      <c r="CV20" s="6">
+        <f t="shared" si="88"/>
+        <v>113499.44843200452</v>
+      </c>
+      <c r="CW20" s="6">
+        <f t="shared" si="88"/>
+        <v>112364.45394768447</v>
+      </c>
+      <c r="CX20" s="6">
+        <f t="shared" si="88"/>
+        <v>111240.80940820761</v>
+      </c>
+      <c r="CY20" s="6">
+        <f t="shared" si="88"/>
+        <v>110128.40131412554</v>
+      </c>
+      <c r="CZ20" s="6">
+        <f t="shared" si="88"/>
+        <v>109027.11730098429</v>
+      </c>
+      <c r="DA20" s="6">
+        <f t="shared" si="88"/>
+        <v>107936.84612797445</v>
+      </c>
+      <c r="DB20" s="6">
+        <f t="shared" si="88"/>
+        <v>106857.4776666947</v>
+      </c>
+      <c r="DC20" s="6">
+        <f t="shared" si="88"/>
+        <v>105788.90289002775</v>
+      </c>
+      <c r="DD20" s="6">
+        <f t="shared" si="88"/>
+        <v>104731.01386112747</v>
+      </c>
+      <c r="DE20" s="6">
+        <f t="shared" si="88"/>
+        <v>103683.70372251621</v>
+      </c>
+      <c r="DF20" s="6">
+        <f t="shared" si="88"/>
+        <v>102646.86668529104</v>
+      </c>
+      <c r="DG20" s="6">
+        <f t="shared" si="88"/>
+        <v>101620.39801843812</v>
+      </c>
+      <c r="DH20" s="6">
+        <f t="shared" si="88"/>
+        <v>100604.19403825374</v>
+      </c>
+      <c r="DI20" s="6">
+        <f t="shared" si="88"/>
+        <v>99598.152097871207</v>
+      </c>
+      <c r="DJ20" s="6">
+        <f t="shared" si="88"/>
+        <v>98602.170576892488</v>
+      </c>
+      <c r="DK20" s="6">
+        <f t="shared" si="88"/>
+        <v>97616.148871123558</v>
+      </c>
+      <c r="DL20" s="6">
+        <f t="shared" si="88"/>
+        <v>96639.987382412321</v>
+      </c>
+      <c r="DM20" s="6">
+        <f t="shared" si="88"/>
+        <v>95673.5875085882</v>
+      </c>
+      <c r="DN20" s="6">
+        <f t="shared" si="88"/>
+        <v>94716.851633502316</v>
+      </c>
+      <c r="DO20" s="6">
+        <f t="shared" si="88"/>
+        <v>93769.683117167297</v>
+      </c>
+      <c r="DP20" s="6">
+        <f t="shared" si="88"/>
+        <v>92831.986285995619</v>
+      </c>
+      <c r="DQ20" s="6">
+        <f t="shared" si="88"/>
+        <v>91903.666423135655</v>
+      </c>
+      <c r="DR20" s="6">
+        <f t="shared" si="88"/>
+        <v>90984.629758904295</v>
+      </c>
+      <c r="DS20" s="6">
+        <f t="shared" si="88"/>
+        <v>90074.783461315252</v>
+      </c>
+      <c r="DT20" s="6">
+        <f t="shared" ref="DT20:GE20" si="89">DS20*(1+$BI$32)</f>
+        <v>89174.035626702098</v>
+      </c>
+      <c r="DU20" s="6">
         <f t="shared" si="89"/>
-        <v>165592.23550763889</v>
-      </c>
-      <c r="BJ20" s="6">
+        <v>88282.295270435076</v>
+      </c>
+      <c r="DV20" s="6">
         <f t="shared" si="89"/>
-        <v>163936.31315256251</v>
-      </c>
-      <c r="BK20" s="6">
+        <v>87399.472317730717</v>
+      </c>
+      <c r="DW20" s="6">
         <f t="shared" si="89"/>
-        <v>162296.95002103687</v>
-      </c>
-      <c r="BL20" s="6">
+        <v>86525.477594553406</v>
+      </c>
+      <c r="DX20" s="6">
         <f t="shared" si="89"/>
-        <v>160673.9805208265</v>
-      </c>
-      <c r="BM20" s="6">
+        <v>85660.222818607872</v>
+      </c>
+      <c r="DY20" s="6">
         <f t="shared" si="89"/>
-        <v>159067.24071561825</v>
-      </c>
-      <c r="BN20" s="6">
+        <v>84803.620590421793</v>
+      </c>
+      <c r="DZ20" s="6">
         <f t="shared" si="89"/>
-        <v>157476.56830846207</v>
-      </c>
-      <c r="BO20" s="6">
+        <v>83955.58438451757</v>
+      </c>
+      <c r="EA20" s="6">
         <f t="shared" si="89"/>
-        <v>155901.80262537746</v>
-      </c>
-      <c r="BP20" s="6">
+        <v>83116.0285406724</v>
+      </c>
+      <c r="EB20" s="6">
         <f t="shared" si="89"/>
-        <v>154342.7845991237</v>
-      </c>
-      <c r="BQ20" s="6">
+        <v>82284.868255265668</v>
+      </c>
+      <c r="EC20" s="6">
         <f t="shared" si="89"/>
-        <v>152799.35675313245</v>
-      </c>
-      <c r="BR20" s="6">
+        <v>81462.019572713005</v>
+      </c>
+      <c r="ED20" s="6">
         <f t="shared" si="89"/>
-        <v>151271.36318560113</v>
-      </c>
-      <c r="BS20" s="6">
+        <v>80647.399376985879</v>
+      </c>
+      <c r="EE20" s="6">
         <f t="shared" si="89"/>
-        <v>149758.64955374511</v>
-      </c>
-      <c r="BT20" s="6">
+        <v>79840.925383216018</v>
+      </c>
+      <c r="EF20" s="6">
         <f t="shared" si="89"/>
-        <v>148261.06305820766</v>
-      </c>
-      <c r="BU20" s="6">
+        <v>79042.516129383861</v>
+      </c>
+      <c r="EG20" s="6">
         <f t="shared" si="89"/>
-        <v>146778.45242762557</v>
-      </c>
-      <c r="BV20" s="6">
+        <v>78252.090968090022</v>
+      </c>
+      <c r="EH20" s="6">
         <f t="shared" si="89"/>
-        <v>145310.6679033493</v>
-      </c>
-      <c r="BW20" s="6">
+        <v>77469.570058409125</v>
+      </c>
+      <c r="EI20" s="6">
         <f t="shared" si="89"/>
-        <v>143857.56122431581</v>
-      </c>
-      <c r="BX20" s="6">
+        <v>76694.874357825029</v>
+      </c>
+      <c r="EJ20" s="6">
         <f t="shared" si="89"/>
-        <v>142418.98561207266</v>
-      </c>
-      <c r="BY20" s="6">
+        <v>75927.925614246778</v>
+      </c>
+      <c r="EK20" s="6">
         <f t="shared" si="89"/>
-        <v>140994.79575595193</v>
-      </c>
-      <c r="BZ20" s="6">
+        <v>75168.646358104306</v>
+      </c>
+      <c r="EL20" s="6">
         <f t="shared" si="89"/>
-        <v>139584.84779839241</v>
-      </c>
-      <c r="CA20" s="6">
+        <v>74416.959894523257</v>
+      </c>
+      <c r="EM20" s="6">
         <f t="shared" si="89"/>
-        <v>138188.99932040847</v>
-      </c>
-      <c r="CB20" s="6">
+        <v>73672.79029557803</v>
+      </c>
+      <c r="EN20" s="6">
         <f t="shared" si="89"/>
-        <v>136807.10932720438</v>
-      </c>
-      <c r="CC20" s="6">
+        <v>72936.062392622247</v>
+      </c>
+      <c r="EO20" s="6">
         <f t="shared" si="89"/>
-        <v>135439.03823393234</v>
-      </c>
-      <c r="CD20" s="6">
+        <v>72206.701768696017</v>
+      </c>
+      <c r="EP20" s="6">
         <f t="shared" si="89"/>
-        <v>134084.64785159301</v>
-      </c>
-      <c r="CE20" s="6">
+        <v>71484.634751009056</v>
+      </c>
+      <c r="EQ20" s="6">
         <f t="shared" si="89"/>
-        <v>132743.80137307706</v>
-      </c>
-      <c r="CF20" s="6">
+        <v>70769.788403498969</v>
+      </c>
+      <c r="ER20" s="6">
         <f t="shared" si="89"/>
-        <v>131416.36335934629</v>
-      </c>
-      <c r="CG20" s="6">
+        <v>70062.090519463978</v>
+      </c>
+      <c r="ES20" s="6">
         <f t="shared" si="89"/>
-        <v>130102.19972575283</v>
-      </c>
-      <c r="CH20" s="6">
+        <v>69361.469614269343</v>
+      </c>
+      <c r="ET20" s="6">
         <f t="shared" si="89"/>
-        <v>128801.1777284953</v>
-      </c>
-      <c r="CI20" s="6">
+        <v>68667.854918126643</v>
+      </c>
+      <c r="EU20" s="6">
         <f t="shared" si="89"/>
-        <v>127513.16595121035</v>
-      </c>
-      <c r="CJ20" s="6">
+        <v>67981.17636894538</v>
+      </c>
+      <c r="EV20" s="6">
         <f t="shared" si="89"/>
-        <v>126238.03429169825</v>
-      </c>
-      <c r="CK20" s="6">
+        <v>67301.36460525592</v>
+      </c>
+      <c r="EW20" s="6">
         <f t="shared" si="89"/>
-        <v>124975.65394878127</v>
-      </c>
-      <c r="CL20" s="6">
+        <v>66628.350959203366</v>
+      </c>
+      <c r="EX20" s="6">
         <f t="shared" si="89"/>
-        <v>123725.89740929345</v>
-      </c>
-      <c r="CM20" s="6">
+        <v>65962.067449611335</v>
+      </c>
+      <c r="EY20" s="6">
         <f t="shared" si="89"/>
-        <v>122488.63843520051</v>
-      </c>
-      <c r="CN20" s="6">
+        <v>65302.446775115219</v>
+      </c>
+      <c r="EZ20" s="6">
         <f t="shared" si="89"/>
-        <v>121263.7520508485</v>
-      </c>
-      <c r="CO20" s="6">
+        <v>64649.422307364068</v>
+      </c>
+      <c r="FA20" s="6">
         <f t="shared" si="89"/>
-        <v>120051.11453034001</v>
-      </c>
-      <c r="CP20" s="6">
+        <v>64002.928084290426</v>
+      </c>
+      <c r="FB20" s="6">
         <f t="shared" si="89"/>
-        <v>118850.60338503661</v>
-      </c>
-      <c r="CQ20" s="6">
+        <v>63362.898803447519</v>
+      </c>
+      <c r="FC20" s="6">
         <f t="shared" si="89"/>
-        <v>117662.09735118624</v>
-      </c>
-      <c r="CR20" s="6">
+        <v>62729.269815413041</v>
+      </c>
+      <c r="FD20" s="6">
         <f t="shared" si="89"/>
-        <v>116485.47637767438</v>
-      </c>
-      <c r="CS20" s="6">
+        <v>62101.97711725891</v>
+      </c>
+      <c r="FE20" s="6">
         <f t="shared" si="89"/>
-        <v>115320.62161389763</v>
-      </c>
-      <c r="CT20" s="6">
+        <v>61480.957346086318</v>
+      </c>
+      <c r="FF20" s="6">
         <f t="shared" si="89"/>
-        <v>114167.41539775865</v>
-      </c>
-      <c r="CU20" s="6">
+        <v>60866.147772625452</v>
+      </c>
+      <c r="FG20" s="6">
         <f t="shared" si="89"/>
-        <v>113025.74124378107</v>
-      </c>
-      <c r="CV20" s="6">
+        <v>60257.486294899194</v>
+      </c>
+      <c r="FH20" s="6">
         <f t="shared" si="89"/>
-        <v>111895.48383134326</v>
-      </c>
-      <c r="CW20" s="6">
+        <v>59654.911431950204</v>
+      </c>
+      <c r="FI20" s="6">
         <f t="shared" si="89"/>
-        <v>110776.52899302982</v>
-      </c>
-      <c r="CX20" s="6">
+        <v>59058.362317630701</v>
+      </c>
+      <c r="FJ20" s="6">
         <f t="shared" si="89"/>
-        <v>109668.76370309952</v>
-      </c>
-      <c r="CY20" s="6">
+        <v>58467.778694454391</v>
+      </c>
+      <c r="FK20" s="6">
         <f t="shared" si="89"/>
-        <v>108572.07606606853</v>
-      </c>
-      <c r="CZ20" s="6">
+        <v>57883.100907509848</v>
+      </c>
+      <c r="FL20" s="6">
         <f t="shared" si="89"/>
-        <v>107486.35530540785</v>
-      </c>
-      <c r="DA20" s="6">
+        <v>57304.269898434752</v>
+      </c>
+      <c r="FM20" s="6">
         <f t="shared" si="89"/>
-        <v>106411.49175235377</v>
-      </c>
-      <c r="DB20" s="6">
+        <v>56731.227199450404</v>
+      </c>
+      <c r="FN20" s="6">
         <f t="shared" si="89"/>
-        <v>105347.37683483024</v>
-      </c>
-      <c r="DC20" s="6">
+        <v>56163.914927455902</v>
+      </c>
+      <c r="FO20" s="6">
         <f t="shared" si="89"/>
-        <v>104293.90306648194</v>
-      </c>
-      <c r="DD20" s="6">
+        <v>55602.275778181342</v>
+      </c>
+      <c r="FP20" s="6">
         <f t="shared" si="89"/>
-        <v>103250.96403581712</v>
-      </c>
-      <c r="DE20" s="6">
+        <v>55046.253020399527</v>
+      </c>
+      <c r="FQ20" s="6">
         <f t="shared" si="89"/>
-        <v>102218.45439545895</v>
-      </c>
-      <c r="DF20" s="6">
+        <v>54495.790490195533</v>
+      </c>
+      <c r="FR20" s="6">
         <f t="shared" si="89"/>
-        <v>101196.26985150436</v>
-      </c>
-      <c r="DG20" s="6">
+        <v>53950.832585293574</v>
+      </c>
+      <c r="FS20" s="6">
         <f t="shared" si="89"/>
-        <v>100184.30715298932</v>
-      </c>
-      <c r="DH20" s="6">
+        <v>53411.32425944064</v>
+      </c>
+      <c r="FT20" s="6">
         <f t="shared" si="89"/>
-        <v>99182.464081459431</v>
-      </c>
-      <c r="DI20" s="6">
+        <v>52877.211016846231</v>
+      </c>
+      <c r="FU20" s="6">
         <f t="shared" si="89"/>
-        <v>98190.639440644838</v>
-      </c>
-      <c r="DJ20" s="6">
+        <v>52348.438906677766</v>
+      </c>
+      <c r="FV20" s="6">
         <f t="shared" si="89"/>
-        <v>97208.733046238383</v>
-      </c>
-      <c r="DK20" s="6">
+        <v>51824.95451761099</v>
+      </c>
+      <c r="FW20" s="6">
         <f t="shared" si="89"/>
-        <v>96236.645715776001</v>
-      </c>
-      <c r="DL20" s="6">
+        <v>51306.704972434876</v>
+      </c>
+      <c r="FX20" s="6">
         <f t="shared" si="89"/>
-        <v>95274.279258618248</v>
-      </c>
-      <c r="DM20" s="6">
+        <v>50793.637922710528</v>
+      </c>
+      <c r="FY20" s="6">
         <f t="shared" si="89"/>
-        <v>94321.536466032063</v>
-      </c>
-      <c r="DN20" s="6">
+        <v>50285.701543483425</v>
+      </c>
+      <c r="FZ20" s="6">
         <f t="shared" si="89"/>
-        <v>93378.321101371737</v>
-      </c>
-      <c r="DO20" s="6">
+        <v>49782.84452804859</v>
+      </c>
+      <c r="GA20" s="6">
         <f t="shared" si="89"/>
-        <v>92444.537890358013</v>
-      </c>
-      <c r="DP20" s="6">
+        <v>49285.016082768103</v>
+      </c>
+      <c r="GB20" s="6">
         <f t="shared" si="89"/>
-        <v>91520.092511454437</v>
-      </c>
-      <c r="DQ20" s="6">
+        <v>48792.165921940425</v>
+      </c>
+      <c r="GC20" s="6">
         <f t="shared" si="89"/>
-        <v>90604.891586339887</v>
-      </c>
-      <c r="DR20" s="6">
+        <v>48304.244262721018</v>
+      </c>
+      <c r="GD20" s="6">
         <f t="shared" si="89"/>
-        <v>89698.842670476486</v>
-      </c>
-      <c r="DS20" s="6">
+        <v>47821.201820093811</v>
+      </c>
+      <c r="GE20" s="6">
         <f t="shared" si="89"/>
-        <v>88801.854243771726</v>
-      </c>
-      <c r="DT20" s="6">
-        <f t="shared" ref="DT20:GE20" si="90">DS20*(1+$BI$32)</f>
-        <v>87913.835701334014</v>
-      </c>
-      <c r="DU20" s="6">
+        <v>47342.989801892872</v>
+      </c>
+      <c r="GF20" s="6">
+        <f t="shared" ref="GF20:GK20" si="90">GE20*(1+$BI$32)</f>
+        <v>46869.559903873946</v>
+      </c>
+      <c r="GG20" s="6">
         <f t="shared" si="90"/>
-        <v>87034.697344320666</v>
-      </c>
-      <c r="DV20" s="6">
+        <v>46400.864304835202</v>
+      </c>
+      <c r="GH20" s="6">
         <f t="shared" si="90"/>
-        <v>86164.350370877451</v>
-      </c>
-      <c r="DW20" s="6">
+        <v>45936.855661786853</v>
+      </c>
+      <c r="GI20" s="6">
         <f t="shared" si="90"/>
-        <v>85302.706867168672</v>
-      </c>
-      <c r="DX20" s="6">
+        <v>45477.487105168984</v>
+      </c>
+      <c r="GJ20" s="6">
         <f t="shared" si="90"/>
-        <v>84449.679798496989</v>
-      </c>
-      <c r="DY20" s="6">
+        <v>45022.712234117294</v>
+      </c>
+      <c r="GK20" s="6">
         <f t="shared" si="90"/>
-        <v>83605.183000512014</v>
-      </c>
-      <c r="DZ20" s="6">
-        <f t="shared" si="90"/>
-        <v>82769.131170506895</v>
-      </c>
-      <c r="EA20" s="6">
-        <f t="shared" si="90"/>
-        <v>81941.439858801823</v>
-      </c>
-      <c r="EB20" s="6">
-        <f t="shared" si="90"/>
-        <v>81122.025460213801</v>
-      </c>
-      <c r="EC20" s="6">
-        <f t="shared" si="90"/>
-        <v>80310.805205611658</v>
-      </c>
-      <c r="ED20" s="6">
-        <f t="shared" si="90"/>
-        <v>79507.697153555535</v>
-      </c>
-      <c r="EE20" s="6">
-        <f t="shared" si="90"/>
-        <v>78712.620182019979</v>
-      </c>
-      <c r="EF20" s="6">
-        <f t="shared" si="90"/>
-        <v>77925.493980199783</v>
-      </c>
-      <c r="EG20" s="6">
-        <f t="shared" si="90"/>
-        <v>77146.239040397777</v>
-      </c>
-      <c r="EH20" s="6">
-        <f t="shared" si="90"/>
-        <v>76374.776649993801</v>
-      </c>
-      <c r="EI20" s="6">
-        <f t="shared" si="90"/>
-        <v>75611.028883493869</v>
-      </c>
-      <c r="EJ20" s="6">
-        <f t="shared" si="90"/>
-        <v>74854.918594658928</v>
-      </c>
-      <c r="EK20" s="6">
-        <f t="shared" si="90"/>
-        <v>74106.369408712344</v>
-      </c>
-      <c r="EL20" s="6">
-        <f t="shared" si="90"/>
-        <v>73365.305714625225</v>
-      </c>
-      <c r="EM20" s="6">
-        <f t="shared" si="90"/>
-        <v>72631.652657478975</v>
-      </c>
-      <c r="EN20" s="6">
-        <f t="shared" si="90"/>
-        <v>71905.336130904179</v>
-      </c>
-      <c r="EO20" s="6">
-        <f t="shared" si="90"/>
-        <v>71186.282769595142</v>
-      </c>
-      <c r="EP20" s="6">
-        <f t="shared" si="90"/>
-        <v>70474.419941899192</v>
-      </c>
-      <c r="EQ20" s="6">
-        <f t="shared" si="90"/>
-        <v>69769.675742480205</v>
-      </c>
-      <c r="ER20" s="6">
-        <f t="shared" si="90"/>
-        <v>69071.978985055408</v>
-      </c>
-      <c r="ES20" s="6">
-        <f t="shared" si="90"/>
-        <v>68381.259195204853</v>
-      </c>
-      <c r="ET20" s="6">
-        <f t="shared" si="90"/>
-        <v>67697.4466032528</v>
-      </c>
-      <c r="EU20" s="6">
-        <f t="shared" si="90"/>
-        <v>67020.472137220277</v>
-      </c>
-      <c r="EV20" s="6">
-        <f t="shared" si="90"/>
-        <v>66350.26741584808</v>
-      </c>
-      <c r="EW20" s="6">
-        <f t="shared" si="90"/>
-        <v>65686.764741689592</v>
-      </c>
-      <c r="EX20" s="6">
-        <f t="shared" si="90"/>
-        <v>65029.897094272696</v>
-      </c>
-      <c r="EY20" s="6">
-        <f t="shared" si="90"/>
-        <v>64379.598123329968</v>
-      </c>
-      <c r="EZ20" s="6">
-        <f t="shared" si="90"/>
-        <v>63735.802142096669</v>
-      </c>
-      <c r="FA20" s="6">
-        <f t="shared" si="90"/>
-        <v>63098.444120675704</v>
-      </c>
-      <c r="FB20" s="6">
-        <f t="shared" si="90"/>
-        <v>62467.45967946895</v>
-      </c>
-      <c r="FC20" s="6">
-        <f t="shared" si="90"/>
-        <v>61842.785082674258</v>
-      </c>
-      <c r="FD20" s="6">
-        <f t="shared" si="90"/>
-        <v>61224.357231847513</v>
-      </c>
-      <c r="FE20" s="6">
-        <f t="shared" si="90"/>
-        <v>60612.113659529037</v>
-      </c>
-      <c r="FF20" s="6">
-        <f t="shared" si="90"/>
-        <v>60005.992522933746</v>
-      </c>
-      <c r="FG20" s="6">
-        <f t="shared" si="90"/>
-        <v>59405.932597704406</v>
-      </c>
-      <c r="FH20" s="6">
-        <f t="shared" si="90"/>
-        <v>58811.87327172736</v>
-      </c>
-      <c r="FI20" s="6">
-        <f t="shared" si="90"/>
-        <v>58223.754539010086</v>
-      </c>
-      <c r="FJ20" s="6">
-        <f t="shared" si="90"/>
-        <v>57641.516993619982</v>
-      </c>
-      <c r="FK20" s="6">
-        <f t="shared" si="90"/>
-        <v>57065.101823683784</v>
-      </c>
-      <c r="FL20" s="6">
-        <f t="shared" si="90"/>
-        <v>56494.450805446948</v>
-      </c>
-      <c r="FM20" s="6">
-        <f t="shared" si="90"/>
-        <v>55929.50629739248</v>
-      </c>
-      <c r="FN20" s="6">
-        <f t="shared" si="90"/>
-        <v>55370.211234418552</v>
-      </c>
-      <c r="FO20" s="6">
-        <f t="shared" si="90"/>
-        <v>54816.509122074363</v>
-      </c>
-      <c r="FP20" s="6">
-        <f t="shared" si="90"/>
-        <v>54268.344030853623</v>
-      </c>
-      <c r="FQ20" s="6">
-        <f t="shared" si="90"/>
-        <v>53725.660590545085</v>
-      </c>
-      <c r="FR20" s="6">
-        <f t="shared" si="90"/>
-        <v>53188.403984639634</v>
-      </c>
-      <c r="FS20" s="6">
-        <f t="shared" si="90"/>
-        <v>52656.519944793239</v>
-      </c>
-      <c r="FT20" s="6">
-        <f t="shared" si="90"/>
-        <v>52129.954745345305</v>
-      </c>
-      <c r="FU20" s="6">
-        <f t="shared" si="90"/>
-        <v>51608.655197891851</v>
-      </c>
-      <c r="FV20" s="6">
-        <f t="shared" si="90"/>
-        <v>51092.568645912928</v>
-      </c>
-      <c r="FW20" s="6">
-        <f t="shared" si="90"/>
-        <v>50581.642959453799</v>
-      </c>
-      <c r="FX20" s="6">
-        <f t="shared" si="90"/>
-        <v>50075.82652985926</v>
-      </c>
-      <c r="FY20" s="6">
-        <f t="shared" si="90"/>
-        <v>49575.068264560665</v>
-      </c>
-      <c r="FZ20" s="6">
-        <f t="shared" si="90"/>
-        <v>49079.317581915057</v>
-      </c>
-      <c r="GA20" s="6">
-        <f t="shared" si="90"/>
-        <v>48588.524406095908</v>
-      </c>
-      <c r="GB20" s="6">
-        <f t="shared" si="90"/>
-        <v>48102.639162034946</v>
-      </c>
-      <c r="GC20" s="6">
-        <f t="shared" si="90"/>
-        <v>47621.612770414598</v>
-      </c>
-      <c r="GD20" s="6">
-        <f t="shared" si="90"/>
-        <v>47145.396642710453</v>
-      </c>
-      <c r="GE20" s="6">
-        <f t="shared" si="90"/>
-        <v>46673.942676283346</v>
-      </c>
-      <c r="GF20" s="6">
-        <f t="shared" ref="GF20:GK20" si="91">GE20*(1+$BI$32)</f>
-        <v>46207.203249520513</v>
-      </c>
-      <c r="GG20" s="6">
-        <f t="shared" si="91"/>
-        <v>45745.131217025308</v>
-      </c>
-      <c r="GH20" s="6">
-        <f t="shared" si="91"/>
-        <v>45287.679904855053</v>
-      </c>
-      <c r="GI20" s="6">
-        <f t="shared" si="91"/>
-        <v>44834.803105806503</v>
-      </c>
-      <c r="GJ20" s="6">
-        <f t="shared" si="91"/>
-        <v>44386.455074748439</v>
-      </c>
-      <c r="GK20" s="6">
-        <f t="shared" si="91"/>
-        <v>43942.590524000952</v>
+        <v>44572.485111776121</v>
       </c>
     </row>
     <row r="21" spans="2:193" x14ac:dyDescent="0.3">
@@ -4994,7 +4984,7 @@
         <v>12190</v>
       </c>
       <c r="AI21" s="1">
-        <f t="shared" ref="AI21" si="92">5833+860+5497</f>
+        <f t="shared" ref="AI21" si="91">5833+860+5497</f>
         <v>12190</v>
       </c>
       <c r="AJ21" s="1">
@@ -5002,12 +4992,10 @@
         <v>12122</v>
       </c>
       <c r="AK21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AL21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AN21" s="1">
         <v>680</v>
@@ -5031,52 +5019,41 @@
         <v>12488</v>
       </c>
       <c r="AU21" s="1">
-        <f t="shared" ref="AU21" si="93">5833+860+5497</f>
+        <f t="shared" ref="AU21" si="92">5833+860+5497</f>
         <v>12190</v>
       </c>
       <c r="AV21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AW21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AX21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AY21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="AZ21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BA21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BB21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BC21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BD21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BE21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
       <c r="BF21" s="1">
-        <f>12122</f>
-        <v>12122</v>
+        <v>12086</v>
       </c>
     </row>
     <row r="22" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -5084,224 +5061,224 @@
         <v>32</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:P22" si="94">C20/C21</f>
+        <f t="shared" ref="C22:P22" si="93">C20/C21</f>
         <v>7.9794117647058824</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>9.2058823529411757</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>9.9</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-4.5750000000000002</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>13.824999999999999</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>12.155882352941177</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>13.517647058823529</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>13.158823529411764</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>9.7897058823529406</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>14.627941176470589</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>10.394117647058824</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>15.69264705882353</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>10.052941176470588</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>10.233823529411765</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" ref="Q22" si="95">Q20/Q21</f>
+        <f t="shared" ref="Q22" si="94">Q20/Q21</f>
         <v>17.036982248520712</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:V22" si="96">R20/R21</f>
+        <f t="shared" ref="R22:V22" si="95">R20/R21</f>
         <v>22.132267441860463</v>
       </c>
       <c r="S22" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>26.061046511627907</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>1.352901229910209</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" ref="U22" si="97">U20/U21</f>
+        <f t="shared" ref="U22" si="96">U20/U21</f>
         <v>1.4288085716441561</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>1.5575341432128575</v>
       </c>
       <c r="W22" s="7">
-        <f t="shared" ref="W22:X22" si="98">W20/W21</f>
+        <f t="shared" ref="W22:X22" si="97">W20/W21</f>
         <v>1.2744049003644258</v>
       </c>
       <c r="X22" s="7">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>1.2407536636427077</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" ref="Y22" si="99">Y20/Y21</f>
+        <f t="shared" ref="Y22" si="98">Y20/Y21</f>
         <v>1.0785453981546096</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" ref="Z22" si="100">Z20/Z21</f>
+        <f t="shared" ref="Z22" si="99">Z20/Z21</f>
         <v>1.0563696983794681</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AB22" si="101">AA20/AA21</f>
+        <f t="shared" ref="AA22:AB22" si="100">AA20/AA21</f>
         <v>1.1670155850197721</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>1.4242071799643328</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" ref="AC22" si="102">AC20/AC21</f>
+        <f t="shared" ref="AC22" si="101">AC20/AC21</f>
         <v>1.5266341009537101</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" ref="AD22" si="103">AD20/AD21</f>
+        <f t="shared" ref="AD22" si="102">AD20/AD21</f>
         <v>1.6565502882767458</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" ref="AE22:AH22" si="104">AE20/AE21</f>
+        <f t="shared" ref="AE22:AH22" si="103">AE20/AE21</f>
         <v>1.8947789878283152</v>
       </c>
       <c r="AF22" s="7">
+        <f t="shared" si="103"/>
+        <v>1.9186839967506093</v>
+      </c>
+      <c r="AG22" s="7">
+        <f t="shared" si="103"/>
+        <v>2.1485989706723307</v>
+      </c>
+      <c r="AH22" s="7">
+        <f t="shared" si="103"/>
+        <v>2.1768662838392125</v>
+      </c>
+      <c r="AI22" s="7">
+        <f t="shared" ref="AI22:AL22" si="104">AI20/AI21</f>
+        <v>2.8334700574241181</v>
+      </c>
+      <c r="AJ22" s="7">
         <f t="shared" si="104"/>
-        <v>1.9186839967506093</v>
-      </c>
-      <c r="AG22" s="7">
+        <v>2.3260188087774294</v>
+      </c>
+      <c r="AK22" s="7">
         <f t="shared" si="104"/>
-        <v>2.1485989706723307</v>
-      </c>
-      <c r="AH22" s="7">
+        <v>2.8941750786033427</v>
+      </c>
+      <c r="AL22" s="7">
         <f t="shared" si="104"/>
-        <v>2.1768662838392125</v>
-      </c>
-      <c r="AI22" s="7">
-        <f t="shared" ref="AI22:AL22" si="105">AI20/AI21</f>
-        <v>2.8334700574241181</v>
-      </c>
-      <c r="AJ22" s="7">
+        <v>2.5563725912212476</v>
+      </c>
+      <c r="AN22" s="7">
+        <f t="shared" ref="AN22:AQ22" si="105">AN20/AN21</f>
+        <v>37.510294117647057</v>
+      </c>
+      <c r="AO22" s="7">
         <f t="shared" si="105"/>
-        <v>2.3260188087774294</v>
-      </c>
-      <c r="AK22" s="7">
+        <v>52.65735294117647</v>
+      </c>
+      <c r="AP22" s="7">
         <f t="shared" si="105"/>
-        <v>2.4968180096106254</v>
-      </c>
-      <c r="AL22" s="7">
+        <v>53.361764705882351</v>
+      </c>
+      <c r="AQ22" s="7">
         <f t="shared" si="105"/>
-        <v>2.5258438582742122</v>
-      </c>
-      <c r="AN22" s="7">
-        <f t="shared" ref="AN22:AQ22" si="106">AN20/AN21</f>
-        <v>37.510294117647057</v>
-      </c>
-      <c r="AO22" s="7">
-        <f t="shared" si="106"/>
-        <v>52.65735294117647</v>
-      </c>
-      <c r="AP22" s="7">
-        <f t="shared" si="106"/>
-        <v>53.361764705882351</v>
-      </c>
-      <c r="AQ22" s="7">
-        <f t="shared" si="106"/>
         <v>59.968934911242606</v>
       </c>
       <c r="AR22" s="7">
-        <f t="shared" ref="AR22" si="107">AR20/AR21</f>
+        <f t="shared" ref="AR22" si="106">AR20/AR21</f>
         <v>109.64825581395348</v>
       </c>
       <c r="AS22" s="7">
-        <f t="shared" ref="AS22" si="108">AS20/AS21</f>
+        <f t="shared" ref="AS22" si="107">AS20/AS21</f>
         <v>4.650073660541211</v>
       </c>
       <c r="AT22" s="7">
-        <f t="shared" ref="AT22" si="109">AT20/AT21</f>
+        <f t="shared" ref="AT22" si="108">AT20/AT21</f>
         <v>5.909272901985906</v>
       </c>
       <c r="AU22" s="7">
-        <f t="shared" ref="AU22" si="110">AU20/AU21</f>
+        <f t="shared" ref="AU22" si="109">AU20/AU21</f>
         <v>8.2131255127153402</v>
       </c>
       <c r="AV22" s="7">
-        <f t="shared" ref="AV22" si="111">AV20/AV21</f>
-        <v>10.198045467950832</v>
+        <f t="shared" ref="AV22" si="110">AV20/AV21</f>
+        <v>10.641346941709415</v>
       </c>
       <c r="AW22" s="7">
-        <f t="shared" ref="AW22" si="112">AW20/AW21</f>
-        <v>10.497107768919319</v>
+        <f t="shared" ref="AW22" si="111">AW20/AW21</f>
+        <v>10.474191141644878</v>
       </c>
       <c r="AX22" s="7">
-        <f t="shared" ref="AX22" si="113">AX20/AX21</f>
-        <v>11.284405971082755</v>
+        <f t="shared" ref="AX22" si="112">AX20/AX21</f>
+        <v>11.36862095983558</v>
       </c>
       <c r="AY22" s="7">
-        <f t="shared" ref="AY22" si="114">AY20/AY21</f>
-        <v>11.939448907851217</v>
+        <f t="shared" ref="AY22" si="113">AY20/AY21</f>
+        <v>12.065703711757022</v>
       </c>
       <c r="AZ22" s="7">
-        <f t="shared" ref="AZ22" si="115">AZ20/AZ21</f>
-        <v>12.442220812901867</v>
+        <f t="shared" ref="AZ22" si="114">AZ20/AZ21</f>
+        <v>12.625844572110228</v>
       </c>
       <c r="BA22" s="7">
-        <f t="shared" ref="BA22:BB22" si="116">BA20/BA21</f>
-        <v>12.85032493101267</v>
+        <f t="shared" ref="BA22:BB22" si="115">BA20/BA21</f>
+        <v>13.068463611624324</v>
       </c>
       <c r="BB22" s="7">
+        <f t="shared" si="115"/>
+        <v>13.450411687786845</v>
+      </c>
+      <c r="BC22" s="7">
+        <f t="shared" ref="BC22:BF22" si="116">BC20/BC21</f>
+        <v>13.769822534056257</v>
+      </c>
+      <c r="BD22" s="7">
         <f t="shared" si="116"/>
-        <v>13.222145035772154</v>
-      </c>
-      <c r="BC22" s="7">
-        <f t="shared" ref="BC22:BF22" si="117">BC20/BC21</f>
-        <v>13.533024282244723</v>
-      </c>
-      <c r="BD22" s="7">
-        <f t="shared" si="117"/>
-        <v>13.711585388613562</v>
+        <v>13.950816169748096</v>
       </c>
       <c r="BE22" s="7">
-        <f t="shared" si="117"/>
-        <v>13.893422624213425</v>
+        <f t="shared" si="116"/>
+        <v>14.135168250516365</v>
       </c>
       <c r="BF22" s="7">
-        <f t="shared" si="117"/>
-        <v>14.078620609454191</v>
+        <f t="shared" si="116"/>
+        <v>14.322966890843928</v>
       </c>
     </row>
     <row r="24" spans="2:193" x14ac:dyDescent="0.3">
@@ -5314,39 +5291,39 @@
         <v>0.14363586808394668</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24:AH24" si="118">AF3/AB3-1</f>
+        <f t="shared" ref="AF24:AH24" si="117">AF3/AB3-1</f>
         <v>0.13796096462419061</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="117"/>
         <v>0.12172352700676869</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="117"/>
         <v>0.12523948354852155</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" ref="AI24:AI29" si="119">AI3/AE3-1</f>
+        <f t="shared" ref="AI24:AI29" si="118">AI3/AE3-1</f>
         <v>9.8492070370049367E-2</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24:AJ29" si="120">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ24:AJ29" si="119">AJ3/AF3-1</f>
         <v>0.11711228844132027</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" ref="AK24:AK29" si="121">AK3/AG3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AK24:AK29" si="120">AK3/AG3-1</f>
+        <v>0.14542877391920617</v>
       </c>
       <c r="AL24" s="8">
-        <f t="shared" ref="AL24:AL29" si="122">AL3/AH3-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="AL24:AL29" si="121">AL3/AH3-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AR24" s="8">
-        <f t="shared" ref="AR24:AS24" si="123">AR3/AQ3-1</f>
+        <f t="shared" ref="AR24:AS24" si="122">AR3/AQ3-1</f>
         <v>0.43136783840402826</v>
       </c>
       <c r="AS24" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="122"/>
         <v>9.0627118985438182E-2</v>
       </c>
       <c r="AT24" s="8">
@@ -5354,51 +5331,51 @@
         <v>7.7457679285934056E-2</v>
       </c>
       <c r="AU24" s="8">
-        <f t="shared" ref="AU24:BF29" si="124">AU3/AT3-1</f>
+        <f t="shared" ref="AU24:BF29" si="123">AU3/AT3-1</f>
         <v>0.13169516605440124</v>
       </c>
       <c r="AV24" s="8">
-        <f t="shared" si="124"/>
-        <v>9.8383615032006544E-2</v>
+        <f t="shared" si="123"/>
+        <v>0.12062094868843531</v>
       </c>
       <c r="AW24" s="8">
-        <f t="shared" si="124"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="123"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AX24" s="8">
-        <f t="shared" si="124"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="123"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AY24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AZ24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF24" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5407,95 +5384,95 @@
         <v>81</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AH25" si="125">AE4/AA4-1</f>
+        <f t="shared" ref="AE25:AH25" si="124">AE4/AA4-1</f>
         <v>0.20872553414014638</v>
       </c>
       <c r="AF25" s="8">
+        <f t="shared" si="124"/>
+        <v>0.13020221787345077</v>
+      </c>
+      <c r="AG25" s="8">
+        <f t="shared" si="124"/>
+        <v>0.12185613682092544</v>
+      </c>
+      <c r="AH25" s="8">
+        <f t="shared" si="124"/>
+        <v>0.1383695652173913</v>
+      </c>
+      <c r="AI25" s="8">
+        <f t="shared" si="118"/>
+        <v>0.10346106304079106</v>
+      </c>
+      <c r="AJ25" s="8">
+        <f t="shared" si="119"/>
+        <v>0.1307861018123051</v>
+      </c>
+      <c r="AK25" s="8">
+        <f t="shared" si="120"/>
+        <v>0.15020737585472488</v>
+      </c>
+      <c r="AL25" s="8">
+        <f t="shared" si="121"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AR25" s="8">
+        <f t="shared" ref="AR25:AS25" si="125">AR4/AQ4-1</f>
+        <v>0.45888124620675708</v>
+      </c>
+      <c r="AS25" s="8">
         <f t="shared" si="125"/>
-        <v>0.13020221787345077</v>
-      </c>
-      <c r="AG25" s="8">
-        <f t="shared" si="125"/>
-        <v>0.12185613682092544</v>
-      </c>
-      <c r="AH25" s="8">
-        <f t="shared" si="125"/>
-        <v>0.1383695652173913</v>
-      </c>
-      <c r="AI25" s="8">
-        <f t="shared" si="119"/>
-        <v>0.10346106304079106</v>
-      </c>
-      <c r="AJ25" s="8">
-        <f t="shared" si="120"/>
-        <v>0.1307861018123051</v>
-      </c>
-      <c r="AK25" s="8">
-        <f t="shared" si="121"/>
-        <v>0.1100000000000001</v>
-      </c>
-      <c r="AL25" s="8">
-        <f t="shared" si="122"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="AR25" s="8">
-        <f t="shared" ref="AR25:AS25" si="126">AR4/AQ4-1</f>
-        <v>0.45888124620675708</v>
-      </c>
-      <c r="AS25" s="8">
-        <f t="shared" si="126"/>
         <v>1.3797885248743258E-2</v>
       </c>
       <c r="AT25" s="8">
-        <f t="shared" ref="AT25" si="127">AT4/AS4-1</f>
+        <f t="shared" ref="AT25" si="126">AT4/AS4-1</f>
         <v>7.7522825975447018E-2</v>
       </c>
       <c r="AU25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.14715963186290071</v>
       </c>
       <c r="AV25" s="8">
-        <f t="shared" si="124"/>
-        <v>0.10772346252801079</v>
+        <f t="shared" si="123"/>
+        <v>0.12633856198301396</v>
       </c>
       <c r="AW25" s="8">
-        <f t="shared" si="124"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="123"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AX25" s="8">
-        <f t="shared" si="124"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="123"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AY25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AZ25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5504,95 +5481,95 @@
         <v>82</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AH26" si="128">AE5/AA5-1</f>
+        <f t="shared" ref="AE26:AH26" si="127">AE5/AA5-1</f>
         <v>-1.1072572038420492E-2</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="127"/>
         <v>-5.1719745222929991E-2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="127"/>
         <v>-1.5777806754466051E-2</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="127"/>
         <v>-4.1340243461492121E-2</v>
       </c>
       <c r="AI26" s="8">
+        <f t="shared" si="118"/>
+        <v>-2.1179009847565045E-2</v>
+      </c>
+      <c r="AJ26" s="8">
         <f t="shared" si="119"/>
-        <v>-2.1179009847565045E-2</v>
-      </c>
-      <c r="AJ26" s="8">
+        <v>-1.2090274046211769E-2</v>
+      </c>
+      <c r="AK26" s="8">
         <f t="shared" si="120"/>
-        <v>-1.2090274046211769E-2</v>
-      </c>
-      <c r="AK26" s="8">
+        <v>-2.5702172760996289E-2</v>
+      </c>
+      <c r="AL26" s="8">
         <f t="shared" si="121"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AL26" s="8">
-        <f t="shared" si="122"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
       <c r="AR26" s="8">
-        <f t="shared" ref="AR26:AS26" si="129">AR5/AQ5-1</f>
+        <f t="shared" ref="AR26:AS26" si="128">AR5/AQ5-1</f>
         <v>0.37293200519705505</v>
       </c>
       <c r="AS26" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="128"/>
         <v>3.4036781174095365E-2</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" ref="AT26" si="130">AT5/AS5-1</f>
+        <f t="shared" ref="AT26" si="129">AT5/AS5-1</f>
         <v>-4.4783404514948111E-2</v>
       </c>
       <c r="AU26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>-3.0435615738375055E-2</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" si="124"/>
-        <v>-1.834843044896084E-2</v>
+        <f t="shared" si="123"/>
+        <v>-1.9766131954280453E-2</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF26" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5601,95 +5578,95 @@
         <v>83</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AH27" si="131">AE6/AA6-1</f>
+        <f t="shared" ref="AE27:AH27" si="130">AE6/AA6-1</f>
         <v>0.17887494941319293</v>
       </c>
       <c r="AF27" s="8">
+        <f t="shared" si="130"/>
+        <v>0.14369933677229185</v>
+      </c>
+      <c r="AG27" s="8">
+        <f t="shared" si="130"/>
+        <v>0.2778510612783307</v>
+      </c>
+      <c r="AH27" s="8">
+        <f t="shared" si="130"/>
+        <v>7.772836761163604E-2</v>
+      </c>
+      <c r="AI27" s="8">
+        <f t="shared" si="118"/>
+        <v>0.18766449250486317</v>
+      </c>
+      <c r="AJ27" s="8">
+        <f t="shared" si="119"/>
+        <v>0.20307130584192445</v>
+      </c>
+      <c r="AK27" s="8">
+        <f t="shared" si="120"/>
+        <v>0.20777027027027017</v>
+      </c>
+      <c r="AL27" s="8">
+        <f t="shared" si="121"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="AR27" s="8">
+        <f t="shared" ref="AR27:AS27" si="131">AR6/AQ6-1</f>
+        <v>0.29114273870388274</v>
+      </c>
+      <c r="AS27" s="8">
         <f t="shared" si="131"/>
-        <v>0.14369933677229185</v>
-      </c>
-      <c r="AG27" s="8">
-        <f t="shared" si="131"/>
-        <v>0.2778510612783307</v>
-      </c>
-      <c r="AH27" s="8">
-        <f t="shared" si="131"/>
-        <v>7.772836761163604E-2</v>
-      </c>
-      <c r="AI27" s="8">
-        <f t="shared" si="119"/>
-        <v>0.18766449250486317</v>
-      </c>
-      <c r="AJ27" s="8">
-        <f t="shared" si="120"/>
-        <v>0.20307130584192445</v>
-      </c>
-      <c r="AK27" s="8">
-        <f t="shared" si="121"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AL27" s="8">
-        <f t="shared" si="122"/>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="AR27" s="8">
-        <f t="shared" ref="AR27:AS27" si="132">AR6/AQ6-1</f>
-        <v>0.29114273870388274</v>
-      </c>
-      <c r="AS27" s="8">
-        <f t="shared" si="132"/>
         <v>3.6494006849315141E-2</v>
       </c>
       <c r="AT27" s="8">
-        <f t="shared" ref="AT27" si="133">AT6/AS6-1</f>
+        <f t="shared" ref="AT27" si="132">AT6/AS6-1</f>
         <v>0.19387368783341929</v>
       </c>
       <c r="AU27" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.16293819188191883</v>
       </c>
       <c r="AV27" s="8">
-        <f t="shared" si="124"/>
-        <v>0.16464278631631135</v>
+        <f t="shared" si="123"/>
+        <v>0.19720550322260766</v>
       </c>
       <c r="AW27" s="8">
-        <f t="shared" si="124"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="123"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AX27" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AY27" s="8">
+        <f t="shared" si="123"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AZ27" s="8">
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AY27" s="8">
-        <f t="shared" si="124"/>
+      <c r="BA27" s="8">
+        <f t="shared" si="123"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AZ27" s="8">
-        <f t="shared" si="124"/>
+      <c r="BB27" s="8">
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA27" s="8">
-        <f t="shared" si="124"/>
+      <c r="BC27" s="8">
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB27" s="8">
-        <f t="shared" si="124"/>
+      <c r="BD27" s="8">
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC27" s="8">
-        <f t="shared" si="124"/>
+      <c r="BE27" s="8">
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BD27" s="8">
-        <f t="shared" si="124"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BE27" s="8">
-        <f t="shared" si="124"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="BF27" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -5698,95 +5675,95 @@
         <v>84</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" ref="AE28:AH28" si="134">AE7/AA7-1</f>
+        <f t="shared" ref="AE28:AH28" si="133">AE7/AA7-1</f>
         <v>0.28441105446740012</v>
       </c>
       <c r="AF28" s="8">
+        <f t="shared" si="133"/>
+        <v>0.28838251774374291</v>
+      </c>
+      <c r="AG28" s="8">
+        <f t="shared" si="133"/>
+        <v>0.34978004993460954</v>
+      </c>
+      <c r="AH28" s="8">
+        <f t="shared" si="133"/>
+        <v>0.3005874673629243</v>
+      </c>
+      <c r="AI28" s="8">
+        <f t="shared" si="118"/>
+        <v>0.28055149362857734</v>
+      </c>
+      <c r="AJ28" s="8">
+        <f t="shared" si="119"/>
+        <v>0.31671015753358467</v>
+      </c>
+      <c r="AK28" s="8">
+        <f t="shared" si="120"/>
+        <v>0.33506562142165075</v>
+      </c>
+      <c r="AL28" s="8">
+        <f t="shared" si="121"/>
+        <v>0.32000000000000006</v>
+      </c>
+      <c r="AR28" s="8">
+        <f t="shared" ref="AR28:AS28" si="134">AR7/AQ7-1</f>
+        <v>0.47070985527222597</v>
+      </c>
+      <c r="AS28" s="8">
         <f t="shared" si="134"/>
-        <v>0.28838251774374291</v>
-      </c>
-      <c r="AG28" s="8">
-        <f t="shared" si="134"/>
-        <v>0.34978004993460954</v>
-      </c>
-      <c r="AH28" s="8">
-        <f t="shared" si="134"/>
-        <v>0.3005874673629243</v>
-      </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="119"/>
-        <v>0.28055149362857734</v>
-      </c>
-      <c r="AJ28" s="8">
-        <f t="shared" si="120"/>
-        <v>0.31671015753358467</v>
-      </c>
-      <c r="AK28" s="8">
-        <f t="shared" si="121"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AL28" s="8">
-        <f t="shared" si="122"/>
-        <v>0.26</v>
-      </c>
-      <c r="AR28" s="8">
-        <f t="shared" ref="AR28:AS28" si="135">AR7/AQ7-1</f>
-        <v>0.47070985527222597</v>
-      </c>
-      <c r="AS28" s="8">
-        <f t="shared" si="135"/>
         <v>0.36832239925023424</v>
       </c>
       <c r="AT28" s="8">
-        <f t="shared" ref="AT28" si="136">AT7/AS7-1</f>
+        <f t="shared" ref="AT28" si="135">AT7/AS7-1</f>
         <v>0.25905631659056327</v>
       </c>
       <c r="AU28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.30648573500967125</v>
       </c>
       <c r="AV28" s="8">
-        <f t="shared" si="124"/>
-        <v>0.28337782507113274</v>
+        <f t="shared" si="123"/>
+        <v>0.31443244118531544</v>
       </c>
       <c r="AW28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AX28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AY28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AZ28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="BA28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BB28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF28" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5795,95 +5772,95 @@
         <v>85</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" ref="AE29:AH29" si="137">AE8/AA8-1</f>
+        <f t="shared" ref="AE29:AH29" si="136">AE8/AA8-1</f>
         <v>0.71875</v>
       </c>
       <c r="AF29" s="8">
+        <f t="shared" si="136"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="AG29" s="8">
+        <f t="shared" si="136"/>
+        <v>0.30639730639730645</v>
+      </c>
+      <c r="AH29" s="8">
+        <f t="shared" si="136"/>
+        <v>-0.39117199391171997</v>
+      </c>
+      <c r="AI29" s="8">
+        <f t="shared" si="118"/>
+        <v>-9.0909090909090939E-2</v>
+      </c>
+      <c r="AJ29" s="8">
+        <f t="shared" si="119"/>
+        <v>2.1917808219177992E-2</v>
+      </c>
+      <c r="AK29" s="8">
+        <f t="shared" si="120"/>
+        <v>-0.11340206185567014</v>
+      </c>
+      <c r="AL29" s="8">
+        <f t="shared" si="121"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AR29" s="8">
+        <f t="shared" ref="AR29:AS29" si="137">AR8/AQ8-1</f>
+        <v>0.14611872146118721</v>
+      </c>
+      <c r="AS29" s="8">
         <f t="shared" si="137"/>
-        <v>0.2807017543859649</v>
-      </c>
-      <c r="AG29" s="8">
-        <f t="shared" si="137"/>
-        <v>0.30639730639730645</v>
-      </c>
-      <c r="AH29" s="8">
-        <f t="shared" si="137"/>
-        <v>-0.39117199391171997</v>
-      </c>
-      <c r="AI29" s="8">
-        <f t="shared" si="119"/>
-        <v>-9.0909090909090939E-2</v>
-      </c>
-      <c r="AJ29" s="8">
-        <f t="shared" si="120"/>
-        <v>2.1917808219177992E-2</v>
-      </c>
-      <c r="AK29" s="8">
-        <f t="shared" si="121"/>
+        <v>0.41832669322709171</v>
+      </c>
+      <c r="AT29" s="8">
+        <f t="shared" ref="AT29" si="138">AT8/AS8-1</f>
+        <v>0.4297752808988764</v>
+      </c>
+      <c r="AU29" s="8">
+        <f t="shared" si="123"/>
+        <v>7.9240340537000575E-2</v>
+      </c>
+      <c r="AV29" s="8">
+        <f t="shared" si="123"/>
+        <v>-3.7014563106796072E-2</v>
+      </c>
+      <c r="AW29" s="8">
+        <f t="shared" si="123"/>
+        <v>0.25</v>
+      </c>
+      <c r="AX29" s="8">
+        <f t="shared" si="123"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AY29" s="8">
+        <f t="shared" si="123"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AZ29" s="8">
+        <f t="shared" si="123"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AL29" s="8">
-        <f t="shared" si="122"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AR29" s="8">
-        <f t="shared" ref="AR29:AS29" si="138">AR8/AQ8-1</f>
-        <v>0.14611872146118721</v>
-      </c>
-      <c r="AS29" s="8">
-        <f t="shared" si="138"/>
-        <v>0.41832669322709171</v>
-      </c>
-      <c r="AT29" s="8">
-        <f t="shared" ref="AT29" si="139">AT8/AS8-1</f>
-        <v>0.4297752808988764</v>
-      </c>
-      <c r="AU29" s="8">
-        <f t="shared" si="124"/>
-        <v>7.9240340537000575E-2</v>
-      </c>
-      <c r="AV29" s="8">
-        <f t="shared" si="124"/>
-        <v>2.5364077669902896E-2</v>
-      </c>
-      <c r="AW29" s="8">
-        <f t="shared" si="124"/>
-        <v>0.25</v>
-      </c>
-      <c r="AX29" s="8">
-        <f t="shared" si="124"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AY29" s="8">
-        <f t="shared" si="124"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AZ29" s="8">
-        <f t="shared" si="124"/>
-        <v>0.10000000000000009</v>
-      </c>
       <c r="BA29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BD29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BE29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BF29" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -5896,39 +5873,39 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="8">
-        <f t="shared" ref="G30" si="140">G10/C10-1</f>
+        <f t="shared" ref="G30" si="139">G10/C10-1</f>
         <v>0.25842424242424245</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" ref="H30" si="141">H10/D10-1</f>
+        <f t="shared" ref="H30" si="140">H10/D10-1</f>
         <v>0.25555555555555554</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" ref="I30" si="142">I10/E10-1</f>
+        <f t="shared" ref="I30" si="141">I10/E10-1</f>
         <v>0.21489269768111763</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" ref="J30" si="143">J10/F10-1</f>
+        <f t="shared" ref="J30" si="142">J10/F10-1</f>
         <v>0.21854058078927774</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" ref="K30:O30" si="144">K10/G10-1</f>
+        <f t="shared" ref="K30:O30" si="143">K10/G10-1</f>
         <v>0.16673088036987083</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>0.19251615273907574</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>0.2003260225251926</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>0.17310825949689379</v>
       </c>
       <c r="O30" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="143"/>
         <v>0.13263986350752632</v>
       </c>
       <c r="P30" s="8">
@@ -5936,164 +5913,164 @@
         <v>-1.6613599013968749E-2</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" ref="Q30:R30" si="145">Q10/M10-1</f>
+        <f t="shared" ref="Q30:R30" si="144">Q10/M10-1</f>
         <v>0.14010222474628997</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="145"/>
+        <f t="shared" si="144"/>
         <v>0.23489962018448174</v>
       </c>
       <c r="S30" s="8">
-        <f t="shared" ref="S30" si="146">S10/O10-1</f>
+        <f t="shared" ref="S30" si="145">S10/O10-1</f>
         <v>0.34391020189994892</v>
       </c>
       <c r="T30" s="8">
-        <f t="shared" ref="T30" si="147">T10/P10-1</f>
+        <f t="shared" ref="T30" si="146">T10/P10-1</f>
         <v>0.44434289892158652</v>
       </c>
       <c r="U30" s="8">
-        <f t="shared" ref="U30" si="148">U10/Q10-1</f>
+        <f t="shared" ref="U30" si="147">U10/Q10-1</f>
         <v>0.41030472353973102</v>
       </c>
       <c r="V30" s="8">
-        <f t="shared" ref="V30" si="149">V10/R10-1</f>
+        <f t="shared" ref="V30" si="148">V10/R10-1</f>
         <v>0.32386024113325607</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" ref="W30" si="150">W10/S10-1</f>
+        <f t="shared" ref="W30" si="149">W10/S10-1</f>
         <v>0.22954405756228069</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" ref="X30" si="151">X10/T10-1</f>
+        <f t="shared" ref="X30" si="150">X10/T10-1</f>
         <v>0.25980764363452291</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" ref="Y30" si="152">Y10/U10-1</f>
+        <f t="shared" ref="Y30" si="151">Y10/U10-1</f>
         <v>6.1027672840074931E-2</v>
       </c>
       <c r="Z30" s="8">
-        <f t="shared" ref="Z30" si="153">Z10/V10-1</f>
+        <f t="shared" ref="Z30" si="152">Z10/V10-1</f>
         <v>9.5984069034185104E-3</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" ref="AA30" si="154">AA10/W10-1</f>
+        <f t="shared" ref="AA30" si="153">AA10/W10-1</f>
         <v>2.6113422828660138E-2</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" ref="AB30" si="155">AB10/X10-1</f>
+        <f t="shared" ref="AB30" si="154">AB10/X10-1</f>
         <v>7.0589079428858392E-2</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" ref="AC30" si="156">AC10/Y10-1</f>
+        <f t="shared" ref="AC30" si="155">AC10/Y10-1</f>
         <v>0.11001273664100042</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" ref="AD30" si="157">AD10/Z10-1</f>
+        <f t="shared" ref="AD30" si="156">AD10/Z10-1</f>
         <v>0.13494108983799702</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" ref="AE30" si="158">AE10/AA10-1</f>
+        <f t="shared" ref="AE30" si="157">AE10/AA10-1</f>
         <v>0.15406880937710454</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" ref="AF30" si="159">AF10/AB10-1</f>
+        <f t="shared" ref="AF30" si="158">AF10/AB10-1</f>
         <v>0.13589083695244231</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" ref="AG30" si="160">AG10/AC10-1</f>
+        <f t="shared" ref="AG30" si="159">AG10/AC10-1</f>
         <v>0.15092642092498654</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" ref="AH30" si="161">AH10/AD10-1</f>
+        <f t="shared" ref="AH30" si="160">AH10/AD10-1</f>
         <v>0.11770362646275045</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" ref="AI30" si="162">AI10/AE10-1</f>
+        <f t="shared" ref="AI30" si="161">AI10/AE10-1</f>
         <v>0.12037646357665222</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" ref="AJ30" si="163">AJ10/AF10-1</f>
+        <f t="shared" ref="AJ30" si="162">AJ10/AF10-1</f>
         <v>0.13790092280097244</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" ref="AK30" si="164">AK10/AG10-1</f>
-        <v>0.1202914986178456</v>
+        <f t="shared" ref="AK30" si="163">AK10/AG10-1</f>
+        <v>0.1594915484660353</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" ref="AL30" si="165">AL10/AH10-1</f>
-        <v>0.10155386704537217</v>
+        <f t="shared" ref="AL30" si="164">AL10/AH10-1</f>
+        <v>0.14167898495889886</v>
       </c>
       <c r="AO30" s="8">
         <f>AO10/AN10-1</f>
         <v>0.23522985807663144</v>
       </c>
       <c r="AP30" s="8">
-        <f t="shared" ref="AP30:BB30" si="166">AP10/AO10-1</f>
+        <f t="shared" ref="AP30:BB30" si="165">AP10/AO10-1</f>
         <v>0.18300089899794614</v>
       </c>
       <c r="AQ30" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>0.12770532012826141</v>
       </c>
       <c r="AR30" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>0.37552800407610931</v>
       </c>
       <c r="AS30" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>0.12651799690127485</v>
       </c>
       <c r="AT30" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>8.6827702272695095E-2</v>
       </c>
       <c r="AU30" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>0.13866243322901561</v>
       </c>
       <c r="AV30" s="8">
-        <f t="shared" si="166"/>
-        <v>0.11941011605117446</v>
+        <f t="shared" si="165"/>
+        <v>0.14035458176436633</v>
       </c>
       <c r="AW30" s="8">
-        <f t="shared" si="166"/>
-        <v>8.6986564200959959E-2</v>
+        <f t="shared" si="165"/>
+        <v>0.10294250883445422</v>
       </c>
       <c r="AX30" s="8">
-        <f t="shared" si="166"/>
-        <v>6.3530869939751655E-2</v>
+        <f t="shared" si="165"/>
+        <v>7.3615075872781155E-2</v>
       </c>
       <c r="AY30" s="8">
-        <f t="shared" si="166"/>
-        <v>4.8732237712674875E-2</v>
+        <f t="shared" si="165"/>
+        <v>5.1053872147143631E-2</v>
       </c>
       <c r="AZ30" s="8">
-        <f t="shared" si="166"/>
-        <v>3.7995706978080523E-2</v>
+        <f t="shared" si="165"/>
+        <v>4.0326140234814956E-2</v>
       </c>
       <c r="BA30" s="8">
-        <f t="shared" si="166"/>
-        <v>2.9090155802546924E-2</v>
+        <f t="shared" si="165"/>
+        <v>3.0268007675239961E-2</v>
       </c>
       <c r="BB30" s="8">
-        <f t="shared" si="166"/>
-        <v>2.6451086908932941E-2</v>
+        <f t="shared" si="165"/>
+        <v>2.642436679095006E-2</v>
       </c>
       <c r="BC30" s="8">
-        <f t="shared" ref="BC30" si="167">BC10/BB10-1</f>
-        <v>2.2713092396257073E-2</v>
+        <f t="shared" ref="BC30" si="166">BC10/BB10-1</f>
+        <v>2.2775780417806368E-2</v>
       </c>
       <c r="BD30" s="8">
-        <f t="shared" ref="BD30" si="168">BD10/BC10-1</f>
-        <v>1.557419382221692E-2</v>
+        <f t="shared" ref="BD30" si="167">BD10/BC10-1</f>
+        <v>1.5683825775720805E-2</v>
       </c>
       <c r="BE30" s="8">
-        <f t="shared" ref="BE30" si="169">BE10/BD10-1</f>
-        <v>1.5629988909741321E-2</v>
+        <f t="shared" ref="BE30" si="168">BE10/BD10-1</f>
+        <v>1.5740619450484994E-2</v>
       </c>
       <c r="BF30" s="8">
-        <f t="shared" ref="BF30" si="170">BF10/BE10-1</f>
-        <v>1.5686324382289119E-2</v>
+        <f t="shared" ref="BF30" si="169">BF10/BE10-1</f>
+        <v>1.5797935425830412E-2</v>
       </c>
     </row>
     <row r="31" spans="2:193" x14ac:dyDescent="0.3">
@@ -6101,55 +6078,55 @@
         <v>34</v>
       </c>
       <c r="C31" s="8">
-        <f t="shared" ref="C31:F31" si="171">C12/C10</f>
+        <f t="shared" ref="C31:F31" si="170">C12/C10</f>
         <v>0.60424242424242425</v>
       </c>
       <c r="D31" s="8">
+        <f t="shared" si="170"/>
+        <v>0.60119184928873515</v>
+      </c>
+      <c r="E31" s="8">
+        <f t="shared" si="170"/>
+        <v>0.59858850640933314</v>
+      </c>
+      <c r="F31" s="8">
+        <f t="shared" si="170"/>
+        <v>0.55736535120377262</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" ref="G31:O31" si="171">G12/G10</f>
+        <v>0.56761702947408976</v>
+      </c>
+      <c r="H31" s="8">
         <f t="shared" si="171"/>
-        <v>0.60119184928873515</v>
-      </c>
-      <c r="E31" s="8">
+        <v>0.57488440456869894</v>
+      </c>
+      <c r="I31" s="8">
         <f t="shared" si="171"/>
-        <v>0.59858850640933314</v>
-      </c>
-      <c r="F31" s="8">
+        <v>0.57673384706579722</v>
+      </c>
+      <c r="J31" s="8">
         <f t="shared" si="171"/>
-        <v>0.55736535120377262</v>
-      </c>
-      <c r="G31" s="8">
-        <f t="shared" ref="G31:O31" si="172">G12/G10</f>
-        <v>0.56761702947408976</v>
-      </c>
-      <c r="H31" s="8">
-        <f t="shared" si="172"/>
-        <v>0.57488440456869894</v>
-      </c>
-      <c r="I31" s="8">
-        <f t="shared" si="172"/>
-        <v>0.57673384706579722</v>
-      </c>
-      <c r="J31" s="8">
-        <f t="shared" si="172"/>
         <v>0.54379264690905382</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.55937147417375277</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.55587510271158591</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.56621151139534309</v>
       </c>
       <c r="N31" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.54378730330982095</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.53881289632887097</v>
       </c>
       <c r="P31" s="8">
@@ -6157,167 +6134,167 @@
         <v>0.51554952085019712</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" ref="Q31:R31" si="173">Q12/Q10</f>
+        <f t="shared" ref="Q31:R31" si="172">Q12/Q10</f>
         <v>0.54265479825872265</v>
       </c>
       <c r="R31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.54163590987380927</v>
+      </c>
+      <c r="S31" s="8">
+        <f t="shared" ref="S31:V31" si="173">S12/S10</f>
+        <v>0.56425136493473627</v>
+      </c>
+      <c r="T31" s="8">
         <f t="shared" si="173"/>
-        <v>0.54163590987380927</v>
-      </c>
-      <c r="S31" s="8">
-        <f t="shared" ref="S31:V31" si="174">S12/S10</f>
         <v>0.56425136493473627</v>
       </c>
-      <c r="T31" s="8">
+      <c r="U31" s="8">
+        <f t="shared" si="173"/>
+        <v>0.57583156730857832</v>
+      </c>
+      <c r="V31" s="8">
+        <f t="shared" si="173"/>
+        <v>0.56205774975107869</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" ref="W31:AE31" si="174">W12/W10</f>
+        <v>0.5647909896928438</v>
+      </c>
+      <c r="X31" s="8">
         <f t="shared" si="174"/>
-        <v>0.56425136493473627</v>
-      </c>
-      <c r="U31" s="8">
+        <v>0.56799885197675248</v>
+      </c>
+      <c r="Y31" s="8">
         <f t="shared" si="174"/>
-        <v>0.57583156730857832</v>
-      </c>
-      <c r="V31" s="8">
+        <v>0.54903606785156023</v>
+      </c>
+      <c r="Z31" s="8">
         <f t="shared" si="174"/>
-        <v>0.56205774975107869</v>
-      </c>
-      <c r="W31" s="8">
-        <f t="shared" ref="W31:AE31" si="175">W12/W10</f>
-        <v>0.5647909896928438</v>
-      </c>
-      <c r="X31" s="8">
+        <v>0.53526719966337055</v>
+      </c>
+      <c r="AA31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.56135096794531936</v>
+      </c>
+      <c r="AB31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.5721945204010509</v>
+      </c>
+      <c r="AC31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.56672708069836886</v>
+      </c>
+      <c r="AD31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.56465067778936395</v>
+      </c>
+      <c r="AE31" s="8">
+        <f t="shared" si="174"/>
+        <v>0.58142018152696207</v>
+      </c>
+      <c r="AF31" s="8">
+        <f t="shared" ref="AF31:AH31" si="175">AF12/AF10</f>
+        <v>0.58099879634655782</v>
+      </c>
+      <c r="AG31" s="8">
         <f t="shared" si="175"/>
-        <v>0.56799885197675248</v>
-      </c>
-      <c r="Y31" s="8">
+        <v>0.58678116644763678</v>
+      </c>
+      <c r="AH31" s="8">
         <f t="shared" si="175"/>
-        <v>0.54903606785156023</v>
-      </c>
-      <c r="Z31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.53526719966337055</v>
-      </c>
-      <c r="AA31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.56135096794531936</v>
-      </c>
-      <c r="AB31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.5721945204010509</v>
-      </c>
-      <c r="AC31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.56672708069836886</v>
-      </c>
-      <c r="AD31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.56465067778936395</v>
-      </c>
-      <c r="AE31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.58142018152696207</v>
-      </c>
-      <c r="AF31" s="8">
-        <f t="shared" ref="AF31:AH31" si="176">AF12/AF10</f>
-        <v>0.58099879634655782</v>
-      </c>
-      <c r="AG31" s="8">
+        <v>0.5790046543449191</v>
+      </c>
+      <c r="AI31" s="8">
+        <f t="shared" ref="AI31:AL31" si="176">AI12/AI10</f>
+        <v>0.5970365937451515</v>
+      </c>
+      <c r="AJ31" s="8">
         <f t="shared" si="176"/>
-        <v>0.58678116644763678</v>
-      </c>
-      <c r="AH31" s="8">
+        <v>0.59514871199236741</v>
+      </c>
+      <c r="AK31" s="8">
         <f t="shared" si="176"/>
-        <v>0.5790046543449191</v>
-      </c>
-      <c r="AI31" s="8">
-        <f t="shared" ref="AI31:AL31" si="177">AI12/AI10</f>
-        <v>0.5970365937451515</v>
-      </c>
-      <c r="AJ31" s="8">
+        <v>0.59579270318331934</v>
+      </c>
+      <c r="AL31" s="8">
+        <f t="shared" si="176"/>
+        <v>0.59999999999999987</v>
+      </c>
+      <c r="AN31" s="8">
+        <f t="shared" ref="AN31:BA31" si="177">AN12/AN10</f>
+        <v>0.58846737207034772</v>
+      </c>
+      <c r="AO31" s="8">
         <f t="shared" si="177"/>
-        <v>0.59514871199236741</v>
-      </c>
-      <c r="AK31" s="8">
+        <v>0.5647607422945643</v>
+      </c>
+      <c r="AP31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.5558054331910266</v>
+      </c>
+      <c r="AQ31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.53578374706207854</v>
+      </c>
+      <c r="AR31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.56659669973832105</v>
+      </c>
+      <c r="AS31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.55379442503783116</v>
+      </c>
+      <c r="AT31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.56625047984020505</v>
+      </c>
+      <c r="AU31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.58200435406179107</v>
+      </c>
+      <c r="AV31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.59707925420417152</v>
+      </c>
+      <c r="AW31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.59999999999999987</v>
+      </c>
+      <c r="AX31" s="8">
         <f t="shared" si="177"/>
         <v>0.6</v>
       </c>
-      <c r="AL31" s="8">
+      <c r="AY31" s="8">
         <f t="shared" si="177"/>
         <v>0.6</v>
       </c>
-      <c r="AN31" s="8">
-        <f t="shared" ref="AN31:BA31" si="178">AN12/AN10</f>
-        <v>0.58846737207034772</v>
-      </c>
-      <c r="AO31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.5647607422945643</v>
-      </c>
-      <c r="AP31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.5558054331910266</v>
-      </c>
-      <c r="AQ31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.53578374706207854</v>
-      </c>
-      <c r="AR31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.56659669973832105</v>
-      </c>
-      <c r="AS31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.55379442503783116</v>
-      </c>
-      <c r="AT31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.56625047984020505</v>
-      </c>
-      <c r="AU31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.58200435406179107</v>
-      </c>
-      <c r="AV31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.59812359797841674</v>
-      </c>
-      <c r="AW31" s="8">
+      <c r="AZ31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.6</v>
+      </c>
+      <c r="BA31" s="8">
+        <f t="shared" si="177"/>
+        <v>0.6</v>
+      </c>
+      <c r="BB31" s="8">
+        <f t="shared" ref="BB31:BF31" si="178">BB12/BB10</f>
+        <v>0.6</v>
+      </c>
+      <c r="BC31" s="8">
         <f t="shared" si="178"/>
         <v>0.6</v>
       </c>
-      <c r="AX31" s="8">
+      <c r="BD31" s="8">
         <f t="shared" si="178"/>
         <v>0.6</v>
       </c>
-      <c r="AY31" s="8">
+      <c r="BE31" s="8">
         <f t="shared" si="178"/>
         <v>0.6</v>
       </c>
-      <c r="AZ31" s="8">
+      <c r="BF31" s="8">
         <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
-      <c r="BA31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
-      <c r="BB31" s="8">
-        <f t="shared" ref="BB31:BF31" si="179">BB12/BB10</f>
-        <v>0.6</v>
-      </c>
-      <c r="BC31" s="8">
-        <f t="shared" si="179"/>
-        <v>0.6</v>
-      </c>
-      <c r="BD31" s="8">
-        <f t="shared" si="179"/>
-        <v>0.6</v>
-      </c>
-      <c r="BE31" s="8">
-        <f t="shared" si="179"/>
-        <v>0.6</v>
-      </c>
-      <c r="BF31" s="8">
-        <f t="shared" si="179"/>
         <v>0.6</v>
       </c>
     </row>
@@ -6326,19 +6303,19 @@
         <v>35</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:F32" si="180">C16/C10</f>
+        <f t="shared" ref="C32:F32" si="179">C16/C10</f>
         <v>0.26537373737373737</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.26405228758169935</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.28021028373901774</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.23495284189625218</v>
       </c>
       <c r="G32" s="8">
@@ -6346,204 +6323,204 @@
         <v>0.24507159827907277</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" ref="H32:R32" si="181">H16/H10</f>
+        <f t="shared" ref="H32:R32" si="180">H16/H10</f>
         <v>0.24852252197078728</v>
       </c>
       <c r="I32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.25563129816241847</v>
+      </c>
+      <c r="J32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.20931357572054179</v>
+      </c>
+      <c r="K32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.18184319876716476</v>
+      </c>
+      <c r="L32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.23572308956450289</v>
+      </c>
+      <c r="M32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.22659818760957059</v>
+      </c>
+      <c r="N32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.20110689093868692</v>
+      </c>
+      <c r="O32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.1938093734055735</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.1666710186176463</v>
+      </c>
+      <c r="Q32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.24284755159941956</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.27507118000632713</v>
+      </c>
+      <c r="S32" s="8">
+        <f t="shared" ref="S32:V32" si="181">S16/S10</f>
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="T32" s="8">
         <f t="shared" si="181"/>
-        <v>0.25563129816241847</v>
-      </c>
-      <c r="J32" s="8">
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="U32" s="8">
         <f t="shared" si="181"/>
-        <v>0.20931357572054179</v>
-      </c>
-      <c r="K32" s="8">
+        <v>0.32296753585798088</v>
+      </c>
+      <c r="V32" s="8">
         <f t="shared" si="181"/>
-        <v>0.18184319876716476</v>
-      </c>
-      <c r="L32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.23572308956450289</v>
-      </c>
-      <c r="M32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.22659818760957059</v>
-      </c>
-      <c r="N32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.20110689093868692</v>
-      </c>
-      <c r="O32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.1938093734055735</v>
-      </c>
-      <c r="P32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.1666710186176463</v>
-      </c>
-      <c r="Q32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.24284755159941956</v>
-      </c>
-      <c r="R32" s="8">
-        <f t="shared" si="181"/>
-        <v>0.27507118000632713</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" ref="S32:V32" si="182">S16/S10</f>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="T32" s="8">
+        <v>0.29054098904746101</v>
+      </c>
+      <c r="W32" s="8">
+        <f t="shared" ref="W32:AE32" si="182">W16/W10</f>
+        <v>0.29545220626075192</v>
+      </c>
+      <c r="X32" s="8">
         <f t="shared" si="182"/>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="U32" s="8">
+        <v>0.279156202913109</v>
+      </c>
+      <c r="Y32" s="8">
         <f t="shared" si="182"/>
-        <v>0.32296753585798088</v>
-      </c>
-      <c r="V32" s="8">
+        <v>0.24800266311584554</v>
+      </c>
+      <c r="Z32" s="8">
         <f t="shared" si="182"/>
-        <v>0.29054098904746101</v>
-      </c>
-      <c r="W32" s="8">
-        <f t="shared" ref="W32:AE32" si="183">W16/W10</f>
-        <v>0.29545220626075192</v>
-      </c>
-      <c r="X32" s="8">
+        <v>0.23879654954765411</v>
+      </c>
+      <c r="AA32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.24954504420594092</v>
+      </c>
+      <c r="AB32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.29271888906761029</v>
+      </c>
+      <c r="AC32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.27829136948613303</v>
+      </c>
+      <c r="AD32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.27455683003128256</v>
+      </c>
+      <c r="AE32" s="8">
+        <f t="shared" si="182"/>
+        <v>0.31626913669154072</v>
+      </c>
+      <c r="AF32" s="8">
+        <f t="shared" ref="AF32:AH32" si="183">AF16/AF10</f>
+        <v>0.32362936914398999</v>
+      </c>
+      <c r="AG32" s="8">
         <f t="shared" si="183"/>
-        <v>0.279156202913109</v>
-      </c>
-      <c r="Y32" s="8">
+        <v>0.32311823084243441</v>
+      </c>
+      <c r="AH32" s="8">
         <f t="shared" si="183"/>
-        <v>0.24800266311584554</v>
-      </c>
-      <c r="Z32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.23879654954765411</v>
-      </c>
-      <c r="AA32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.24954504420594092</v>
-      </c>
-      <c r="AB32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.29271888906761029</v>
-      </c>
-      <c r="AC32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.27829136948613303</v>
-      </c>
-      <c r="AD32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.27455683003128256</v>
-      </c>
-      <c r="AE32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.31626913669154072</v>
-      </c>
-      <c r="AF32" s="8">
-        <f t="shared" ref="AF32:AH32" si="184">AF16/AF10</f>
-        <v>0.32362936914398999</v>
-      </c>
-      <c r="AG32" s="8">
+        <v>0.32105650519856122</v>
+      </c>
+      <c r="AI32" s="8">
+        <f t="shared" ref="AI32:AL32" si="184">AI16/AI10</f>
+        <v>0.33918478622248821</v>
+      </c>
+      <c r="AJ32" s="8">
         <f t="shared" si="184"/>
-        <v>0.32311823084243441</v>
-      </c>
-      <c r="AH32" s="8">
+        <v>0.32429377359273243</v>
+      </c>
+      <c r="AK32" s="8">
         <f t="shared" si="184"/>
-        <v>0.32105650519856122</v>
-      </c>
-      <c r="AI32" s="8">
-        <f t="shared" ref="AI32:AL32" si="185">AI16/AI10</f>
-        <v>0.33918478622248821</v>
-      </c>
-      <c r="AJ32" s="8">
+        <v>0.30512184159615424</v>
+      </c>
+      <c r="AL32" s="8">
+        <f t="shared" si="184"/>
+        <v>0.31814556837266583</v>
+      </c>
+      <c r="AN32" s="8">
+        <f t="shared" ref="AN32:BA32" si="185">AN16/AN10</f>
+        <v>0.25993102452060235</v>
+      </c>
+      <c r="AO32" s="8">
         <f t="shared" si="185"/>
-        <v>0.32429377359273243</v>
-      </c>
-      <c r="AK32" s="8">
+        <v>0.23823445574079624</v>
+      </c>
+      <c r="AP32" s="8">
         <f t="shared" si="185"/>
-        <v>0.32691228495794494</v>
-      </c>
-      <c r="AL32" s="8">
+        <v>0.22349357766423447</v>
+      </c>
+      <c r="AQ32" s="8">
         <f t="shared" si="185"/>
-        <v>0.32665613019428641</v>
-      </c>
-      <c r="AN32" s="8">
-        <f t="shared" ref="AN32:BA32" si="186">AN16/AN10</f>
-        <v>0.25993102452060235</v>
-      </c>
-      <c r="AO32" s="8">
+        <v>0.22585151785763202</v>
+      </c>
+      <c r="AR32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.30186680261758625</v>
+      </c>
+      <c r="AS32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.26461270842467011</v>
+      </c>
+      <c r="AT32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.27421810445226646</v>
+      </c>
+      <c r="AU32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.32109777211457696</v>
+      </c>
+      <c r="AV32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.32104773838495582</v>
+      </c>
+      <c r="AW32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.32529188213701632</v>
+      </c>
+      <c r="AX32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.3300569014211342</v>
+      </c>
+      <c r="AY32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.33406200196425256</v>
+      </c>
+      <c r="AZ32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.33655934115523295</v>
+      </c>
+      <c r="BA32" s="8">
+        <f t="shared" si="185"/>
+        <v>0.33848723773643757</v>
+      </c>
+      <c r="BB32" s="8">
+        <f t="shared" ref="BB32:BF32" si="186">BB16/BB10</f>
+        <v>0.33968591176419455</v>
+      </c>
+      <c r="BC32" s="8">
         <f t="shared" si="186"/>
-        <v>0.23823445574079624</v>
-      </c>
-      <c r="AP32" s="8">
+        <v>0.34020241804980672</v>
+      </c>
+      <c r="BD32" s="8">
         <f t="shared" si="186"/>
-        <v>0.22349357766423447</v>
-      </c>
-      <c r="AQ32" s="8">
+        <v>0.33939586840290425</v>
+      </c>
+      <c r="BE32" s="8">
         <f t="shared" si="186"/>
-        <v>0.22585151785763202</v>
-      </c>
-      <c r="AR32" s="8">
+        <v>0.33859659394716657</v>
+      </c>
+      <c r="BF32" s="8">
         <f t="shared" si="186"/>
-        <v>0.30186680261758625</v>
-      </c>
-      <c r="AS32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.26461270842467011</v>
-      </c>
-      <c r="AT32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.27421810445226646</v>
-      </c>
-      <c r="AU32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.32109777211457696</v>
-      </c>
-      <c r="AV32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.32902471388888938</v>
-      </c>
-      <c r="AW32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.33807300160269294</v>
-      </c>
-      <c r="AX32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.34279542787760608</v>
-      </c>
-      <c r="AY32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.3466067313879449</v>
-      </c>
-      <c r="AZ32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.34847880367214262</v>
-      </c>
-      <c r="BA32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.35008221611057772</v>
-      </c>
-      <c r="BB32" s="8">
-        <f t="shared" ref="BB32:BF32" si="187">BB16/BB10</f>
-        <v>0.35121297165766235</v>
-      </c>
-      <c r="BC32" s="8">
-        <f t="shared" si="187"/>
-        <v>0.35168726472260053</v>
-      </c>
-      <c r="BD32" s="8">
-        <f t="shared" si="187"/>
-        <v>0.35091018943832414</v>
-      </c>
-      <c r="BE32" s="8">
-        <f t="shared" si="187"/>
-        <v>0.3501396091415106</v>
-      </c>
-      <c r="BF32" s="8">
-        <f t="shared" si="187"/>
-        <v>0.34937573218066825</v>
+        <v>0.33780481297981019</v>
       </c>
       <c r="BH32" t="s">
         <v>44</v>
@@ -6561,204 +6538,204 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33" si="188">G13/C13-1</f>
+        <f t="shared" ref="G33" si="187">G13/C13-1</f>
         <v>0.27828513444951808</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" ref="H33" si="189">H13/D13-1</f>
+        <f t="shared" ref="H33" si="188">H13/D13-1</f>
         <v>0.22579098753595406</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" ref="I33" si="190">I13/E13-1</f>
+        <f t="shared" ref="I33" si="189">I13/E13-1</f>
         <v>0.24423305588585009</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" ref="J33" si="191">J13/F13-1</f>
+        <f t="shared" ref="J33" si="190">J13/F13-1</f>
         <v>0.4013005109150023</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" ref="K33" si="192">K13/G13-1</f>
+        <f t="shared" ref="K33" si="191">K13/G13-1</f>
         <v>0.19646755308592967</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" ref="L33" si="193">L13/H13-1</f>
+        <f t="shared" ref="L33" si="192">L13/H13-1</f>
         <v>0.21490027375831056</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" ref="M33" si="194">M13/I13-1</f>
+        <f t="shared" ref="M33" si="193">M13/I13-1</f>
         <v>0.25267584097859319</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" ref="N33" si="195">N13/J13-1</f>
+        <f t="shared" ref="N33" si="194">N13/J13-1</f>
         <v>0.19688432217434548</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" ref="O33" si="196">O13/K13-1</f>
+        <f t="shared" ref="O33" si="195">O13/K13-1</f>
         <v>0.1311992038480676</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" ref="P33" si="197">P13/L13-1</f>
+        <f t="shared" ref="P33" si="196">P13/L13-1</f>
         <v>0.10655078062127799</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" ref="Q33" si="198">Q13/M13-1</f>
+        <f t="shared" ref="Q33" si="197">Q13/M13-1</f>
         <v>4.607873054623135E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" ref="R33" si="199">R13/N13-1</f>
+        <f t="shared" ref="R33" si="198">R13/N13-1</f>
         <v>-2.7693159789532018E-2</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" ref="S33" si="200">S13/O13-1</f>
+        <f t="shared" ref="S33" si="199">S13/O13-1</f>
         <v>9.7507331378299034E-2</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" ref="T33" si="201">T13/P13-1</f>
+        <f t="shared" ref="T33" si="200">T13/P13-1</f>
         <v>8.8727272727272766E-2</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" ref="U33" si="202">U13/Q13-1</f>
+        <f t="shared" ref="U33" si="201">U13/Q13-1</f>
         <v>0.12222870478413062</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" ref="V33" si="203">V13/R13-1</f>
+        <f t="shared" ref="V33" si="202">V13/R13-1</f>
         <v>0.24010253489034472</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="204">W13/S13-1</f>
+        <f t="shared" ref="W33" si="203">W13/S13-1</f>
         <v>0.21830327321309295</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" ref="X33" si="205">X13/T13-1</f>
+        <f t="shared" ref="X33" si="204">X13/T13-1</f>
         <v>0.31476285905143619</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" ref="Y33" si="206">Y13/U13-1</f>
+        <f t="shared" ref="Y33" si="205">Y13/U13-1</f>
         <v>0.33519625682349874</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" ref="Z33" si="207">Z13/V13-1</f>
+        <f t="shared" ref="Z33" si="206">Z13/V13-1</f>
         <v>0.17903077629765729</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33" si="208">AA13/W13-1</f>
+        <f t="shared" ref="AA33" si="207">AA13/W13-1</f>
         <v>0.25759403443360007</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" ref="AB33" si="209">AB13/X13-1</f>
+        <f t="shared" ref="AB33" si="208">AB13/X13-1</f>
         <v>7.590692002845234E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" ref="AC33" si="210">AC13/Y13-1</f>
+        <f t="shared" ref="AC33" si="209">AC13/Y13-1</f>
         <v>9.5882410201499013E-2</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" ref="AD33" si="211">AD13/Z13-1</f>
+        <f t="shared" ref="AD33" si="210">AD13/Z13-1</f>
         <v>0.17979935716372841</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33" si="212">AE13/AA13-1</f>
+        <f t="shared" ref="AE33" si="211">AE13/AA13-1</f>
         <v>3.7931635856295776E-2</v>
       </c>
       <c r="AF33" s="8">
-        <f t="shared" ref="AF33" si="213">AF13/AB13-1</f>
+        <f t="shared" ref="AF33" si="212">AF13/AB13-1</f>
         <v>0.12013600302228933</v>
       </c>
       <c r="AG33" s="8">
-        <f t="shared" ref="AG33" si="214">AG13/AC13-1</f>
+        <f t="shared" ref="AG33" si="213">AG13/AC13-1</f>
         <v>0.10561378575235381</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" ref="AH33" si="215">AH13/AD13-1</f>
+        <f t="shared" ref="AH33" si="214">AH13/AD13-1</f>
         <v>8.2803599438619591E-2</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33" si="216">AI13/AE13-1</f>
+        <f t="shared" ref="AI33" si="215">AI13/AE13-1</f>
         <v>0.13887255313786451</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33" si="217">AJ13/AF13-1</f>
+        <f t="shared" ref="AJ33" si="216">AJ13/AF13-1</f>
         <v>0.16424957841483989</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" ref="AK33" si="218">AK13/AG13-1</f>
-        <v>0.1399999999999999</v>
+        <f t="shared" ref="AK33" si="217">AK13/AG13-1</f>
+        <v>0.21724110227364024</v>
       </c>
       <c r="AL33" s="8">
-        <f t="shared" ref="AL33" si="219">AL13/AH13-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="AL33" si="218">AL13/AH13-1</f>
+        <v>0.25</v>
       </c>
       <c r="AN33" s="8"/>
       <c r="AO33" s="8">
-        <f t="shared" ref="AO33:BB35" si="220">AO13/AN13-1</f>
+        <f t="shared" ref="AO33:BB35" si="219">AO13/AN13-1</f>
         <v>0.28836090225563904</v>
       </c>
       <c r="AP33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.21471590643820915</v>
       </c>
       <c r="AQ33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>5.9766315627642452E-2</v>
       </c>
       <c r="AR33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.13777971203713779</v>
       </c>
       <c r="AS33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.25908453397934461</v>
       </c>
       <c r="AT33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.15005063291139242</v>
       </c>
       <c r="AU33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>8.583001298787063E-2</v>
       </c>
       <c r="AV33" s="8">
-        <f t="shared" si="220"/>
-        <v>0.1402404411466569</v>
+        <f t="shared" si="219"/>
+        <v>0.19429915257673436</v>
       </c>
       <c r="AW33" s="8">
-        <f t="shared" si="220"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="219"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AX33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AY33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB33" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="8">
-        <f t="shared" ref="BC33" si="221">BC13/BB13-1</f>
+        <f t="shared" ref="BC33" si="220">BC13/BB13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="8">
-        <f t="shared" ref="BD33" si="222">BD13/BC13-1</f>
+        <f t="shared" ref="BD33" si="221">BD13/BC13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE33" s="8">
-        <f t="shared" ref="BE33" si="223">BE13/BD13-1</f>
+        <f t="shared" ref="BE33" si="222">BE13/BD13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF33" s="8">
-        <f t="shared" ref="BF33" si="224">BF13/BE13-1</f>
+        <f t="shared" ref="BF33" si="223">BF13/BE13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH33" t="s">
@@ -6773,19 +6750,19 @@
         <v>36</v>
       </c>
       <c r="C34" s="8">
-        <f t="shared" ref="C34:F34" si="225">C14/C10</f>
+        <f t="shared" ref="C34:F34" si="224">C14/C10</f>
         <v>0.10682828282828283</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="225"/>
+        <f t="shared" si="224"/>
         <v>0.11138023836985775</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="225"/>
+        <f t="shared" si="224"/>
         <v>0.10953478323491286</v>
       </c>
       <c r="F34" s="8">
-        <f t="shared" si="225"/>
+        <f t="shared" si="224"/>
         <v>0.13371804417969718</v>
       </c>
       <c r="G34" s="8">
@@ -6793,211 +6770,211 @@
         <v>0.11571309317408335</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" ref="H34:R34" si="226">H14/H10</f>
+        <f t="shared" ref="H34:R34" si="225">H14/H10</f>
         <v>0.11574853783262394</v>
       </c>
       <c r="I34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.11407824540604623</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.12985029025358999</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.10746030435620132</v>
+      </c>
+      <c r="L34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.10815529991783072</v>
+      </c>
+      <c r="M34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.11380527914269488</v>
+      </c>
+      <c r="N34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.1245360824742268</v>
+      </c>
+      <c r="O34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.10933210233484779</v>
+      </c>
+      <c r="P34" s="8">
+        <f t="shared" si="225"/>
+        <v>0.10186176462908322</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="225"/>
+        <v>9.1633638706603432E-2</v>
+      </c>
+      <c r="R34" s="8">
+        <f t="shared" si="225"/>
+        <v>9.3395198425252207E-2</v>
+      </c>
+      <c r="S34" s="8">
+        <f t="shared" ref="S34:V34" si="226">S14/S10</f>
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="T34" s="8">
         <f t="shared" si="226"/>
-        <v>0.11407824540604623</v>
-      </c>
-      <c r="J34" s="8">
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="U34" s="8">
         <f t="shared" si="226"/>
-        <v>0.12985029025358999</v>
-      </c>
-      <c r="K34" s="8">
+        <v>8.4707761294880057E-2</v>
+      </c>
+      <c r="V34" s="8">
         <f t="shared" si="226"/>
-        <v>0.10746030435620132</v>
-      </c>
-      <c r="L34" s="8">
-        <f t="shared" si="226"/>
-        <v>0.10815529991783072</v>
-      </c>
-      <c r="M34" s="8">
-        <f t="shared" si="226"/>
-        <v>0.11380527914269488</v>
-      </c>
-      <c r="N34" s="8">
-        <f t="shared" si="226"/>
-        <v>0.1245360824742268</v>
-      </c>
-      <c r="O34" s="8">
-        <f t="shared" si="226"/>
-        <v>0.10933210233484779</v>
-      </c>
-      <c r="P34" s="8">
-        <f t="shared" si="226"/>
-        <v>0.10186176462908322</v>
-      </c>
-      <c r="Q34" s="8">
-        <f t="shared" si="226"/>
-        <v>9.1633638706603432E-2</v>
-      </c>
-      <c r="R34" s="8">
-        <f t="shared" si="226"/>
-        <v>9.3395198425252207E-2</v>
-      </c>
-      <c r="S34" s="8">
-        <f t="shared" ref="S34:V34" si="227">S14/S10</f>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="T34" s="8">
+        <v>0.10094922004646532</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" ref="W34:AE34" si="227">W14/W10</f>
+        <v>8.5647909896928442E-2</v>
+      </c>
+      <c r="X34" s="8">
         <f t="shared" si="227"/>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="U34" s="8">
+        <v>9.514242663413934E-2</v>
+      </c>
+      <c r="Y34" s="8">
         <f t="shared" si="227"/>
-        <v>8.4707761294880057E-2</v>
-      </c>
-      <c r="V34" s="8">
+        <v>0.10028657442250911</v>
+      </c>
+      <c r="Z34" s="8">
         <f t="shared" si="227"/>
-        <v>0.10094922004646532</v>
-      </c>
-      <c r="W34" s="8">
-        <f t="shared" ref="W34:AE34" si="228">W14/W10</f>
-        <v>8.5647909896928442E-2</v>
-      </c>
-      <c r="X34" s="8">
+        <v>9.4453503050704823E-2</v>
+      </c>
+      <c r="AA34" s="8">
+        <f t="shared" si="227"/>
+        <v>9.3613423703555104E-2</v>
+      </c>
+      <c r="AB34" s="8">
+        <f t="shared" si="227"/>
+        <v>9.0893249691705535E-2</v>
+      </c>
+      <c r="AC34" s="8">
+        <f t="shared" si="227"/>
+        <v>8.9760473576467215E-2</v>
+      </c>
+      <c r="AD34" s="8">
+        <f t="shared" si="227"/>
+        <v>8.9433437608620089E-2</v>
+      </c>
+      <c r="AE34" s="8">
+        <f t="shared" si="227"/>
+        <v>7.9787432175716114E-2</v>
+      </c>
+      <c r="AF34" s="8">
+        <f t="shared" ref="AF34:AH34" si="228">AF14/AF10</f>
+        <v>8.0149158622642852E-2</v>
+      </c>
+      <c r="AG34" s="8">
         <f t="shared" si="228"/>
-        <v>9.514242663413934E-2</v>
-      </c>
-      <c r="Y34" s="8">
+        <v>8.1875651425205059E-2</v>
+      </c>
+      <c r="AH34" s="8">
         <f t="shared" si="228"/>
-        <v>0.10028657442250911</v>
-      </c>
-      <c r="Z34" s="8">
-        <f t="shared" si="228"/>
-        <v>9.4453503050704823E-2</v>
-      </c>
-      <c r="AA34" s="8">
-        <f t="shared" si="228"/>
-        <v>9.3613423703555104E-2</v>
-      </c>
-      <c r="AB34" s="8">
-        <f t="shared" si="228"/>
-        <v>9.0893249691705535E-2</v>
-      </c>
-      <c r="AC34" s="8">
-        <f t="shared" si="228"/>
-        <v>8.9760473576467215E-2</v>
-      </c>
-      <c r="AD34" s="8">
-        <f t="shared" si="228"/>
-        <v>8.9433437608620089E-2</v>
-      </c>
-      <c r="AE34" s="8">
-        <f t="shared" si="228"/>
-        <v>7.9787432175716114E-2</v>
-      </c>
-      <c r="AF34" s="8">
-        <f t="shared" ref="AF34:AH34" si="229">AF14/AF10</f>
-        <v>8.0149158622642852E-2</v>
-      </c>
-      <c r="AG34" s="8">
+        <v>7.6325037058536938E-2</v>
+      </c>
+      <c r="AI34" s="8">
+        <f t="shared" ref="AI34:AL34" si="229">AI14/AI10</f>
+        <v>6.8399937939136027E-2</v>
+      </c>
+      <c r="AJ34" s="8">
         <f t="shared" si="229"/>
-        <v>8.1875651425205059E-2</v>
-      </c>
-      <c r="AH34" s="8">
+        <v>7.3640436387771194E-2</v>
+      </c>
+      <c r="AK34" s="8">
         <f t="shared" si="229"/>
-        <v>7.6325037058536938E-2</v>
-      </c>
-      <c r="AI34" s="8">
-        <f t="shared" ref="AI34:AL34" si="230">AI14/AI10</f>
-        <v>6.8399937939136027E-2</v>
-      </c>
-      <c r="AJ34" s="8">
+        <v>7.0398452308834736E-2</v>
+      </c>
+      <c r="AL34" s="8">
+        <f t="shared" si="229"/>
+        <v>7.4999999999999983E-2</v>
+      </c>
+      <c r="AN34" s="8">
+        <f t="shared" ref="AN34:BA34" si="230">AN14/AN10</f>
+        <v>0.11640063558556932</v>
+      </c>
+      <c r="AO34" s="8">
         <f t="shared" si="230"/>
-        <v>7.3640436387771194E-2</v>
-      </c>
-      <c r="AK34" s="8">
+        <v>0.1193766947573071</v>
+      </c>
+      <c r="AP34" s="8">
         <f t="shared" si="230"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AL34" s="8">
+        <v>0.11407600536275848</v>
+      </c>
+      <c r="AQ34" s="8">
         <f t="shared" si="230"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AN34" s="8">
-        <f t="shared" ref="AN34:BA34" si="231">AN14/AN10</f>
-        <v>0.11640063558556932</v>
-      </c>
-      <c r="AO34" s="8">
-        <f t="shared" si="231"/>
-        <v>0.1193766947573071</v>
-      </c>
-      <c r="AP34" s="8">
-        <f t="shared" si="231"/>
-        <v>0.11407600536275848</v>
-      </c>
-      <c r="AQ34" s="8">
-        <f t="shared" si="231"/>
         <v>9.8319700647027566E-2</v>
       </c>
       <c r="AR34" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>8.823002258325334E-2</v>
       </c>
       <c r="AS34" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>9.3930758460733427E-2</v>
       </c>
       <c r="AT34" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>9.0818298340240869E-2</v>
       </c>
       <c r="AU34" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>7.94473427080893E-2</v>
       </c>
       <c r="AV34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.3145419574287968E-2</v>
+        <f t="shared" si="230"/>
+        <v>7.1999583835062497E-2</v>
       </c>
       <c r="AW34" s="8">
+        <f t="shared" si="230"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AX34" s="8">
+        <f t="shared" si="230"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AY34" s="8">
+        <f t="shared" si="230"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AZ34" s="8">
+        <f t="shared" si="230"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BA34" s="8">
+        <f t="shared" si="230"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BB34" s="8">
+        <f t="shared" ref="BB34:BF34" si="231">BB14/BB10</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BC34" s="8">
         <f t="shared" si="231"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AX34" s="8">
+      <c r="BD34" s="8">
         <f t="shared" si="231"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AY34" s="8">
+      <c r="BE34" s="8">
         <f t="shared" si="231"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AZ34" s="8">
+      <c r="BF34" s="8">
         <f t="shared" si="231"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BA34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BB34" s="8">
-        <f t="shared" ref="BB34:BF34" si="232">BB14/BB10</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BC34" s="8">
-        <f t="shared" si="232"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BD34" s="8">
-        <f t="shared" si="232"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BE34" s="8">
-        <f t="shared" si="232"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BF34" s="8">
-        <f t="shared" si="232"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
       <c r="BH34" t="s">
         <v>46</v>
       </c>
       <c r="BI34" s="1">
         <f>NPV(BI33,AV20:GK20)</f>
-        <v>2885873.2308964119</v>
+        <v>2925756.5309859086</v>
       </c>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.3">
@@ -7009,204 +6986,204 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
-        <f t="shared" ref="G35" si="233">G15/C15-1</f>
+        <f t="shared" ref="G35" si="232">G15/C15-1</f>
         <v>-0.22098833981121602</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" ref="H35" si="234">H15/D15-1</f>
+        <f t="shared" ref="H35" si="233">H15/D15-1</f>
         <v>3.7647058823529367E-2</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35" si="235">I15/E15-1</f>
+        <f t="shared" ref="I35" si="234">I15/E15-1</f>
         <v>9.9059561128526541E-2</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" ref="J35" si="236">J15/F15-1</f>
+        <f t="shared" ref="J35" si="235">J15/F15-1</f>
         <v>0.12781531531531543</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" ref="K35" si="237">K15/G15-1</f>
+        <f t="shared" ref="K35" si="236">K15/G15-1</f>
         <v>1.6977904490377762</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" ref="L35" si="238">L15/H15-1</f>
+        <f t="shared" ref="L35" si="237">L15/H15-1</f>
         <v>0.15816326530612246</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" ref="M35" si="239">M15/I15-1</f>
+        <f t="shared" ref="M35" si="238">M15/I15-1</f>
         <v>0.47803764974329721</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" ref="N35" si="240">N15/J15-1</f>
+        <f t="shared" ref="N35" si="239">N15/J15-1</f>
         <v>0.41238142785821275</v>
       </c>
       <c r="O35" s="8">
-        <f t="shared" ref="O35" si="241">O15/K15-1</f>
+        <f t="shared" ref="O35" si="240">O15/K15-1</f>
         <v>-0.23910171730515195</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" ref="P35" si="242">P15/L15-1</f>
+        <f t="shared" ref="P35" si="241">P15/L15-1</f>
         <v>0.26529613313754274</v>
       </c>
       <c r="Q35" s="8">
-        <f t="shared" ref="Q35" si="243">Q15/M15-1</f>
+        <f t="shared" ref="Q35" si="242">Q15/M15-1</f>
         <v>6.3681976071015001E-2</v>
       </c>
       <c r="R35" s="8">
-        <f t="shared" ref="R35" si="244">R15/N15-1</f>
+        <f t="shared" ref="R35" si="243">R15/N15-1</f>
         <v>7.0696359137500941E-4</v>
       </c>
       <c r="S35" s="8">
-        <f t="shared" ref="S35" si="245">S15/O15-1</f>
+        <f t="shared" ref="S35" si="244">S15/O15-1</f>
         <v>-3.7152777777777812E-2</v>
       </c>
       <c r="T35" s="8">
-        <f t="shared" ref="T35" si="246">T15/P15-1</f>
+        <f t="shared" ref="T35" si="245">T15/P15-1</f>
         <v>7.2727272727272751E-2</v>
       </c>
       <c r="U35" s="8">
-        <f t="shared" ref="U35" si="247">U15/Q15-1</f>
+        <f t="shared" ref="U35" si="246">U15/Q15-1</f>
         <v>0.1814223512336719</v>
       </c>
       <c r="V35" s="8">
-        <f t="shared" ref="V35" si="248">V15/R15-1</f>
+        <f t="shared" ref="V35" si="247">V15/R15-1</f>
         <v>0.46238078417520301</v>
       </c>
       <c r="W35" s="8">
-        <f t="shared" ref="W35" si="249">W15/S15-1</f>
+        <f t="shared" ref="W35" si="248">W15/S15-1</f>
         <v>0.21673278038225741</v>
       </c>
       <c r="X35" s="8">
-        <f t="shared" ref="X35" si="250">X15/T15-1</f>
+        <f t="shared" ref="X35" si="249">X15/T15-1</f>
         <v>0.31878831590335377</v>
       </c>
       <c r="Y35" s="8">
-        <f t="shared" ref="Y35" si="251">Y15/U15-1</f>
+        <f t="shared" ref="Y35" si="250">Y15/U15-1</f>
         <v>0.10472972972972983</v>
       </c>
       <c r="Z35" s="8">
-        <f t="shared" ref="Z35" si="252">Z15/V15-1</f>
+        <f t="shared" ref="Z35" si="251">Z15/V15-1</f>
         <v>0.23091787439613531</v>
       </c>
       <c r="AA35" s="8">
-        <f t="shared" ref="AA35" si="253">AA15/W15-1</f>
+        <f t="shared" ref="AA35" si="252">AA15/W15-1</f>
         <v>0.11410788381742742</v>
       </c>
       <c r="AB35" s="8">
-        <f t="shared" ref="AB35" si="254">AB15/X15-1</f>
+        <f t="shared" ref="AB35" si="253">AB15/X15-1</f>
         <v>-4.8126879956248314E-2</v>
       </c>
       <c r="AC35" s="8">
-        <f t="shared" ref="AC35" si="255">AC15/Y15-1</f>
+        <f t="shared" ref="AC35" si="254">AC15/Y15-1</f>
         <v>0.10619961078676665</v>
       </c>
       <c r="AD35" s="8">
-        <f t="shared" ref="AD35" si="256">AD15/Z15-1</f>
+        <f t="shared" ref="AD35" si="255">AD15/Z15-1</f>
         <v>2.1585557299842906E-2</v>
       </c>
       <c r="AE35" s="8">
-        <f t="shared" ref="AE35" si="257">AE15/AA15-1</f>
+        <f t="shared" ref="AE35" si="256">AE15/AA15-1</f>
         <v>-0.19499866985900505</v>
       </c>
       <c r="AF35" s="8">
-        <f t="shared" ref="AF35" si="258">AF15/AB15-1</f>
+        <f t="shared" ref="AF35" si="257">AF15/AB15-1</f>
         <v>-9.2789428325193879E-2</v>
       </c>
       <c r="AG35" s="8">
-        <f t="shared" ref="AG35" si="259">AG15/AC15-1</f>
+        <f t="shared" ref="AG35" si="258">AG15/AC15-1</f>
         <v>-9.5501382256848455E-2</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" ref="AH35" si="260">AH15/AD15-1</f>
+        <f t="shared" ref="AH35" si="259">AH15/AD15-1</f>
         <v>-0.153860929696504</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" ref="AI35" si="261">AI15/AE15-1</f>
+        <f t="shared" ref="AI35" si="260">AI15/AE15-1</f>
         <v>0.16953073364177129</v>
       </c>
       <c r="AJ35" s="8">
-        <f t="shared" ref="AJ35" si="262">AJ15/AF15-1</f>
+        <f t="shared" ref="AJ35" si="261">AJ15/AF15-1</f>
         <v>0.64946168461051301</v>
       </c>
       <c r="AK35" s="8">
-        <f t="shared" ref="AK35" si="263">AK15/AG15-1</f>
-        <v>0.5</v>
+        <f t="shared" ref="AK35" si="262">AK15/AG15-1</f>
+        <v>1.0541817171436509</v>
       </c>
       <c r="AL35" s="8">
-        <f t="shared" ref="AL35" si="264">AL15/AH15-1</f>
+        <f t="shared" ref="AL35" si="263">AL15/AH15-1</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="AN35" s="8"/>
       <c r="AO35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>7.4214202561118103E-3</v>
       </c>
       <c r="AP35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.3440704896721074</v>
       </c>
       <c r="AQ35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.18774852229983874</v>
       </c>
       <c r="AR35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.17100977198697076</v>
       </c>
       <c r="AS35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>0.21495904806057786</v>
       </c>
       <c r="AT35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>4.4581531416942211E-2</v>
       </c>
       <c r="AU35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>-0.13619482496194824</v>
       </c>
       <c r="AV35" s="8">
-        <f t="shared" si="220"/>
-        <v>0.44726177051029037</v>
+        <f t="shared" si="219"/>
+        <v>0.58783831406822662</v>
       </c>
       <c r="AW35" s="8">
-        <f t="shared" si="220"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="219"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AX35" s="8">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AY35" s="8">
+        <f t="shared" si="219"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AY35" s="8">
-        <f t="shared" si="220"/>
+      <c r="AZ35" s="8">
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AZ35" s="8">
-        <f t="shared" si="220"/>
+      <c r="BA35" s="8">
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA35" s="8">
-        <f t="shared" si="220"/>
+      <c r="BB35" s="8">
+        <f t="shared" si="219"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB35" s="8">
-        <f t="shared" si="220"/>
+      <c r="BC35" s="8">
+        <f t="shared" ref="BC35" si="264">BC15/BB15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC35" s="8">
-        <f t="shared" ref="BC35" si="265">BC15/BB15-1</f>
+      <c r="BD35" s="8">
+        <f t="shared" ref="BD35" si="265">BD15/BC15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD35" s="8">
-        <f t="shared" ref="BD35" si="266">BD15/BC15-1</f>
+      <c r="BE35" s="8">
+        <f t="shared" ref="BE35" si="266">BE15/BD15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE35" s="8">
-        <f t="shared" ref="BE35" si="267">BE15/BD15-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BF35" s="8">
-        <f t="shared" ref="BF35" si="268">BF15/BE15-1</f>
+        <f t="shared" ref="BF35" si="267">BF15/BE15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH35" t="s">
@@ -7214,7 +7191,7 @@
       </c>
       <c r="BI35" s="1">
         <f>Main!D8</f>
-        <v>124115</v>
+        <v>122756</v>
       </c>
     </row>
     <row r="36" spans="2:61" x14ac:dyDescent="0.3">
@@ -7222,19 +7199,19 @@
         <v>37</v>
       </c>
       <c r="C36" s="8">
-        <f t="shared" ref="C36:F36" si="269">C19/C18</f>
+        <f t="shared" ref="C36:F36" si="268">C19/C18</f>
         <v>0.20428215280832968</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="268"/>
         <v>0.11992127091241389</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="268"/>
         <v>0.15628524877804237</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="268"/>
         <v>1.3924561624826541</v>
       </c>
       <c r="G36" s="8">
@@ -7242,211 +7219,211 @@
         <v>0.10831831546998008</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" ref="H36:R36" si="270">H19/H18</f>
+        <f t="shared" ref="H36:R36" si="269">H19/H18</f>
         <v>0.1098427740684902</v>
       </c>
       <c r="I36" s="8">
+        <f t="shared" si="269"/>
+        <v>8.8366557572151144E-2</v>
+      </c>
+      <c r="J36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.11159650516282764</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.18278909894426712</v>
+      </c>
+      <c r="L36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.18111467852144564</v>
+      </c>
+      <c r="M36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.1808066759388039</v>
+      </c>
+      <c r="N36" s="8">
+        <f t="shared" si="269"/>
+        <v>3.0829596412556052E-3</v>
+      </c>
+      <c r="O36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.11873146835116669</v>
+      </c>
+      <c r="P36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.15923643832306392</v>
+      </c>
+      <c r="Q36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.15496368038740921</v>
+      </c>
+      <c r="R36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.18524265610787094</v>
+      </c>
+      <c r="S36" s="8">
+        <f t="shared" ref="S36:V36" si="270">S19/S18</f>
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="T36" s="8">
         <f t="shared" si="270"/>
-        <v>8.8366557572151144E-2</v>
-      </c>
-      <c r="J36" s="8">
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="U36" s="8">
         <f t="shared" si="270"/>
-        <v>0.11159650516282764</v>
-      </c>
-      <c r="K36" s="8">
+        <v>0.17898022892819979</v>
+      </c>
+      <c r="V36" s="8">
         <f t="shared" si="270"/>
-        <v>0.18278909894426712</v>
-      </c>
-      <c r="L36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.18111467852144564</v>
-      </c>
-      <c r="M36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.1808066759388039</v>
-      </c>
-      <c r="N36" s="8">
-        <f t="shared" si="270"/>
-        <v>3.0829596412556052E-3</v>
-      </c>
-      <c r="O36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.11873146835116669</v>
-      </c>
-      <c r="P36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.15923643832306392</v>
-      </c>
-      <c r="Q36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.15496368038740921</v>
-      </c>
-      <c r="R36" s="8">
-        <f t="shared" si="270"/>
-        <v>0.18524265610787094</v>
-      </c>
-      <c r="S36" s="8">
-        <f t="shared" ref="S36:V36" si="271">S19/S18</f>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="T36" s="8">
+        <v>0.15408573067781328</v>
+      </c>
+      <c r="W36" s="8">
+        <f t="shared" ref="W36:AE36" si="271">W19/W18</f>
+        <v>0.13193197422625963</v>
+      </c>
+      <c r="X36" s="8">
         <f t="shared" si="271"/>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="U36" s="8">
+        <v>0.15840959293152415</v>
+      </c>
+      <c r="Y36" s="8">
         <f t="shared" si="271"/>
-        <v>0.17898022892819979</v>
-      </c>
-      <c r="V36" s="8">
+        <v>0.14310355448777182</v>
+      </c>
+      <c r="Z36" s="8">
         <f t="shared" si="271"/>
-        <v>0.15408573067781328</v>
-      </c>
-      <c r="W36" s="8">
-        <f t="shared" ref="W36:AE36" si="272">W19/W18</f>
-        <v>0.13193197422625963</v>
-      </c>
-      <c r="X36" s="8">
+        <v>0.20545868081880211</v>
+      </c>
+      <c r="AA36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.17324910738808019</v>
+      </c>
+      <c r="AB36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.16139341642697347</v>
+      </c>
+      <c r="AC36" s="8">
+        <f t="shared" si="271"/>
+        <v>7.1142142756050381E-2</v>
+      </c>
+      <c r="AD36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.15258889070948714</v>
+      </c>
+      <c r="AE36" s="8">
+        <f t="shared" si="271"/>
+        <v>0.16432986049796927</v>
+      </c>
+      <c r="AF36" s="8">
+        <f t="shared" ref="AF36:AH36" si="272">AF19/AF18</f>
+        <v>0.14271714275343908</v>
+      </c>
+      <c r="AG36" s="8">
         <f t="shared" si="272"/>
-        <v>0.15840959293152415</v>
-      </c>
-      <c r="Y36" s="8">
+        <v>0.17047246577934777</v>
+      </c>
+      <c r="AH36" s="8">
         <f t="shared" si="272"/>
-        <v>0.14310355448777182</v>
-      </c>
-      <c r="Z36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.20545868081880211</v>
-      </c>
-      <c r="AA36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.17324910738808019</v>
-      </c>
-      <c r="AB36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.16139341642697347</v>
-      </c>
-      <c r="AC36" s="8">
-        <f t="shared" si="272"/>
-        <v>7.1142142756050381E-2</v>
-      </c>
-      <c r="AD36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.15258889070948714</v>
-      </c>
-      <c r="AE36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.16432986049796927</v>
-      </c>
-      <c r="AF36" s="8">
-        <f t="shared" ref="AF36:AH36" si="273">AF19/AF18</f>
-        <v>0.14271714275343908</v>
-      </c>
-      <c r="AG36" s="8">
+        <v>0.17699965884067859</v>
+      </c>
+      <c r="AI36" s="8">
+        <f t="shared" ref="AI36:AL36" si="273">AI19/AI18</f>
+        <v>0.173466701763622</v>
+      </c>
+      <c r="AJ36" s="8">
         <f t="shared" si="273"/>
-        <v>0.17047246577934777</v>
-      </c>
-      <c r="AH36" s="8">
+        <v>0.16906845843279403</v>
+      </c>
+      <c r="AK36" s="8">
         <f t="shared" si="273"/>
-        <v>0.17699965884067859</v>
-      </c>
-      <c r="AI36" s="8">
-        <f t="shared" ref="AI36:AL36" si="274">AI19/AI18</f>
-        <v>0.173466701763622</v>
-      </c>
-      <c r="AJ36" s="8">
+        <v>0.20478777820719757</v>
+      </c>
+      <c r="AL36" s="8">
+        <f t="shared" si="273"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN36" s="8">
+        <f t="shared" ref="AN36:BA36" si="274">AN19/AN18</f>
+        <v>0.14515047925464172</v>
+      </c>
+      <c r="AO36" s="8">
         <f t="shared" si="274"/>
-        <v>0.16906845843279403</v>
-      </c>
-      <c r="AK36" s="8">
+        <v>0.10446678671468587</v>
+      </c>
+      <c r="AP36" s="8">
         <f t="shared" si="274"/>
-        <v>0.15</v>
-      </c>
-      <c r="AL36" s="8">
+        <v>0.12706889915319478</v>
+      </c>
+      <c r="AQ36" s="8">
         <f t="shared" si="274"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN36" s="8">
-        <f t="shared" ref="AN36:BA36" si="275">AN19/AN18</f>
-        <v>0.14515047925464172</v>
-      </c>
-      <c r="AO36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.10446678671468587</v>
-      </c>
-      <c r="AP36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.12706889915319478</v>
-      </c>
-      <c r="AQ36" s="8">
-        <f t="shared" si="275"/>
         <v>0.16158587028457974</v>
       </c>
       <c r="AR36" s="8">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v>0.16209792073929269</v>
       </c>
       <c r="AS36" s="8">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v>0.1592081650964558</v>
       </c>
       <c r="AT36" s="8">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v>0.13908559562280529</v>
       </c>
       <c r="AU36" s="8">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v>0.16439510912657013</v>
       </c>
       <c r="AV36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16104640794517217</v>
+        <f t="shared" si="274"/>
+        <v>0.17587281697185667</v>
       </c>
       <c r="AW36" s="8">
+        <f t="shared" si="274"/>
+        <v>0.16</v>
+      </c>
+      <c r="AX36" s="8">
+        <f t="shared" si="274"/>
+        <v>0.16</v>
+      </c>
+      <c r="AY36" s="8">
+        <f t="shared" si="274"/>
+        <v>0.16</v>
+      </c>
+      <c r="AZ36" s="8">
+        <f t="shared" si="274"/>
+        <v>0.16</v>
+      </c>
+      <c r="BA36" s="8">
+        <f t="shared" si="274"/>
+        <v>0.16</v>
+      </c>
+      <c r="BB36" s="8">
+        <f t="shared" ref="BB36:BF36" si="275">BB19/BB18</f>
+        <v>0.16</v>
+      </c>
+      <c r="BC36" s="8">
         <f t="shared" si="275"/>
         <v>0.16</v>
       </c>
-      <c r="AX36" s="8">
+      <c r="BD36" s="8">
         <f t="shared" si="275"/>
         <v>0.16</v>
       </c>
-      <c r="AY36" s="8">
+      <c r="BE36" s="8">
         <f t="shared" si="275"/>
         <v>0.16</v>
       </c>
-      <c r="AZ36" s="8">
+      <c r="BF36" s="8">
         <f t="shared" si="275"/>
         <v>0.16</v>
       </c>
-      <c r="BA36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB36" s="8">
-        <f t="shared" ref="BB36:BF36" si="276">BB19/BB18</f>
-        <v>0.16</v>
-      </c>
-      <c r="BC36" s="8">
-        <f t="shared" si="276"/>
-        <v>0.16</v>
-      </c>
-      <c r="BD36" s="8">
-        <f t="shared" si="276"/>
-        <v>0.16</v>
-      </c>
-      <c r="BE36" s="8">
-        <f t="shared" si="276"/>
-        <v>0.16</v>
-      </c>
-      <c r="BF36" s="8">
-        <f t="shared" si="276"/>
-        <v>0.16</v>
-      </c>
       <c r="BH36" t="s">
         <v>48</v>
       </c>
       <c r="BI36" s="1">
         <f>BI34+BI35</f>
-        <v>3009988.2308964119</v>
+        <v>3048512.5309859086</v>
       </c>
     </row>
     <row r="37" spans="2:61" x14ac:dyDescent="0.3">
@@ -7458,227 +7435,227 @@
         <v>0.21923232323232322</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" ref="D37:V37" si="277">D20/D10</f>
+        <f t="shared" ref="D37:V37" si="276">D20/D10</f>
         <v>0.24067666282199154</v>
       </c>
       <c r="E37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.24240241970329829</v>
+      </c>
+      <c r="F37" s="8">
+        <f t="shared" si="276"/>
+        <v>-9.6518987341772153E-2</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.30183651191164196</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.25311571791652632</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.2724362774155305</v>
+      </c>
+      <c r="J37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.22782360729198492</v>
+      </c>
+      <c r="K37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.18319161231734502</v>
+      </c>
+      <c r="L37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.25541803615447822</v>
+      </c>
+      <c r="M37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.17452282772414135</v>
+      </c>
+      <c r="N37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.23160065111231687</v>
+      </c>
+      <c r="O37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.16608761145800433</v>
+      </c>
+      <c r="P37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.1817113612032274</v>
+      </c>
+      <c r="Q37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.24943148593333767</v>
+      </c>
+      <c r="R37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.26761924847973567</v>
+      </c>
+      <c r="S37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="T37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="U37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.29079517184188702</v>
+      </c>
+      <c r="V37" s="8">
+        <f t="shared" si="276"/>
+        <v>0.2740391636242947</v>
+      </c>
+      <c r="W37" s="8">
+        <f t="shared" ref="W37:AE37" si="277">W20/W10</f>
+        <v>0.24166678919586537</v>
+      </c>
+      <c r="X37" s="8">
         <f t="shared" si="277"/>
-        <v>0.24240241970329829</v>
-      </c>
-      <c r="F37" s="8">
+        <v>0.22963335007533903</v>
+      </c>
+      <c r="Y37" s="8">
         <f t="shared" si="277"/>
-        <v>-9.6518987341772153E-2</v>
-      </c>
-      <c r="G37" s="8">
+        <v>0.20132576854049672</v>
+      </c>
+      <c r="Z37" s="8">
         <f t="shared" si="277"/>
-        <v>0.30183651191164196</v>
-      </c>
-      <c r="H37" s="8">
+        <v>0.17915001051967178</v>
+      </c>
+      <c r="AA37" s="8">
         <f t="shared" si="277"/>
-        <v>0.25311571791652632</v>
-      </c>
-      <c r="I37" s="8">
+        <v>0.21567054035851949</v>
+      </c>
+      <c r="AB37" s="8">
         <f t="shared" si="277"/>
-        <v>0.2724362774155305</v>
-      </c>
-      <c r="J37" s="8">
+        <v>0.2462066377137955</v>
+      </c>
+      <c r="AC37" s="8">
         <f t="shared" si="277"/>
-        <v>0.22782360729198492</v>
-      </c>
-      <c r="K37" s="8">
+        <v>0.25672486406842865</v>
+      </c>
+      <c r="AD37" s="8">
         <f t="shared" si="277"/>
-        <v>0.18319161231734502</v>
-      </c>
-      <c r="L37" s="8">
+        <v>0.23968253968253969</v>
+      </c>
+      <c r="AE37" s="8">
         <f t="shared" si="277"/>
-        <v>0.25541803615447822</v>
-      </c>
-      <c r="M37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.17452282772414135</v>
-      </c>
-      <c r="N37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.23160065111231687</v>
-      </c>
-      <c r="O37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.16608761145800433</v>
-      </c>
-      <c r="P37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.1817113612032274</v>
-      </c>
-      <c r="Q37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.24943148593333767</v>
-      </c>
-      <c r="R37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.26761924847973567</v>
-      </c>
-      <c r="S37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="T37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="U37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.29079517184188702</v>
-      </c>
-      <c r="V37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.2740391636242947</v>
-      </c>
-      <c r="W37" s="8">
-        <f t="shared" ref="W37:AE37" si="278">W20/W10</f>
-        <v>0.24166678919586537</v>
-      </c>
-      <c r="X37" s="8">
+        <v>0.29379555246526529</v>
+      </c>
+      <c r="AF37" s="8">
+        <f t="shared" ref="AF37:AH37" si="278">AF20/AF10</f>
+        <v>0.27871657501593072</v>
+      </c>
+      <c r="AG37" s="8">
         <f t="shared" si="278"/>
-        <v>0.22963335007533903</v>
-      </c>
-      <c r="Y37" s="8">
+        <v>0.29796755336022113</v>
+      </c>
+      <c r="AH37" s="8">
         <f t="shared" si="278"/>
-        <v>0.20132576854049672</v>
-      </c>
-      <c r="Z37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.17915001051967178</v>
-      </c>
-      <c r="AA37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.21567054035851949</v>
-      </c>
-      <c r="AB37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.2462066377137955</v>
-      </c>
-      <c r="AC37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.25672486406842865</v>
-      </c>
-      <c r="AD37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.23968253968253969</v>
-      </c>
-      <c r="AE37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.29379555246526529</v>
-      </c>
-      <c r="AF37" s="8">
-        <f t="shared" ref="AF37:AH37" si="279">AF20/AF10</f>
-        <v>0.27871657501593072</v>
-      </c>
-      <c r="AG37" s="8">
+        <v>0.27507282132083882</v>
+      </c>
+      <c r="AI37" s="8">
+        <f t="shared" ref="AI37:AL37" si="279">AI20/AI10</f>
+        <v>0.38278254316554733</v>
+      </c>
+      <c r="AJ37" s="8">
         <f t="shared" si="279"/>
-        <v>0.29796755336022113</v>
-      </c>
-      <c r="AH37" s="8">
+        <v>0.29240469573153027</v>
+      </c>
+      <c r="AK37" s="8">
         <f t="shared" si="279"/>
-        <v>0.27507282132083882</v>
-      </c>
-      <c r="AI37" s="8">
-        <f t="shared" ref="AI37:AL37" si="280">AI20/AI10</f>
-        <v>0.38278254316554733</v>
-      </c>
-      <c r="AJ37" s="8">
+        <v>0.34177202821800556</v>
+      </c>
+      <c r="AL37" s="8">
+        <f t="shared" si="279"/>
+        <v>0.28052718825244599</v>
+      </c>
+      <c r="AN37" s="8">
+        <f t="shared" ref="AN37:BA37" si="280">AN20/AN10</f>
+        <v>0.23028240222454949</v>
+      </c>
+      <c r="AO37" s="8">
         <f t="shared" si="280"/>
-        <v>0.29240469573153027</v>
-      </c>
-      <c r="AK37" s="8">
+        <v>0.26171072731126527</v>
+      </c>
+      <c r="AP37" s="8">
         <f t="shared" si="280"/>
-        <v>0.30607428332292913</v>
-      </c>
-      <c r="AL37" s="8">
+        <v>0.22418554650092365</v>
+      </c>
+      <c r="AQ37" s="8">
         <f t="shared" si="280"/>
-        <v>0.28812919349404981</v>
-      </c>
-      <c r="AN37" s="8">
-        <f t="shared" ref="AN37:BA37" si="281">AN20/AN10</f>
-        <v>0.23028240222454949</v>
-      </c>
-      <c r="AO37" s="8">
+        <v>0.22209864841913798</v>
+      </c>
+      <c r="AR37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.30046480875927528</v>
+      </c>
+      <c r="AS37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.21203807153261961</v>
+      </c>
+      <c r="AT37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.24006649446638517</v>
+      </c>
+      <c r="AU37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.28603671811164</v>
+      </c>
+      <c r="AV37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.32221733544930814</v>
+      </c>
+      <c r="AW37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.28755433479868059</v>
+      </c>
+      <c r="AX37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.29070908855078209</v>
+      </c>
+      <c r="AY37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.29354757870763037</v>
+      </c>
+      <c r="AZ37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.29526826601498057</v>
+      </c>
+      <c r="BA37" s="8">
+        <f t="shared" si="280"/>
+        <v>0.29664064290171399</v>
+      </c>
+      <c r="BB37" s="8">
+        <f t="shared" ref="BB37:BF37" si="281">BB20/BB10</f>
+        <v>0.29745052835951458</v>
+      </c>
+      <c r="BC37" s="8">
         <f t="shared" si="281"/>
-        <v>0.26171072731126527</v>
-      </c>
-      <c r="AP37" s="8">
+        <v>0.29773306972476565</v>
+      </c>
+      <c r="BD37" s="8">
         <f t="shared" si="281"/>
-        <v>0.22418554650092365</v>
-      </c>
-      <c r="AQ37" s="8">
+        <v>0.29698862216162819</v>
+      </c>
+      <c r="BE37" s="8">
         <f t="shared" si="281"/>
-        <v>0.22209864841913798</v>
-      </c>
-      <c r="AR37" s="8">
+        <v>0.29624999896132798</v>
+      </c>
+      <c r="BF37" s="8">
         <f t="shared" si="281"/>
-        <v>0.30046480875927528</v>
-      </c>
-      <c r="AS37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.21203807153261961</v>
-      </c>
-      <c r="AT37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.24006649446638517</v>
-      </c>
-      <c r="AU37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.28603671811164</v>
-      </c>
-      <c r="AV37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.3155089021072745</v>
-      </c>
-      <c r="AW37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.29877217825691943</v>
-      </c>
-      <c r="AX37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.30199454575349749</v>
-      </c>
-      <c r="AY37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.30467727341820067</v>
-      </c>
-      <c r="AZ37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.30588496170396001</v>
-      </c>
-      <c r="BA37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.30698765200874695</v>
-      </c>
-      <c r="BB37" s="8">
-        <f t="shared" ref="BB37:BF37" si="282">BB20/BB10</f>
-        <v>0.30773043846369302</v>
-      </c>
-      <c r="BC37" s="8">
-        <f t="shared" si="282"/>
-        <v>0.30797083061398067</v>
-      </c>
-      <c r="BD37" s="8">
-        <f t="shared" si="282"/>
-        <v>0.30724918467952417</v>
-      </c>
-      <c r="BE37" s="8">
-        <f t="shared" si="282"/>
-        <v>0.306532690625272</v>
-      </c>
-      <c r="BF37" s="8">
-        <f t="shared" si="282"/>
-        <v>0.30582152620024472</v>
+        <v>0.29551738660094518</v>
       </c>
       <c r="BH37" t="s">
         <v>49</v>
       </c>
       <c r="BI37" s="2">
         <f>BI36/BA21</f>
-        <v>248.30788903616664</v>
+        <v>252.23502655848986</v>
       </c>
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.3">
@@ -7687,7 +7664,7 @@
       </c>
       <c r="BI38" s="2">
         <f>Main!D3</f>
-        <v>249.85</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="39" spans="2:61" x14ac:dyDescent="0.3">
@@ -7696,15 +7673,25 @@
       </c>
       <c r="BI39" s="10">
         <f>BI37/BI38-1</f>
-        <v>-6.1721471436195774E-3</v>
+        <v>-0.14871742639726682</v>
       </c>
     </row>
     <row r="40" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG40" s="1">
+        <v>181269</v>
+      </c>
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1">
+        <v>190167</v>
+      </c>
       <c r="BH40" t="s">
         <v>52</v>
       </c>
       <c r="BI40" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/GOOG.xlsx
+++ b/Financial Analysis/GOOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA209DE-0E65-475A-95AC-9D48A73C9F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1158014C-8301-4962-86BE-D47DFB51FE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1C0874DB-3046-4806-9648-99CA4AF089C9}"/>
   </bookViews>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN19" authorId="0" shapeId="0" xr:uid="{BEB3E783-DDE4-4379-8D6C-2D62B9B58AC5}">
+    <comment ref="AR19" authorId="0" shapeId="0" xr:uid="{BEB3E783-DDE4-4379-8D6C-2D62B9B58AC5}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
   <si>
     <t>GOOG</t>
   </si>
@@ -383,10 +383,22 @@
     <t>Employees</t>
   </si>
   <si>
-    <t>Q325 8K</t>
-  </si>
-  <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -502,14 +514,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -526,7 +538,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23027640" y="0"/>
+          <a:off x="24239220" y="0"/>
           <a:ext cx="0" cy="8862060"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -552,14 +564,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -576,7 +588,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29169360" y="0"/>
+          <a:off x="32209740" y="0"/>
           <a:ext cx="0" cy="8511540"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -925,17 +937,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>296.3</v>
+        <v>329.3</v>
       </c>
       <c r="E3" s="4">
-        <v>45960</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45960</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
-        <v>46056</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -943,10 +955,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -955,7 +968,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>3581081.8000000003</v>
+        <v>3983542.1</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -963,11 +976,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <f>23466+72191+37982</f>
-        <v>133639</v>
+        <f>30708+96135+68687</f>
+        <v>195530</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -975,11 +988,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="1">
-        <f>10883</f>
-        <v>10883</v>
+        <f>46547</f>
+        <v>46547</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -988,7 +1001,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>122756</v>
+        <v>148983</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -997,7 +1010,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>3458325.8000000003</v>
+        <v>3834559.1</v>
       </c>
     </row>
   </sheetData>
@@ -1007,23 +1020,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB8BF10-D372-4210-91C6-9A1DF33E84B0}">
-  <dimension ref="B1:GK40"/>
+  <dimension ref="B1:GO40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="40" max="40" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="57" width="8.88671875" customWidth="1"/>
-    <col min="60" max="60" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="8.88671875" customWidth="1"/>
+    <col min="64" max="64" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:58" x14ac:dyDescent="0.3">
-      <c r="AN1" t="s">
+    <row r="1" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:62" x14ac:dyDescent="0.3">
       <c r="C2" s="5" t="s">
         <v>39</v>
       </c>
@@ -1132,65 +1145,77 @@
       <c r="AL2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AN2">
+      <c r="AM2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR2">
         <v>2017</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2018</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2019</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2020</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2021</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2022</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2023</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2024</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2025</v>
       </c>
-      <c r="AW2">
+      <c r="BA2">
         <v>2026</v>
       </c>
-      <c r="AX2">
+      <c r="BB2">
         <v>2027</v>
       </c>
-      <c r="AY2">
+      <c r="BC2">
         <v>2028</v>
       </c>
-      <c r="AZ2">
+      <c r="BD2">
         <v>2029</v>
       </c>
-      <c r="BA2">
+      <c r="BE2">
         <v>2030</v>
       </c>
-      <c r="BB2">
+      <c r="BF2">
         <v>2031</v>
       </c>
-      <c r="BC2">
+      <c r="BG2">
         <v>2032</v>
       </c>
-      <c r="BD2">
+      <c r="BH2">
         <v>2033</v>
       </c>
-      <c r="BE2">
+      <c r="BI2">
         <v>2034</v>
       </c>
-      <c r="BF2">
+      <c r="BJ2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>74</v>
       </c>
@@ -1228,7 +1253,7 @@
         <v>44026</v>
       </c>
       <c r="AD3" s="11">
-        <f>AT3-AC3-AB3-AA3</f>
+        <f>AX3-AC3-AB3-AA3</f>
         <v>48020</v>
       </c>
       <c r="AE3" s="11">
@@ -1253,74 +1278,77 @@
         <v>56567</v>
       </c>
       <c r="AL3" s="11">
-        <f>AH3*1.12</f>
-        <v>60518.080000000009</v>
-      </c>
-      <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1"/>
-      <c r="AQ3" s="1">
+        <v>63073</v>
+      </c>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1">
         <v>104062</v>
       </c>
-      <c r="AR3" s="1">
+      <c r="AV3" s="1">
         <v>148951</v>
       </c>
-      <c r="AS3" s="1">
+      <c r="AW3" s="1">
         <v>162450</v>
       </c>
-      <c r="AT3" s="1">
+      <c r="AX3" s="1">
         <v>175033</v>
       </c>
-      <c r="AU3" s="1">
+      <c r="AY3" s="1">
         <f>SUM(AE3:AH3)</f>
         <v>198084</v>
       </c>
-      <c r="AV3" s="1">
+      <c r="AZ3" s="1">
         <f>SUM(AI3:AL3)</f>
-        <v>221977.08000000002</v>
-      </c>
-      <c r="AW3" s="1">
-        <f>AV3*1.09</f>
-        <v>241955.01720000003</v>
-      </c>
-      <c r="AX3" s="1">
-        <f>AW3*1.06</f>
-        <v>256472.31823200005</v>
-      </c>
-      <c r="AY3" s="1">
-        <f>AX3*1.04</f>
-        <v>266731.21096128004</v>
-      </c>
-      <c r="AZ3" s="1">
-        <f>AY3*1.03</f>
-        <v>274733.14729011845</v>
+        <v>224532</v>
       </c>
       <c r="BA3" s="1">
-        <f t="shared" ref="BA3" si="0">AZ3*1.02</f>
-        <v>280227.81023592083</v>
+        <f>AZ3*1.09</f>
+        <v>244739.88</v>
       </c>
       <c r="BB3" s="1">
-        <f t="shared" ref="BB3" si="1">BA3*1.02</f>
-        <v>285832.36644063925</v>
+        <f>BA3*1.06</f>
+        <v>259424.27280000001</v>
       </c>
       <c r="BC3" s="1">
-        <f t="shared" ref="BC3" si="2">BB3*1.02</f>
-        <v>291549.01376945205</v>
+        <f>BB3*1.04</f>
+        <v>269801.24371200002</v>
       </c>
       <c r="BD3" s="1">
-        <f t="shared" ref="BD3:BF3" si="3">BC3*1.01</f>
-        <v>294464.50390714657</v>
+        <f>BC3*1.03</f>
+        <v>277895.28102336003</v>
       </c>
       <c r="BE3" s="1">
+        <f t="shared" ref="BE3" si="0">BD3*1.02</f>
+        <v>283453.18664382724</v>
+      </c>
+      <c r="BF3" s="1">
+        <f t="shared" ref="BF3" si="1">BE3*1.02</f>
+        <v>289122.2503767038</v>
+      </c>
+      <c r="BG3" s="1">
+        <f t="shared" ref="BG3" si="2">BF3*1.02</f>
+        <v>294904.69538423786</v>
+      </c>
+      <c r="BH3" s="1">
+        <f t="shared" ref="BH3:BJ3" si="3">BG3*1.01</f>
+        <v>297853.74233808025</v>
+      </c>
+      <c r="BI3" s="1">
         <f t="shared" si="3"/>
-        <v>297409.14894621802</v>
-      </c>
-      <c r="BF3" s="1">
+        <v>300832.27976146108</v>
+      </c>
+      <c r="BJ3" s="1">
         <f t="shared" si="3"/>
-        <v>300383.2404356802</v>
+        <v>303840.60255907569</v>
       </c>
     </row>
-    <row r="4" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>73</v>
       </c>
@@ -1358,7 +1386,7 @@
         <v>7952</v>
       </c>
       <c r="AD4" s="11">
-        <f t="shared" ref="AD4:AD9" si="4">AT4-AC4-AB4-AA4</f>
+        <f t="shared" ref="AD4:AD9" si="4">AX4-AC4-AB4-AA4</f>
         <v>9200</v>
       </c>
       <c r="AE4" s="11">
@@ -1383,74 +1411,77 @@
         <v>10261</v>
       </c>
       <c r="AL4" s="11">
-        <f>AH4*1.12</f>
-        <v>11729.76</v>
-      </c>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="1">
+        <v>11383</v>
+      </c>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AR4" s="1"/>
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="1"/>
+      <c r="AU4" s="1">
         <v>19772</v>
       </c>
-      <c r="AR4" s="1">
+      <c r="AV4" s="1">
         <v>28845</v>
       </c>
-      <c r="AS4" s="1">
+      <c r="AW4" s="1">
         <v>29243</v>
       </c>
-      <c r="AT4" s="1">
+      <c r="AX4" s="1">
         <v>31510</v>
       </c>
-      <c r="AU4" s="1">
-        <f t="shared" ref="AU4:AU9" si="5">SUM(AE4:AH4)</f>
+      <c r="AY4" s="1">
+        <f t="shared" ref="AY4:AY9" si="5">SUM(AE4:AH4)</f>
         <v>36147</v>
       </c>
-      <c r="AV4" s="1">
-        <f t="shared" ref="AV4:AV9" si="6">SUM(AI4:AL4)</f>
-        <v>40713.760000000002</v>
-      </c>
-      <c r="AW4" s="1">
-        <f>AV4*1.08</f>
-        <v>43970.860800000002</v>
-      </c>
-      <c r="AX4" s="1">
-        <f>AW4*1.06</f>
-        <v>46609.112448000007</v>
-      </c>
-      <c r="AY4" s="1">
-        <f>AX4*1.04</f>
-        <v>48473.476945920011</v>
-      </c>
       <c r="AZ4" s="1">
-        <f>AY4*1.03</f>
-        <v>49927.681254297611</v>
+        <f t="shared" ref="AZ4:AZ9" si="6">SUM(AI4:AL4)</f>
+        <v>40367</v>
       </c>
       <c r="BA4" s="1">
-        <f>AZ4*1.03</f>
-        <v>51425.511691926542</v>
+        <f>AZ4*1.08</f>
+        <v>43596.36</v>
       </c>
       <c r="BB4" s="1">
-        <f>BA4*1.02</f>
-        <v>52454.021925765075</v>
+        <f>BA4*1.06</f>
+        <v>46212.141600000003</v>
       </c>
       <c r="BC4" s="1">
-        <f t="shared" ref="BC4:BF4" si="7">BB4*1.02</f>
-        <v>53503.102364280378</v>
+        <f>BB4*1.04</f>
+        <v>48060.627264000002</v>
       </c>
       <c r="BD4" s="1">
+        <f>BC4*1.03</f>
+        <v>49502.446081920003</v>
+      </c>
+      <c r="BE4" s="1">
+        <f>BD4*1.03</f>
+        <v>50987.519464377605</v>
+      </c>
+      <c r="BF4" s="1">
+        <f>BE4*1.02</f>
+        <v>52007.269853665159</v>
+      </c>
+      <c r="BG4" s="1">
+        <f t="shared" ref="BG4:BJ4" si="7">BF4*1.02</f>
+        <v>53047.415250738464</v>
+      </c>
+      <c r="BH4" s="1">
         <f t="shared" si="7"/>
-        <v>54573.164411565987</v>
-      </c>
-      <c r="BE4" s="1">
+        <v>54108.363555753233</v>
+      </c>
+      <c r="BI4" s="1">
         <f t="shared" si="7"/>
-        <v>55664.627699797311</v>
-      </c>
-      <c r="BF4" s="1">
+        <v>55190.5308268683</v>
+      </c>
+      <c r="BJ4" s="1">
         <f t="shared" si="7"/>
-        <v>56777.920253793258</v>
+        <v>56294.341443405669</v>
       </c>
     </row>
-    <row r="5" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>75</v>
       </c>
@@ -1513,74 +1544,77 @@
         <v>7354</v>
       </c>
       <c r="AL5" s="11">
-        <f t="shared" ref="AL5" si="8">AH5*0.98</f>
-        <v>7794.92</v>
-      </c>
-      <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1"/>
-      <c r="AQ5" s="1">
+        <v>7828</v>
+      </c>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1">
         <v>23090</v>
       </c>
-      <c r="AR5" s="1">
+      <c r="AV5" s="1">
         <v>31701</v>
       </c>
-      <c r="AS5" s="1">
+      <c r="AW5" s="1">
         <v>32780</v>
       </c>
-      <c r="AT5" s="1">
+      <c r="AX5" s="1">
         <v>31312</v>
       </c>
-      <c r="AU5" s="1">
+      <c r="AY5" s="1">
         <f t="shared" si="5"/>
         <v>30359</v>
       </c>
-      <c r="AV5" s="1">
+      <c r="AZ5" s="1">
         <f t="shared" si="6"/>
-        <v>29758.92</v>
-      </c>
-      <c r="AW5" s="1">
-        <f>AV5*1.01</f>
-        <v>30056.509199999997</v>
-      </c>
-      <c r="AX5" s="1">
-        <f t="shared" ref="AX5:BF5" si="9">AW5*1.01</f>
-        <v>30357.074291999998</v>
-      </c>
-      <c r="AY5" s="1">
-        <f t="shared" si="9"/>
-        <v>30660.645034919999</v>
-      </c>
-      <c r="AZ5" s="1">
-        <f t="shared" si="9"/>
-        <v>30967.2514852692</v>
+        <v>29792</v>
       </c>
       <c r="BA5" s="1">
-        <f t="shared" si="9"/>
-        <v>31276.924000121893</v>
+        <f>AZ5*1.01</f>
+        <v>30089.920000000002</v>
       </c>
       <c r="BB5" s="1">
-        <f t="shared" si="9"/>
-        <v>31589.693240123113</v>
+        <f t="shared" ref="BB5:BJ5" si="8">BA5*1.01</f>
+        <v>30390.819200000002</v>
       </c>
       <c r="BC5" s="1">
-        <f t="shared" si="9"/>
-        <v>31905.590172524346</v>
+        <f t="shared" si="8"/>
+        <v>30694.727392000001</v>
       </c>
       <c r="BD5" s="1">
-        <f t="shared" si="9"/>
-        <v>32224.646074249591</v>
+        <f t="shared" si="8"/>
+        <v>31001.67466592</v>
       </c>
       <c r="BE5" s="1">
-        <f t="shared" si="9"/>
-        <v>32546.892534992086</v>
+        <f t="shared" si="8"/>
+        <v>31311.691412579199</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" si="9"/>
-        <v>32872.361460342006</v>
+        <f t="shared" si="8"/>
+        <v>31624.808326704991</v>
+      </c>
+      <c r="BG5" s="1">
+        <f t="shared" si="8"/>
+        <v>31941.056409972043</v>
+      </c>
+      <c r="BH5" s="1">
+        <f t="shared" si="8"/>
+        <v>32260.466974071765</v>
+      </c>
+      <c r="BI5" s="1">
+        <f t="shared" si="8"/>
+        <v>32583.071643812484</v>
+      </c>
+      <c r="BJ5" s="1">
+        <f t="shared" si="8"/>
+        <v>32908.902360250606</v>
       </c>
     </row>
-    <row r="6" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>76</v>
       </c>
@@ -1643,74 +1677,77 @@
         <v>12870</v>
       </c>
       <c r="AL6" s="11">
-        <f>AH6*1.19</f>
-        <v>13843.269999999999</v>
-      </c>
-      <c r="AN6" s="1"/>
-      <c r="AO6" s="1"/>
-      <c r="AP6" s="1"/>
-      <c r="AQ6" s="1">
+        <v>13578</v>
+      </c>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1">
         <v>21711</v>
       </c>
-      <c r="AR6" s="1">
+      <c r="AV6" s="1">
         <v>28032</v>
       </c>
-      <c r="AS6" s="1">
+      <c r="AW6" s="1">
         <v>29055</v>
       </c>
-      <c r="AT6" s="1">
+      <c r="AX6" s="1">
         <v>34688</v>
       </c>
-      <c r="AU6" s="1">
+      <c r="AY6" s="1">
         <f t="shared" si="5"/>
         <v>40340</v>
       </c>
-      <c r="AV6" s="1">
+      <c r="AZ6" s="1">
         <f t="shared" si="6"/>
-        <v>48295.27</v>
-      </c>
-      <c r="AW6" s="1">
-        <f>AV6*1.12</f>
-        <v>54090.702400000002</v>
-      </c>
-      <c r="AX6" s="1">
-        <f>AW6*1.08</f>
-        <v>58417.958592000003</v>
-      </c>
-      <c r="AY6" s="1">
-        <f>AX6*1.06</f>
-        <v>61923.036107520005</v>
-      </c>
-      <c r="AZ6" s="1">
-        <f>AY6*1.05</f>
-        <v>65019.187912896006</v>
+        <v>48030</v>
       </c>
       <c r="BA6" s="1">
-        <f>AZ6*1.04</f>
-        <v>67619.955429411842</v>
+        <f>AZ6*1.12</f>
+        <v>53793.600000000006</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" ref="BB6:BF6" si="10">BA6*1.03</f>
-        <v>69648.554092294202</v>
+        <f>BA6*1.08</f>
+        <v>58097.088000000011</v>
       </c>
       <c r="BC6" s="1">
-        <f t="shared" si="10"/>
-        <v>71738.010715063036</v>
+        <f>BB6*1.06</f>
+        <v>61582.913280000015</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="10"/>
-        <v>73890.15103651493</v>
+        <f>BC6*1.05</f>
+        <v>64662.058944000019</v>
       </c>
       <c r="BE6" s="1">
-        <f t="shared" si="10"/>
-        <v>76106.855567610386</v>
+        <f>BD6*1.04</f>
+        <v>67248.541301760022</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="10"/>
-        <v>78390.061234638706</v>
+        <f t="shared" ref="BF6:BJ6" si="9">BE6*1.03</f>
+        <v>69265.997540812823</v>
+      </c>
+      <c r="BG6" s="1">
+        <f t="shared" si="9"/>
+        <v>71343.977467037214</v>
+      </c>
+      <c r="BH6" s="1">
+        <f t="shared" si="9"/>
+        <v>73484.296791048328</v>
+      </c>
+      <c r="BI6" s="1">
+        <f t="shared" si="9"/>
+        <v>75688.825694779778</v>
+      </c>
+      <c r="BJ6" s="1">
+        <f t="shared" si="9"/>
+        <v>77959.490465623167</v>
       </c>
     </row>
-    <row r="7" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>77</v>
       </c>
@@ -1773,74 +1810,77 @@
         <v>15157</v>
       </c>
       <c r="AL7" s="11">
-        <f>AH7*1.32</f>
-        <v>15780.6</v>
-      </c>
-      <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="1">
+        <v>17664</v>
+      </c>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="11"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1">
         <v>13059</v>
       </c>
-      <c r="AR7" s="1">
+      <c r="AV7" s="1">
         <v>19206</v>
       </c>
-      <c r="AS7" s="1">
+      <c r="AW7" s="1">
         <v>26280</v>
       </c>
-      <c r="AT7" s="1">
+      <c r="AX7" s="1">
         <v>33088</v>
       </c>
-      <c r="AU7" s="1">
+      <c r="AY7" s="1">
         <f t="shared" si="5"/>
         <v>43229</v>
       </c>
-      <c r="AV7" s="1">
+      <c r="AZ7" s="1">
         <f t="shared" si="6"/>
-        <v>56821.599999999999</v>
-      </c>
-      <c r="AW7" s="1">
-        <f>AV7*1.2</f>
-        <v>68185.919999999998</v>
-      </c>
-      <c r="AX7" s="1">
-        <f>AW7*1.15</f>
-        <v>78413.80799999999</v>
-      </c>
-      <c r="AY7" s="1">
-        <f>AX7*1.1</f>
-        <v>86255.188799999989</v>
-      </c>
-      <c r="AZ7" s="1">
-        <f>AY7*1.08</f>
-        <v>93155.603903999989</v>
+        <v>58705</v>
       </c>
       <c r="BA7" s="1">
-        <f>AZ7*1.06</f>
-        <v>98744.940138239996</v>
+        <f>AZ7*1.2</f>
+        <v>70446</v>
       </c>
       <c r="BB7" s="1">
-        <f>BA7*1.05</f>
-        <v>103682.187145152</v>
+        <f>BA7*1.15</f>
+        <v>81012.899999999994</v>
       </c>
       <c r="BC7" s="1">
-        <f>BB7*1.03</f>
-        <v>106792.65275950656</v>
+        <f>BB7*1.1</f>
+        <v>89114.19</v>
       </c>
       <c r="BD7" s="1">
-        <f>BC7*1.02</f>
-        <v>108928.50581469669</v>
+        <f>BC7*1.08</f>
+        <v>96243.325200000007</v>
       </c>
       <c r="BE7" s="1">
-        <f t="shared" ref="BE7:BF7" si="11">BD7*1.02</f>
-        <v>111107.07593099063</v>
+        <f>BD7*1.06</f>
+        <v>102017.92471200001</v>
       </c>
       <c r="BF7" s="1">
-        <f t="shared" si="11"/>
-        <v>113329.21744961044</v>
+        <f>BE7*1.05</f>
+        <v>107118.82094760002</v>
+      </c>
+      <c r="BG7" s="1">
+        <f>BF7*1.03</f>
+        <v>110332.38557602803</v>
+      </c>
+      <c r="BH7" s="1">
+        <f>BG7*1.02</f>
+        <v>112539.03328754859</v>
+      </c>
+      <c r="BI7" s="1">
+        <f t="shared" ref="BI7:BJ7" si="10">BH7*1.02</f>
+        <v>114789.81395329957</v>
+      </c>
+      <c r="BJ7" s="1">
+        <f t="shared" si="10"/>
+        <v>117085.61023236557</v>
       </c>
     </row>
-    <row r="8" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>78</v>
       </c>
@@ -1903,74 +1943,77 @@
         <v>344</v>
       </c>
       <c r="AL8" s="11">
-        <f>AH8*1.05</f>
-        <v>420</v>
-      </c>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="1">
+        <v>370</v>
+      </c>
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="11"/>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="11"/>
+      <c r="AR8" s="1"/>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="1"/>
+      <c r="AU8" s="1">
         <v>657</v>
       </c>
-      <c r="AR8" s="1">
+      <c r="AV8" s="1">
         <v>753</v>
       </c>
-      <c r="AS8" s="1">
+      <c r="AW8" s="1">
         <v>1068</v>
       </c>
-      <c r="AT8" s="1">
+      <c r="AX8" s="1">
         <v>1527</v>
       </c>
-      <c r="AU8" s="1">
+      <c r="AY8" s="1">
         <f t="shared" si="5"/>
         <v>1648</v>
       </c>
-      <c r="AV8" s="1">
+      <c r="AZ8" s="1">
         <f t="shared" si="6"/>
-        <v>1587</v>
-      </c>
-      <c r="AW8" s="1">
-        <f>AV8*1.25</f>
-        <v>1983.75</v>
-      </c>
-      <c r="AX8" s="1">
-        <f>AW8*1.2</f>
-        <v>2380.5</v>
-      </c>
-      <c r="AY8" s="1">
-        <f>AX8*1.15</f>
-        <v>2737.5749999999998</v>
-      </c>
-      <c r="AZ8" s="1">
-        <f>AY8*1.1</f>
-        <v>3011.3325</v>
+        <v>1537</v>
       </c>
       <c r="BA8" s="1">
-        <f>AZ8*1.05</f>
-        <v>3161.8991249999999</v>
+        <f>AZ8*1.25</f>
+        <v>1921.25</v>
       </c>
       <c r="BB8" s="1">
-        <f t="shared" ref="BB8:BF8" si="12">BA8*1.05</f>
-        <v>3319.9940812499999</v>
+        <f>BA8*1.2</f>
+        <v>2305.5</v>
       </c>
       <c r="BC8" s="1">
-        <f t="shared" si="12"/>
-        <v>3485.9937853125002</v>
+        <f>BB8*1.15</f>
+        <v>2651.3249999999998</v>
       </c>
       <c r="BD8" s="1">
-        <f t="shared" si="12"/>
-        <v>3660.2934745781254</v>
+        <f>BC8*1.1</f>
+        <v>2916.4575</v>
       </c>
       <c r="BE8" s="1">
-        <f t="shared" si="12"/>
-        <v>3843.3081483070318</v>
+        <f>BD8*1.05</f>
+        <v>3062.2803750000003</v>
       </c>
       <c r="BF8" s="1">
-        <f t="shared" si="12"/>
-        <v>4035.4735557223835</v>
+        <f t="shared" ref="BF8:BJ8" si="11">BE8*1.05</f>
+        <v>3215.3943937500003</v>
+      </c>
+      <c r="BG8" s="1">
+        <f t="shared" si="11"/>
+        <v>3376.1641134375004</v>
+      </c>
+      <c r="BH8" s="1">
+        <f t="shared" si="11"/>
+        <v>3544.9723191093758</v>
+      </c>
+      <c r="BI8" s="1">
+        <f t="shared" si="11"/>
+        <v>3722.2209350648445</v>
+      </c>
+      <c r="BJ8" s="1">
+        <f t="shared" si="11"/>
+        <v>3908.3319818180871</v>
       </c>
     </row>
-    <row r="9" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>79</v>
       </c>
@@ -2033,73 +2076,77 @@
         <v>-207</v>
       </c>
       <c r="AL9" s="11">
-        <v>50</v>
-      </c>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="1">
+        <v>-68</v>
+      </c>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="11"/>
+      <c r="AP9" s="11"/>
+      <c r="AR9" s="1"/>
+      <c r="AS9" s="1"/>
+      <c r="AT9" s="1"/>
+      <c r="AU9" s="1">
         <v>176</v>
       </c>
-      <c r="AR9" s="1">
+      <c r="AV9" s="1">
         <v>149</v>
       </c>
-      <c r="AS9" s="1">
+      <c r="AW9" s="1">
         <v>1960</v>
       </c>
-      <c r="AT9" s="1">
+      <c r="AX9" s="1">
         <v>236</v>
       </c>
-      <c r="AU9" s="1">
+      <c r="AY9" s="1">
         <f t="shared" si="5"/>
         <v>211</v>
       </c>
-      <c r="AV9" s="1">
+      <c r="AZ9" s="1">
         <f t="shared" si="6"/>
-        <v>-9</v>
-      </c>
-      <c r="AW9" s="1">
-        <f t="shared" ref="AW9:BF9" si="13">AV9*1.02</f>
-        <v>-9.18</v>
-      </c>
-      <c r="AX9" s="1">
-        <f t="shared" si="13"/>
-        <v>-9.3635999999999999</v>
-      </c>
-      <c r="AY9" s="1">
-        <f t="shared" si="13"/>
-        <v>-9.550872</v>
-      </c>
-      <c r="AZ9" s="1">
-        <f t="shared" si="13"/>
-        <v>-9.7418894399999996</v>
+        <v>-127</v>
       </c>
       <c r="BA9" s="1">
-        <f t="shared" si="13"/>
-        <v>-9.9367272288000006</v>
+        <f t="shared" ref="BA9:BJ9" si="12">AZ9*1.02</f>
+        <v>-129.54</v>
       </c>
       <c r="BB9" s="1">
-        <f t="shared" si="13"/>
-        <v>-10.135461773376001</v>
+        <f t="shared" si="12"/>
+        <v>-132.13079999999999</v>
       </c>
       <c r="BC9" s="1">
-        <f t="shared" si="13"/>
-        <v>-10.338171008843521</v>
+        <f t="shared" si="12"/>
+        <v>-134.773416</v>
       </c>
       <c r="BD9" s="1">
-        <f t="shared" si="13"/>
-        <v>-10.54493442902039</v>
+        <f t="shared" si="12"/>
+        <v>-137.46888432</v>
       </c>
       <c r="BE9" s="1">
-        <f t="shared" si="13"/>
-        <v>-10.755833117600798</v>
+        <f t="shared" si="12"/>
+        <v>-140.21826200640001</v>
       </c>
       <c r="BF9" s="1">
-        <f t="shared" si="13"/>
-        <v>-10.970949779952814</v>
+        <f t="shared" si="12"/>
+        <v>-143.022627246528</v>
+      </c>
+      <c r="BG9" s="1">
+        <f t="shared" si="12"/>
+        <v>-145.88307979145856</v>
+      </c>
+      <c r="BH9" s="1">
+        <f t="shared" si="12"/>
+        <v>-148.80074138728773</v>
+      </c>
+      <c r="BI9" s="1">
+        <f t="shared" si="12"/>
+        <v>-151.77675621503349</v>
+      </c>
+      <c r="BJ9" s="1">
+        <f t="shared" si="12"/>
+        <v>-154.81229133933417</v>
       </c>
     </row>
-    <row r="10" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:62" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
@@ -2210,95 +2257,99 @@
         <v>90234</v>
       </c>
       <c r="AJ10" s="9">
-        <f t="shared" ref="AJ10:AL10" si="14">SUM(AJ3:AJ9)</f>
+        <f t="shared" ref="AJ10:AL10" si="13">SUM(AJ3:AJ9)</f>
         <v>96428</v>
       </c>
       <c r="AK10" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>102346</v>
       </c>
       <c r="AL10" s="9">
-        <f t="shared" si="14"/>
-        <v>110136.63000000002</v>
-      </c>
-      <c r="AN10" s="9">
+        <f t="shared" si="13"/>
+        <v>113828</v>
+      </c>
+      <c r="AM10" s="9"/>
+      <c r="AN10" s="9"/>
+      <c r="AO10" s="9"/>
+      <c r="AP10" s="9"/>
+      <c r="AR10" s="9">
         <f>SUM(C10:F10)</f>
         <v>110764</v>
       </c>
-      <c r="AO10" s="9">
+      <c r="AS10" s="9">
         <f>SUM(G10:J10)</f>
         <v>136819</v>
       </c>
-      <c r="AP10" s="9">
+      <c r="AT10" s="9">
         <f>SUM(K10:N10)</f>
         <v>161857</v>
       </c>
-      <c r="AQ10" s="9">
+      <c r="AU10" s="9">
         <f>SUM(O10:R10)</f>
         <v>182527</v>
       </c>
-      <c r="AR10" s="9">
+      <c r="AV10" s="9">
         <f>SUM(S10:V10)</f>
         <v>251071</v>
       </c>
-      <c r="AS10" s="9">
+      <c r="AW10" s="9">
         <f>SUM(W10:Z10)</f>
         <v>282836</v>
       </c>
-      <c r="AT10" s="9">
+      <c r="AX10" s="9">
         <f>SUM(AA10:AD10)</f>
         <v>307394</v>
       </c>
-      <c r="AU10" s="9">
-        <f>SUM(AU3:AU9)</f>
+      <c r="AY10" s="9">
+        <f>SUM(AY3:AY9)</f>
         <v>350018</v>
       </c>
-      <c r="AV10" s="9">
-        <f>SUM(AV3:AV9)</f>
-        <v>399144.63</v>
-      </c>
-      <c r="AW10" s="9">
-        <f t="shared" ref="AW10:BF10" si="15">SUM(AW3:AW9)</f>
-        <v>440233.5796</v>
-      </c>
-      <c r="AX10" s="9">
-        <f t="shared" si="15"/>
-        <v>472641.40796400007</v>
-      </c>
-      <c r="AY10" s="9">
-        <f t="shared" si="15"/>
-        <v>496771.5819776401</v>
-      </c>
       <c r="AZ10" s="9">
-        <f t="shared" si="15"/>
-        <v>516804.46245714126</v>
+        <f>SUM(AZ3:AZ9)</f>
+        <v>402836</v>
       </c>
       <c r="BA10" s="9">
-        <f t="shared" si="15"/>
-        <v>532447.10389339225</v>
+        <f t="shared" ref="BA10:BJ10" si="14">SUM(BA3:BA9)</f>
+        <v>444457.47000000003</v>
       </c>
       <c r="BB10" s="9">
-        <f t="shared" si="15"/>
-        <v>546516.68146345031</v>
+        <f t="shared" si="14"/>
+        <v>477310.59080000006</v>
       </c>
       <c r="BC10" s="9">
-        <f t="shared" si="15"/>
-        <v>558964.02539513004</v>
+        <f t="shared" si="14"/>
+        <v>501770.25323200005</v>
       </c>
       <c r="BD10" s="9">
-        <f t="shared" si="15"/>
-        <v>567730.71978432289</v>
+        <f t="shared" si="14"/>
+        <v>522083.77453088009</v>
       </c>
       <c r="BE10" s="9">
-        <f t="shared" si="15"/>
-        <v>576667.1529947978</v>
+        <f t="shared" si="14"/>
+        <v>537940.92564753769</v>
       </c>
       <c r="BF10" s="9">
-        <f t="shared" si="15"/>
-        <v>585777.30344000703</v>
+        <f t="shared" si="14"/>
+        <v>552211.51881199027</v>
+      </c>
+      <c r="BG10" s="9">
+        <f t="shared" si="14"/>
+        <v>564799.81112165959</v>
+      </c>
+      <c r="BH10" s="9">
+        <f t="shared" si="14"/>
+        <v>573642.07452422427</v>
+      </c>
+      <c r="BI10" s="9">
+        <f t="shared" si="14"/>
+        <v>582654.96605907101</v>
+      </c>
+      <c r="BJ10" s="9">
+        <f t="shared" si="14"/>
+        <v>591842.46675119933</v>
       </c>
     </row>
-    <row r="11" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>23</v>
       </c>
@@ -2408,312 +2459,319 @@
         <v>41369</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" ref="AL11" si="16">AL10-AL12</f>
-        <v>44054.652000000016</v>
-      </c>
-      <c r="AN11" s="1">
+        <v>45766</v>
+      </c>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="1"/>
+      <c r="AP11" s="1"/>
+      <c r="AR11" s="1">
         <f>SUM(C11:F11)</f>
         <v>45583</v>
       </c>
-      <c r="AO11" s="1">
+      <c r="AS11" s="1">
         <f>SUM(G11:J11)</f>
         <v>59549</v>
       </c>
-      <c r="AP11" s="1">
+      <c r="AT11" s="1">
         <f>SUM(K11:N11)</f>
         <v>71896</v>
       </c>
-      <c r="AQ11" s="1">
+      <c r="AU11" s="1">
         <f>SUM(O11:R11)</f>
         <v>84732</v>
       </c>
-      <c r="AR11" s="1">
+      <c r="AV11" s="1">
         <f>SUM(S11:V11)</f>
         <v>108815</v>
       </c>
-      <c r="AS11" s="1">
+      <c r="AW11" s="1">
         <f>SUM(W11:Z11)</f>
         <v>126203</v>
       </c>
-      <c r="AT11" s="1">
+      <c r="AX11" s="1">
         <f>SUM(AA11:AD11)</f>
         <v>133332</v>
       </c>
-      <c r="AU11" s="1">
+      <c r="AY11" s="1">
         <f>SUM(AE11:AH11)</f>
         <v>146306</v>
       </c>
-      <c r="AV11" s="1">
+      <c r="AZ11" s="1">
         <f>SUM(AI11:AL11)</f>
-        <v>160823.652</v>
-      </c>
-      <c r="AW11" s="1">
-        <f t="shared" ref="AW11:BA11" si="17">AW10-AW12</f>
-        <v>176093.43184000003</v>
-      </c>
-      <c r="AX11" s="1">
-        <f t="shared" si="17"/>
-        <v>189056.56318560004</v>
-      </c>
-      <c r="AY11" s="1">
-        <f t="shared" si="17"/>
-        <v>198708.63279105606</v>
-      </c>
-      <c r="AZ11" s="1">
-        <f t="shared" si="17"/>
-        <v>206721.78498285654</v>
+        <v>162535</v>
       </c>
       <c r="BA11" s="1">
-        <f t="shared" si="17"/>
-        <v>212978.84155735694</v>
+        <f t="shared" ref="BA11:BE11" si="15">BA10-BA12</f>
+        <v>177782.98800000001</v>
       </c>
       <c r="BB11" s="1">
-        <f t="shared" ref="BB11:BF11" si="18">BB10-BB12</f>
-        <v>218606.67258538015</v>
+        <f t="shared" si="15"/>
+        <v>190924.23632000003</v>
       </c>
       <c r="BC11" s="1">
-        <f t="shared" si="18"/>
-        <v>223585.610158052</v>
+        <f t="shared" si="15"/>
+        <v>200708.10129280004</v>
       </c>
       <c r="BD11" s="1">
-        <f t="shared" si="18"/>
-        <v>227092.28791372915</v>
+        <f t="shared" si="15"/>
+        <v>208833.50981235207</v>
       </c>
       <c r="BE11" s="1">
-        <f t="shared" si="18"/>
-        <v>230666.86119791912</v>
+        <f t="shared" si="15"/>
+        <v>215176.37025901506</v>
       </c>
       <c r="BF11" s="1">
-        <f t="shared" si="18"/>
-        <v>234310.92137600284</v>
+        <f t="shared" ref="BF11:BJ11" si="16">BF10-BF12</f>
+        <v>220884.6075247961</v>
+      </c>
+      <c r="BG11" s="1">
+        <f t="shared" si="16"/>
+        <v>225919.92444866383</v>
+      </c>
+      <c r="BH11" s="1">
+        <f t="shared" si="16"/>
+        <v>229456.82980968972</v>
+      </c>
+      <c r="BI11" s="1">
+        <f t="shared" si="16"/>
+        <v>233061.9864236284</v>
+      </c>
+      <c r="BJ11" s="1">
+        <f t="shared" si="16"/>
+        <v>236736.98670047976</v>
       </c>
     </row>
-    <row r="12" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:62" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" ref="C12:T12" si="19">C10-C11</f>
+        <f t="shared" ref="C12:T12" si="17">C10-C11</f>
         <v>14955</v>
       </c>
       <c r="D12" s="9">
+        <f t="shared" si="17"/>
+        <v>15637</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="17"/>
+        <v>16624</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="17"/>
+        <v>17965</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" si="17"/>
+        <v>17679</v>
+      </c>
+      <c r="H12" s="9">
+        <f t="shared" si="17"/>
+        <v>18774</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="17"/>
+        <v>19459</v>
+      </c>
+      <c r="J12" s="9">
+        <f t="shared" si="17"/>
+        <v>21358</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="17"/>
+        <v>20327</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="17"/>
+        <v>21648</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="17"/>
+        <v>22931</v>
+      </c>
+      <c r="N12" s="9">
+        <f t="shared" si="17"/>
+        <v>25055</v>
+      </c>
+      <c r="O12" s="9">
+        <f t="shared" si="17"/>
+        <v>22177</v>
+      </c>
+      <c r="P12" s="9">
+        <f t="shared" si="17"/>
+        <v>19744</v>
+      </c>
+      <c r="Q12" s="9">
+        <f t="shared" si="17"/>
+        <v>25056</v>
+      </c>
+      <c r="R12" s="9">
+        <f t="shared" si="17"/>
+        <v>30818</v>
+      </c>
+      <c r="S12" s="9">
+        <f t="shared" si="17"/>
+        <v>31211</v>
+      </c>
+      <c r="T12" s="9">
+        <f t="shared" si="17"/>
+        <v>31211</v>
+      </c>
+      <c r="U12" s="9">
+        <f t="shared" ref="U12:V12" si="18">U10-U11</f>
+        <v>37497</v>
+      </c>
+      <c r="V12" s="9">
+        <f t="shared" si="18"/>
+        <v>42337</v>
+      </c>
+      <c r="W12" s="9">
+        <f t="shared" ref="W12:X12" si="19">W10-W11</f>
+        <v>38412</v>
+      </c>
+      <c r="X12" s="9">
         <f t="shared" si="19"/>
-        <v>15637</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="19"/>
-        <v>16624</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="19"/>
-        <v>17965</v>
-      </c>
-      <c r="G12" s="9">
-        <f t="shared" si="19"/>
-        <v>17679</v>
-      </c>
-      <c r="H12" s="9">
-        <f t="shared" si="19"/>
-        <v>18774</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="19"/>
-        <v>19459</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="19"/>
-        <v>21358</v>
-      </c>
-      <c r="K12" s="9">
-        <f t="shared" si="19"/>
-        <v>20327</v>
-      </c>
-      <c r="L12" s="9">
-        <f t="shared" si="19"/>
-        <v>21648</v>
-      </c>
-      <c r="M12" s="9">
-        <f t="shared" si="19"/>
-        <v>22931</v>
-      </c>
-      <c r="N12" s="9">
-        <f t="shared" si="19"/>
-        <v>25055</v>
-      </c>
-      <c r="O12" s="9">
-        <f t="shared" si="19"/>
-        <v>22177</v>
-      </c>
-      <c r="P12" s="9">
-        <f t="shared" si="19"/>
-        <v>19744</v>
-      </c>
-      <c r="Q12" s="9">
-        <f t="shared" si="19"/>
-        <v>25056</v>
-      </c>
-      <c r="R12" s="9">
-        <f t="shared" si="19"/>
-        <v>30818</v>
-      </c>
-      <c r="S12" s="9">
-        <f t="shared" si="19"/>
-        <v>31211</v>
-      </c>
-      <c r="T12" s="9">
-        <f t="shared" si="19"/>
-        <v>31211</v>
-      </c>
-      <c r="U12" s="9">
-        <f t="shared" ref="U12:V12" si="20">U10-U11</f>
-        <v>37497</v>
-      </c>
-      <c r="V12" s="9">
-        <f t="shared" si="20"/>
-        <v>42337</v>
-      </c>
-      <c r="W12" s="9">
-        <f t="shared" ref="W12:X12" si="21">W10-W11</f>
-        <v>38412</v>
-      </c>
-      <c r="X12" s="9">
-        <f t="shared" si="21"/>
         <v>39581</v>
       </c>
       <c r="Y12" s="9">
-        <f t="shared" ref="Y12" si="22">Y10-Y11</f>
+        <f t="shared" ref="Y12" si="20">Y10-Y11</f>
         <v>37934</v>
       </c>
       <c r="Z12" s="9">
-        <f t="shared" ref="Z12" si="23">Z10-Z11</f>
+        <f t="shared" ref="Z12" si="21">Z10-Z11</f>
         <v>40706</v>
       </c>
       <c r="AA12" s="9">
-        <f t="shared" ref="AA12:AB12" si="24">AA10-AA11</f>
+        <f t="shared" ref="AA12:AB12" si="22">AA10-AA11</f>
         <v>39175</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>42688</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" ref="AC12" si="25">AC10-AC11</f>
+        <f t="shared" ref="AC12" si="23">AC10-AC11</f>
         <v>43464</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" ref="AD12" si="26">AD10-AD11</f>
+        <f t="shared" ref="AD12" si="24">AD10-AD11</f>
         <v>48735</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" ref="AE12:AK12" si="27">AE10-AE11</f>
+        <f t="shared" ref="AE12:AL12" si="25">AE10-AE11</f>
         <v>46827</v>
       </c>
       <c r="AF12" s="9">
+        <f t="shared" si="25"/>
+        <v>49235</v>
+      </c>
+      <c r="AG12" s="9">
+        <f t="shared" si="25"/>
+        <v>51794</v>
+      </c>
+      <c r="AH12" s="9">
+        <f t="shared" si="25"/>
+        <v>55856</v>
+      </c>
+      <c r="AI12" s="9">
+        <f t="shared" si="25"/>
+        <v>53873</v>
+      </c>
+      <c r="AJ12" s="9">
+        <f t="shared" si="25"/>
+        <v>57389</v>
+      </c>
+      <c r="AK12" s="9">
+        <f t="shared" si="25"/>
+        <v>60977</v>
+      </c>
+      <c r="AL12" s="9">
+        <f t="shared" si="25"/>
+        <v>68062</v>
+      </c>
+      <c r="AM12" s="9"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AR12" s="9">
+        <f t="shared" ref="AR12:AZ12" si="26">AR10-AR11</f>
+        <v>65181</v>
+      </c>
+      <c r="AS12" s="9">
+        <f t="shared" si="26"/>
+        <v>77270</v>
+      </c>
+      <c r="AT12" s="9">
+        <f t="shared" si="26"/>
+        <v>89961</v>
+      </c>
+      <c r="AU12" s="9">
+        <f t="shared" si="26"/>
+        <v>97795</v>
+      </c>
+      <c r="AV12" s="9">
+        <f t="shared" si="26"/>
+        <v>142256</v>
+      </c>
+      <c r="AW12" s="9">
+        <f t="shared" si="26"/>
+        <v>156633</v>
+      </c>
+      <c r="AX12" s="9">
+        <f t="shared" si="26"/>
+        <v>174062</v>
+      </c>
+      <c r="AY12" s="9">
+        <f t="shared" si="26"/>
+        <v>203712</v>
+      </c>
+      <c r="AZ12" s="9">
+        <f t="shared" si="26"/>
+        <v>240301</v>
+      </c>
+      <c r="BA12" s="9">
+        <f>BA10*0.6</f>
+        <v>266674.48200000002</v>
+      </c>
+      <c r="BB12" s="9">
+        <f t="shared" ref="BB12:BJ12" si="27">BB10*0.6</f>
+        <v>286386.35448000004</v>
+      </c>
+      <c r="BC12" s="9">
         <f t="shared" si="27"/>
-        <v>49235</v>
-      </c>
-      <c r="AG12" s="9">
+        <v>301062.1519392</v>
+      </c>
+      <c r="BD12" s="9">
         <f t="shared" si="27"/>
-        <v>51794</v>
-      </c>
-      <c r="AH12" s="9">
+        <v>313250.26471852802</v>
+      </c>
+      <c r="BE12" s="9">
         <f t="shared" si="27"/>
-        <v>55856</v>
-      </c>
-      <c r="AI12" s="9">
+        <v>322764.55538852263</v>
+      </c>
+      <c r="BF12" s="9">
         <f t="shared" si="27"/>
-        <v>53873</v>
-      </c>
-      <c r="AJ12" s="9">
+        <v>331326.91128719418</v>
+      </c>
+      <c r="BG12" s="9">
         <f t="shared" si="27"/>
-        <v>57389</v>
-      </c>
-      <c r="AK12" s="9">
+        <v>338879.88667299575</v>
+      </c>
+      <c r="BH12" s="9">
         <f t="shared" si="27"/>
-        <v>60977</v>
-      </c>
-      <c r="AL12" s="9">
-        <f t="shared" ref="AL12" si="28">AL10*0.6</f>
-        <v>66081.978000000003</v>
-      </c>
-      <c r="AN12" s="9">
-        <f t="shared" ref="AN12:AV12" si="29">AN10-AN11</f>
-        <v>65181</v>
-      </c>
-      <c r="AO12" s="9">
-        <f t="shared" si="29"/>
-        <v>77270</v>
-      </c>
-      <c r="AP12" s="9">
-        <f t="shared" si="29"/>
-        <v>89961</v>
-      </c>
-      <c r="AQ12" s="9">
-        <f t="shared" si="29"/>
-        <v>97795</v>
-      </c>
-      <c r="AR12" s="9">
-        <f t="shared" si="29"/>
-        <v>142256</v>
-      </c>
-      <c r="AS12" s="9">
-        <f t="shared" si="29"/>
-        <v>156633</v>
-      </c>
-      <c r="AT12" s="9">
-        <f t="shared" si="29"/>
-        <v>174062</v>
-      </c>
-      <c r="AU12" s="9">
-        <f t="shared" si="29"/>
-        <v>203712</v>
-      </c>
-      <c r="AV12" s="9">
-        <f t="shared" si="29"/>
-        <v>238320.978</v>
-      </c>
-      <c r="AW12" s="9">
-        <f>AW10*0.6</f>
-        <v>264140.14775999996</v>
-      </c>
-      <c r="AX12" s="9">
-        <f t="shared" ref="AX12:BF12" si="30">AX10*0.6</f>
-        <v>283584.84477840003</v>
-      </c>
-      <c r="AY12" s="9">
-        <f t="shared" si="30"/>
-        <v>298062.94918658404</v>
-      </c>
-      <c r="AZ12" s="9">
-        <f t="shared" si="30"/>
-        <v>310082.67747428472</v>
-      </c>
-      <c r="BA12" s="9">
-        <f t="shared" si="30"/>
-        <v>319468.26233603532</v>
-      </c>
-      <c r="BB12" s="9">
-        <f t="shared" si="30"/>
-        <v>327910.00887807016</v>
-      </c>
-      <c r="BC12" s="9">
-        <f t="shared" si="30"/>
-        <v>335378.41523707804</v>
-      </c>
-      <c r="BD12" s="9">
-        <f t="shared" si="30"/>
-        <v>340638.43187059375</v>
-      </c>
-      <c r="BE12" s="9">
-        <f t="shared" si="30"/>
-        <v>346000.29179687868</v>
-      </c>
-      <c r="BF12" s="9">
-        <f t="shared" si="30"/>
-        <v>351466.3820640042</v>
+        <v>344185.24471453455</v>
+      </c>
+      <c r="BI12" s="9">
+        <f t="shared" si="27"/>
+        <v>349592.97963544261</v>
+      </c>
+      <c r="BJ12" s="9">
+        <f t="shared" si="27"/>
+        <v>355105.48005071958</v>
       </c>
     </row>
-    <row r="13" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -2823,87 +2881,90 @@
         <v>15151</v>
       </c>
       <c r="AL13" s="1">
-        <f>AH13*1.25</f>
-        <v>16395</v>
-      </c>
-      <c r="AN13" s="1">
+        <v>18572</v>
+      </c>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+      <c r="AO13" s="1"/>
+      <c r="AP13" s="1"/>
+      <c r="AR13" s="1">
         <f>SUM(C13:F13)</f>
         <v>16625</v>
       </c>
-      <c r="AO13" s="1">
+      <c r="AS13" s="1">
         <f>SUM(G13:J13)</f>
         <v>21419</v>
       </c>
-      <c r="AP13" s="1">
+      <c r="AT13" s="1">
         <f>SUM(K13:N13)</f>
         <v>26018</v>
       </c>
-      <c r="AQ13" s="1">
+      <c r="AU13" s="1">
         <f>SUM(O13:R13)</f>
         <v>27573</v>
       </c>
-      <c r="AR13" s="1">
+      <c r="AV13" s="1">
         <f>SUM(S13:V13)</f>
         <v>31372</v>
       </c>
-      <c r="AS13" s="1">
+      <c r="AW13" s="1">
         <f>SUM(W13:Z13)</f>
         <v>39500</v>
       </c>
-      <c r="AT13" s="1">
+      <c r="AX13" s="1">
         <f>SUM(AA13:AD13)</f>
         <v>45427</v>
       </c>
-      <c r="AU13" s="1">
+      <c r="AY13" s="1">
         <f>SUM(AE13:AH13)</f>
         <v>49326</v>
       </c>
-      <c r="AV13" s="1">
+      <c r="AZ13" s="1">
         <f>SUM(AI13:AL13)</f>
-        <v>58910</v>
-      </c>
-      <c r="AW13" s="1">
-        <f>AV13*1.09</f>
-        <v>64211.9</v>
-      </c>
-      <c r="AX13" s="1">
-        <f>AW13*1.04</f>
-        <v>66780.376000000004</v>
-      </c>
-      <c r="AY13" s="1">
-        <f t="shared" ref="AY13" si="31">AX13*1.03</f>
-        <v>68783.787280000004</v>
-      </c>
-      <c r="AZ13" s="1">
-        <f>AY13*1.03</f>
-        <v>70847.300898400004</v>
+        <v>61087</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" ref="BA13:BB13" si="32">AZ13*1.02</f>
-        <v>72264.246916368007</v>
+        <f>AZ13*1.09</f>
+        <v>66584.83</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="32"/>
-        <v>73709.531854695364</v>
+        <f>BA13*1.04</f>
+        <v>69248.223200000008</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" ref="BC13" si="33">BB13*1.02</f>
-        <v>75183.722491789274</v>
+        <f t="shared" ref="BC13" si="28">BB13*1.03</f>
+        <v>71325.669896000007</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" ref="BD13" si="34">BC13*1.02</f>
-        <v>76687.396941625062</v>
+        <f>BC13*1.03</f>
+        <v>73465.439992880012</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" ref="BE13" si="35">BD13*1.02</f>
-        <v>78221.144880457563</v>
+        <f t="shared" ref="BE13:BF13" si="29">BD13*1.02</f>
+        <v>74934.748792737621</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" ref="BF13" si="36">BE13*1.02</f>
-        <v>79785.567778066717</v>
+        <f t="shared" si="29"/>
+        <v>76433.443768592377</v>
+      </c>
+      <c r="BG13" s="1">
+        <f t="shared" ref="BG13" si="30">BF13*1.02</f>
+        <v>77962.112643964225</v>
+      </c>
+      <c r="BH13" s="1">
+        <f t="shared" ref="BH13" si="31">BG13*1.02</f>
+        <v>79521.354896843506</v>
+      </c>
+      <c r="BI13" s="1">
+        <f t="shared" ref="BI13" si="32">BH13*1.02</f>
+        <v>81111.78199478038</v>
+      </c>
+      <c r="BJ13" s="1">
+        <f t="shared" ref="BJ13" si="33">BI13*1.02</f>
+        <v>82734.017634675984</v>
       </c>
     </row>
-    <row r="14" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>26</v>
       </c>
@@ -3013,87 +3074,90 @@
         <v>7205</v>
       </c>
       <c r="AL14" s="1">
-        <f>AL10*0.075</f>
-        <v>8260.2472500000003</v>
-      </c>
-      <c r="AN14" s="1">
+        <v>8215</v>
+      </c>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="1"/>
+      <c r="AR14" s="1">
         <f>SUM(C14:F14)</f>
         <v>12893</v>
       </c>
-      <c r="AO14" s="1">
+      <c r="AS14" s="1">
         <f>SUM(G14:J14)</f>
         <v>16333</v>
       </c>
-      <c r="AP14" s="1">
+      <c r="AT14" s="1">
         <f>SUM(K14:N14)</f>
         <v>18464</v>
       </c>
-      <c r="AQ14" s="1">
+      <c r="AU14" s="1">
         <f>SUM(O14:R14)</f>
         <v>17946</v>
       </c>
-      <c r="AR14" s="1">
+      <c r="AV14" s="1">
         <f>SUM(S14:V14)</f>
         <v>22152</v>
       </c>
-      <c r="AS14" s="1">
+      <c r="AW14" s="1">
         <f>SUM(W14:Z14)</f>
         <v>26567</v>
       </c>
-      <c r="AT14" s="1">
+      <c r="AX14" s="1">
         <f>SUM(AA14:AD14)</f>
         <v>27917</v>
       </c>
-      <c r="AU14" s="1">
+      <c r="AY14" s="1">
         <f>SUM(AE14:AH14)</f>
         <v>27808</v>
       </c>
-      <c r="AV14" s="1">
+      <c r="AZ14" s="1">
         <f>SUM(AI14:AL14)</f>
-        <v>28738.24725</v>
-      </c>
-      <c r="AW14" s="1">
-        <f>AW10*0.07</f>
-        <v>30816.350572000003</v>
-      </c>
-      <c r="AX14" s="1">
-        <f t="shared" ref="AX14:BF14" si="37">AX10*0.07</f>
-        <v>33084.89855748001</v>
-      </c>
-      <c r="AY14" s="1">
-        <f t="shared" si="37"/>
-        <v>34774.010738434808</v>
-      </c>
-      <c r="AZ14" s="1">
-        <f t="shared" si="37"/>
-        <v>36176.312371999891</v>
+        <v>28693</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="37"/>
-        <v>37271.297272537464</v>
+        <f>BA10*0.07</f>
+        <v>31112.022900000004</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="37"/>
-        <v>38256.167702441526</v>
+        <f t="shared" ref="BB14:BJ14" si="34">BB10*0.07</f>
+        <v>33411.741356000006</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="37"/>
-        <v>39127.481777659108</v>
+        <f t="shared" si="34"/>
+        <v>35123.917726240004</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="37"/>
-        <v>39741.150384902605</v>
+        <f t="shared" si="34"/>
+        <v>36545.864217161608</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="37"/>
-        <v>40366.70070963585</v>
+        <f t="shared" si="34"/>
+        <v>37655.864795327645</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="37"/>
-        <v>41004.411240800495</v>
+        <f t="shared" si="34"/>
+        <v>38654.80631683932</v>
+      </c>
+      <c r="BG14" s="1">
+        <f t="shared" si="34"/>
+        <v>39535.986778516177</v>
+      </c>
+      <c r="BH14" s="1">
+        <f t="shared" si="34"/>
+        <v>40154.945216695705</v>
+      </c>
+      <c r="BI14" s="1">
+        <f t="shared" si="34"/>
+        <v>40785.847624134978</v>
+      </c>
+      <c r="BJ14" s="1">
+        <f t="shared" si="34"/>
+        <v>41428.972672583957</v>
       </c>
     </row>
-    <row r="15" spans="2:58" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>27</v>
       </c>
@@ -3204,312 +3268,319 @@
         <v>7393</v>
       </c>
       <c r="AL15" s="1">
-        <f>AH15*1.45</f>
-        <v>6387.25</v>
-      </c>
-      <c r="AN15" s="1">
+        <v>5341</v>
+      </c>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+      <c r="AP15" s="1"/>
+      <c r="AR15" s="1">
         <f>SUM(C15:F15)</f>
         <v>6872</v>
       </c>
-      <c r="AO15" s="1">
+      <c r="AS15" s="1">
         <f>SUM(G15:J15)</f>
         <v>6923</v>
       </c>
-      <c r="AP15" s="1">
+      <c r="AT15" s="1">
         <f>SUM(H15:K15)</f>
         <v>9305</v>
       </c>
-      <c r="AQ15" s="1">
+      <c r="AU15" s="1">
         <f>SUM(O15:R15)</f>
         <v>11052</v>
       </c>
-      <c r="AR15" s="1">
+      <c r="AV15" s="1">
         <f>SUM(S15:V15)</f>
         <v>12942</v>
       </c>
-      <c r="AS15" s="1">
+      <c r="AW15" s="1">
         <f>SUM(W15:Z15)</f>
         <v>15724</v>
       </c>
-      <c r="AT15" s="1">
+      <c r="AX15" s="1">
         <f>SUM(AA15:AD15)</f>
         <v>16425</v>
       </c>
-      <c r="AU15" s="1">
+      <c r="AY15" s="1">
         <f>SUM(AE15:AH15)</f>
         <v>14188</v>
       </c>
-      <c r="AV15" s="1">
+      <c r="AZ15" s="1">
         <f>SUM(AI15:AL15)</f>
-        <v>22528.25</v>
-      </c>
-      <c r="AW15" s="1">
-        <f>AV15*1.15</f>
-        <v>25907.487499999999</v>
-      </c>
-      <c r="AX15" s="1">
-        <f>AW15*1.07</f>
-        <v>27721.011624999999</v>
-      </c>
-      <c r="AY15" s="1">
-        <f>AX15*1.03</f>
-        <v>28552.64197375</v>
-      </c>
-      <c r="AZ15" s="1">
-        <f t="shared" ref="AZ15:BB15" si="38">AY15*1.02</f>
-        <v>29123.694813225</v>
+        <v>21482</v>
       </c>
       <c r="BA15" s="1">
-        <f t="shared" si="38"/>
-        <v>29706.168709489499</v>
+        <f>AZ15*1.15</f>
+        <v>24704.3</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="38"/>
-        <v>30300.292083679291</v>
+        <f>BA15*1.07</f>
+        <v>26433.601000000002</v>
       </c>
       <c r="BC15" s="1">
-        <f t="shared" ref="BC15" si="39">BB15*1.02</f>
-        <v>30906.297925352876</v>
+        <f>BB15*1.03</f>
+        <v>27226.609030000003</v>
       </c>
       <c r="BD15" s="1">
-        <f t="shared" ref="BD15" si="40">BC15*1.02</f>
-        <v>31524.423883859934</v>
+        <f t="shared" ref="BD15:BF15" si="35">BC15*1.02</f>
+        <v>27771.141210600003</v>
       </c>
       <c r="BE15" s="1">
-        <f t="shared" ref="BE15" si="41">BD15*1.02</f>
-        <v>32154.912361537132</v>
+        <f t="shared" si="35"/>
+        <v>28326.564034812003</v>
       </c>
       <c r="BF15" s="1">
-        <f t="shared" ref="BF15" si="42">BE15*1.02</f>
-        <v>32798.010608767872</v>
+        <f t="shared" si="35"/>
+        <v>28893.095315508242</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" ref="BG15" si="36">BF15*1.02</f>
+        <v>29470.957221818408</v>
+      </c>
+      <c r="BH15" s="1">
+        <f t="shared" ref="BH15" si="37">BG15*1.02</f>
+        <v>30060.376366254775</v>
+      </c>
+      <c r="BI15" s="1">
+        <f t="shared" ref="BI15" si="38">BH15*1.02</f>
+        <v>30661.583893579871</v>
+      </c>
+      <c r="BJ15" s="1">
+        <f t="shared" ref="BJ15" si="39">BI15*1.02</f>
+        <v>31274.815571451469</v>
       </c>
     </row>
-    <row r="16" spans="2:58" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:62" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:P16" si="43">C12-C13-C14-C15</f>
+        <f t="shared" ref="C16:P16" si="40">C12-C13-C14-C15</f>
         <v>6568</v>
       </c>
       <c r="D16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>6868</v>
       </c>
       <c r="E16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>7782</v>
       </c>
       <c r="F16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>7573</v>
       </c>
       <c r="G16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>7633</v>
       </c>
       <c r="H16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>8116</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>8625</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>8221</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>6608</v>
       </c>
       <c r="L16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>9180</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>9177</v>
       </c>
       <c r="N16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>9266</v>
       </c>
       <c r="O16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>7977</v>
       </c>
       <c r="P16" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="40"/>
         <v>6383</v>
       </c>
       <c r="Q16" s="9">
-        <f t="shared" ref="Q16" si="44">Q12-Q13-Q14-Q15</f>
+        <f t="shared" ref="Q16" si="41">Q12-Q13-Q14-Q15</f>
         <v>11213</v>
       </c>
       <c r="R16" s="9">
-        <f t="shared" ref="R16:V16" si="45">R12-R13-R14-R15</f>
+        <f t="shared" ref="R16:V16" si="42">R12-R13-R14-R15</f>
         <v>15651</v>
       </c>
       <c r="S16" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="42"/>
         <v>16437</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="42"/>
         <v>16437</v>
       </c>
       <c r="U16" s="9">
-        <f t="shared" ref="U16" si="46">U12-U13-U14-U15</f>
+        <f t="shared" ref="U16" si="43">U12-U13-U14-U15</f>
         <v>21031</v>
       </c>
       <c r="V16" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="42"/>
         <v>21885</v>
       </c>
       <c r="W16" s="9">
-        <f t="shared" ref="W16:X16" si="47">W12-W13-W14-W15</f>
+        <f t="shared" ref="W16:X16" si="44">W12-W13-W14-W15</f>
         <v>20094</v>
       </c>
       <c r="X16" s="9">
+        <f t="shared" si="44"/>
+        <v>19453</v>
+      </c>
+      <c r="Y16" s="9">
+        <f t="shared" ref="Y16" si="45">Y12-Y13-Y14-Y15</f>
+        <v>17135</v>
+      </c>
+      <c r="Z16" s="9">
+        <f t="shared" ref="Z16" si="46">Z12-Z13-Z14-Z15</f>
+        <v>18160</v>
+      </c>
+      <c r="AA16" s="9">
+        <f t="shared" ref="AA16:AB16" si="47">AA12-AA13-AA14-AA15</f>
+        <v>17415</v>
+      </c>
+      <c r="AB16" s="9">
         <f t="shared" si="47"/>
-        <v>19453</v>
-      </c>
-      <c r="Y16" s="9">
-        <f t="shared" ref="Y16" si="48">Y12-Y13-Y14-Y15</f>
-        <v>17135</v>
-      </c>
-      <c r="Z16" s="9">
-        <f t="shared" ref="Z16" si="49">Z12-Z13-Z14-Z15</f>
-        <v>18160</v>
-      </c>
-      <c r="AA16" s="9">
-        <f t="shared" ref="AA16:AB16" si="50">AA12-AA13-AA14-AA15</f>
-        <v>17415</v>
-      </c>
-      <c r="AB16" s="9">
+        <v>21838</v>
+      </c>
+      <c r="AC16" s="9">
+        <f t="shared" ref="AC16" si="48">AC12-AC13-AC14-AC15</f>
+        <v>21343</v>
+      </c>
+      <c r="AD16" s="9">
+        <f t="shared" ref="AD16" si="49">AD12-AD13-AD14-AD15</f>
+        <v>23697</v>
+      </c>
+      <c r="AE16" s="9">
+        <f t="shared" ref="AE16:AL16" si="50">AE12-AE13-AE14-AE15</f>
+        <v>25472</v>
+      </c>
+      <c r="AF16" s="9">
         <f t="shared" si="50"/>
-        <v>21838</v>
-      </c>
-      <c r="AC16" s="9">
-        <f t="shared" ref="AC16" si="51">AC12-AC13-AC14-AC15</f>
-        <v>21343</v>
-      </c>
-      <c r="AD16" s="9">
-        <f t="shared" ref="AD16" si="52">AD12-AD13-AD14-AD15</f>
-        <v>23697</v>
-      </c>
-      <c r="AE16" s="9">
-        <f t="shared" ref="AE16:AL16" si="53">AE12-AE13-AE14-AE15</f>
-        <v>25472</v>
-      </c>
-      <c r="AF16" s="9">
-        <f t="shared" si="53"/>
         <v>27425</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>28521</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>30972</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>30606</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>31271</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>31228</v>
       </c>
       <c r="AL16" s="9">
-        <f t="shared" si="53"/>
-        <v>35039.480750000002</v>
-      </c>
-      <c r="AN16" s="9">
-        <f>AN12-AN13-AN14-AN15</f>
+        <f t="shared" si="50"/>
+        <v>35934</v>
+      </c>
+      <c r="AM16" s="9"/>
+      <c r="AN16" s="9"/>
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="9"/>
+      <c r="AR16" s="9">
+        <f>AR12-AR13-AR14-AR15</f>
         <v>28791</v>
       </c>
-      <c r="AO16" s="9">
-        <f>AO12-AO13-AO14-AO15</f>
+      <c r="AS16" s="9">
+        <f>AS12-AS13-AS14-AS15</f>
         <v>32595</v>
       </c>
-      <c r="AP16" s="9">
-        <f>AP12-AP13-AP14-AP15</f>
+      <c r="AT16" s="9">
+        <f>AT12-AT13-AT14-AT15</f>
         <v>36174</v>
       </c>
-      <c r="AQ16" s="9">
-        <f>AQ12-AQ13-AQ14-AQ15</f>
+      <c r="AU16" s="9">
+        <f>AU12-AU13-AU14-AU15</f>
         <v>41224</v>
       </c>
-      <c r="AR16" s="9">
-        <f t="shared" ref="AR16:BA16" si="54">AR12-AR13-AR14-AR15</f>
+      <c r="AV16" s="9">
+        <f t="shared" ref="AV16:BE16" si="51">AV12-AV13-AV14-AV15</f>
         <v>75790</v>
       </c>
-      <c r="AS16" s="9">
-        <f t="shared" si="54"/>
+      <c r="AW16" s="9">
+        <f t="shared" si="51"/>
         <v>74842</v>
       </c>
-      <c r="AT16" s="9">
-        <f t="shared" si="54"/>
+      <c r="AX16" s="9">
+        <f t="shared" si="51"/>
         <v>84293</v>
       </c>
-      <c r="AU16" s="9">
-        <f t="shared" si="54"/>
+      <c r="AY16" s="9">
+        <f t="shared" si="51"/>
         <v>112390</v>
       </c>
-      <c r="AV16" s="9">
-        <f t="shared" si="54"/>
-        <v>128144.48074999999</v>
-      </c>
-      <c r="AW16" s="9">
-        <f t="shared" si="54"/>
-        <v>143204.40968799999</v>
-      </c>
-      <c r="AX16" s="9">
-        <f t="shared" si="54"/>
-        <v>155998.55859592004</v>
-      </c>
-      <c r="AY16" s="9">
-        <f t="shared" si="54"/>
-        <v>165952.50919439926</v>
-      </c>
       <c r="AZ16" s="9">
-        <f t="shared" si="54"/>
-        <v>173935.36939065979</v>
+        <f t="shared" si="51"/>
+        <v>129039</v>
       </c>
       <c r="BA16" s="9">
-        <f t="shared" si="54"/>
-        <v>180226.54943764035</v>
+        <f t="shared" si="51"/>
+        <v>144273.3291</v>
       </c>
       <c r="BB16" s="9">
-        <f t="shared" ref="BB16:BF16" si="55">BB12-BB13-BB14-BB15</f>
-        <v>185644.01723725401</v>
+        <f t="shared" si="51"/>
+        <v>157292.78892400002</v>
       </c>
       <c r="BC16" s="9">
-        <f t="shared" si="55"/>
-        <v>190160.91304227681</v>
+        <f t="shared" si="51"/>
+        <v>167385.95528696</v>
       </c>
       <c r="BD16" s="9">
-        <f t="shared" si="55"/>
-        <v>192685.46066020615</v>
+        <f t="shared" si="51"/>
+        <v>175467.8192978864</v>
       </c>
       <c r="BE16" s="9">
-        <f t="shared" si="55"/>
-        <v>195257.53384524814</v>
+        <f t="shared" si="51"/>
+        <v>181847.37776564536</v>
       </c>
       <c r="BF16" s="9">
-        <f t="shared" si="55"/>
-        <v>197878.39243636909</v>
+        <f t="shared" ref="BF16:BJ16" si="52">BF12-BF13-BF14-BF15</f>
+        <v>187345.56588625422</v>
+      </c>
+      <c r="BG16" s="9">
+        <f t="shared" si="52"/>
+        <v>191910.83002869692</v>
+      </c>
+      <c r="BH16" s="9">
+        <f t="shared" si="52"/>
+        <v>194448.56823474055</v>
+      </c>
+      <c r="BI16" s="9">
+        <f t="shared" si="52"/>
+        <v>197033.76612294736</v>
+      </c>
+      <c r="BJ16" s="9">
+        <f t="shared" si="52"/>
+        <v>199667.67417200821</v>
       </c>
     </row>
-    <row r="17" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>33</v>
       </c>
@@ -3619,312 +3690,319 @@
         <v>-12759</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" ref="AL17" si="56">AH17*1.03</f>
-        <v>-1309.1300000000001</v>
-      </c>
-      <c r="AN17" s="1">
+        <v>-3183</v>
+      </c>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AR17" s="1">
         <f>SUM(C17:F17)</f>
         <v>-1047</v>
       </c>
-      <c r="AO17" s="1">
+      <c r="AS17" s="1">
         <f>SUM(G17:J17)</f>
         <v>-7389</v>
       </c>
-      <c r="AP17" s="1">
+      <c r="AT17" s="1">
         <f>SUM(K17:N17)</f>
         <v>-5394</v>
       </c>
-      <c r="AQ17" s="1">
+      <c r="AU17" s="1">
         <f>SUM(O17:R17)</f>
         <v>-7128</v>
       </c>
-      <c r="AR17" s="1">
+      <c r="AV17" s="1">
         <f>SUM(S17:V17)</f>
         <v>-14242</v>
       </c>
-      <c r="AS17" s="1">
+      <c r="AW17" s="1">
         <f>SUM(W17:Z17)</f>
         <v>3514</v>
       </c>
-      <c r="AT17" s="1">
+      <c r="AX17" s="1">
         <f>SUM(AA17:AD17)</f>
         <v>-1424</v>
       </c>
-      <c r="AU17" s="1">
+      <c r="AY17" s="1">
         <f>SUM(AE17:AH17)</f>
         <v>-7425</v>
       </c>
-      <c r="AV17" s="1">
+      <c r="AZ17" s="1">
         <f>SUM(AI17:AL17)</f>
-        <v>-27913.13</v>
-      </c>
-      <c r="AW17" s="1">
-        <f>AU17*1.01</f>
+        <v>-29787</v>
+      </c>
+      <c r="BA17" s="1">
+        <f>AY17*1.01</f>
         <v>-7499.25</v>
       </c>
-      <c r="AX17" s="1">
-        <f t="shared" ref="AX17:BF17" si="57">AW17*1.01</f>
+      <c r="BB17" s="1">
+        <f t="shared" ref="BB17:BJ17" si="53">BA17*1.01</f>
         <v>-7574.2425000000003</v>
       </c>
-      <c r="AY17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BC17" s="1">
+        <f t="shared" si="53"/>
         <v>-7649.9849250000007</v>
       </c>
-      <c r="AZ17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BD17" s="1">
+        <f t="shared" si="53"/>
         <v>-7726.4847742500006</v>
       </c>
-      <c r="BA17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BE17" s="1">
+        <f t="shared" si="53"/>
         <v>-7803.7496219925006</v>
       </c>
-      <c r="BB17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BF17" s="1">
+        <f t="shared" si="53"/>
         <v>-7881.7871182124254</v>
       </c>
-      <c r="BC17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BG17" s="1">
+        <f t="shared" si="53"/>
         <v>-7960.6049893945501</v>
       </c>
-      <c r="BD17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BH17" s="1">
+        <f t="shared" si="53"/>
         <v>-8040.2110392884961</v>
       </c>
-      <c r="BE17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BI17" s="1">
+        <f t="shared" si="53"/>
         <v>-8120.6131496813814</v>
       </c>
-      <c r="BF17" s="1">
-        <f t="shared" si="57"/>
+      <c r="BJ17" s="1">
+        <f t="shared" si="53"/>
         <v>-8201.8192811781955</v>
       </c>
     </row>
-    <row r="18" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:197" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:P18" si="58">C16-C17</f>
+        <f t="shared" ref="C18:P18" si="54">C16-C17</f>
         <v>6819</v>
       </c>
       <c r="D18" s="9">
+        <f t="shared" si="54"/>
+        <v>7113</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="54"/>
+        <v>7979</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="54"/>
+        <v>7927</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="54"/>
+        <v>10543</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="54"/>
+        <v>9286</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="54"/>
+        <v>10083</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="54"/>
+        <v>10072</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="54"/>
+        <v>8146</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="54"/>
+        <v>12147</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="54"/>
+        <v>8628</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="54"/>
+        <v>10704</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="54"/>
+        <v>7757</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="54"/>
+        <v>8277</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" ref="Q18" si="55">Q16-Q17</f>
+        <v>13629</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" ref="R18:V18" si="56">R16-R17</f>
+        <v>18689</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" si="56"/>
+        <v>21283</v>
+      </c>
+      <c r="T18" s="9">
+        <f t="shared" si="56"/>
+        <v>21283</v>
+      </c>
+      <c r="U18" s="9">
+        <f t="shared" ref="U18" si="57">U16-U17</f>
+        <v>23064</v>
+      </c>
+      <c r="V18" s="9">
+        <f t="shared" si="56"/>
+        <v>24402</v>
+      </c>
+      <c r="W18" s="9">
+        <f t="shared" ref="W18:X18" si="58">W16-W17</f>
+        <v>18934</v>
+      </c>
+      <c r="X18" s="9">
         <f t="shared" si="58"/>
-        <v>7113</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" si="58"/>
-        <v>7979</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="58"/>
-        <v>7927</v>
-      </c>
-      <c r="G18" s="9">
-        <f t="shared" si="58"/>
-        <v>10543</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="58"/>
-        <v>9286</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="58"/>
-        <v>10083</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="58"/>
-        <v>10072</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="58"/>
-        <v>8146</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="58"/>
-        <v>12147</v>
-      </c>
-      <c r="M18" s="9">
-        <f t="shared" si="58"/>
-        <v>8628</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="58"/>
-        <v>10704</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="58"/>
-        <v>7757</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="58"/>
-        <v>8277</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" ref="Q18" si="59">Q16-Q17</f>
-        <v>13629</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" ref="R18:V18" si="60">R16-R17</f>
-        <v>18689</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" si="60"/>
-        <v>21283</v>
-      </c>
-      <c r="T18" s="9">
-        <f t="shared" si="60"/>
-        <v>21283</v>
-      </c>
-      <c r="U18" s="9">
-        <f t="shared" ref="U18" si="61">U16-U17</f>
-        <v>23064</v>
-      </c>
-      <c r="V18" s="9">
-        <f t="shared" si="60"/>
-        <v>24402</v>
-      </c>
-      <c r="W18" s="9">
-        <f t="shared" ref="W18:X18" si="62">W16-W17</f>
-        <v>18934</v>
-      </c>
-      <c r="X18" s="9">
-        <f t="shared" si="62"/>
         <v>19014</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="63">Y16-Y17</f>
+        <f t="shared" ref="Y18" si="59">Y16-Y17</f>
         <v>16233</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="64">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="60">Z16-Z17</f>
         <v>17147</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18:AB18" si="65">AA16-AA17</f>
+        <f t="shared" ref="AA18:AB18" si="61">AA16-AA17</f>
         <v>18205</v>
       </c>
       <c r="AB18" s="9">
+        <f t="shared" si="61"/>
+        <v>21903</v>
+      </c>
+      <c r="AC18" s="9">
+        <f t="shared" ref="AC18" si="62">AC16-AC17</f>
+        <v>21197</v>
+      </c>
+      <c r="AD18" s="9">
+        <f t="shared" ref="AD18" si="63">AD16-AD17</f>
+        <v>24412</v>
+      </c>
+      <c r="AE18" s="9">
+        <f t="shared" ref="AE18:AL18" si="64">AE16-AE17</f>
+        <v>28315</v>
+      </c>
+      <c r="AF18" s="9">
+        <f t="shared" si="64"/>
+        <v>27551</v>
+      </c>
+      <c r="AG18" s="9">
+        <f t="shared" si="64"/>
+        <v>31706</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" si="64"/>
+        <v>32243</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" si="64"/>
+        <v>41789</v>
+      </c>
+      <c r="AJ18" s="9">
+        <f t="shared" si="64"/>
+        <v>33933</v>
+      </c>
+      <c r="AK18" s="9">
+        <f t="shared" si="64"/>
+        <v>43987</v>
+      </c>
+      <c r="AL18" s="9">
+        <f t="shared" si="64"/>
+        <v>39117</v>
+      </c>
+      <c r="AM18" s="9"/>
+      <c r="AN18" s="9"/>
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="9"/>
+      <c r="AR18" s="9">
+        <f>AR16-AR17</f>
+        <v>29838</v>
+      </c>
+      <c r="AS18" s="9">
+        <f>AS16-AS17</f>
+        <v>39984</v>
+      </c>
+      <c r="AT18" s="9">
+        <f>AT16-AT17</f>
+        <v>41568</v>
+      </c>
+      <c r="AU18" s="9">
+        <f>AU16-AU17</f>
+        <v>48352</v>
+      </c>
+      <c r="AV18" s="9">
+        <f t="shared" ref="AV18:BE18" si="65">AV16-AV17</f>
+        <v>90032</v>
+      </c>
+      <c r="AW18" s="9">
         <f t="shared" si="65"/>
-        <v>21903</v>
-      </c>
-      <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="66">AC16-AC17</f>
-        <v>21197</v>
-      </c>
-      <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="67">AD16-AD17</f>
-        <v>24412</v>
-      </c>
-      <c r="AE18" s="9">
-        <f t="shared" ref="AE18:AL18" si="68">AE16-AE17</f>
-        <v>28315</v>
-      </c>
-      <c r="AF18" s="9">
-        <f t="shared" si="68"/>
-        <v>27551</v>
-      </c>
-      <c r="AG18" s="9">
-        <f t="shared" si="68"/>
-        <v>31706</v>
-      </c>
-      <c r="AH18" s="9">
-        <f t="shared" si="68"/>
-        <v>32243</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" si="68"/>
-        <v>41789</v>
-      </c>
-      <c r="AJ18" s="9">
-        <f t="shared" si="68"/>
-        <v>33933</v>
-      </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="68"/>
-        <v>43987</v>
-      </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="68"/>
-        <v>36348.61075</v>
-      </c>
-      <c r="AN18" s="9">
-        <f>AN16-AN17</f>
-        <v>29838</v>
-      </c>
-      <c r="AO18" s="9">
-        <f>AO16-AO17</f>
-        <v>39984</v>
-      </c>
-      <c r="AP18" s="9">
-        <f>AP16-AP17</f>
-        <v>41568</v>
-      </c>
-      <c r="AQ18" s="9">
-        <f>AQ16-AQ17</f>
-        <v>48352</v>
-      </c>
-      <c r="AR18" s="9">
-        <f t="shared" ref="AR18:BA18" si="69">AR16-AR17</f>
-        <v>90032</v>
-      </c>
-      <c r="AS18" s="9">
-        <f t="shared" si="69"/>
         <v>71328</v>
       </c>
-      <c r="AT18" s="9">
-        <f t="shared" si="69"/>
+      <c r="AX18" s="9">
+        <f t="shared" si="65"/>
         <v>85717</v>
       </c>
-      <c r="AU18" s="9">
-        <f t="shared" si="69"/>
+      <c r="AY18" s="9">
+        <f t="shared" si="65"/>
         <v>119815</v>
       </c>
-      <c r="AV18" s="9">
-        <f t="shared" si="69"/>
-        <v>156057.61074999999</v>
-      </c>
-      <c r="AW18" s="9">
-        <f t="shared" si="69"/>
-        <v>150703.65968799999</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="69"/>
-        <v>163572.80109592003</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="69"/>
-        <v>173602.49411939926</v>
-      </c>
       <c r="AZ18" s="9">
-        <f t="shared" si="69"/>
-        <v>181661.8541649098</v>
+        <f t="shared" si="65"/>
+        <v>158826</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="69"/>
-        <v>188030.29905963285</v>
+        <f t="shared" si="65"/>
+        <v>151772.5791</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="70">BB16-BB17</f>
-        <v>193525.80435546645</v>
+        <f t="shared" si="65"/>
+        <v>164867.03142400002</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="70"/>
-        <v>198121.51803167135</v>
+        <f t="shared" si="65"/>
+        <v>175035.94021196</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="70"/>
-        <v>200725.67169949465</v>
+        <f t="shared" si="65"/>
+        <v>183194.30407213641</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="70"/>
-        <v>203378.14699492953</v>
+        <f t="shared" si="65"/>
+        <v>189651.12738763785</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" si="70"/>
-        <v>206080.2117175473</v>
+        <f t="shared" ref="BF18:BJ18" si="66">BF16-BF17</f>
+        <v>195227.35300446665</v>
+      </c>
+      <c r="BG18" s="9">
+        <f t="shared" si="66"/>
+        <v>199871.43501809146</v>
+      </c>
+      <c r="BH18" s="9">
+        <f t="shared" si="66"/>
+        <v>202488.77927402905</v>
+      </c>
+      <c r="BI18" s="9">
+        <f t="shared" si="66"/>
+        <v>205154.37927262875</v>
+      </c>
+      <c r="BJ18" s="9">
+        <f t="shared" si="66"/>
+        <v>207869.49345318641</v>
       </c>
     </row>
-    <row r="19" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>30</v>
       </c>
@@ -4035,852 +4113,859 @@
         <v>9008</v>
       </c>
       <c r="AL19" s="1">
-        <f t="shared" ref="AL19" si="71">AL18*0.15</f>
-        <v>5452.2916125000002</v>
-      </c>
-      <c r="AN19" s="1">
+        <v>4662</v>
+      </c>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AR19" s="1">
         <f>SUM(C19:F19)-10200</f>
         <v>4331</v>
       </c>
-      <c r="AO19" s="1">
+      <c r="AS19" s="1">
         <f>SUM(G19:J19)</f>
         <v>4177</v>
       </c>
-      <c r="AP19" s="1">
+      <c r="AT19" s="1">
         <f>SUM(K19:N19)</f>
         <v>5282</v>
       </c>
-      <c r="AQ19" s="1">
+      <c r="AU19" s="1">
         <f>SUM(O19:R19)</f>
         <v>7813</v>
       </c>
-      <c r="AR19" s="1">
+      <c r="AV19" s="1">
         <f>SUM(S19:V19)</f>
         <v>14594</v>
       </c>
-      <c r="AS19" s="1">
+      <c r="AW19" s="1">
         <f>SUM(W19:Z19)</f>
         <v>11356</v>
       </c>
-      <c r="AT19" s="1">
+      <c r="AX19" s="1">
         <f>SUM(AA19:AD19)</f>
         <v>11922</v>
       </c>
-      <c r="AU19" s="1">
+      <c r="AY19" s="1">
         <f>SUM(AE19:AH19)</f>
         <v>19697</v>
       </c>
-      <c r="AV19" s="1">
+      <c r="AZ19" s="1">
         <f>SUM(AI19:AL19)</f>
-        <v>27446.291612500001</v>
-      </c>
-      <c r="AW19" s="1">
-        <f t="shared" ref="AW19:BA19" si="72">AW18*0.16</f>
-        <v>24112.585550079999</v>
-      </c>
-      <c r="AX19" s="1">
-        <f t="shared" si="72"/>
-        <v>26171.648175347207</v>
-      </c>
-      <c r="AY19" s="1">
-        <f t="shared" si="72"/>
-        <v>27776.399059103882</v>
-      </c>
-      <c r="AZ19" s="1">
-        <f t="shared" si="72"/>
-        <v>29065.896666385568</v>
+        <v>26656</v>
       </c>
       <c r="BA19" s="1">
-        <f t="shared" si="72"/>
-        <v>30084.847849541256</v>
+        <f t="shared" ref="BA19:BE19" si="67">BA18*0.16</f>
+        <v>24283.612656000001</v>
       </c>
       <c r="BB19" s="1">
-        <f t="shared" ref="BB19:BF19" si="73">BB18*0.16</f>
-        <v>30964.128696874632</v>
+        <f t="shared" si="67"/>
+        <v>26378.725027840002</v>
       </c>
       <c r="BC19" s="1">
-        <f t="shared" si="73"/>
-        <v>31699.442885067416</v>
+        <f t="shared" si="67"/>
+        <v>28005.750433913599</v>
       </c>
       <c r="BD19" s="1">
-        <f t="shared" si="73"/>
-        <v>32116.107471919146</v>
+        <f t="shared" si="67"/>
+        <v>29311.088651541824</v>
       </c>
       <c r="BE19" s="1">
-        <f t="shared" si="73"/>
-        <v>32540.503519188725</v>
+        <f t="shared" si="67"/>
+        <v>30344.180382022056</v>
       </c>
       <c r="BF19" s="1">
-        <f t="shared" si="73"/>
-        <v>32972.833874807569</v>
+        <f t="shared" ref="BF19:BJ19" si="68">BF18*0.16</f>
+        <v>31236.376480714665</v>
+      </c>
+      <c r="BG19" s="1">
+        <f t="shared" si="68"/>
+        <v>31979.429602894634</v>
+      </c>
+      <c r="BH19" s="1">
+        <f t="shared" si="68"/>
+        <v>32398.204683844648</v>
+      </c>
+      <c r="BI19" s="1">
+        <f t="shared" si="68"/>
+        <v>32824.700683620598</v>
+      </c>
+      <c r="BJ19" s="1">
+        <f t="shared" si="68"/>
+        <v>33259.118952509823</v>
       </c>
     </row>
-    <row r="20" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:197" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:P20" si="74">C18-C19</f>
+        <f t="shared" ref="C20:P20" si="69">C18-C19</f>
         <v>5426</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6260</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6732</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>-3111</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>9401</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>8266</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>9192</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>8948</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6657</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>9947</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>7068</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>10671</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6836</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6959</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20" si="75">Q18-Q19</f>
+        <f t="shared" ref="Q20" si="70">Q18-Q19</f>
         <v>11517</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" ref="R20:V20" si="76">R18-R19</f>
+        <f t="shared" ref="R20:V20" si="71">R18-R19</f>
         <v>15227</v>
       </c>
       <c r="S20" s="9">
+        <f t="shared" si="71"/>
+        <v>17930</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" si="71"/>
+        <v>17930</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" ref="U20" si="72">U18-U19</f>
+        <v>18936</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="71"/>
+        <v>20642</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" ref="W20:X20" si="73">W18-W19</f>
+        <v>16436</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="73"/>
+        <v>16002</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" ref="Y20" si="74">Y18-Y19</f>
+        <v>13910</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" ref="Z20" si="75">Z18-Z19</f>
+        <v>13624</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" ref="AA20:AB20" si="76">AA18-AA19</f>
+        <v>15051</v>
+      </c>
+      <c r="AB20" s="9">
         <f t="shared" si="76"/>
-        <v>17930</v>
-      </c>
-      <c r="T20" s="9">
-        <f t="shared" si="76"/>
-        <v>17930</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" ref="U20" si="77">U18-U19</f>
-        <v>18936</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="76"/>
-        <v>20642</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" ref="W20:X20" si="78">W18-W19</f>
-        <v>16436</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="78"/>
-        <v>16002</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="79">Y18-Y19</f>
-        <v>13910</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="80">Z18-Z19</f>
-        <v>13624</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" ref="AA20:AB20" si="81">AA18-AA19</f>
-        <v>15051</v>
-      </c>
-      <c r="AB20" s="9">
+        <v>18368</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" ref="AC20" si="77">AC18-AC19</f>
+        <v>19689</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" ref="AD20" si="78">AD18-AD19</f>
+        <v>20687</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="79">AE18-AE19</f>
+        <v>23662</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="79"/>
+        <v>23619</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="79"/>
+        <v>26301</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="79"/>
+        <v>26536</v>
+      </c>
+      <c r="AI20" s="9">
+        <f t="shared" ref="AI20:AL20" si="80">AI18-AI19</f>
+        <v>34540</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" si="80"/>
+        <v>28196</v>
+      </c>
+      <c r="AK20" s="9">
+        <f t="shared" si="80"/>
+        <v>34979</v>
+      </c>
+      <c r="AL20" s="9">
+        <f t="shared" si="80"/>
+        <v>34455</v>
+      </c>
+      <c r="AM20" s="9"/>
+      <c r="AN20" s="9"/>
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AR20" s="9">
+        <f>AR18-AR19</f>
+        <v>25507</v>
+      </c>
+      <c r="AS20" s="9">
+        <f>AS18-AS19</f>
+        <v>35807</v>
+      </c>
+      <c r="AT20" s="9">
+        <f>AT18-AT19</f>
+        <v>36286</v>
+      </c>
+      <c r="AU20" s="9">
+        <f>AU18-AU19</f>
+        <v>40539</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" ref="AV20:BE20" si="81">AV18-AV19</f>
+        <v>75438</v>
+      </c>
+      <c r="AW20" s="9">
         <f t="shared" si="81"/>
-        <v>18368</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="82">AC18-AC19</f>
-        <v>19689</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="83">AD18-AD19</f>
-        <v>20687</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="84">AE18-AE19</f>
-        <v>23662</v>
-      </c>
-      <c r="AF20" s="9">
+        <v>59972</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" si="81"/>
+        <v>73795</v>
+      </c>
+      <c r="AY20" s="9">
+        <f t="shared" si="81"/>
+        <v>100118</v>
+      </c>
+      <c r="AZ20" s="9">
+        <f t="shared" si="81"/>
+        <v>132170</v>
+      </c>
+      <c r="BA20" s="9">
+        <f t="shared" si="81"/>
+        <v>127488.96644400001</v>
+      </c>
+      <c r="BB20" s="9">
+        <f t="shared" si="81"/>
+        <v>138488.30639616001</v>
+      </c>
+      <c r="BC20" s="9">
+        <f t="shared" si="81"/>
+        <v>147030.18977804639</v>
+      </c>
+      <c r="BD20" s="9">
+        <f t="shared" si="81"/>
+        <v>153883.21542059458</v>
+      </c>
+      <c r="BE20" s="9">
+        <f t="shared" si="81"/>
+        <v>159306.9470056158</v>
+      </c>
+      <c r="BF20" s="9">
+        <f t="shared" ref="BF20:BJ20" si="82">BF18-BF19</f>
+        <v>163990.97652375198</v>
+      </c>
+      <c r="BG20" s="9">
+        <f t="shared" si="82"/>
+        <v>167892.00541519682</v>
+      </c>
+      <c r="BH20" s="9">
+        <f t="shared" si="82"/>
+        <v>170090.57459018441</v>
+      </c>
+      <c r="BI20" s="9">
+        <f t="shared" si="82"/>
+        <v>172329.67858900817</v>
+      </c>
+      <c r="BJ20" s="9">
+        <f t="shared" si="82"/>
+        <v>174610.37450067658</v>
+      </c>
+      <c r="BK20" s="6">
+        <f>BJ20*(1+$BM$32)</f>
+        <v>172864.2707556698</v>
+      </c>
+      <c r="BL20" s="6">
+        <f t="shared" ref="BL20:DW20" si="83">BK20*(1+$BM$32)</f>
+        <v>171135.62804811311</v>
+      </c>
+      <c r="BM20" s="6">
+        <f t="shared" si="83"/>
+        <v>169424.27176763199</v>
+      </c>
+      <c r="BN20" s="6">
+        <f t="shared" si="83"/>
+        <v>167730.02904995566</v>
+      </c>
+      <c r="BO20" s="6">
+        <f t="shared" si="83"/>
+        <v>166052.72875945611</v>
+      </c>
+      <c r="BP20" s="6">
+        <f t="shared" si="83"/>
+        <v>164392.20147186154</v>
+      </c>
+      <c r="BQ20" s="6">
+        <f t="shared" si="83"/>
+        <v>162748.27945714293</v>
+      </c>
+      <c r="BR20" s="6">
+        <f t="shared" si="83"/>
+        <v>161120.79666257149</v>
+      </c>
+      <c r="BS20" s="6">
+        <f t="shared" si="83"/>
+        <v>159509.58869594577</v>
+      </c>
+      <c r="BT20" s="6">
+        <f t="shared" si="83"/>
+        <v>157914.49280898631</v>
+      </c>
+      <c r="BU20" s="6">
+        <f t="shared" si="83"/>
+        <v>156335.34788089644</v>
+      </c>
+      <c r="BV20" s="6">
+        <f t="shared" si="83"/>
+        <v>154771.99440208747</v>
+      </c>
+      <c r="BW20" s="6">
+        <f t="shared" si="83"/>
+        <v>153224.27445806659</v>
+      </c>
+      <c r="BX20" s="6">
+        <f t="shared" si="83"/>
+        <v>151692.03171348592</v>
+      </c>
+      <c r="BY20" s="6">
+        <f t="shared" si="83"/>
+        <v>150175.11139635107</v>
+      </c>
+      <c r="BZ20" s="6">
+        <f t="shared" si="83"/>
+        <v>148673.36028238756</v>
+      </c>
+      <c r="CA20" s="6">
+        <f t="shared" si="83"/>
+        <v>147186.62667956369</v>
+      </c>
+      <c r="CB20" s="6">
+        <f t="shared" si="83"/>
+        <v>145714.76041276805</v>
+      </c>
+      <c r="CC20" s="6">
+        <f t="shared" si="83"/>
+        <v>144257.61280864038</v>
+      </c>
+      <c r="CD20" s="6">
+        <f t="shared" si="83"/>
+        <v>142815.03668055398</v>
+      </c>
+      <c r="CE20" s="6">
+        <f t="shared" si="83"/>
+        <v>141386.88631374843</v>
+      </c>
+      <c r="CF20" s="6">
+        <f t="shared" si="83"/>
+        <v>139973.01745061093</v>
+      </c>
+      <c r="CG20" s="6">
+        <f t="shared" si="83"/>
+        <v>138573.28727610482</v>
+      </c>
+      <c r="CH20" s="6">
+        <f t="shared" si="83"/>
+        <v>137187.55440334376</v>
+      </c>
+      <c r="CI20" s="6">
+        <f t="shared" si="83"/>
+        <v>135815.67885931031</v>
+      </c>
+      <c r="CJ20" s="6">
+        <f t="shared" si="83"/>
+        <v>134457.52207071721</v>
+      </c>
+      <c r="CK20" s="6">
+        <f t="shared" si="83"/>
+        <v>133112.94685001005</v>
+      </c>
+      <c r="CL20" s="6">
+        <f t="shared" si="83"/>
+        <v>131781.81738150996</v>
+      </c>
+      <c r="CM20" s="6">
+        <f t="shared" si="83"/>
+        <v>130463.99920769485</v>
+      </c>
+      <c r="CN20" s="6">
+        <f t="shared" si="83"/>
+        <v>129159.35921561791</v>
+      </c>
+      <c r="CO20" s="6">
+        <f t="shared" si="83"/>
+        <v>127867.76562346173</v>
+      </c>
+      <c r="CP20" s="6">
+        <f t="shared" si="83"/>
+        <v>126589.08796722711</v>
+      </c>
+      <c r="CQ20" s="6">
+        <f t="shared" si="83"/>
+        <v>125323.19708755484</v>
+      </c>
+      <c r="CR20" s="6">
+        <f t="shared" si="83"/>
+        <v>124069.96511667929</v>
+      </c>
+      <c r="CS20" s="6">
+        <f t="shared" si="83"/>
+        <v>122829.26546551249</v>
+      </c>
+      <c r="CT20" s="6">
+        <f t="shared" si="83"/>
+        <v>121600.97281085736</v>
+      </c>
+      <c r="CU20" s="6">
+        <f t="shared" si="83"/>
+        <v>120384.96308274879</v>
+      </c>
+      <c r="CV20" s="6">
+        <f t="shared" si="83"/>
+        <v>119181.11345192129</v>
+      </c>
+      <c r="CW20" s="6">
+        <f t="shared" si="83"/>
+        <v>117989.30231740208</v>
+      </c>
+      <c r="CX20" s="6">
+        <f t="shared" si="83"/>
+        <v>116809.40929422805</v>
+      </c>
+      <c r="CY20" s="6">
+        <f t="shared" si="83"/>
+        <v>115641.31520128578</v>
+      </c>
+      <c r="CZ20" s="6">
+        <f t="shared" si="83"/>
+        <v>114484.90204927292</v>
+      </c>
+      <c r="DA20" s="6">
+        <f t="shared" si="83"/>
+        <v>113340.05302878018</v>
+      </c>
+      <c r="DB20" s="6">
+        <f t="shared" si="83"/>
+        <v>112206.65249849237</v>
+      </c>
+      <c r="DC20" s="6">
+        <f t="shared" si="83"/>
+        <v>111084.58597350745</v>
+      </c>
+      <c r="DD20" s="6">
+        <f t="shared" si="83"/>
+        <v>109973.74011377238</v>
+      </c>
+      <c r="DE20" s="6">
+        <f t="shared" si="83"/>
+        <v>108874.00271263465</v>
+      </c>
+      <c r="DF20" s="6">
+        <f t="shared" si="83"/>
+        <v>107785.26268550831</v>
+      </c>
+      <c r="DG20" s="6">
+        <f t="shared" si="83"/>
+        <v>106707.41005865323</v>
+      </c>
+      <c r="DH20" s="6">
+        <f t="shared" si="83"/>
+        <v>105640.3359580667</v>
+      </c>
+      <c r="DI20" s="6">
+        <f t="shared" si="83"/>
+        <v>104583.93259848603</v>
+      </c>
+      <c r="DJ20" s="6">
+        <f t="shared" si="83"/>
+        <v>103538.09327250117</v>
+      </c>
+      <c r="DK20" s="6">
+        <f t="shared" si="83"/>
+        <v>102502.71233977616</v>
+      </c>
+      <c r="DL20" s="6">
+        <f t="shared" si="83"/>
+        <v>101477.68521637839</v>
+      </c>
+      <c r="DM20" s="6">
+        <f t="shared" si="83"/>
+        <v>100462.9083642146</v>
+      </c>
+      <c r="DN20" s="6">
+        <f t="shared" si="83"/>
+        <v>99458.279280572446</v>
+      </c>
+      <c r="DO20" s="6">
+        <f t="shared" si="83"/>
+        <v>98463.69648776672</v>
+      </c>
+      <c r="DP20" s="6">
+        <f t="shared" si="83"/>
+        <v>97479.059522889045</v>
+      </c>
+      <c r="DQ20" s="6">
+        <f t="shared" si="83"/>
+        <v>96504.26892766016</v>
+      </c>
+      <c r="DR20" s="6">
+        <f t="shared" si="83"/>
+        <v>95539.226238383562</v>
+      </c>
+      <c r="DS20" s="6">
+        <f t="shared" si="83"/>
+        <v>94583.833975999733</v>
+      </c>
+      <c r="DT20" s="6">
+        <f t="shared" si="83"/>
+        <v>93637.995636239735</v>
+      </c>
+      <c r="DU20" s="6">
+        <f t="shared" si="83"/>
+        <v>92701.61567987733</v>
+      </c>
+      <c r="DV20" s="6">
+        <f t="shared" si="83"/>
+        <v>91774.599523078563</v>
+      </c>
+      <c r="DW20" s="6">
+        <f t="shared" si="83"/>
+        <v>90856.853527847779</v>
+      </c>
+      <c r="DX20" s="6">
+        <f t="shared" ref="DX20:GI20" si="84">DW20*(1+$BM$32)</f>
+        <v>89948.284992569301</v>
+      </c>
+      <c r="DY20" s="6">
         <f t="shared" si="84"/>
-        <v>23619</v>
-      </c>
-      <c r="AG20" s="9">
+        <v>89048.802142643603</v>
+      </c>
+      <c r="DZ20" s="6">
         <f t="shared" si="84"/>
-        <v>26301</v>
-      </c>
-      <c r="AH20" s="9">
+        <v>88158.314121217161</v>
+      </c>
+      <c r="EA20" s="6">
         <f t="shared" si="84"/>
-        <v>26536</v>
-      </c>
-      <c r="AI20" s="9">
-        <f t="shared" ref="AI20:AL20" si="85">AI18-AI19</f>
-        <v>34540</v>
-      </c>
-      <c r="AJ20" s="9">
+        <v>87276.730980004984</v>
+      </c>
+      <c r="EB20" s="6">
+        <f t="shared" si="84"/>
+        <v>86403.963670204932</v>
+      </c>
+      <c r="EC20" s="6">
+        <f t="shared" si="84"/>
+        <v>85539.924033502888</v>
+      </c>
+      <c r="ED20" s="6">
+        <f t="shared" si="84"/>
+        <v>84684.52479316786</v>
+      </c>
+      <c r="EE20" s="6">
+        <f t="shared" si="84"/>
+        <v>83837.679545236184</v>
+      </c>
+      <c r="EF20" s="6">
+        <f t="shared" si="84"/>
+        <v>82999.302749783819</v>
+      </c>
+      <c r="EG20" s="6">
+        <f t="shared" si="84"/>
+        <v>82169.30972228598</v>
+      </c>
+      <c r="EH20" s="6">
+        <f t="shared" si="84"/>
+        <v>81347.616625063121</v>
+      </c>
+      <c r="EI20" s="6">
+        <f t="shared" si="84"/>
+        <v>80534.140458812486</v>
+      </c>
+      <c r="EJ20" s="6">
+        <f t="shared" si="84"/>
+        <v>79728.799054224364</v>
+      </c>
+      <c r="EK20" s="6">
+        <f t="shared" si="84"/>
+        <v>78931.511063682119</v>
+      </c>
+      <c r="EL20" s="6">
+        <f t="shared" si="84"/>
+        <v>78142.195953045302</v>
+      </c>
+      <c r="EM20" s="6">
+        <f t="shared" si="84"/>
+        <v>77360.773993514842</v>
+      </c>
+      <c r="EN20" s="6">
+        <f t="shared" si="84"/>
+        <v>76587.166253579693</v>
+      </c>
+      <c r="EO20" s="6">
+        <f t="shared" si="84"/>
+        <v>75821.294591043901</v>
+      </c>
+      <c r="EP20" s="6">
+        <f t="shared" si="84"/>
+        <v>75063.081645133469</v>
+      </c>
+      <c r="EQ20" s="6">
+        <f t="shared" si="84"/>
+        <v>74312.450828682136</v>
+      </c>
+      <c r="ER20" s="6">
+        <f t="shared" si="84"/>
+        <v>73569.32632039531</v>
+      </c>
+      <c r="ES20" s="6">
+        <f t="shared" si="84"/>
+        <v>72833.633057191357</v>
+      </c>
+      <c r="ET20" s="6">
+        <f t="shared" si="84"/>
+        <v>72105.296726619446</v>
+      </c>
+      <c r="EU20" s="6">
+        <f t="shared" si="84"/>
+        <v>71384.243759353252</v>
+      </c>
+      <c r="EV20" s="6">
+        <f t="shared" si="84"/>
+        <v>70670.401321759724</v>
+      </c>
+      <c r="EW20" s="6">
+        <f t="shared" si="84"/>
+        <v>69963.69730854212</v>
+      </c>
+      <c r="EX20" s="6">
+        <f t="shared" si="84"/>
+        <v>69264.060335456699</v>
+      </c>
+      <c r="EY20" s="6">
+        <f t="shared" si="84"/>
+        <v>68571.419732102135</v>
+      </c>
+      <c r="EZ20" s="6">
+        <f t="shared" si="84"/>
+        <v>67885.705534781111</v>
+      </c>
+      <c r="FA20" s="6">
+        <f t="shared" si="84"/>
+        <v>67206.848479433305</v>
+      </c>
+      <c r="FB20" s="6">
+        <f t="shared" si="84"/>
+        <v>66534.779994638971</v>
+      </c>
+      <c r="FC20" s="6">
+        <f t="shared" si="84"/>
+        <v>65869.432194692577</v>
+      </c>
+      <c r="FD20" s="6">
+        <f t="shared" si="84"/>
+        <v>65210.737872745653</v>
+      </c>
+      <c r="FE20" s="6">
+        <f t="shared" si="84"/>
+        <v>64558.630494018194</v>
+      </c>
+      <c r="FF20" s="6">
+        <f t="shared" si="84"/>
+        <v>63913.044189078013</v>
+      </c>
+      <c r="FG20" s="6">
+        <f t="shared" si="84"/>
+        <v>63273.913747187231</v>
+      </c>
+      <c r="FH20" s="6">
+        <f t="shared" si="84"/>
+        <v>62641.174609715359</v>
+      </c>
+      <c r="FI20" s="6">
+        <f t="shared" si="84"/>
+        <v>62014.762863618205</v>
+      </c>
+      <c r="FJ20" s="6">
+        <f t="shared" si="84"/>
+        <v>61394.615234982026</v>
+      </c>
+      <c r="FK20" s="6">
+        <f t="shared" si="84"/>
+        <v>60780.669082632208</v>
+      </c>
+      <c r="FL20" s="6">
+        <f t="shared" si="84"/>
+        <v>60172.862391805887</v>
+      </c>
+      <c r="FM20" s="6">
+        <f t="shared" si="84"/>
+        <v>59571.133767887826</v>
+      </c>
+      <c r="FN20" s="6">
+        <f t="shared" si="84"/>
+        <v>58975.42243020895</v>
+      </c>
+      <c r="FO20" s="6">
+        <f t="shared" si="84"/>
+        <v>58385.668205906863</v>
+      </c>
+      <c r="FP20" s="6">
+        <f t="shared" si="84"/>
+        <v>57801.811523847791</v>
+      </c>
+      <c r="FQ20" s="6">
+        <f t="shared" si="84"/>
+        <v>57223.793408609316</v>
+      </c>
+      <c r="FR20" s="6">
+        <f t="shared" si="84"/>
+        <v>56651.555474523222</v>
+      </c>
+      <c r="FS20" s="6">
+        <f t="shared" si="84"/>
+        <v>56085.039919777992</v>
+      </c>
+      <c r="FT20" s="6">
+        <f t="shared" si="84"/>
+        <v>55524.189520580214</v>
+      </c>
+      <c r="FU20" s="6">
+        <f t="shared" si="84"/>
+        <v>54968.947625374414</v>
+      </c>
+      <c r="FV20" s="6">
+        <f t="shared" si="84"/>
+        <v>54419.258149120673</v>
+      </c>
+      <c r="FW20" s="6">
+        <f t="shared" si="84"/>
+        <v>53875.065567629463</v>
+      </c>
+      <c r="FX20" s="6">
+        <f t="shared" si="84"/>
+        <v>53336.314911953166</v>
+      </c>
+      <c r="FY20" s="6">
+        <f t="shared" si="84"/>
+        <v>52802.951762833633</v>
+      </c>
+      <c r="FZ20" s="6">
+        <f t="shared" si="84"/>
+        <v>52274.922245205293</v>
+      </c>
+      <c r="GA20" s="6">
+        <f t="shared" si="84"/>
+        <v>51752.173022753239</v>
+      </c>
+      <c r="GB20" s="6">
+        <f t="shared" si="84"/>
+        <v>51234.651292525705</v>
+      </c>
+      <c r="GC20" s="6">
+        <f t="shared" si="84"/>
+        <v>50722.304779600447</v>
+      </c>
+      <c r="GD20" s="6">
+        <f t="shared" si="84"/>
+        <v>50215.081731804443</v>
+      </c>
+      <c r="GE20" s="6">
+        <f t="shared" si="84"/>
+        <v>49712.930914486395</v>
+      </c>
+      <c r="GF20" s="6">
+        <f t="shared" si="84"/>
+        <v>49215.801605341527</v>
+      </c>
+      <c r="GG20" s="6">
+        <f t="shared" si="84"/>
+        <v>48723.643589288113</v>
+      </c>
+      <c r="GH20" s="6">
+        <f t="shared" si="84"/>
+        <v>48236.40715339523</v>
+      </c>
+      <c r="GI20" s="6">
+        <f t="shared" si="84"/>
+        <v>47754.04308186128</v>
+      </c>
+      <c r="GJ20" s="6">
+        <f t="shared" ref="GJ20:GO20" si="85">GI20*(1+$BM$32)</f>
+        <v>47276.502651042669</v>
+      </c>
+      <c r="GK20" s="6">
         <f t="shared" si="85"/>
-        <v>28196</v>
-      </c>
-      <c r="AK20" s="9">
+        <v>46803.737624532245</v>
+      </c>
+      <c r="GL20" s="6">
         <f t="shared" si="85"/>
-        <v>34979</v>
-      </c>
-      <c r="AL20" s="9">
+        <v>46335.700248286921</v>
+      </c>
+      <c r="GM20" s="6">
         <f t="shared" si="85"/>
-        <v>30896.319137499999</v>
-      </c>
-      <c r="AN20" s="9">
-        <f>AN18-AN19</f>
-        <v>25507</v>
-      </c>
-      <c r="AO20" s="9">
-        <f>AO18-AO19</f>
-        <v>35807</v>
-      </c>
-      <c r="AP20" s="9">
-        <f>AP18-AP19</f>
-        <v>36286</v>
-      </c>
-      <c r="AQ20" s="9">
-        <f>AQ18-AQ19</f>
-        <v>40539</v>
-      </c>
-      <c r="AR20" s="9">
-        <f t="shared" ref="AR20:BA20" si="86">AR18-AR19</f>
-        <v>75438</v>
-      </c>
-      <c r="AS20" s="9">
-        <f t="shared" si="86"/>
-        <v>59972</v>
-      </c>
-      <c r="AT20" s="9">
-        <f t="shared" si="86"/>
-        <v>73795</v>
-      </c>
-      <c r="AU20" s="9">
-        <f t="shared" si="86"/>
-        <v>100118</v>
-      </c>
-      <c r="AV20" s="9">
-        <f t="shared" si="86"/>
-        <v>128611.31913749999</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="86"/>
-        <v>126591.07413791999</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" si="86"/>
-        <v>137401.15292057281</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="86"/>
-        <v>145826.09506029537</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="86"/>
-        <v>152595.95749852422</v>
-      </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="86"/>
-        <v>157945.45121009159</v>
-      </c>
-      <c r="BB20" s="9">
-        <f t="shared" ref="BB20:BF20" si="87">BB18-BB19</f>
-        <v>162561.67565859182</v>
-      </c>
-      <c r="BC20" s="9">
-        <f t="shared" si="87"/>
-        <v>166422.07514660392</v>
-      </c>
-      <c r="BD20" s="9">
-        <f t="shared" si="87"/>
-        <v>168609.56422757549</v>
-      </c>
-      <c r="BE20" s="9">
-        <f t="shared" si="87"/>
-        <v>170837.6434757408</v>
-      </c>
-      <c r="BF20" s="9">
-        <f t="shared" si="87"/>
-        <v>173107.37784273972</v>
-      </c>
-      <c r="BG20" s="6">
-        <f>BF20*(1+$BI$32)</f>
-        <v>171376.30406431231</v>
-      </c>
-      <c r="BH20" s="6">
-        <f t="shared" ref="BH20:DS20" si="88">BG20*(1+$BI$32)</f>
-        <v>169662.54102366918</v>
-      </c>
-      <c r="BI20" s="6">
-        <f t="shared" si="88"/>
-        <v>167965.9156134325</v>
-      </c>
-      <c r="BJ20" s="6">
-        <f t="shared" si="88"/>
-        <v>166286.25645729818</v>
-      </c>
-      <c r="BK20" s="6">
-        <f t="shared" si="88"/>
-        <v>164623.3938927252</v>
-      </c>
-      <c r="BL20" s="6">
-        <f t="shared" si="88"/>
-        <v>162977.15995379793</v>
-      </c>
-      <c r="BM20" s="6">
-        <f t="shared" si="88"/>
-        <v>161347.38835425995</v>
-      </c>
-      <c r="BN20" s="6">
-        <f t="shared" si="88"/>
-        <v>159733.91447071734</v>
-      </c>
-      <c r="BO20" s="6">
-        <f t="shared" si="88"/>
-        <v>158136.57532601018</v>
-      </c>
-      <c r="BP20" s="6">
-        <f t="shared" si="88"/>
-        <v>156555.20957275009</v>
-      </c>
-      <c r="BQ20" s="6">
-        <f t="shared" si="88"/>
-        <v>154989.65747702259</v>
-      </c>
-      <c r="BR20" s="6">
-        <f t="shared" si="88"/>
-        <v>153439.76090225237</v>
-      </c>
-      <c r="BS20" s="6">
-        <f t="shared" si="88"/>
-        <v>151905.36329322984</v>
-      </c>
-      <c r="BT20" s="6">
-        <f t="shared" si="88"/>
-        <v>150386.30966029753</v>
-      </c>
-      <c r="BU20" s="6">
-        <f t="shared" si="88"/>
-        <v>148882.44656369454</v>
-      </c>
-      <c r="BV20" s="6">
-        <f t="shared" si="88"/>
-        <v>147393.62209805759</v>
-      </c>
-      <c r="BW20" s="6">
-        <f t="shared" si="88"/>
-        <v>145919.68587707702</v>
-      </c>
-      <c r="BX20" s="6">
-        <f t="shared" si="88"/>
-        <v>144460.48901830625</v>
-      </c>
-      <c r="BY20" s="6">
-        <f t="shared" si="88"/>
-        <v>143015.8841281232</v>
-      </c>
-      <c r="BZ20" s="6">
-        <f t="shared" si="88"/>
-        <v>141585.72528684197</v>
-      </c>
-      <c r="CA20" s="6">
-        <f t="shared" si="88"/>
-        <v>140169.86803397356</v>
-      </c>
-      <c r="CB20" s="6">
-        <f t="shared" si="88"/>
-        <v>138768.16935363383</v>
-      </c>
-      <c r="CC20" s="6">
-        <f t="shared" si="88"/>
-        <v>137380.48766009748</v>
-      </c>
-      <c r="CD20" s="6">
-        <f t="shared" si="88"/>
-        <v>136006.68278349651</v>
-      </c>
-      <c r="CE20" s="6">
-        <f t="shared" si="88"/>
-        <v>134646.61595566155</v>
-      </c>
-      <c r="CF20" s="6">
-        <f t="shared" si="88"/>
-        <v>133300.14979610493</v>
-      </c>
-      <c r="CG20" s="6">
-        <f t="shared" si="88"/>
-        <v>131967.14829814387</v>
-      </c>
-      <c r="CH20" s="6">
-        <f t="shared" si="88"/>
-        <v>130647.47681516243</v>
-      </c>
-      <c r="CI20" s="6">
-        <f t="shared" si="88"/>
-        <v>129341.0020470108</v>
-      </c>
-      <c r="CJ20" s="6">
-        <f t="shared" si="88"/>
-        <v>128047.59202654069</v>
-      </c>
-      <c r="CK20" s="6">
-        <f t="shared" si="88"/>
-        <v>126767.11610627528</v>
-      </c>
-      <c r="CL20" s="6">
-        <f t="shared" si="88"/>
-        <v>125499.44494521253</v>
-      </c>
-      <c r="CM20" s="6">
-        <f t="shared" si="88"/>
-        <v>124244.45049576039</v>
-      </c>
-      <c r="CN20" s="6">
-        <f t="shared" si="88"/>
-        <v>123002.00599080279</v>
-      </c>
-      <c r="CO20" s="6">
-        <f t="shared" si="88"/>
-        <v>121771.98593089476</v>
-      </c>
-      <c r="CP20" s="6">
-        <f t="shared" si="88"/>
-        <v>120554.26607158582</v>
-      </c>
-      <c r="CQ20" s="6">
-        <f t="shared" si="88"/>
-        <v>119348.72341086996</v>
-      </c>
-      <c r="CR20" s="6">
-        <f t="shared" si="88"/>
-        <v>118155.23617676126</v>
-      </c>
-      <c r="CS20" s="6">
-        <f t="shared" si="88"/>
-        <v>116973.68381499365</v>
-      </c>
-      <c r="CT20" s="6">
-        <f t="shared" si="88"/>
-        <v>115803.94697684371</v>
-      </c>
-      <c r="CU20" s="6">
-        <f t="shared" si="88"/>
-        <v>114645.90750707527</v>
-      </c>
-      <c r="CV20" s="6">
-        <f t="shared" si="88"/>
-        <v>113499.44843200452</v>
-      </c>
-      <c r="CW20" s="6">
-        <f t="shared" si="88"/>
-        <v>112364.45394768447</v>
-      </c>
-      <c r="CX20" s="6">
-        <f t="shared" si="88"/>
-        <v>111240.80940820761</v>
-      </c>
-      <c r="CY20" s="6">
-        <f t="shared" si="88"/>
-        <v>110128.40131412554</v>
-      </c>
-      <c r="CZ20" s="6">
-        <f t="shared" si="88"/>
-        <v>109027.11730098429</v>
-      </c>
-      <c r="DA20" s="6">
-        <f t="shared" si="88"/>
-        <v>107936.84612797445</v>
-      </c>
-      <c r="DB20" s="6">
-        <f t="shared" si="88"/>
-        <v>106857.4776666947</v>
-      </c>
-      <c r="DC20" s="6">
-        <f t="shared" si="88"/>
-        <v>105788.90289002775</v>
-      </c>
-      <c r="DD20" s="6">
-        <f t="shared" si="88"/>
-        <v>104731.01386112747</v>
-      </c>
-      <c r="DE20" s="6">
-        <f t="shared" si="88"/>
-        <v>103683.70372251621</v>
-      </c>
-      <c r="DF20" s="6">
-        <f t="shared" si="88"/>
-        <v>102646.86668529104</v>
-      </c>
-      <c r="DG20" s="6">
-        <f t="shared" si="88"/>
-        <v>101620.39801843812</v>
-      </c>
-      <c r="DH20" s="6">
-        <f t="shared" si="88"/>
-        <v>100604.19403825374</v>
-      </c>
-      <c r="DI20" s="6">
-        <f t="shared" si="88"/>
-        <v>99598.152097871207</v>
-      </c>
-      <c r="DJ20" s="6">
-        <f t="shared" si="88"/>
-        <v>98602.170576892488</v>
-      </c>
-      <c r="DK20" s="6">
-        <f t="shared" si="88"/>
-        <v>97616.148871123558</v>
-      </c>
-      <c r="DL20" s="6">
-        <f t="shared" si="88"/>
-        <v>96639.987382412321</v>
-      </c>
-      <c r="DM20" s="6">
-        <f t="shared" si="88"/>
-        <v>95673.5875085882</v>
-      </c>
-      <c r="DN20" s="6">
-        <f t="shared" si="88"/>
-        <v>94716.851633502316</v>
-      </c>
-      <c r="DO20" s="6">
-        <f t="shared" si="88"/>
-        <v>93769.683117167297</v>
-      </c>
-      <c r="DP20" s="6">
-        <f t="shared" si="88"/>
-        <v>92831.986285995619</v>
-      </c>
-      <c r="DQ20" s="6">
-        <f t="shared" si="88"/>
-        <v>91903.666423135655</v>
-      </c>
-      <c r="DR20" s="6">
-        <f t="shared" si="88"/>
-        <v>90984.629758904295</v>
-      </c>
-      <c r="DS20" s="6">
-        <f t="shared" si="88"/>
-        <v>90074.783461315252</v>
-      </c>
-      <c r="DT20" s="6">
-        <f t="shared" ref="DT20:GE20" si="89">DS20*(1+$BI$32)</f>
-        <v>89174.035626702098</v>
-      </c>
-      <c r="DU20" s="6">
-        <f t="shared" si="89"/>
-        <v>88282.295270435076</v>
-      </c>
-      <c r="DV20" s="6">
-        <f t="shared" si="89"/>
-        <v>87399.472317730717</v>
-      </c>
-      <c r="DW20" s="6">
-        <f t="shared" si="89"/>
-        <v>86525.477594553406</v>
-      </c>
-      <c r="DX20" s="6">
-        <f t="shared" si="89"/>
-        <v>85660.222818607872</v>
-      </c>
-      <c r="DY20" s="6">
-        <f t="shared" si="89"/>
-        <v>84803.620590421793</v>
-      </c>
-      <c r="DZ20" s="6">
-        <f t="shared" si="89"/>
-        <v>83955.58438451757</v>
-      </c>
-      <c r="EA20" s="6">
-        <f t="shared" si="89"/>
-        <v>83116.0285406724</v>
-      </c>
-      <c r="EB20" s="6">
-        <f t="shared" si="89"/>
-        <v>82284.868255265668</v>
-      </c>
-      <c r="EC20" s="6">
-        <f t="shared" si="89"/>
-        <v>81462.019572713005</v>
-      </c>
-      <c r="ED20" s="6">
-        <f t="shared" si="89"/>
-        <v>80647.399376985879</v>
-      </c>
-      <c r="EE20" s="6">
-        <f t="shared" si="89"/>
-        <v>79840.925383216018</v>
-      </c>
-      <c r="EF20" s="6">
-        <f t="shared" si="89"/>
-        <v>79042.516129383861</v>
-      </c>
-      <c r="EG20" s="6">
-        <f t="shared" si="89"/>
-        <v>78252.090968090022</v>
-      </c>
-      <c r="EH20" s="6">
-        <f t="shared" si="89"/>
-        <v>77469.570058409125</v>
-      </c>
-      <c r="EI20" s="6">
-        <f t="shared" si="89"/>
-        <v>76694.874357825029</v>
-      </c>
-      <c r="EJ20" s="6">
-        <f t="shared" si="89"/>
-        <v>75927.925614246778</v>
-      </c>
-      <c r="EK20" s="6">
-        <f t="shared" si="89"/>
-        <v>75168.646358104306</v>
-      </c>
-      <c r="EL20" s="6">
-        <f t="shared" si="89"/>
-        <v>74416.959894523257</v>
-      </c>
-      <c r="EM20" s="6">
-        <f t="shared" si="89"/>
-        <v>73672.79029557803</v>
-      </c>
-      <c r="EN20" s="6">
-        <f t="shared" si="89"/>
-        <v>72936.062392622247</v>
-      </c>
-      <c r="EO20" s="6">
-        <f t="shared" si="89"/>
-        <v>72206.701768696017</v>
-      </c>
-      <c r="EP20" s="6">
-        <f t="shared" si="89"/>
-        <v>71484.634751009056</v>
-      </c>
-      <c r="EQ20" s="6">
-        <f t="shared" si="89"/>
-        <v>70769.788403498969</v>
-      </c>
-      <c r="ER20" s="6">
-        <f t="shared" si="89"/>
-        <v>70062.090519463978</v>
-      </c>
-      <c r="ES20" s="6">
-        <f t="shared" si="89"/>
-        <v>69361.469614269343</v>
-      </c>
-      <c r="ET20" s="6">
-        <f t="shared" si="89"/>
-        <v>68667.854918126643</v>
-      </c>
-      <c r="EU20" s="6">
-        <f t="shared" si="89"/>
-        <v>67981.17636894538</v>
-      </c>
-      <c r="EV20" s="6">
-        <f t="shared" si="89"/>
-        <v>67301.36460525592</v>
-      </c>
-      <c r="EW20" s="6">
-        <f t="shared" si="89"/>
-        <v>66628.350959203366</v>
-      </c>
-      <c r="EX20" s="6">
-        <f t="shared" si="89"/>
-        <v>65962.067449611335</v>
-      </c>
-      <c r="EY20" s="6">
-        <f t="shared" si="89"/>
-        <v>65302.446775115219</v>
-      </c>
-      <c r="EZ20" s="6">
-        <f t="shared" si="89"/>
-        <v>64649.422307364068</v>
-      </c>
-      <c r="FA20" s="6">
-        <f t="shared" si="89"/>
-        <v>64002.928084290426</v>
-      </c>
-      <c r="FB20" s="6">
-        <f t="shared" si="89"/>
-        <v>63362.898803447519</v>
-      </c>
-      <c r="FC20" s="6">
-        <f t="shared" si="89"/>
-        <v>62729.269815413041</v>
-      </c>
-      <c r="FD20" s="6">
-        <f t="shared" si="89"/>
-        <v>62101.97711725891</v>
-      </c>
-      <c r="FE20" s="6">
-        <f t="shared" si="89"/>
-        <v>61480.957346086318</v>
-      </c>
-      <c r="FF20" s="6">
-        <f t="shared" si="89"/>
-        <v>60866.147772625452</v>
-      </c>
-      <c r="FG20" s="6">
-        <f t="shared" si="89"/>
-        <v>60257.486294899194</v>
-      </c>
-      <c r="FH20" s="6">
-        <f t="shared" si="89"/>
-        <v>59654.911431950204</v>
-      </c>
-      <c r="FI20" s="6">
-        <f t="shared" si="89"/>
-        <v>59058.362317630701</v>
-      </c>
-      <c r="FJ20" s="6">
-        <f t="shared" si="89"/>
-        <v>58467.778694454391</v>
-      </c>
-      <c r="FK20" s="6">
-        <f t="shared" si="89"/>
-        <v>57883.100907509848</v>
-      </c>
-      <c r="FL20" s="6">
-        <f t="shared" si="89"/>
-        <v>57304.269898434752</v>
-      </c>
-      <c r="FM20" s="6">
-        <f t="shared" si="89"/>
-        <v>56731.227199450404</v>
-      </c>
-      <c r="FN20" s="6">
-        <f t="shared" si="89"/>
-        <v>56163.914927455902</v>
-      </c>
-      <c r="FO20" s="6">
-        <f t="shared" si="89"/>
-        <v>55602.275778181342</v>
-      </c>
-      <c r="FP20" s="6">
-        <f t="shared" si="89"/>
-        <v>55046.253020399527</v>
-      </c>
-      <c r="FQ20" s="6">
-        <f t="shared" si="89"/>
-        <v>54495.790490195533</v>
-      </c>
-      <c r="FR20" s="6">
-        <f t="shared" si="89"/>
-        <v>53950.832585293574</v>
-      </c>
-      <c r="FS20" s="6">
-        <f t="shared" si="89"/>
-        <v>53411.32425944064</v>
-      </c>
-      <c r="FT20" s="6">
-        <f t="shared" si="89"/>
-        <v>52877.211016846231</v>
-      </c>
-      <c r="FU20" s="6">
-        <f t="shared" si="89"/>
-        <v>52348.438906677766</v>
-      </c>
-      <c r="FV20" s="6">
-        <f t="shared" si="89"/>
-        <v>51824.95451761099</v>
-      </c>
-      <c r="FW20" s="6">
-        <f t="shared" si="89"/>
-        <v>51306.704972434876</v>
-      </c>
-      <c r="FX20" s="6">
-        <f t="shared" si="89"/>
-        <v>50793.637922710528</v>
-      </c>
-      <c r="FY20" s="6">
-        <f t="shared" si="89"/>
-        <v>50285.701543483425</v>
-      </c>
-      <c r="FZ20" s="6">
-        <f t="shared" si="89"/>
-        <v>49782.84452804859</v>
-      </c>
-      <c r="GA20" s="6">
-        <f t="shared" si="89"/>
-        <v>49285.016082768103</v>
-      </c>
-      <c r="GB20" s="6">
-        <f t="shared" si="89"/>
-        <v>48792.165921940425</v>
-      </c>
-      <c r="GC20" s="6">
-        <f t="shared" si="89"/>
-        <v>48304.244262721018</v>
-      </c>
-      <c r="GD20" s="6">
-        <f t="shared" si="89"/>
-        <v>47821.201820093811</v>
-      </c>
-      <c r="GE20" s="6">
-        <f t="shared" si="89"/>
-        <v>47342.989801892872</v>
-      </c>
-      <c r="GF20" s="6">
-        <f t="shared" ref="GF20:GK20" si="90">GE20*(1+$BI$32)</f>
-        <v>46869.559903873946</v>
-      </c>
-      <c r="GG20" s="6">
-        <f t="shared" si="90"/>
-        <v>46400.864304835202</v>
-      </c>
-      <c r="GH20" s="6">
-        <f t="shared" si="90"/>
-        <v>45936.855661786853</v>
-      </c>
-      <c r="GI20" s="6">
-        <f t="shared" si="90"/>
-        <v>45477.487105168984</v>
-      </c>
-      <c r="GJ20" s="6">
-        <f t="shared" si="90"/>
-        <v>45022.712234117294</v>
-      </c>
-      <c r="GK20" s="6">
-        <f t="shared" si="90"/>
-        <v>44572.485111776121</v>
+        <v>45872.343245804048</v>
+      </c>
+      <c r="GN20" s="6">
+        <f t="shared" si="85"/>
+        <v>45413.619813346006</v>
+      </c>
+      <c r="GO20" s="6">
+        <f t="shared" si="85"/>
+        <v>44959.483615212543</v>
       </c>
     </row>
-    <row r="21" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>2</v>
       </c>
@@ -4984,7 +5069,7 @@
         <v>12190</v>
       </c>
       <c r="AI21" s="1">
-        <f t="shared" ref="AI21" si="91">5833+860+5497</f>
+        <f t="shared" ref="AI21" si="86">5833+860+5497</f>
         <v>12190</v>
       </c>
       <c r="AJ21" s="1">
@@ -4995,293 +5080,313 @@
         <v>12086</v>
       </c>
       <c r="AL21" s="1">
-        <v>12086</v>
-      </c>
-      <c r="AN21" s="1">
+        <f>5822+837+5438</f>
+        <v>12097</v>
+      </c>
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="1"/>
+      <c r="AO21" s="1"/>
+      <c r="AP21" s="1"/>
+      <c r="AR21" s="1">
         <v>680</v>
       </c>
-      <c r="AO21" s="1">
+      <c r="AS21" s="1">
         <v>680</v>
       </c>
-      <c r="AP21" s="1">
+      <c r="AT21" s="1">
         <v>680</v>
       </c>
-      <c r="AQ21" s="1">
+      <c r="AU21" s="1">
         <v>676</v>
       </c>
-      <c r="AR21" s="1">
+      <c r="AV21" s="1">
         <v>688</v>
       </c>
-      <c r="AS21" s="1">
+      <c r="AW21" s="1">
         <v>12897</v>
       </c>
-      <c r="AT21" s="1">
+      <c r="AX21" s="1">
         <v>12488</v>
       </c>
-      <c r="AU21" s="1">
-        <f t="shared" ref="AU21" si="92">5833+860+5497</f>
+      <c r="AY21" s="1">
+        <f t="shared" ref="AY21" si="87">5833+860+5497</f>
         <v>12190</v>
       </c>
-      <c r="AV21" s="1">
-        <v>12086</v>
-      </c>
-      <c r="AW21" s="1">
-        <v>12086</v>
-      </c>
-      <c r="AX21" s="1">
-        <v>12086</v>
-      </c>
-      <c r="AY21" s="1">
-        <v>12086</v>
-      </c>
       <c r="AZ21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BA21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BB21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BC21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BD21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BE21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
       <c r="BF21" s="1">
-        <v>12086</v>
+        <f>5822+837+5438</f>
+        <v>12097</v>
+      </c>
+      <c r="BG21" s="1">
+        <f>5822+837+5438</f>
+        <v>12097</v>
+      </c>
+      <c r="BH21" s="1">
+        <f>5822+837+5438</f>
+        <v>12097</v>
+      </c>
+      <c r="BI21" s="1">
+        <f>5822+837+5438</f>
+        <v>12097</v>
+      </c>
+      <c r="BJ21" s="1">
+        <f>5822+837+5438</f>
+        <v>12097</v>
       </c>
     </row>
-    <row r="22" spans="2:193" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:197" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:P22" si="93">C20/C21</f>
+        <f t="shared" ref="C22:P22" si="88">C20/C21</f>
         <v>7.9794117647058824</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>9.2058823529411757</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>9.9</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>-4.5750000000000002</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>13.824999999999999</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>12.155882352941177</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>13.517647058823529</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>13.158823529411764</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>9.7897058823529406</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>14.627941176470589</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>10.394117647058824</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>15.69264705882353</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>10.052941176470588</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v>10.233823529411765</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" ref="Q22" si="94">Q20/Q21</f>
+        <f t="shared" ref="Q22" si="89">Q20/Q21</f>
         <v>17.036982248520712</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:V22" si="95">R20/R21</f>
+        <f t="shared" ref="R22:V22" si="90">R20/R21</f>
         <v>22.132267441860463</v>
       </c>
       <c r="S22" s="7">
+        <f t="shared" si="90"/>
+        <v>26.061046511627907</v>
+      </c>
+      <c r="T22" s="7">
+        <f t="shared" si="90"/>
+        <v>1.352901229910209</v>
+      </c>
+      <c r="U22" s="7">
+        <f t="shared" ref="U22" si="91">U20/U21</f>
+        <v>1.4288085716441561</v>
+      </c>
+      <c r="V22" s="7">
+        <f t="shared" si="90"/>
+        <v>1.5575341432128575</v>
+      </c>
+      <c r="W22" s="7">
+        <f t="shared" ref="W22:X22" si="92">W20/W21</f>
+        <v>1.2744049003644258</v>
+      </c>
+      <c r="X22" s="7">
+        <f t="shared" si="92"/>
+        <v>1.2407536636427077</v>
+      </c>
+      <c r="Y22" s="7">
+        <f t="shared" ref="Y22" si="93">Y20/Y21</f>
+        <v>1.0785453981546096</v>
+      </c>
+      <c r="Z22" s="7">
+        <f t="shared" ref="Z22" si="94">Z20/Z21</f>
+        <v>1.0563696983794681</v>
+      </c>
+      <c r="AA22" s="7">
+        <f t="shared" ref="AA22:AB22" si="95">AA20/AA21</f>
+        <v>1.1670155850197721</v>
+      </c>
+      <c r="AB22" s="7">
         <f t="shared" si="95"/>
-        <v>26.061046511627907</v>
-      </c>
-      <c r="T22" s="7">
-        <f t="shared" si="95"/>
-        <v>1.352901229910209</v>
-      </c>
-      <c r="U22" s="7">
-        <f t="shared" ref="U22" si="96">U20/U21</f>
-        <v>1.4288085716441561</v>
-      </c>
-      <c r="V22" s="7">
-        <f t="shared" si="95"/>
-        <v>1.5575341432128575</v>
-      </c>
-      <c r="W22" s="7">
-        <f t="shared" ref="W22:X22" si="97">W20/W21</f>
-        <v>1.2744049003644258</v>
-      </c>
-      <c r="X22" s="7">
-        <f t="shared" si="97"/>
-        <v>1.2407536636427077</v>
-      </c>
-      <c r="Y22" s="7">
-        <f t="shared" ref="Y22" si="98">Y20/Y21</f>
-        <v>1.0785453981546096</v>
-      </c>
-      <c r="Z22" s="7">
-        <f t="shared" ref="Z22" si="99">Z20/Z21</f>
-        <v>1.0563696983794681</v>
-      </c>
-      <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AB22" si="100">AA20/AA21</f>
-        <v>1.1670155850197721</v>
-      </c>
-      <c r="AB22" s="7">
+        <v>1.4242071799643328</v>
+      </c>
+      <c r="AC22" s="7">
+        <f t="shared" ref="AC22" si="96">AC20/AC21</f>
+        <v>1.5266341009537101</v>
+      </c>
+      <c r="AD22" s="7">
+        <f t="shared" ref="AD22" si="97">AD20/AD21</f>
+        <v>1.6565502882767458</v>
+      </c>
+      <c r="AE22" s="7">
+        <f t="shared" ref="AE22:AH22" si="98">AE20/AE21</f>
+        <v>1.8947789878283152</v>
+      </c>
+      <c r="AF22" s="7">
+        <f t="shared" si="98"/>
+        <v>1.9186839967506093</v>
+      </c>
+      <c r="AG22" s="7">
+        <f t="shared" si="98"/>
+        <v>2.1485989706723307</v>
+      </c>
+      <c r="AH22" s="7">
+        <f t="shared" si="98"/>
+        <v>2.1768662838392125</v>
+      </c>
+      <c r="AI22" s="7">
+        <f t="shared" ref="AI22:AL22" si="99">AI20/AI21</f>
+        <v>2.8334700574241181</v>
+      </c>
+      <c r="AJ22" s="7">
+        <f t="shared" si="99"/>
+        <v>2.3260188087774294</v>
+      </c>
+      <c r="AK22" s="7">
+        <f t="shared" si="99"/>
+        <v>2.8941750786033427</v>
+      </c>
+      <c r="AL22" s="7">
+        <f t="shared" si="99"/>
+        <v>2.8482268330991154</v>
+      </c>
+      <c r="AM22" s="7"/>
+      <c r="AN22" s="7"/>
+      <c r="AO22" s="7"/>
+      <c r="AP22" s="7"/>
+      <c r="AR22" s="7">
+        <f t="shared" ref="AR22:AU22" si="100">AR20/AR21</f>
+        <v>37.510294117647057</v>
+      </c>
+      <c r="AS22" s="7">
         <f t="shared" si="100"/>
-        <v>1.4242071799643328</v>
-      </c>
-      <c r="AC22" s="7">
-        <f t="shared" ref="AC22" si="101">AC20/AC21</f>
-        <v>1.5266341009537101</v>
-      </c>
-      <c r="AD22" s="7">
-        <f t="shared" ref="AD22" si="102">AD20/AD21</f>
-        <v>1.6565502882767458</v>
-      </c>
-      <c r="AE22" s="7">
-        <f t="shared" ref="AE22:AH22" si="103">AE20/AE21</f>
-        <v>1.8947789878283152</v>
-      </c>
-      <c r="AF22" s="7">
-        <f t="shared" si="103"/>
-        <v>1.9186839967506093</v>
-      </c>
-      <c r="AG22" s="7">
-        <f t="shared" si="103"/>
-        <v>2.1485989706723307</v>
-      </c>
-      <c r="AH22" s="7">
-        <f t="shared" si="103"/>
-        <v>2.1768662838392125</v>
-      </c>
-      <c r="AI22" s="7">
-        <f t="shared" ref="AI22:AL22" si="104">AI20/AI21</f>
-        <v>2.8334700574241181</v>
-      </c>
-      <c r="AJ22" s="7">
-        <f t="shared" si="104"/>
-        <v>2.3260188087774294</v>
-      </c>
-      <c r="AK22" s="7">
-        <f t="shared" si="104"/>
-        <v>2.8941750786033427</v>
-      </c>
-      <c r="AL22" s="7">
-        <f t="shared" si="104"/>
-        <v>2.5563725912212476</v>
-      </c>
-      <c r="AN22" s="7">
-        <f t="shared" ref="AN22:AQ22" si="105">AN20/AN21</f>
-        <v>37.510294117647057</v>
-      </c>
-      <c r="AO22" s="7">
-        <f t="shared" si="105"/>
         <v>52.65735294117647</v>
       </c>
-      <c r="AP22" s="7">
-        <f t="shared" si="105"/>
+      <c r="AT22" s="7">
+        <f t="shared" si="100"/>
         <v>53.361764705882351</v>
       </c>
-      <c r="AQ22" s="7">
-        <f t="shared" si="105"/>
+      <c r="AU22" s="7">
+        <f t="shared" si="100"/>
         <v>59.968934911242606</v>
       </c>
-      <c r="AR22" s="7">
-        <f t="shared" ref="AR22" si="106">AR20/AR21</f>
+      <c r="AV22" s="7">
+        <f t="shared" ref="AV22" si="101">AV20/AV21</f>
         <v>109.64825581395348</v>
       </c>
-      <c r="AS22" s="7">
-        <f t="shared" ref="AS22" si="107">AS20/AS21</f>
+      <c r="AW22" s="7">
+        <f t="shared" ref="AW22" si="102">AW20/AW21</f>
         <v>4.650073660541211</v>
       </c>
-      <c r="AT22" s="7">
-        <f t="shared" ref="AT22" si="108">AT20/AT21</f>
+      <c r="AX22" s="7">
+        <f t="shared" ref="AX22" si="103">AX20/AX21</f>
         <v>5.909272901985906</v>
       </c>
-      <c r="AU22" s="7">
-        <f t="shared" ref="AU22" si="109">AU20/AU21</f>
+      <c r="AY22" s="7">
+        <f t="shared" ref="AY22" si="104">AY20/AY21</f>
         <v>8.2131255127153402</v>
       </c>
-      <c r="AV22" s="7">
-        <f t="shared" ref="AV22" si="110">AV20/AV21</f>
-        <v>10.641346941709415</v>
-      </c>
-      <c r="AW22" s="7">
-        <f t="shared" ref="AW22" si="111">AW20/AW21</f>
-        <v>10.474191141644878</v>
-      </c>
-      <c r="AX22" s="7">
-        <f t="shared" ref="AX22" si="112">AX20/AX21</f>
-        <v>11.36862095983558</v>
-      </c>
-      <c r="AY22" s="7">
-        <f t="shared" ref="AY22" si="113">AY20/AY21</f>
-        <v>12.065703711757022</v>
-      </c>
       <c r="AZ22" s="7">
-        <f t="shared" ref="AZ22" si="114">AZ20/AZ21</f>
-        <v>12.625844572110228</v>
+        <f t="shared" ref="AZ22" si="105">AZ20/AZ21</f>
+        <v>10.925849384144829</v>
       </c>
       <c r="BA22" s="7">
-        <f t="shared" ref="BA22:BB22" si="115">BA20/BA21</f>
-        <v>13.068463611624324</v>
+        <f t="shared" ref="BA22" si="106">BA20/BA21</f>
+        <v>10.538891166735555</v>
       </c>
       <c r="BB22" s="7">
-        <f t="shared" si="115"/>
-        <v>13.450411687786845</v>
+        <f t="shared" ref="BB22" si="107">BB20/BB21</f>
+        <v>11.448152963227248</v>
       </c>
       <c r="BC22" s="7">
-        <f t="shared" ref="BC22:BF22" si="116">BC20/BC21</f>
-        <v>13.769822534056257</v>
+        <f t="shared" ref="BC22" si="108">BC20/BC21</f>
+        <v>12.154268808634074</v>
       </c>
       <c r="BD22" s="7">
-        <f t="shared" si="116"/>
-        <v>13.950816169748096</v>
+        <f t="shared" ref="BD22" si="109">BD20/BD21</f>
+        <v>12.720775020302106</v>
       </c>
       <c r="BE22" s="7">
-        <f t="shared" si="116"/>
-        <v>14.135168250516365</v>
+        <f t="shared" ref="BE22:BF22" si="110">BE20/BE21</f>
+        <v>13.169128462066281</v>
       </c>
       <c r="BF22" s="7">
-        <f t="shared" si="116"/>
-        <v>14.322966890843928</v>
+        <f t="shared" si="110"/>
+        <v>13.556334341055797</v>
+      </c>
+      <c r="BG22" s="7">
+        <f t="shared" ref="BG22:BJ22" si="111">BG20/BG21</f>
+        <v>13.878813376473243</v>
+      </c>
+      <c r="BH22" s="7">
+        <f t="shared" si="111"/>
+        <v>14.060558369032355</v>
+      </c>
+      <c r="BI22" s="7">
+        <f t="shared" si="111"/>
+        <v>14.245654177813355</v>
+      </c>
+      <c r="BJ22" s="7">
+        <f t="shared" si="111"/>
+        <v>14.43418818720977</v>
       </c>
     </row>
-    <row r="24" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>80</v>
       </c>
@@ -5291,580 +5396,604 @@
         <v>0.14363586808394668</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24:AH24" si="117">AF3/AB3-1</f>
+        <f t="shared" ref="AF24:AH24" si="112">AF3/AB3-1</f>
         <v>0.13796096462419061</v>
       </c>
       <c r="AG24" s="8">
+        <f t="shared" si="112"/>
+        <v>0.12172352700676869</v>
+      </c>
+      <c r="AH24" s="8">
+        <f t="shared" si="112"/>
+        <v>0.12523948354852155</v>
+      </c>
+      <c r="AI24" s="8">
+        <f t="shared" ref="AI24:AI29" si="113">AI3/AE3-1</f>
+        <v>9.8492070370049367E-2</v>
+      </c>
+      <c r="AJ24" s="8">
+        <f t="shared" ref="AJ24:AJ29" si="114">AJ3/AF3-1</f>
+        <v>0.11711228844132027</v>
+      </c>
+      <c r="AK24" s="8">
+        <f t="shared" ref="AK24:AK29" si="115">AK3/AG3-1</f>
+        <v>0.14542877391920617</v>
+      </c>
+      <c r="AL24" s="8">
+        <f t="shared" ref="AL24:AL29" si="116">AL3/AH3-1</f>
+        <v>0.1672835622015767</v>
+      </c>
+      <c r="AM24" s="8"/>
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8"/>
+      <c r="AP24" s="8"/>
+      <c r="AV24" s="8">
+        <f t="shared" ref="AV24:AW24" si="117">AV3/AU3-1</f>
+        <v>0.43136783840402826</v>
+      </c>
+      <c r="AW24" s="8">
         <f t="shared" si="117"/>
-        <v>0.12172352700676869</v>
-      </c>
-      <c r="AH24" s="8">
-        <f t="shared" si="117"/>
-        <v>0.12523948354852155</v>
-      </c>
-      <c r="AI24" s="8">
-        <f t="shared" ref="AI24:AI29" si="118">AI3/AE3-1</f>
-        <v>9.8492070370049367E-2</v>
-      </c>
-      <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24:AJ29" si="119">AJ3/AF3-1</f>
-        <v>0.11711228844132027</v>
-      </c>
-      <c r="AK24" s="8">
-        <f t="shared" ref="AK24:AK29" si="120">AK3/AG3-1</f>
-        <v>0.14542877391920617</v>
-      </c>
-      <c r="AL24" s="8">
-        <f t="shared" ref="AL24:AL29" si="121">AL3/AH3-1</f>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AR24" s="8">
-        <f t="shared" ref="AR24:AS24" si="122">AR3/AQ3-1</f>
-        <v>0.43136783840402826</v>
-      </c>
-      <c r="AS24" s="8">
-        <f t="shared" si="122"/>
         <v>9.0627118985438182E-2</v>
       </c>
-      <c r="AT24" s="8">
-        <f>AT3/AS3-1</f>
+      <c r="AX24" s="8">
+        <f>AX3/AW3-1</f>
         <v>7.7457679285934056E-2</v>
       </c>
-      <c r="AU24" s="8">
-        <f t="shared" ref="AU24:BF29" si="123">AU3/AT3-1</f>
+      <c r="AY24" s="8">
+        <f t="shared" ref="AY24:BJ29" si="118">AY3/AX3-1</f>
         <v>0.13169516605440124</v>
       </c>
-      <c r="AV24" s="8">
-        <f t="shared" si="123"/>
-        <v>0.12062094868843531</v>
-      </c>
-      <c r="AW24" s="8">
-        <f t="shared" si="123"/>
+      <c r="AZ24" s="8">
+        <f t="shared" si="118"/>
+        <v>0.13351911310353182</v>
+      </c>
+      <c r="BA24" s="8">
+        <f t="shared" si="118"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AX24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BB24" s="8">
+        <f t="shared" si="118"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AY24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BC24" s="8">
+        <f t="shared" si="118"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AZ24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BD24" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BE24" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF24" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG24" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH24" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI24" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF24" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ24" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>81</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AH25" si="124">AE4/AA4-1</f>
+        <f t="shared" ref="AE25:AH25" si="119">AE4/AA4-1</f>
         <v>0.20872553414014638</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="119"/>
         <v>0.13020221787345077</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="119"/>
         <v>0.12185613682092544</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="119"/>
         <v>0.1383695652173913</v>
       </c>
       <c r="AI25" s="8">
+        <f t="shared" si="113"/>
+        <v>0.10346106304079106</v>
+      </c>
+      <c r="AJ25" s="8">
+        <f t="shared" si="114"/>
+        <v>0.1307861018123051</v>
+      </c>
+      <c r="AK25" s="8">
+        <f t="shared" si="115"/>
+        <v>0.15020737585472488</v>
+      </c>
+      <c r="AL25" s="8">
+        <f t="shared" si="116"/>
+        <v>8.6890098348133327E-2</v>
+      </c>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+      <c r="AP25" s="8"/>
+      <c r="AV25" s="8">
+        <f t="shared" ref="AV25:AW25" si="120">AV4/AU4-1</f>
+        <v>0.45888124620675708</v>
+      </c>
+      <c r="AW25" s="8">
+        <f t="shared" si="120"/>
+        <v>1.3797885248743258E-2</v>
+      </c>
+      <c r="AX25" s="8">
+        <f t="shared" ref="AX25" si="121">AX4/AW4-1</f>
+        <v>7.7522825975447018E-2</v>
+      </c>
+      <c r="AY25" s="8">
         <f t="shared" si="118"/>
-        <v>0.10346106304079106</v>
-      </c>
-      <c r="AJ25" s="8">
-        <f t="shared" si="119"/>
-        <v>0.1307861018123051</v>
-      </c>
-      <c r="AK25" s="8">
-        <f t="shared" si="120"/>
-        <v>0.15020737585472488</v>
-      </c>
-      <c r="AL25" s="8">
-        <f t="shared" si="121"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AR25" s="8">
-        <f t="shared" ref="AR25:AS25" si="125">AR4/AQ4-1</f>
-        <v>0.45888124620675708</v>
-      </c>
-      <c r="AS25" s="8">
-        <f t="shared" si="125"/>
-        <v>1.3797885248743258E-2</v>
-      </c>
-      <c r="AT25" s="8">
-        <f t="shared" ref="AT25" si="126">AT4/AS4-1</f>
-        <v>7.7522825975447018E-2</v>
-      </c>
-      <c r="AU25" s="8">
-        <f t="shared" si="123"/>
         <v>0.14715963186290071</v>
       </c>
-      <c r="AV25" s="8">
-        <f t="shared" si="123"/>
-        <v>0.12633856198301396</v>
-      </c>
-      <c r="AW25" s="8">
-        <f t="shared" si="123"/>
+      <c r="AZ25" s="8">
+        <f t="shared" si="118"/>
+        <v>0.11674551138407052</v>
+      </c>
+      <c r="BA25" s="8">
+        <f t="shared" si="118"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AX25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BB25" s="8">
+        <f t="shared" si="118"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AY25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BC25" s="8">
+        <f t="shared" si="118"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AZ25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BD25" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BE25" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF25" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG25" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH25" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI25" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF25" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ25" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>82</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AH26" si="127">AE5/AA5-1</f>
+        <f t="shared" ref="AE26:AH26" si="122">AE5/AA5-1</f>
         <v>-1.1072572038420492E-2</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="122"/>
         <v>-5.1719745222929991E-2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="122"/>
         <v>-1.5777806754466051E-2</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="122"/>
         <v>-4.1340243461492121E-2</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="113"/>
         <v>-2.1179009847565045E-2</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="114"/>
         <v>-1.2090274046211769E-2</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>-2.5702172760996289E-2</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="121"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="AR26" s="8">
-        <f t="shared" ref="AR26:AS26" si="128">AR5/AQ5-1</f>
+        <f t="shared" si="116"/>
+        <v>-1.584108624591396E-2</v>
+      </c>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
+      <c r="AP26" s="8"/>
+      <c r="AV26" s="8">
+        <f t="shared" ref="AV26:AW26" si="123">AV5/AU5-1</f>
         <v>0.37293200519705505</v>
-      </c>
-      <c r="AS26" s="8">
-        <f t="shared" si="128"/>
-        <v>3.4036781174095365E-2</v>
-      </c>
-      <c r="AT26" s="8">
-        <f t="shared" ref="AT26" si="129">AT5/AS5-1</f>
-        <v>-4.4783404514948111E-2</v>
-      </c>
-      <c r="AU26" s="8">
-        <f t="shared" si="123"/>
-        <v>-3.0435615738375055E-2</v>
-      </c>
-      <c r="AV26" s="8">
-        <f t="shared" si="123"/>
-        <v>-1.9766131954280453E-2</v>
       </c>
       <c r="AW26" s="8">
         <f t="shared" si="123"/>
+        <v>3.4036781174095365E-2</v>
+      </c>
+      <c r="AX26" s="8">
+        <f t="shared" ref="AX26" si="124">AX5/AW5-1</f>
+        <v>-4.4783404514948111E-2</v>
+      </c>
+      <c r="AY26" s="8">
+        <f t="shared" si="118"/>
+        <v>-3.0435615738375055E-2</v>
+      </c>
+      <c r="AZ26" s="8">
+        <f t="shared" si="118"/>
+        <v>-1.8676504496195512E-2</v>
+      </c>
+      <c r="BA26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BB26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BC26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BD26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BA26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BE26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF26" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ26" s="8">
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>83</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AH27" si="130">AE6/AA6-1</f>
+        <f t="shared" ref="AE27:AH27" si="125">AE6/AA6-1</f>
         <v>0.17887494941319293</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="125"/>
         <v>0.14369933677229185</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="125"/>
         <v>0.2778510612783307</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="125"/>
         <v>7.772836761163604E-2</v>
       </c>
       <c r="AI27" s="8">
+        <f t="shared" si="113"/>
+        <v>0.18766449250486317</v>
+      </c>
+      <c r="AJ27" s="8">
+        <f t="shared" si="114"/>
+        <v>0.20307130584192445</v>
+      </c>
+      <c r="AK27" s="8">
+        <f t="shared" si="115"/>
+        <v>0.20777027027027017</v>
+      </c>
+      <c r="AL27" s="8">
+        <f t="shared" si="116"/>
+        <v>0.1671967678156967</v>
+      </c>
+      <c r="AM27" s="8"/>
+      <c r="AN27" s="8"/>
+      <c r="AO27" s="8"/>
+      <c r="AP27" s="8"/>
+      <c r="AV27" s="8">
+        <f t="shared" ref="AV27:AW27" si="126">AV6/AU6-1</f>
+        <v>0.29114273870388274</v>
+      </c>
+      <c r="AW27" s="8">
+        <f t="shared" si="126"/>
+        <v>3.6494006849315141E-2</v>
+      </c>
+      <c r="AX27" s="8">
+        <f t="shared" ref="AX27" si="127">AX6/AW6-1</f>
+        <v>0.19387368783341929</v>
+      </c>
+      <c r="AY27" s="8">
         <f t="shared" si="118"/>
-        <v>0.18766449250486317</v>
-      </c>
-      <c r="AJ27" s="8">
-        <f t="shared" si="119"/>
-        <v>0.20307130584192445</v>
-      </c>
-      <c r="AK27" s="8">
-        <f t="shared" si="120"/>
-        <v>0.20777027027027017</v>
-      </c>
-      <c r="AL27" s="8">
-        <f t="shared" si="121"/>
-        <v>0.18999999999999995</v>
-      </c>
-      <c r="AR27" s="8">
-        <f t="shared" ref="AR27:AS27" si="131">AR6/AQ6-1</f>
-        <v>0.29114273870388274</v>
-      </c>
-      <c r="AS27" s="8">
-        <f t="shared" si="131"/>
-        <v>3.6494006849315141E-2</v>
-      </c>
-      <c r="AT27" s="8">
-        <f t="shared" ref="AT27" si="132">AT6/AS6-1</f>
-        <v>0.19387368783341929</v>
-      </c>
-      <c r="AU27" s="8">
-        <f t="shared" si="123"/>
         <v>0.16293819188191883</v>
       </c>
-      <c r="AV27" s="8">
-        <f t="shared" si="123"/>
-        <v>0.19720550322260766</v>
-      </c>
-      <c r="AW27" s="8">
-        <f t="shared" si="123"/>
+      <c r="AZ27" s="8">
+        <f t="shared" si="118"/>
+        <v>0.1906296479920675</v>
+      </c>
+      <c r="BA27" s="8">
+        <f t="shared" si="118"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="AX27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BB27" s="8">
+        <f t="shared" si="118"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AY27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BC27" s="8">
+        <f t="shared" si="118"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AZ27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BD27" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BA27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BE27" s="8">
+        <f t="shared" si="118"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BB27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF27" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG27" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BD27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH27" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BE27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI27" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BF27" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ27" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>84</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" ref="AE28:AH28" si="133">AE7/AA7-1</f>
+        <f t="shared" ref="AE28:AH28" si="128">AE7/AA7-1</f>
         <v>0.28441105446740012</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="128"/>
         <v>0.28838251774374291</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="128"/>
         <v>0.34978004993460954</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="128"/>
         <v>0.3005874673629243</v>
       </c>
       <c r="AI28" s="8">
+        <f t="shared" si="113"/>
+        <v>0.28055149362857734</v>
+      </c>
+      <c r="AJ28" s="8">
+        <f t="shared" si="114"/>
+        <v>0.31671015753358467</v>
+      </c>
+      <c r="AK28" s="8">
+        <f t="shared" si="115"/>
+        <v>0.33506562142165075</v>
+      </c>
+      <c r="AL28" s="8">
+        <f t="shared" si="116"/>
+        <v>0.47754077791718941</v>
+      </c>
+      <c r="AM28" s="8"/>
+      <c r="AN28" s="8"/>
+      <c r="AO28" s="8"/>
+      <c r="AP28" s="8"/>
+      <c r="AV28" s="8">
+        <f t="shared" ref="AV28:AW28" si="129">AV7/AU7-1</f>
+        <v>0.47070985527222597</v>
+      </c>
+      <c r="AW28" s="8">
+        <f t="shared" si="129"/>
+        <v>0.36832239925023424</v>
+      </c>
+      <c r="AX28" s="8">
+        <f t="shared" ref="AX28" si="130">AX7/AW7-1</f>
+        <v>0.25905631659056327</v>
+      </c>
+      <c r="AY28" s="8">
         <f t="shared" si="118"/>
-        <v>0.28055149362857734</v>
-      </c>
-      <c r="AJ28" s="8">
-        <f t="shared" si="119"/>
-        <v>0.31671015753358467</v>
-      </c>
-      <c r="AK28" s="8">
-        <f t="shared" si="120"/>
-        <v>0.33506562142165075</v>
-      </c>
-      <c r="AL28" s="8">
-        <f t="shared" si="121"/>
-        <v>0.32000000000000006</v>
-      </c>
-      <c r="AR28" s="8">
-        <f t="shared" ref="AR28:AS28" si="134">AR7/AQ7-1</f>
-        <v>0.47070985527222597</v>
-      </c>
-      <c r="AS28" s="8">
-        <f t="shared" si="134"/>
-        <v>0.36832239925023424</v>
-      </c>
-      <c r="AT28" s="8">
-        <f t="shared" ref="AT28" si="135">AT7/AS7-1</f>
-        <v>0.25905631659056327</v>
-      </c>
-      <c r="AU28" s="8">
-        <f t="shared" si="123"/>
         <v>0.30648573500967125</v>
       </c>
-      <c r="AV28" s="8">
-        <f t="shared" si="123"/>
-        <v>0.31443244118531544</v>
-      </c>
-      <c r="AW28" s="8">
-        <f t="shared" si="123"/>
+      <c r="AZ28" s="8">
+        <f t="shared" si="118"/>
+        <v>0.35800041638714752</v>
+      </c>
+      <c r="BA28" s="8">
+        <f t="shared" si="118"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AX28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BB28" s="8">
+        <f t="shared" si="118"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AY28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BC28" s="8">
+        <f t="shared" si="118"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AZ28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BD28" s="8">
+        <f t="shared" si="118"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="BA28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BE28" s="8">
+        <f t="shared" si="118"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="BB28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF28" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BC28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG28" s="8">
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BD28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH28" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI28" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF28" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ28" s="8">
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>85</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" ref="AE29:AH29" si="136">AE8/AA8-1</f>
+        <f t="shared" ref="AE29:AH29" si="131">AE8/AA8-1</f>
         <v>0.71875</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="131"/>
         <v>0.2807017543859649</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="131"/>
         <v>0.30639730639730645</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="131"/>
         <v>-0.39117199391171997</v>
       </c>
       <c r="AI29" s="8">
+        <f t="shared" si="113"/>
+        <v>-9.0909090909090939E-2</v>
+      </c>
+      <c r="AJ29" s="8">
+        <f t="shared" si="114"/>
+        <v>2.1917808219177992E-2</v>
+      </c>
+      <c r="AK29" s="8">
+        <f t="shared" si="115"/>
+        <v>-0.11340206185567014</v>
+      </c>
+      <c r="AL29" s="8">
+        <f t="shared" si="116"/>
+        <v>-7.4999999999999956E-2</v>
+      </c>
+      <c r="AM29" s="8"/>
+      <c r="AN29" s="8"/>
+      <c r="AO29" s="8"/>
+      <c r="AP29" s="8"/>
+      <c r="AV29" s="8">
+        <f t="shared" ref="AV29:AW29" si="132">AV8/AU8-1</f>
+        <v>0.14611872146118721</v>
+      </c>
+      <c r="AW29" s="8">
+        <f t="shared" si="132"/>
+        <v>0.41832669322709171</v>
+      </c>
+      <c r="AX29" s="8">
+        <f t="shared" ref="AX29" si="133">AX8/AW8-1</f>
+        <v>0.4297752808988764</v>
+      </c>
+      <c r="AY29" s="8">
         <f t="shared" si="118"/>
-        <v>-9.0909090909090939E-2</v>
-      </c>
-      <c r="AJ29" s="8">
-        <f t="shared" si="119"/>
-        <v>2.1917808219177992E-2</v>
-      </c>
-      <c r="AK29" s="8">
-        <f t="shared" si="120"/>
-        <v>-0.11340206185567014</v>
-      </c>
-      <c r="AL29" s="8">
-        <f t="shared" si="121"/>
+        <v>7.9240340537000575E-2</v>
+      </c>
+      <c r="AZ29" s="8">
+        <f t="shared" si="118"/>
+        <v>-6.7354368932038833E-2</v>
+      </c>
+      <c r="BA29" s="8">
+        <f t="shared" si="118"/>
+        <v>0.25</v>
+      </c>
+      <c r="BB29" s="8">
+        <f t="shared" si="118"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="BC29" s="8">
+        <f t="shared" si="118"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="BD29" s="8">
+        <f t="shared" si="118"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="BE29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AR29" s="8">
-        <f t="shared" ref="AR29:AS29" si="137">AR8/AQ8-1</f>
-        <v>0.14611872146118721</v>
-      </c>
-      <c r="AS29" s="8">
-        <f t="shared" si="137"/>
-        <v>0.41832669322709171</v>
-      </c>
-      <c r="AT29" s="8">
-        <f t="shared" ref="AT29" si="138">AT8/AS8-1</f>
-        <v>0.4297752808988764</v>
-      </c>
-      <c r="AU29" s="8">
-        <f t="shared" si="123"/>
-        <v>7.9240340537000575E-2</v>
-      </c>
-      <c r="AV29" s="8">
-        <f t="shared" si="123"/>
-        <v>-3.7014563106796072E-2</v>
-      </c>
-      <c r="AW29" s="8">
-        <f t="shared" si="123"/>
-        <v>0.25</v>
-      </c>
-      <c r="AX29" s="8">
-        <f t="shared" si="123"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AY29" s="8">
-        <f t="shared" si="123"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AZ29" s="8">
-        <f t="shared" si="123"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="BA29" s="8">
-        <f t="shared" si="123"/>
+      <c r="BF29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BB29" s="8">
-        <f t="shared" si="123"/>
+      <c r="BG29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BC29" s="8">
-        <f t="shared" si="123"/>
+      <c r="BH29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BD29" s="8">
-        <f t="shared" si="123"/>
+      <c r="BI29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BE29" s="8">
-        <f t="shared" si="123"/>
+      <c r="BJ29" s="8">
+        <f t="shared" si="118"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BF29" s="8">
-        <f t="shared" si="123"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
     </row>
-    <row r="30" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>38</v>
       </c>
@@ -5873,39 +6002,39 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="8">
-        <f t="shared" ref="G30" si="139">G10/C10-1</f>
+        <f t="shared" ref="G30" si="134">G10/C10-1</f>
         <v>0.25842424242424245</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" ref="H30" si="140">H10/D10-1</f>
+        <f t="shared" ref="H30" si="135">H10/D10-1</f>
         <v>0.25555555555555554</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" ref="I30" si="141">I10/E10-1</f>
+        <f t="shared" ref="I30" si="136">I10/E10-1</f>
         <v>0.21489269768111763</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" ref="J30" si="142">J10/F10-1</f>
+        <f t="shared" ref="J30" si="137">J10/F10-1</f>
         <v>0.21854058078927774</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" ref="K30:O30" si="143">K10/G10-1</f>
+        <f t="shared" ref="K30:O30" si="138">K10/G10-1</f>
         <v>0.16673088036987083</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="138"/>
         <v>0.19251615273907574</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="138"/>
         <v>0.2003260225251926</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="138"/>
         <v>0.17310825949689379</v>
       </c>
       <c r="O30" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="138"/>
         <v>0.13263986350752632</v>
       </c>
       <c r="P30" s="8">
@@ -5913,220 +6042,224 @@
         <v>-1.6613599013968749E-2</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" ref="Q30:R30" si="144">Q10/M10-1</f>
+        <f t="shared" ref="Q30:R30" si="139">Q10/M10-1</f>
         <v>0.14010222474628997</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>0.23489962018448174</v>
       </c>
       <c r="S30" s="8">
-        <f t="shared" ref="S30" si="145">S10/O10-1</f>
+        <f t="shared" ref="S30" si="140">S10/O10-1</f>
         <v>0.34391020189994892</v>
       </c>
       <c r="T30" s="8">
-        <f t="shared" ref="T30" si="146">T10/P10-1</f>
+        <f t="shared" ref="T30" si="141">T10/P10-1</f>
         <v>0.44434289892158652</v>
       </c>
       <c r="U30" s="8">
-        <f t="shared" ref="U30" si="147">U10/Q10-1</f>
+        <f t="shared" ref="U30" si="142">U10/Q10-1</f>
         <v>0.41030472353973102</v>
       </c>
       <c r="V30" s="8">
-        <f t="shared" ref="V30" si="148">V10/R10-1</f>
+        <f t="shared" ref="V30" si="143">V10/R10-1</f>
         <v>0.32386024113325607</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" ref="W30" si="149">W10/S10-1</f>
+        <f t="shared" ref="W30" si="144">W10/S10-1</f>
         <v>0.22954405756228069</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" ref="X30" si="150">X10/T10-1</f>
+        <f t="shared" ref="X30" si="145">X10/T10-1</f>
         <v>0.25980764363452291</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" ref="Y30" si="151">Y10/U10-1</f>
+        <f t="shared" ref="Y30" si="146">Y10/U10-1</f>
         <v>6.1027672840074931E-2</v>
       </c>
       <c r="Z30" s="8">
-        <f t="shared" ref="Z30" si="152">Z10/V10-1</f>
+        <f t="shared" ref="Z30" si="147">Z10/V10-1</f>
         <v>9.5984069034185104E-3</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" ref="AA30" si="153">AA10/W10-1</f>
+        <f t="shared" ref="AA30" si="148">AA10/W10-1</f>
         <v>2.6113422828660138E-2</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" ref="AB30" si="154">AB10/X10-1</f>
+        <f t="shared" ref="AB30" si="149">AB10/X10-1</f>
         <v>7.0589079428858392E-2</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" ref="AC30" si="155">AC10/Y10-1</f>
+        <f t="shared" ref="AC30" si="150">AC10/Y10-1</f>
         <v>0.11001273664100042</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" ref="AD30" si="156">AD10/Z10-1</f>
+        <f t="shared" ref="AD30" si="151">AD10/Z10-1</f>
         <v>0.13494108983799702</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" ref="AE30" si="157">AE10/AA10-1</f>
+        <f t="shared" ref="AE30" si="152">AE10/AA10-1</f>
         <v>0.15406880937710454</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" ref="AF30" si="158">AF10/AB10-1</f>
+        <f t="shared" ref="AF30" si="153">AF10/AB10-1</f>
         <v>0.13589083695244231</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" ref="AG30" si="159">AG10/AC10-1</f>
+        <f t="shared" ref="AG30" si="154">AG10/AC10-1</f>
         <v>0.15092642092498654</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" ref="AH30" si="160">AH10/AD10-1</f>
+        <f t="shared" ref="AH30" si="155">AH10/AD10-1</f>
         <v>0.11770362646275045</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" ref="AI30" si="161">AI10/AE10-1</f>
+        <f t="shared" ref="AI30" si="156">AI10/AE10-1</f>
         <v>0.12037646357665222</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" ref="AJ30" si="162">AJ10/AF10-1</f>
+        <f t="shared" ref="AJ30" si="157">AJ10/AF10-1</f>
         <v>0.13790092280097244</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" ref="AK30" si="163">AK10/AG10-1</f>
+        <f t="shared" ref="AK30" si="158">AK10/AG10-1</f>
         <v>0.1594915484660353</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" ref="AL30" si="164">AL10/AH10-1</f>
-        <v>0.14167898495889886</v>
-      </c>
-      <c r="AO30" s="8">
-        <f>AO10/AN10-1</f>
+        <f t="shared" ref="AL30" si="159">AL10/AH10-1</f>
+        <v>0.17994381614819277</v>
+      </c>
+      <c r="AM30" s="8"/>
+      <c r="AN30" s="8"/>
+      <c r="AO30" s="8"/>
+      <c r="AP30" s="8"/>
+      <c r="AS30" s="8">
+        <f>AS10/AR10-1</f>
         <v>0.23522985807663144</v>
       </c>
-      <c r="AP30" s="8">
-        <f t="shared" ref="AP30:BB30" si="165">AP10/AO10-1</f>
+      <c r="AT30" s="8">
+        <f t="shared" ref="AT30:BF30" si="160">AT10/AS10-1</f>
         <v>0.18300089899794614</v>
       </c>
-      <c r="AQ30" s="8">
-        <f t="shared" si="165"/>
+      <c r="AU30" s="8">
+        <f t="shared" si="160"/>
         <v>0.12770532012826141</v>
       </c>
-      <c r="AR30" s="8">
-        <f t="shared" si="165"/>
+      <c r="AV30" s="8">
+        <f t="shared" si="160"/>
         <v>0.37552800407610931</v>
       </c>
-      <c r="AS30" s="8">
-        <f t="shared" si="165"/>
+      <c r="AW30" s="8">
+        <f t="shared" si="160"/>
         <v>0.12651799690127485</v>
       </c>
-      <c r="AT30" s="8">
-        <f t="shared" si="165"/>
+      <c r="AX30" s="8">
+        <f t="shared" si="160"/>
         <v>8.6827702272695095E-2</v>
       </c>
-      <c r="AU30" s="8">
-        <f t="shared" si="165"/>
+      <c r="AY30" s="8">
+        <f t="shared" si="160"/>
         <v>0.13866243322901561</v>
       </c>
-      <c r="AV30" s="8">
-        <f t="shared" si="165"/>
-        <v>0.14035458176436633</v>
-      </c>
-      <c r="AW30" s="8">
-        <f t="shared" si="165"/>
-        <v>0.10294250883445422</v>
-      </c>
-      <c r="AX30" s="8">
-        <f t="shared" si="165"/>
-        <v>7.3615075872781155E-2</v>
-      </c>
-      <c r="AY30" s="8">
-        <f t="shared" si="165"/>
-        <v>5.1053872147143631E-2</v>
-      </c>
       <c r="AZ30" s="8">
-        <f t="shared" si="165"/>
-        <v>4.0326140234814956E-2</v>
+        <f t="shared" si="160"/>
+        <v>0.15090081081544371</v>
       </c>
       <c r="BA30" s="8">
-        <f t="shared" si="165"/>
-        <v>3.0268007675239961E-2</v>
+        <f t="shared" si="160"/>
+        <v>0.10332112820105466</v>
       </c>
       <c r="BB30" s="8">
-        <f t="shared" si="165"/>
-        <v>2.642436679095006E-2</v>
+        <f t="shared" si="160"/>
+        <v>7.3917355467104651E-2</v>
       </c>
       <c r="BC30" s="8">
-        <f t="shared" ref="BC30" si="166">BC10/BB10-1</f>
-        <v>2.2775780417806368E-2</v>
+        <f t="shared" si="160"/>
+        <v>5.1244751118981524E-2</v>
       </c>
       <c r="BD30" s="8">
-        <f t="shared" ref="BD30" si="167">BD10/BC10-1</f>
-        <v>1.5683825775720805E-2</v>
+        <f t="shared" si="160"/>
+        <v>4.0483709761662157E-2</v>
       </c>
       <c r="BE30" s="8">
-        <f t="shared" ref="BE30" si="168">BE10/BD10-1</f>
-        <v>1.5740619450484994E-2</v>
+        <f t="shared" si="160"/>
+        <v>3.0372809671984413E-2</v>
       </c>
       <c r="BF30" s="8">
-        <f t="shared" ref="BF30" si="169">BF10/BE10-1</f>
-        <v>1.5797935425830412E-2</v>
+        <f t="shared" si="160"/>
+        <v>2.6528178995257834E-2</v>
+      </c>
+      <c r="BG30" s="8">
+        <f t="shared" ref="BG30" si="161">BG10/BF10-1</f>
+        <v>2.2796142204261516E-2</v>
+      </c>
+      <c r="BH30" s="8">
+        <f t="shared" ref="BH30" si="162">BH10/BG10-1</f>
+        <v>1.56555707499344E-2</v>
+      </c>
+      <c r="BI30" s="8">
+        <f t="shared" ref="BI30" si="163">BI10/BH10-1</f>
+        <v>1.5711698871324842E-2</v>
+      </c>
+      <c r="BJ30" s="8">
+        <f t="shared" ref="BJ30" si="164">BJ10/BI10-1</f>
+        <v>1.5768338428950868E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="8">
-        <f t="shared" ref="C31:F31" si="170">C12/C10</f>
+        <f t="shared" ref="C31:F31" si="165">C12/C10</f>
         <v>0.60424242424242425</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="165"/>
         <v>0.60119184928873515</v>
       </c>
       <c r="E31" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="165"/>
         <v>0.59858850640933314</v>
       </c>
       <c r="F31" s="8">
-        <f t="shared" si="170"/>
+        <f t="shared" si="165"/>
         <v>0.55736535120377262</v>
       </c>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:O31" si="171">G12/G10</f>
+        <f t="shared" ref="G31:O31" si="166">G12/G10</f>
         <v>0.56761702947408976</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.57488440456869894</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.57673384706579722</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.54379264690905382</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.55937147417375277</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.55587510271158591</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.56621151139534309</v>
       </c>
       <c r="N31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.54378730330982095</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.53881289632887097</v>
       </c>
       <c r="P31" s="8">
@@ -6134,188 +6267,192 @@
         <v>0.51554952085019712</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" ref="Q31:R31" si="172">Q12/Q10</f>
+        <f t="shared" ref="Q31:R31" si="167">Q12/Q10</f>
         <v>0.54265479825872265</v>
       </c>
       <c r="R31" s="8">
+        <f t="shared" si="167"/>
+        <v>0.54163590987380927</v>
+      </c>
+      <c r="S31" s="8">
+        <f t="shared" ref="S31:V31" si="168">S12/S10</f>
+        <v>0.56425136493473627</v>
+      </c>
+      <c r="T31" s="8">
+        <f t="shared" si="168"/>
+        <v>0.56425136493473627</v>
+      </c>
+      <c r="U31" s="8">
+        <f t="shared" si="168"/>
+        <v>0.57583156730857832</v>
+      </c>
+      <c r="V31" s="8">
+        <f t="shared" si="168"/>
+        <v>0.56205774975107869</v>
+      </c>
+      <c r="W31" s="8">
+        <f t="shared" ref="W31:AE31" si="169">W12/W10</f>
+        <v>0.5647909896928438</v>
+      </c>
+      <c r="X31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.56799885197675248</v>
+      </c>
+      <c r="Y31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.54903606785156023</v>
+      </c>
+      <c r="Z31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.53526719966337055</v>
+      </c>
+      <c r="AA31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.56135096794531936</v>
+      </c>
+      <c r="AB31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.5721945204010509</v>
+      </c>
+      <c r="AC31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.56672708069836886</v>
+      </c>
+      <c r="AD31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.56465067778936395</v>
+      </c>
+      <c r="AE31" s="8">
+        <f t="shared" si="169"/>
+        <v>0.58142018152696207</v>
+      </c>
+      <c r="AF31" s="8">
+        <f t="shared" ref="AF31:AH31" si="170">AF12/AF10</f>
+        <v>0.58099879634655782</v>
+      </c>
+      <c r="AG31" s="8">
+        <f t="shared" si="170"/>
+        <v>0.58678116644763678</v>
+      </c>
+      <c r="AH31" s="8">
+        <f t="shared" si="170"/>
+        <v>0.5790046543449191</v>
+      </c>
+      <c r="AI31" s="8">
+        <f t="shared" ref="AI31:AL31" si="171">AI12/AI10</f>
+        <v>0.5970365937451515</v>
+      </c>
+      <c r="AJ31" s="8">
+        <f t="shared" si="171"/>
+        <v>0.59514871199236741</v>
+      </c>
+      <c r="AK31" s="8">
+        <f t="shared" si="171"/>
+        <v>0.59579270318331934</v>
+      </c>
+      <c r="AL31" s="8">
+        <f t="shared" si="171"/>
+        <v>0.59793723864075621</v>
+      </c>
+      <c r="AM31" s="8"/>
+      <c r="AN31" s="8"/>
+      <c r="AO31" s="8"/>
+      <c r="AP31" s="8"/>
+      <c r="AR31" s="8">
+        <f t="shared" ref="AR31:BE31" si="172">AR12/AR10</f>
+        <v>0.58846737207034772</v>
+      </c>
+      <c r="AS31" s="8">
         <f t="shared" si="172"/>
-        <v>0.54163590987380927</v>
-      </c>
-      <c r="S31" s="8">
-        <f t="shared" ref="S31:V31" si="173">S12/S10</f>
-        <v>0.56425136493473627</v>
-      </c>
-      <c r="T31" s="8">
+        <v>0.5647607422945643</v>
+      </c>
+      <c r="AT31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.5558054331910266</v>
+      </c>
+      <c r="AU31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.53578374706207854</v>
+      </c>
+      <c r="AV31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.56659669973832105</v>
+      </c>
+      <c r="AW31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.55379442503783116</v>
+      </c>
+      <c r="AX31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.56625047984020505</v>
+      </c>
+      <c r="AY31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.58200435406179107</v>
+      </c>
+      <c r="AZ31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.59652315086039975</v>
+      </c>
+      <c r="BA31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.6</v>
+      </c>
+      <c r="BB31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.6</v>
+      </c>
+      <c r="BC31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.6</v>
+      </c>
+      <c r="BD31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.6</v>
+      </c>
+      <c r="BE31" s="8">
+        <f t="shared" si="172"/>
+        <v>0.6</v>
+      </c>
+      <c r="BF31" s="8">
+        <f t="shared" ref="BF31:BJ31" si="173">BF12/BF10</f>
+        <v>0.6</v>
+      </c>
+      <c r="BG31" s="8">
         <f t="shared" si="173"/>
-        <v>0.56425136493473627</v>
-      </c>
-      <c r="U31" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BH31" s="8">
         <f t="shared" si="173"/>
-        <v>0.57583156730857832</v>
-      </c>
-      <c r="V31" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="BI31" s="8">
         <f t="shared" si="173"/>
-        <v>0.56205774975107869</v>
-      </c>
-      <c r="W31" s="8">
-        <f t="shared" ref="W31:AE31" si="174">W12/W10</f>
-        <v>0.5647909896928438</v>
-      </c>
-      <c r="X31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.56799885197675248</v>
-      </c>
-      <c r="Y31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.54903606785156023</v>
-      </c>
-      <c r="Z31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.53526719966337055</v>
-      </c>
-      <c r="AA31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.56135096794531936</v>
-      </c>
-      <c r="AB31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.5721945204010509</v>
-      </c>
-      <c r="AC31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.56672708069836886</v>
-      </c>
-      <c r="AD31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.56465067778936395</v>
-      </c>
-      <c r="AE31" s="8">
-        <f t="shared" si="174"/>
-        <v>0.58142018152696207</v>
-      </c>
-      <c r="AF31" s="8">
-        <f t="shared" ref="AF31:AH31" si="175">AF12/AF10</f>
-        <v>0.58099879634655782</v>
-      </c>
-      <c r="AG31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.58678116644763678</v>
-      </c>
-      <c r="AH31" s="8">
-        <f t="shared" si="175"/>
-        <v>0.5790046543449191</v>
-      </c>
-      <c r="AI31" s="8">
-        <f t="shared" ref="AI31:AL31" si="176">AI12/AI10</f>
-        <v>0.5970365937451515</v>
-      </c>
-      <c r="AJ31" s="8">
-        <f t="shared" si="176"/>
-        <v>0.59514871199236741</v>
-      </c>
-      <c r="AK31" s="8">
-        <f t="shared" si="176"/>
-        <v>0.59579270318331934</v>
-      </c>
-      <c r="AL31" s="8">
-        <f t="shared" si="176"/>
-        <v>0.59999999999999987</v>
-      </c>
-      <c r="AN31" s="8">
-        <f t="shared" ref="AN31:BA31" si="177">AN12/AN10</f>
-        <v>0.58846737207034772</v>
-      </c>
-      <c r="AO31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.5647607422945643</v>
-      </c>
-      <c r="AP31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.5558054331910266</v>
-      </c>
-      <c r="AQ31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.53578374706207854</v>
-      </c>
-      <c r="AR31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.56659669973832105</v>
-      </c>
-      <c r="AS31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.55379442503783116</v>
-      </c>
-      <c r="AT31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.56625047984020505</v>
-      </c>
-      <c r="AU31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.58200435406179107</v>
-      </c>
-      <c r="AV31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.59707925420417152</v>
-      </c>
-      <c r="AW31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.59999999999999987</v>
-      </c>
-      <c r="AX31" s="8">
-        <f t="shared" si="177"/>
         <v>0.6</v>
       </c>
-      <c r="AY31" s="8">
-        <f t="shared" si="177"/>
+      <c r="BJ31" s="8">
+        <f t="shared" si="173"/>
         <v>0.6</v>
       </c>
-      <c r="AZ31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.6</v>
-      </c>
-      <c r="BA31" s="8">
-        <f t="shared" si="177"/>
-        <v>0.6</v>
-      </c>
-      <c r="BB31" s="8">
-        <f t="shared" ref="BB31:BF31" si="178">BB12/BB10</f>
-        <v>0.6</v>
-      </c>
-      <c r="BC31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
-      <c r="BD31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
-      <c r="BE31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
-      <c r="BF31" s="8">
-        <f t="shared" si="178"/>
-        <v>0.6</v>
-      </c>
     </row>
-    <row r="32" spans="2:193" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:197" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:F32" si="179">C16/C10</f>
+        <f t="shared" ref="C32:F32" si="174">C16/C10</f>
         <v>0.26537373737373737</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="179"/>
+        <f t="shared" si="174"/>
         <v>0.26405228758169935</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="179"/>
+        <f t="shared" si="174"/>
         <v>0.28021028373901774</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="179"/>
+        <f t="shared" si="174"/>
         <v>0.23495284189625218</v>
       </c>
       <c r="G32" s="8">
@@ -6323,213 +6460,217 @@
         <v>0.24507159827907277</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" ref="H32:R32" si="180">H16/H10</f>
+        <f t="shared" ref="H32:R32" si="175">H16/H10</f>
         <v>0.24852252197078728</v>
       </c>
       <c r="I32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.25563129816241847</v>
+      </c>
+      <c r="J32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.20931357572054179</v>
+      </c>
+      <c r="K32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.18184319876716476</v>
+      </c>
+      <c r="L32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.23572308956450289</v>
+      </c>
+      <c r="M32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.22659818760957059</v>
+      </c>
+      <c r="N32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.20110689093868692</v>
+      </c>
+      <c r="O32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.1938093734055735</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.1666710186176463</v>
+      </c>
+      <c r="Q32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.24284755159941956</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="175"/>
+        <v>0.27507118000632713</v>
+      </c>
+      <c r="S32" s="8">
+        <f t="shared" ref="S32:V32" si="176">S16/S10</f>
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="T32" s="8">
+        <f t="shared" si="176"/>
+        <v>0.29715804317171057</v>
+      </c>
+      <c r="U32" s="8">
+        <f t="shared" si="176"/>
+        <v>0.32296753585798088</v>
+      </c>
+      <c r="V32" s="8">
+        <f t="shared" si="176"/>
+        <v>0.29054098904746101</v>
+      </c>
+      <c r="W32" s="8">
+        <f t="shared" ref="W32:AE32" si="177">W16/W10</f>
+        <v>0.29545220626075192</v>
+      </c>
+      <c r="X32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.279156202913109</v>
+      </c>
+      <c r="Y32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.24800266311584554</v>
+      </c>
+      <c r="Z32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.23879654954765411</v>
+      </c>
+      <c r="AA32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.24954504420594092</v>
+      </c>
+      <c r="AB32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.29271888906761029</v>
+      </c>
+      <c r="AC32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.27829136948613303</v>
+      </c>
+      <c r="AD32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.27455683003128256</v>
+      </c>
+      <c r="AE32" s="8">
+        <f t="shared" si="177"/>
+        <v>0.31626913669154072</v>
+      </c>
+      <c r="AF32" s="8">
+        <f t="shared" ref="AF32:AH32" si="178">AF16/AF10</f>
+        <v>0.32362936914398999</v>
+      </c>
+      <c r="AG32" s="8">
+        <f t="shared" si="178"/>
+        <v>0.32311823084243441</v>
+      </c>
+      <c r="AH32" s="8">
+        <f t="shared" si="178"/>
+        <v>0.32105650519856122</v>
+      </c>
+      <c r="AI32" s="8">
+        <f t="shared" ref="AI32:AL32" si="179">AI16/AI10</f>
+        <v>0.33918478622248821</v>
+      </c>
+      <c r="AJ32" s="8">
+        <f t="shared" si="179"/>
+        <v>0.32429377359273243</v>
+      </c>
+      <c r="AK32" s="8">
+        <f t="shared" si="179"/>
+        <v>0.30512184159615424</v>
+      </c>
+      <c r="AL32" s="8">
+        <f t="shared" si="179"/>
+        <v>0.31568682573707701</v>
+      </c>
+      <c r="AM32" s="8"/>
+      <c r="AN32" s="8"/>
+      <c r="AO32" s="8"/>
+      <c r="AP32" s="8"/>
+      <c r="AR32" s="8">
+        <f t="shared" ref="AR32:BE32" si="180">AR16/AR10</f>
+        <v>0.25993102452060235</v>
+      </c>
+      <c r="AS32" s="8">
         <f t="shared" si="180"/>
-        <v>0.25563129816241847</v>
-      </c>
-      <c r="J32" s="8">
+        <v>0.23823445574079624</v>
+      </c>
+      <c r="AT32" s="8">
         <f t="shared" si="180"/>
-        <v>0.20931357572054179</v>
-      </c>
-      <c r="K32" s="8">
+        <v>0.22349357766423447</v>
+      </c>
+      <c r="AU32" s="8">
         <f t="shared" si="180"/>
-        <v>0.18184319876716476</v>
-      </c>
-      <c r="L32" s="8">
+        <v>0.22585151785763202</v>
+      </c>
+      <c r="AV32" s="8">
         <f t="shared" si="180"/>
-        <v>0.23572308956450289</v>
-      </c>
-      <c r="M32" s="8">
+        <v>0.30186680261758625</v>
+      </c>
+      <c r="AW32" s="8">
         <f t="shared" si="180"/>
-        <v>0.22659818760957059</v>
-      </c>
-      <c r="N32" s="8">
+        <v>0.26461270842467011</v>
+      </c>
+      <c r="AX32" s="8">
         <f t="shared" si="180"/>
-        <v>0.20110689093868692</v>
-      </c>
-      <c r="O32" s="8">
+        <v>0.27421810445226646</v>
+      </c>
+      <c r="AY32" s="8">
         <f t="shared" si="180"/>
-        <v>0.1938093734055735</v>
-      </c>
-      <c r="P32" s="8">
+        <v>0.32109777211457696</v>
+      </c>
+      <c r="AZ32" s="8">
         <f t="shared" si="180"/>
-        <v>0.1666710186176463</v>
-      </c>
-      <c r="Q32" s="8">
+        <v>0.32032638592380025</v>
+      </c>
+      <c r="BA32" s="8">
         <f t="shared" si="180"/>
-        <v>0.24284755159941956</v>
-      </c>
-      <c r="R32" s="8">
+        <v>0.32460547709997989</v>
+      </c>
+      <c r="BB32" s="8">
         <f t="shared" si="180"/>
-        <v>0.27507118000632713</v>
-      </c>
-      <c r="S32" s="8">
-        <f t="shared" ref="S32:V32" si="181">S16/S10</f>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="T32" s="8">
+        <v>0.32953970005226207</v>
+      </c>
+      <c r="BC32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.33359083008367757</v>
+      </c>
+      <c r="BD32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.33609130920713542</v>
+      </c>
+      <c r="BE32" s="8">
+        <f t="shared" si="180"/>
+        <v>0.33804339676656786</v>
+      </c>
+      <c r="BF32" s="8">
+        <f t="shared" ref="BF32:BJ32" si="181">BF16/BF10</f>
+        <v>0.33926413974359554</v>
+      </c>
+      <c r="BG32" s="8">
         <f t="shared" si="181"/>
-        <v>0.29715804317171057</v>
-      </c>
-      <c r="U32" s="8">
+        <v>0.33978557756167299</v>
+      </c>
+      <c r="BH32" s="8">
         <f t="shared" si="181"/>
-        <v>0.32296753585798088</v>
-      </c>
-      <c r="V32" s="8">
+        <v>0.33897194238413419</v>
+      </c>
+      <c r="BI32" s="8">
         <f t="shared" si="181"/>
-        <v>0.29054098904746101</v>
-      </c>
-      <c r="W32" s="8">
-        <f t="shared" ref="W32:AE32" si="182">W16/W10</f>
-        <v>0.29545220626075192</v>
-      </c>
-      <c r="X32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.279156202913109</v>
-      </c>
-      <c r="Y32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.24800266311584554</v>
-      </c>
-      <c r="Z32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.23879654954765411</v>
-      </c>
-      <c r="AA32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.24954504420594092</v>
-      </c>
-      <c r="AB32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.29271888906761029</v>
-      </c>
-      <c r="AC32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.27829136948613303</v>
-      </c>
-      <c r="AD32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.27455683003128256</v>
-      </c>
-      <c r="AE32" s="8">
-        <f t="shared" si="182"/>
-        <v>0.31626913669154072</v>
-      </c>
-      <c r="AF32" s="8">
-        <f t="shared" ref="AF32:AH32" si="183">AF16/AF10</f>
-        <v>0.32362936914398999</v>
-      </c>
-      <c r="AG32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.32311823084243441</v>
-      </c>
-      <c r="AH32" s="8">
-        <f t="shared" si="183"/>
-        <v>0.32105650519856122</v>
-      </c>
-      <c r="AI32" s="8">
-        <f t="shared" ref="AI32:AL32" si="184">AI16/AI10</f>
-        <v>0.33918478622248821</v>
-      </c>
-      <c r="AJ32" s="8">
-        <f t="shared" si="184"/>
-        <v>0.32429377359273243</v>
-      </c>
-      <c r="AK32" s="8">
-        <f t="shared" si="184"/>
-        <v>0.30512184159615424</v>
-      </c>
-      <c r="AL32" s="8">
-        <f t="shared" si="184"/>
-        <v>0.31814556837266583</v>
-      </c>
-      <c r="AN32" s="8">
-        <f t="shared" ref="AN32:BA32" si="185">AN16/AN10</f>
-        <v>0.25993102452060235</v>
-      </c>
-      <c r="AO32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.23823445574079624</v>
-      </c>
-      <c r="AP32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.22349357766423447</v>
-      </c>
-      <c r="AQ32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.22585151785763202</v>
-      </c>
-      <c r="AR32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.30186680261758625</v>
-      </c>
-      <c r="AS32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.26461270842467011</v>
-      </c>
-      <c r="AT32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.27421810445226646</v>
-      </c>
-      <c r="AU32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.32109777211457696</v>
-      </c>
-      <c r="AV32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.32104773838495582</v>
-      </c>
-      <c r="AW32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.32529188213701632</v>
-      </c>
-      <c r="AX32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.3300569014211342</v>
-      </c>
-      <c r="AY32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.33406200196425256</v>
-      </c>
-      <c r="AZ32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.33655934115523295</v>
-      </c>
-      <c r="BA32" s="8">
-        <f t="shared" si="185"/>
-        <v>0.33848723773643757</v>
-      </c>
-      <c r="BB32" s="8">
-        <f t="shared" ref="BB32:BF32" si="186">BB16/BB10</f>
-        <v>0.33968591176419455</v>
-      </c>
-      <c r="BC32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.34020241804980672</v>
-      </c>
-      <c r="BD32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.33939586840290425</v>
-      </c>
-      <c r="BE32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.33859659394716657</v>
-      </c>
-      <c r="BF32" s="8">
-        <f t="shared" si="186"/>
-        <v>0.33780481297981019</v>
-      </c>
-      <c r="BH32" t="s">
+        <v>0.33816542825616558</v>
+      </c>
+      <c r="BJ32" s="8">
+        <f t="shared" si="181"/>
+        <v>0.3373662509688497</v>
+      </c>
+      <c r="BL32" t="s">
         <v>44</v>
       </c>
-      <c r="BI32" s="8">
+      <c r="BM32" s="8">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="33" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>58</v>
       </c>
@@ -6538,231 +6679,235 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33" si="187">G13/C13-1</f>
+        <f t="shared" ref="G33" si="182">G13/C13-1</f>
         <v>0.27828513444951808</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" ref="H33" si="188">H13/D13-1</f>
+        <f t="shared" ref="H33" si="183">H13/D13-1</f>
         <v>0.22579098753595406</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" ref="I33" si="189">I13/E13-1</f>
+        <f t="shared" ref="I33" si="184">I13/E13-1</f>
         <v>0.24423305588585009</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" ref="J33" si="190">J13/F13-1</f>
+        <f t="shared" ref="J33" si="185">J13/F13-1</f>
         <v>0.4013005109150023</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" ref="K33" si="191">K13/G13-1</f>
+        <f t="shared" ref="K33" si="186">K13/G13-1</f>
         <v>0.19646755308592967</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" ref="L33" si="192">L13/H13-1</f>
+        <f t="shared" ref="L33" si="187">L13/H13-1</f>
         <v>0.21490027375831056</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" ref="M33" si="193">M13/I13-1</f>
+        <f t="shared" ref="M33" si="188">M13/I13-1</f>
         <v>0.25267584097859319</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" ref="N33" si="194">N13/J13-1</f>
+        <f t="shared" ref="N33" si="189">N13/J13-1</f>
         <v>0.19688432217434548</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" ref="O33" si="195">O13/K13-1</f>
+        <f t="shared" ref="O33" si="190">O13/K13-1</f>
         <v>0.1311992038480676</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" ref="P33" si="196">P13/L13-1</f>
+        <f t="shared" ref="P33" si="191">P13/L13-1</f>
         <v>0.10655078062127799</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" ref="Q33" si="197">Q13/M13-1</f>
+        <f t="shared" ref="Q33" si="192">Q13/M13-1</f>
         <v>4.607873054623135E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" ref="R33" si="198">R13/N13-1</f>
+        <f t="shared" ref="R33" si="193">R13/N13-1</f>
         <v>-2.7693159789532018E-2</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" ref="S33" si="199">S13/O13-1</f>
+        <f t="shared" ref="S33" si="194">S13/O13-1</f>
         <v>9.7507331378299034E-2</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" ref="T33" si="200">T13/P13-1</f>
+        <f t="shared" ref="T33" si="195">T13/P13-1</f>
         <v>8.8727272727272766E-2</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" ref="U33" si="201">U13/Q13-1</f>
+        <f t="shared" ref="U33" si="196">U13/Q13-1</f>
         <v>0.12222870478413062</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" ref="V33" si="202">V13/R13-1</f>
+        <f t="shared" ref="V33" si="197">V13/R13-1</f>
         <v>0.24010253489034472</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="203">W13/S13-1</f>
+        <f t="shared" ref="W33" si="198">W13/S13-1</f>
         <v>0.21830327321309295</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" ref="X33" si="204">X13/T13-1</f>
+        <f t="shared" ref="X33" si="199">X13/T13-1</f>
         <v>0.31476285905143619</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" ref="Y33" si="205">Y13/U13-1</f>
+        <f t="shared" ref="Y33" si="200">Y13/U13-1</f>
         <v>0.33519625682349874</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" ref="Z33" si="206">Z13/V13-1</f>
+        <f t="shared" ref="Z33" si="201">Z13/V13-1</f>
         <v>0.17903077629765729</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33" si="207">AA13/W13-1</f>
+        <f t="shared" ref="AA33" si="202">AA13/W13-1</f>
         <v>0.25759403443360007</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" ref="AB33" si="208">AB13/X13-1</f>
+        <f t="shared" ref="AB33" si="203">AB13/X13-1</f>
         <v>7.590692002845234E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" ref="AC33" si="209">AC13/Y13-1</f>
+        <f t="shared" ref="AC33" si="204">AC13/Y13-1</f>
         <v>9.5882410201499013E-2</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" ref="AD33" si="210">AD13/Z13-1</f>
+        <f t="shared" ref="AD33" si="205">AD13/Z13-1</f>
         <v>0.17979935716372841</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33" si="211">AE13/AA13-1</f>
+        <f t="shared" ref="AE33" si="206">AE13/AA13-1</f>
         <v>3.7931635856295776E-2</v>
       </c>
       <c r="AF33" s="8">
-        <f t="shared" ref="AF33" si="212">AF13/AB13-1</f>
+        <f t="shared" ref="AF33" si="207">AF13/AB13-1</f>
         <v>0.12013600302228933</v>
       </c>
       <c r="AG33" s="8">
-        <f t="shared" ref="AG33" si="213">AG13/AC13-1</f>
+        <f t="shared" ref="AG33" si="208">AG13/AC13-1</f>
         <v>0.10561378575235381</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" ref="AH33" si="214">AH13/AD13-1</f>
+        <f t="shared" ref="AH33" si="209">AH13/AD13-1</f>
         <v>8.2803599438619591E-2</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33" si="215">AI13/AE13-1</f>
+        <f t="shared" ref="AI33" si="210">AI13/AE13-1</f>
         <v>0.13887255313786451</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33" si="216">AJ13/AF13-1</f>
+        <f t="shared" ref="AJ33" si="211">AJ13/AF13-1</f>
         <v>0.16424957841483989</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" ref="AK33" si="217">AK13/AG13-1</f>
+        <f t="shared" ref="AK33" si="212">AK13/AG13-1</f>
         <v>0.21724110227364024</v>
       </c>
       <c r="AL33" s="8">
-        <f t="shared" ref="AL33" si="218">AL13/AH13-1</f>
-        <v>0.25</v>
-      </c>
+        <f t="shared" ref="AL33" si="213">AL13/AH13-1</f>
+        <v>0.41598048185422387</v>
+      </c>
+      <c r="AM33" s="8"/>
       <c r="AN33" s="8"/>
-      <c r="AO33" s="8">
-        <f t="shared" ref="AO33:BB35" si="219">AO13/AN13-1</f>
+      <c r="AO33" s="8"/>
+      <c r="AP33" s="8"/>
+      <c r="AR33" s="8"/>
+      <c r="AS33" s="8">
+        <f t="shared" ref="AS33:BF35" si="214">AS13/AR13-1</f>
         <v>0.28836090225563904</v>
       </c>
-      <c r="AP33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AT33" s="8">
+        <f t="shared" si="214"/>
         <v>0.21471590643820915</v>
       </c>
-      <c r="AQ33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AU33" s="8">
+        <f t="shared" si="214"/>
         <v>5.9766315627642452E-2</v>
       </c>
-      <c r="AR33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AV33" s="8">
+        <f t="shared" si="214"/>
         <v>0.13777971203713779</v>
       </c>
-      <c r="AS33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AW33" s="8">
+        <f t="shared" si="214"/>
         <v>0.25908453397934461</v>
       </c>
-      <c r="AT33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AX33" s="8">
+        <f t="shared" si="214"/>
         <v>0.15005063291139242</v>
       </c>
-      <c r="AU33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AY33" s="8">
+        <f t="shared" si="214"/>
         <v>8.583001298787063E-2</v>
       </c>
-      <c r="AV33" s="8">
-        <f t="shared" si="219"/>
-        <v>0.19429915257673436</v>
-      </c>
-      <c r="AW33" s="8">
-        <f t="shared" si="219"/>
+      <c r="AZ33" s="8">
+        <f t="shared" si="214"/>
+        <v>0.23843409155414985</v>
+      </c>
+      <c r="BA33" s="8">
+        <f t="shared" si="214"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AX33" s="8">
-        <f t="shared" si="219"/>
+      <c r="BB33" s="8">
+        <f t="shared" si="214"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AY33" s="8">
-        <f t="shared" si="219"/>
+      <c r="BC33" s="8">
+        <f t="shared" si="214"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ33" s="8">
-        <f t="shared" si="219"/>
+      <c r="BD33" s="8">
+        <f t="shared" si="214"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA33" s="8">
-        <f t="shared" si="219"/>
+      <c r="BE33" s="8">
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB33" s="8">
-        <f t="shared" si="219"/>
+      <c r="BF33" s="8">
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC33" s="8">
-        <f t="shared" ref="BC33" si="220">BC13/BB13-1</f>
+      <c r="BG33" s="8">
+        <f t="shared" ref="BG33" si="215">BG13/BF13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD33" s="8">
-        <f t="shared" ref="BD33" si="221">BD13/BC13-1</f>
+      <c r="BH33" s="8">
+        <f t="shared" ref="BH33" si="216">BH13/BG13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE33" s="8">
-        <f t="shared" ref="BE33" si="222">BE13/BD13-1</f>
+      <c r="BI33" s="8">
+        <f t="shared" ref="BI33" si="217">BI13/BH13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF33" s="8">
-        <f t="shared" ref="BF33" si="223">BF13/BE13-1</f>
+      <c r="BJ33" s="8">
+        <f t="shared" ref="BJ33" si="218">BJ13/BI13-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BH33" t="s">
+      <c r="BL33" t="s">
         <v>45</v>
       </c>
-      <c r="BI33" s="8">
+      <c r="BM33" s="8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="34" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="8">
-        <f t="shared" ref="C34:F34" si="224">C14/C10</f>
+        <f t="shared" ref="C34:F34" si="219">C14/C10</f>
         <v>0.10682828282828283</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="224"/>
+        <f t="shared" si="219"/>
         <v>0.11138023836985775</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="224"/>
+        <f t="shared" si="219"/>
         <v>0.10953478323491286</v>
       </c>
       <c r="F34" s="8">
-        <f t="shared" si="224"/>
+        <f t="shared" si="219"/>
         <v>0.13371804417969718</v>
       </c>
       <c r="G34" s="8">
@@ -6770,214 +6915,218 @@
         <v>0.11571309317408335</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" ref="H34:R34" si="225">H14/H10</f>
+        <f t="shared" ref="H34:R34" si="220">H14/H10</f>
         <v>0.11574853783262394</v>
       </c>
       <c r="I34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.11407824540604623</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.12985029025358999</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.10746030435620132</v>
+      </c>
+      <c r="L34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.10815529991783072</v>
+      </c>
+      <c r="M34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.11380527914269488</v>
+      </c>
+      <c r="N34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.1245360824742268</v>
+      </c>
+      <c r="O34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.10933210233484779</v>
+      </c>
+      <c r="P34" s="8">
+        <f t="shared" si="220"/>
+        <v>0.10186176462908322</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="220"/>
+        <v>9.1633638706603432E-2</v>
+      </c>
+      <c r="R34" s="8">
+        <f t="shared" si="220"/>
+        <v>9.3395198425252207E-2</v>
+      </c>
+      <c r="S34" s="8">
+        <f t="shared" ref="S34:V34" si="221">S14/S10</f>
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="T34" s="8">
+        <f t="shared" si="221"/>
+        <v>8.1642983693097582E-2</v>
+      </c>
+      <c r="U34" s="8">
+        <f t="shared" si="221"/>
+        <v>8.4707761294880057E-2</v>
+      </c>
+      <c r="V34" s="8">
+        <f t="shared" si="221"/>
+        <v>0.10094922004646532</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" ref="W34:AE34" si="222">W14/W10</f>
+        <v>8.5647909896928442E-2</v>
+      </c>
+      <c r="X34" s="8">
+        <f t="shared" si="222"/>
+        <v>9.514242663413934E-2</v>
+      </c>
+      <c r="Y34" s="8">
+        <f t="shared" si="222"/>
+        <v>0.10028657442250911</v>
+      </c>
+      <c r="Z34" s="8">
+        <f t="shared" si="222"/>
+        <v>9.4453503050704823E-2</v>
+      </c>
+      <c r="AA34" s="8">
+        <f t="shared" si="222"/>
+        <v>9.3613423703555104E-2</v>
+      </c>
+      <c r="AB34" s="8">
+        <f t="shared" si="222"/>
+        <v>9.0893249691705535E-2</v>
+      </c>
+      <c r="AC34" s="8">
+        <f t="shared" si="222"/>
+        <v>8.9760473576467215E-2</v>
+      </c>
+      <c r="AD34" s="8">
+        <f t="shared" si="222"/>
+        <v>8.9433437608620089E-2</v>
+      </c>
+      <c r="AE34" s="8">
+        <f t="shared" si="222"/>
+        <v>7.9787432175716114E-2</v>
+      </c>
+      <c r="AF34" s="8">
+        <f t="shared" ref="AF34:AH34" si="223">AF14/AF10</f>
+        <v>8.0149158622642852E-2</v>
+      </c>
+      <c r="AG34" s="8">
+        <f t="shared" si="223"/>
+        <v>8.1875651425205059E-2</v>
+      </c>
+      <c r="AH34" s="8">
+        <f t="shared" si="223"/>
+        <v>7.6325037058536938E-2</v>
+      </c>
+      <c r="AI34" s="8">
+        <f t="shared" ref="AI34:AL34" si="224">AI14/AI10</f>
+        <v>6.8399937939136027E-2</v>
+      </c>
+      <c r="AJ34" s="8">
+        <f t="shared" si="224"/>
+        <v>7.3640436387771194E-2</v>
+      </c>
+      <c r="AK34" s="8">
+        <f t="shared" si="224"/>
+        <v>7.0398452308834736E-2</v>
+      </c>
+      <c r="AL34" s="8">
+        <f t="shared" si="224"/>
+        <v>7.2170292019538257E-2</v>
+      </c>
+      <c r="AM34" s="8"/>
+      <c r="AN34" s="8"/>
+      <c r="AO34" s="8"/>
+      <c r="AP34" s="8"/>
+      <c r="AR34" s="8">
+        <f t="shared" ref="AR34:BE34" si="225">AR14/AR10</f>
+        <v>0.11640063558556932</v>
+      </c>
+      <c r="AS34" s="8">
         <f t="shared" si="225"/>
-        <v>0.11407824540604623</v>
-      </c>
-      <c r="J34" s="8">
+        <v>0.1193766947573071</v>
+      </c>
+      <c r="AT34" s="8">
         <f t="shared" si="225"/>
-        <v>0.12985029025358999</v>
-      </c>
-      <c r="K34" s="8">
+        <v>0.11407600536275848</v>
+      </c>
+      <c r="AU34" s="8">
         <f t="shared" si="225"/>
-        <v>0.10746030435620132</v>
-      </c>
-      <c r="L34" s="8">
+        <v>9.8319700647027566E-2</v>
+      </c>
+      <c r="AV34" s="8">
         <f t="shared" si="225"/>
-        <v>0.10815529991783072</v>
-      </c>
-      <c r="M34" s="8">
+        <v>8.823002258325334E-2</v>
+      </c>
+      <c r="AW34" s="8">
         <f t="shared" si="225"/>
-        <v>0.11380527914269488</v>
-      </c>
-      <c r="N34" s="8">
+        <v>9.3930758460733427E-2</v>
+      </c>
+      <c r="AX34" s="8">
         <f t="shared" si="225"/>
-        <v>0.1245360824742268</v>
-      </c>
-      <c r="O34" s="8">
+        <v>9.0818298340240869E-2</v>
+      </c>
+      <c r="AY34" s="8">
         <f t="shared" si="225"/>
-        <v>0.10933210233484779</v>
-      </c>
-      <c r="P34" s="8">
+        <v>7.94473427080893E-2</v>
+      </c>
+      <c r="AZ34" s="8">
         <f t="shared" si="225"/>
-        <v>0.10186176462908322</v>
-      </c>
-      <c r="Q34" s="8">
+        <v>7.1227497045944249E-2</v>
+      </c>
+      <c r="BA34" s="8">
         <f t="shared" si="225"/>
-        <v>9.1633638706603432E-2</v>
-      </c>
-      <c r="R34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BB34" s="8">
         <f t="shared" si="225"/>
-        <v>9.3395198425252207E-2</v>
-      </c>
-      <c r="S34" s="8">
-        <f t="shared" ref="S34:V34" si="226">S14/S10</f>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="T34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BC34" s="8">
+        <f t="shared" si="225"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BD34" s="8">
+        <f t="shared" si="225"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BE34" s="8">
+        <f t="shared" si="225"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BF34" s="8">
+        <f t="shared" ref="BF34:BJ34" si="226">BF14/BF10</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BG34" s="8">
         <f t="shared" si="226"/>
-        <v>8.1642983693097582E-2</v>
-      </c>
-      <c r="U34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BH34" s="8">
         <f t="shared" si="226"/>
-        <v>8.4707761294880057E-2</v>
-      </c>
-      <c r="V34" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BI34" s="8">
         <f t="shared" si="226"/>
-        <v>0.10094922004646532</v>
-      </c>
-      <c r="W34" s="8">
-        <f t="shared" ref="W34:AE34" si="227">W14/W10</f>
-        <v>8.5647909896928442E-2</v>
-      </c>
-      <c r="X34" s="8">
-        <f t="shared" si="227"/>
-        <v>9.514242663413934E-2</v>
-      </c>
-      <c r="Y34" s="8">
-        <f t="shared" si="227"/>
-        <v>0.10028657442250911</v>
-      </c>
-      <c r="Z34" s="8">
-        <f t="shared" si="227"/>
-        <v>9.4453503050704823E-2</v>
-      </c>
-      <c r="AA34" s="8">
-        <f t="shared" si="227"/>
-        <v>9.3613423703555104E-2</v>
-      </c>
-      <c r="AB34" s="8">
-        <f t="shared" si="227"/>
-        <v>9.0893249691705535E-2</v>
-      </c>
-      <c r="AC34" s="8">
-        <f t="shared" si="227"/>
-        <v>8.9760473576467215E-2</v>
-      </c>
-      <c r="AD34" s="8">
-        <f t="shared" si="227"/>
-        <v>8.9433437608620089E-2</v>
-      </c>
-      <c r="AE34" s="8">
-        <f t="shared" si="227"/>
-        <v>7.9787432175716114E-2</v>
-      </c>
-      <c r="AF34" s="8">
-        <f t="shared" ref="AF34:AH34" si="228">AF14/AF10</f>
-        <v>8.0149158622642852E-2</v>
-      </c>
-      <c r="AG34" s="8">
-        <f t="shared" si="228"/>
-        <v>8.1875651425205059E-2</v>
-      </c>
-      <c r="AH34" s="8">
-        <f t="shared" si="228"/>
-        <v>7.6325037058536938E-2</v>
-      </c>
-      <c r="AI34" s="8">
-        <f t="shared" ref="AI34:AL34" si="229">AI14/AI10</f>
-        <v>6.8399937939136027E-2</v>
-      </c>
-      <c r="AJ34" s="8">
-        <f t="shared" si="229"/>
-        <v>7.3640436387771194E-2</v>
-      </c>
-      <c r="AK34" s="8">
-        <f t="shared" si="229"/>
-        <v>7.0398452308834736E-2</v>
-      </c>
-      <c r="AL34" s="8">
-        <f t="shared" si="229"/>
-        <v>7.4999999999999983E-2</v>
-      </c>
-      <c r="AN34" s="8">
-        <f t="shared" ref="AN34:BA34" si="230">AN14/AN10</f>
-        <v>0.11640063558556932</v>
-      </c>
-      <c r="AO34" s="8">
-        <f t="shared" si="230"/>
-        <v>0.1193766947573071</v>
-      </c>
-      <c r="AP34" s="8">
-        <f t="shared" si="230"/>
-        <v>0.11407600536275848</v>
-      </c>
-      <c r="AQ34" s="8">
-        <f t="shared" si="230"/>
-        <v>9.8319700647027566E-2</v>
-      </c>
-      <c r="AR34" s="8">
-        <f t="shared" si="230"/>
-        <v>8.823002258325334E-2</v>
-      </c>
-      <c r="AS34" s="8">
-        <f t="shared" si="230"/>
-        <v>9.3930758460733427E-2</v>
-      </c>
-      <c r="AT34" s="8">
-        <f t="shared" si="230"/>
-        <v>9.0818298340240869E-2</v>
-      </c>
-      <c r="AU34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.94473427080893E-2</v>
-      </c>
-      <c r="AV34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.1999583835062497E-2</v>
-      </c>
-      <c r="AW34" s="8">
-        <f t="shared" si="230"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AX34" s="8">
-        <f t="shared" si="230"/>
+      <c r="BJ34" s="8">
+        <f t="shared" si="226"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AY34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AZ34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BA34" s="8">
-        <f t="shared" si="230"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BB34" s="8">
-        <f t="shared" ref="BB34:BF34" si="231">BB14/BB10</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BC34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BD34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BE34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BF34" s="8">
-        <f t="shared" si="231"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BH34" t="s">
+      <c r="BL34" t="s">
         <v>46</v>
       </c>
-      <c r="BI34" s="1">
-        <f>NPV(BI33,AV20:GK20)</f>
-        <v>2925756.5309859086</v>
+      <c r="BM34" s="1">
+        <f>NPV(BM33,BA20:GO20)</f>
+        <v>2968657.6109614405</v>
       </c>
     </row>
-    <row r="35" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>59</v>
       </c>
@@ -6986,232 +7135,236 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
-        <f t="shared" ref="G35" si="232">G15/C15-1</f>
+        <f t="shared" ref="G35" si="227">G15/C15-1</f>
         <v>-0.22098833981121602</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" ref="H35" si="233">H15/D15-1</f>
+        <f t="shared" ref="H35" si="228">H15/D15-1</f>
         <v>3.7647058823529367E-2</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35" si="234">I15/E15-1</f>
+        <f t="shared" ref="I35" si="229">I15/E15-1</f>
         <v>9.9059561128526541E-2</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" ref="J35" si="235">J15/F15-1</f>
+        <f t="shared" ref="J35" si="230">J15/F15-1</f>
         <v>0.12781531531531543</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" ref="K35" si="236">K15/G15-1</f>
+        <f t="shared" ref="K35" si="231">K15/G15-1</f>
         <v>1.6977904490377762</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" ref="L35" si="237">L15/H15-1</f>
+        <f t="shared" ref="L35" si="232">L15/H15-1</f>
         <v>0.15816326530612246</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" ref="M35" si="238">M15/I15-1</f>
+        <f t="shared" ref="M35" si="233">M15/I15-1</f>
         <v>0.47803764974329721</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" ref="N35" si="239">N15/J15-1</f>
+        <f t="shared" ref="N35" si="234">N15/J15-1</f>
         <v>0.41238142785821275</v>
       </c>
       <c r="O35" s="8">
-        <f t="shared" ref="O35" si="240">O15/K15-1</f>
+        <f t="shared" ref="O35" si="235">O15/K15-1</f>
         <v>-0.23910171730515195</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" ref="P35" si="241">P15/L15-1</f>
+        <f t="shared" ref="P35" si="236">P15/L15-1</f>
         <v>0.26529613313754274</v>
       </c>
       <c r="Q35" s="8">
-        <f t="shared" ref="Q35" si="242">Q15/M15-1</f>
+        <f t="shared" ref="Q35" si="237">Q15/M15-1</f>
         <v>6.3681976071015001E-2</v>
       </c>
       <c r="R35" s="8">
-        <f t="shared" ref="R35" si="243">R15/N15-1</f>
+        <f t="shared" ref="R35" si="238">R15/N15-1</f>
         <v>7.0696359137500941E-4</v>
       </c>
       <c r="S35" s="8">
-        <f t="shared" ref="S35" si="244">S15/O15-1</f>
+        <f t="shared" ref="S35" si="239">S15/O15-1</f>
         <v>-3.7152777777777812E-2</v>
       </c>
       <c r="T35" s="8">
-        <f t="shared" ref="T35" si="245">T15/P15-1</f>
+        <f t="shared" ref="T35" si="240">T15/P15-1</f>
         <v>7.2727272727272751E-2</v>
       </c>
       <c r="U35" s="8">
-        <f t="shared" ref="U35" si="246">U15/Q15-1</f>
+        <f t="shared" ref="U35" si="241">U15/Q15-1</f>
         <v>0.1814223512336719</v>
       </c>
       <c r="V35" s="8">
-        <f t="shared" ref="V35" si="247">V15/R15-1</f>
+        <f t="shared" ref="V35" si="242">V15/R15-1</f>
         <v>0.46238078417520301</v>
       </c>
       <c r="W35" s="8">
-        <f t="shared" ref="W35" si="248">W15/S15-1</f>
+        <f t="shared" ref="W35" si="243">W15/S15-1</f>
         <v>0.21673278038225741</v>
       </c>
       <c r="X35" s="8">
-        <f t="shared" ref="X35" si="249">X15/T15-1</f>
+        <f t="shared" ref="X35" si="244">X15/T15-1</f>
         <v>0.31878831590335377</v>
       </c>
       <c r="Y35" s="8">
-        <f t="shared" ref="Y35" si="250">Y15/U15-1</f>
+        <f t="shared" ref="Y35" si="245">Y15/U15-1</f>
         <v>0.10472972972972983</v>
       </c>
       <c r="Z35" s="8">
-        <f t="shared" ref="Z35" si="251">Z15/V15-1</f>
+        <f t="shared" ref="Z35" si="246">Z15/V15-1</f>
         <v>0.23091787439613531</v>
       </c>
       <c r="AA35" s="8">
-        <f t="shared" ref="AA35" si="252">AA15/W15-1</f>
+        <f t="shared" ref="AA35" si="247">AA15/W15-1</f>
         <v>0.11410788381742742</v>
       </c>
       <c r="AB35" s="8">
-        <f t="shared" ref="AB35" si="253">AB15/X15-1</f>
+        <f t="shared" ref="AB35" si="248">AB15/X15-1</f>
         <v>-4.8126879956248314E-2</v>
       </c>
       <c r="AC35" s="8">
-        <f t="shared" ref="AC35" si="254">AC15/Y15-1</f>
+        <f t="shared" ref="AC35" si="249">AC15/Y15-1</f>
         <v>0.10619961078676665</v>
       </c>
       <c r="AD35" s="8">
-        <f t="shared" ref="AD35" si="255">AD15/Z15-1</f>
+        <f t="shared" ref="AD35" si="250">AD15/Z15-1</f>
         <v>2.1585557299842906E-2</v>
       </c>
       <c r="AE35" s="8">
-        <f t="shared" ref="AE35" si="256">AE15/AA15-1</f>
+        <f t="shared" ref="AE35" si="251">AE15/AA15-1</f>
         <v>-0.19499866985900505</v>
       </c>
       <c r="AF35" s="8">
-        <f t="shared" ref="AF35" si="257">AF15/AB15-1</f>
+        <f t="shared" ref="AF35" si="252">AF15/AB15-1</f>
         <v>-9.2789428325193879E-2</v>
       </c>
       <c r="AG35" s="8">
-        <f t="shared" ref="AG35" si="258">AG15/AC15-1</f>
+        <f t="shared" ref="AG35" si="253">AG15/AC15-1</f>
         <v>-9.5501382256848455E-2</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" ref="AH35" si="259">AH15/AD15-1</f>
+        <f t="shared" ref="AH35" si="254">AH15/AD15-1</f>
         <v>-0.153860929696504</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" ref="AI35" si="260">AI15/AE15-1</f>
+        <f t="shared" ref="AI35" si="255">AI15/AE15-1</f>
         <v>0.16953073364177129</v>
       </c>
       <c r="AJ35" s="8">
-        <f t="shared" ref="AJ35" si="261">AJ15/AF15-1</f>
+        <f t="shared" ref="AJ35" si="256">AJ15/AF15-1</f>
         <v>0.64946168461051301</v>
       </c>
       <c r="AK35" s="8">
-        <f t="shared" ref="AK35" si="262">AK15/AG15-1</f>
+        <f t="shared" ref="AK35" si="257">AK15/AG15-1</f>
         <v>1.0541817171436509</v>
       </c>
       <c r="AL35" s="8">
-        <f t="shared" ref="AL35" si="263">AL15/AH15-1</f>
-        <v>0.44999999999999996</v>
-      </c>
+        <f t="shared" ref="AL35" si="258">AL15/AH15-1</f>
+        <v>0.21248581157775259</v>
+      </c>
+      <c r="AM35" s="8"/>
       <c r="AN35" s="8"/>
-      <c r="AO35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AO35" s="8"/>
+      <c r="AP35" s="8"/>
+      <c r="AR35" s="8"/>
+      <c r="AS35" s="8">
+        <f t="shared" si="214"/>
         <v>7.4214202561118103E-3</v>
       </c>
-      <c r="AP35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AT35" s="8">
+        <f t="shared" si="214"/>
         <v>0.3440704896721074</v>
       </c>
-      <c r="AQ35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AU35" s="8">
+        <f t="shared" si="214"/>
         <v>0.18774852229983874</v>
       </c>
-      <c r="AR35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AV35" s="8">
+        <f t="shared" si="214"/>
         <v>0.17100977198697076</v>
       </c>
-      <c r="AS35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AW35" s="8">
+        <f t="shared" si="214"/>
         <v>0.21495904806057786</v>
       </c>
-      <c r="AT35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AX35" s="8">
+        <f t="shared" si="214"/>
         <v>4.4581531416942211E-2</v>
       </c>
-      <c r="AU35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AY35" s="8">
+        <f t="shared" si="214"/>
         <v>-0.13619482496194824</v>
       </c>
-      <c r="AV35" s="8">
-        <f t="shared" si="219"/>
-        <v>0.58783831406822662</v>
-      </c>
-      <c r="AW35" s="8">
-        <f t="shared" si="219"/>
+      <c r="AZ35" s="8">
+        <f t="shared" si="214"/>
+        <v>0.51409641950944462</v>
+      </c>
+      <c r="BA35" s="8">
+        <f t="shared" si="214"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AX35" s="8">
-        <f t="shared" si="219"/>
+      <c r="BB35" s="8">
+        <f t="shared" si="214"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AY35" s="8">
-        <f t="shared" si="219"/>
+      <c r="BC35" s="8">
+        <f t="shared" si="214"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ35" s="8">
-        <f t="shared" si="219"/>
+      <c r="BD35" s="8">
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA35" s="8">
-        <f t="shared" si="219"/>
+      <c r="BE35" s="8">
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB35" s="8">
-        <f t="shared" si="219"/>
+      <c r="BF35" s="8">
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC35" s="8">
-        <f t="shared" ref="BC35" si="264">BC15/BB15-1</f>
+      <c r="BG35" s="8">
+        <f t="shared" ref="BG35" si="259">BG15/BF15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD35" s="8">
-        <f t="shared" ref="BD35" si="265">BD15/BC15-1</f>
+      <c r="BH35" s="8">
+        <f t="shared" ref="BH35" si="260">BH15/BG15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE35" s="8">
-        <f t="shared" ref="BE35" si="266">BE15/BD15-1</f>
+      <c r="BI35" s="8">
+        <f t="shared" ref="BI35" si="261">BI15/BH15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF35" s="8">
-        <f t="shared" ref="BF35" si="267">BF15/BE15-1</f>
+      <c r="BJ35" s="8">
+        <f t="shared" ref="BJ35" si="262">BJ15/BI15-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BH35" t="s">
+      <c r="BL35" t="s">
         <v>47</v>
       </c>
-      <c r="BI35" s="1">
+      <c r="BM35" s="1">
         <f>Main!D8</f>
-        <v>122756</v>
+        <v>148983</v>
       </c>
     </row>
-    <row r="36" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="8">
-        <f t="shared" ref="C36:F36" si="268">C19/C18</f>
+        <f t="shared" ref="C36:F36" si="263">C19/C18</f>
         <v>0.20428215280832968</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.11992127091241389</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.15628524877804237</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>1.3924561624826541</v>
       </c>
       <c r="G36" s="8">
@@ -7219,214 +7372,218 @@
         <v>0.10831831546998008</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" ref="H36:R36" si="269">H19/H18</f>
+        <f t="shared" ref="H36:R36" si="264">H19/H18</f>
         <v>0.1098427740684902</v>
       </c>
       <c r="I36" s="8">
+        <f t="shared" si="264"/>
+        <v>8.8366557572151144E-2</v>
+      </c>
+      <c r="J36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.11159650516282764</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.18278909894426712</v>
+      </c>
+      <c r="L36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.18111467852144564</v>
+      </c>
+      <c r="M36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.1808066759388039</v>
+      </c>
+      <c r="N36" s="8">
+        <f t="shared" si="264"/>
+        <v>3.0829596412556052E-3</v>
+      </c>
+      <c r="O36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.11873146835116669</v>
+      </c>
+      <c r="P36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.15923643832306392</v>
+      </c>
+      <c r="Q36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.15496368038740921</v>
+      </c>
+      <c r="R36" s="8">
+        <f t="shared" si="264"/>
+        <v>0.18524265610787094</v>
+      </c>
+      <c r="S36" s="8">
+        <f t="shared" ref="S36:V36" si="265">S19/S18</f>
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="T36" s="8">
+        <f t="shared" si="265"/>
+        <v>0.15754357938260583</v>
+      </c>
+      <c r="U36" s="8">
+        <f t="shared" si="265"/>
+        <v>0.17898022892819979</v>
+      </c>
+      <c r="V36" s="8">
+        <f t="shared" si="265"/>
+        <v>0.15408573067781328</v>
+      </c>
+      <c r="W36" s="8">
+        <f t="shared" ref="W36:AE36" si="266">W19/W18</f>
+        <v>0.13193197422625963</v>
+      </c>
+      <c r="X36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.15840959293152415</v>
+      </c>
+      <c r="Y36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.14310355448777182</v>
+      </c>
+      <c r="Z36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.20545868081880211</v>
+      </c>
+      <c r="AA36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.17324910738808019</v>
+      </c>
+      <c r="AB36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.16139341642697347</v>
+      </c>
+      <c r="AC36" s="8">
+        <f t="shared" si="266"/>
+        <v>7.1142142756050381E-2</v>
+      </c>
+      <c r="AD36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.15258889070948714</v>
+      </c>
+      <c r="AE36" s="8">
+        <f t="shared" si="266"/>
+        <v>0.16432986049796927</v>
+      </c>
+      <c r="AF36" s="8">
+        <f t="shared" ref="AF36:AH36" si="267">AF19/AF18</f>
+        <v>0.14271714275343908</v>
+      </c>
+      <c r="AG36" s="8">
+        <f t="shared" si="267"/>
+        <v>0.17047246577934777</v>
+      </c>
+      <c r="AH36" s="8">
+        <f t="shared" si="267"/>
+        <v>0.17699965884067859</v>
+      </c>
+      <c r="AI36" s="8">
+        <f t="shared" ref="AI36:AL36" si="268">AI19/AI18</f>
+        <v>0.173466701763622</v>
+      </c>
+      <c r="AJ36" s="8">
+        <f t="shared" si="268"/>
+        <v>0.16906845843279403</v>
+      </c>
+      <c r="AK36" s="8">
+        <f t="shared" si="268"/>
+        <v>0.20478777820719757</v>
+      </c>
+      <c r="AL36" s="8">
+        <f t="shared" si="268"/>
+        <v>0.11918091878211519</v>
+      </c>
+      <c r="AM36" s="8"/>
+      <c r="AN36" s="8"/>
+      <c r="AO36" s="8"/>
+      <c r="AP36" s="8"/>
+      <c r="AR36" s="8">
+        <f t="shared" ref="AR36:BE36" si="269">AR19/AR18</f>
+        <v>0.14515047925464172</v>
+      </c>
+      <c r="AS36" s="8">
         <f t="shared" si="269"/>
-        <v>8.8366557572151144E-2</v>
-      </c>
-      <c r="J36" s="8">
+        <v>0.10446678671468587</v>
+      </c>
+      <c r="AT36" s="8">
         <f t="shared" si="269"/>
-        <v>0.11159650516282764</v>
-      </c>
-      <c r="K36" s="8">
+        <v>0.12706889915319478</v>
+      </c>
+      <c r="AU36" s="8">
         <f t="shared" si="269"/>
-        <v>0.18278909894426712</v>
-      </c>
-      <c r="L36" s="8">
+        <v>0.16158587028457974</v>
+      </c>
+      <c r="AV36" s="8">
         <f t="shared" si="269"/>
-        <v>0.18111467852144564</v>
-      </c>
-      <c r="M36" s="8">
+        <v>0.16209792073929269</v>
+      </c>
+      <c r="AW36" s="8">
         <f t="shared" si="269"/>
-        <v>0.1808066759388039</v>
-      </c>
-      <c r="N36" s="8">
+        <v>0.1592081650964558</v>
+      </c>
+      <c r="AX36" s="8">
         <f t="shared" si="269"/>
-        <v>3.0829596412556052E-3</v>
-      </c>
-      <c r="O36" s="8">
+        <v>0.13908559562280529</v>
+      </c>
+      <c r="AY36" s="8">
         <f t="shared" si="269"/>
-        <v>0.11873146835116669</v>
-      </c>
-      <c r="P36" s="8">
+        <v>0.16439510912657013</v>
+      </c>
+      <c r="AZ36" s="8">
         <f t="shared" si="269"/>
-        <v>0.15923643832306392</v>
-      </c>
-      <c r="Q36" s="8">
+        <v>0.16783146336242177</v>
+      </c>
+      <c r="BA36" s="8">
         <f t="shared" si="269"/>
-        <v>0.15496368038740921</v>
-      </c>
-      <c r="R36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BB36" s="8">
         <f t="shared" si="269"/>
-        <v>0.18524265610787094</v>
-      </c>
-      <c r="S36" s="8">
-        <f t="shared" ref="S36:V36" si="270">S19/S18</f>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="T36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BC36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.16</v>
+      </c>
+      <c r="BD36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.16</v>
+      </c>
+      <c r="BE36" s="8">
+        <f t="shared" si="269"/>
+        <v>0.16</v>
+      </c>
+      <c r="BF36" s="8">
+        <f t="shared" ref="BF36:BJ36" si="270">BF19/BF18</f>
+        <v>0.16</v>
+      </c>
+      <c r="BG36" s="8">
         <f t="shared" si="270"/>
-        <v>0.15754357938260583</v>
-      </c>
-      <c r="U36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BH36" s="8">
         <f t="shared" si="270"/>
-        <v>0.17898022892819979</v>
-      </c>
-      <c r="V36" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="BI36" s="8">
         <f t="shared" si="270"/>
-        <v>0.15408573067781328</v>
-      </c>
-      <c r="W36" s="8">
-        <f t="shared" ref="W36:AE36" si="271">W19/W18</f>
-        <v>0.13193197422625963</v>
-      </c>
-      <c r="X36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.15840959293152415</v>
-      </c>
-      <c r="Y36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.14310355448777182</v>
-      </c>
-      <c r="Z36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.20545868081880211</v>
-      </c>
-      <c r="AA36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.17324910738808019</v>
-      </c>
-      <c r="AB36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.16139341642697347</v>
-      </c>
-      <c r="AC36" s="8">
-        <f t="shared" si="271"/>
-        <v>7.1142142756050381E-2</v>
-      </c>
-      <c r="AD36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.15258889070948714</v>
-      </c>
-      <c r="AE36" s="8">
-        <f t="shared" si="271"/>
-        <v>0.16432986049796927</v>
-      </c>
-      <c r="AF36" s="8">
-        <f t="shared" ref="AF36:AH36" si="272">AF19/AF18</f>
-        <v>0.14271714275343908</v>
-      </c>
-      <c r="AG36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.17047246577934777</v>
-      </c>
-      <c r="AH36" s="8">
-        <f t="shared" si="272"/>
-        <v>0.17699965884067859</v>
-      </c>
-      <c r="AI36" s="8">
-        <f t="shared" ref="AI36:AL36" si="273">AI19/AI18</f>
-        <v>0.173466701763622</v>
-      </c>
-      <c r="AJ36" s="8">
-        <f t="shared" si="273"/>
-        <v>0.16906845843279403</v>
-      </c>
-      <c r="AK36" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20478777820719757</v>
-      </c>
-      <c r="AL36" s="8">
-        <f t="shared" si="273"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN36" s="8">
-        <f t="shared" ref="AN36:BA36" si="274">AN19/AN18</f>
-        <v>0.14515047925464172</v>
-      </c>
-      <c r="AO36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.10446678671468587</v>
-      </c>
-      <c r="AP36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.12706889915319478</v>
-      </c>
-      <c r="AQ36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16158587028457974</v>
-      </c>
-      <c r="AR36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16209792073929269</v>
-      </c>
-      <c r="AS36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.1592081650964558</v>
-      </c>
-      <c r="AT36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.13908559562280529</v>
-      </c>
-      <c r="AU36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16439510912657013</v>
-      </c>
-      <c r="AV36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.17587281697185667</v>
-      </c>
-      <c r="AW36" s="8">
-        <f t="shared" si="274"/>
         <v>0.16</v>
       </c>
-      <c r="AX36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16</v>
-      </c>
-      <c r="AY36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16</v>
-      </c>
-      <c r="AZ36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16</v>
-      </c>
-      <c r="BA36" s="8">
-        <f t="shared" si="274"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB36" s="8">
-        <f t="shared" ref="BB36:BF36" si="275">BB19/BB18</f>
-        <v>0.16</v>
-      </c>
-      <c r="BC36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16</v>
-      </c>
-      <c r="BD36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16</v>
-      </c>
-      <c r="BE36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16</v>
-      </c>
-      <c r="BF36" s="8">
-        <f t="shared" si="275"/>
-        <v>0.16</v>
-      </c>
-      <c r="BH36" t="s">
+      <c r="BJ36" s="8">
+        <f t="shared" si="270"/>
+        <v>0.15999999999999998</v>
+      </c>
+      <c r="BL36" t="s">
         <v>48</v>
       </c>
-      <c r="BI36" s="1">
-        <f>BI34+BI35</f>
-        <v>3048512.5309859086</v>
+      <c r="BM36" s="1">
+        <f>BM34+BM35</f>
+        <v>3117640.6109614405</v>
       </c>
     </row>
-    <row r="37" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>60</v>
       </c>
@@ -7435,263 +7592,273 @@
         <v>0.21923232323232322</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" ref="D37:V37" si="276">D20/D10</f>
+        <f t="shared" ref="D37:V37" si="271">D20/D10</f>
         <v>0.24067666282199154</v>
       </c>
       <c r="E37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.24240241970329829</v>
+      </c>
+      <c r="F37" s="8">
+        <f t="shared" si="271"/>
+        <v>-9.6518987341772153E-2</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.30183651191164196</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.25311571791652632</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.2724362774155305</v>
+      </c>
+      <c r="J37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.22782360729198492</v>
+      </c>
+      <c r="K37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.18319161231734502</v>
+      </c>
+      <c r="L37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.25541803615447822</v>
+      </c>
+      <c r="M37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.17452282772414135</v>
+      </c>
+      <c r="N37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.23160065111231687</v>
+      </c>
+      <c r="O37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.16608761145800433</v>
+      </c>
+      <c r="P37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.1817113612032274</v>
+      </c>
+      <c r="Q37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.24943148593333767</v>
+      </c>
+      <c r="R37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.26761924847973567</v>
+      </c>
+      <c r="S37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="T37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.32414940159814876</v>
+      </c>
+      <c r="U37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.29079517184188702</v>
+      </c>
+      <c r="V37" s="8">
+        <f t="shared" si="271"/>
+        <v>0.2740391636242947</v>
+      </c>
+      <c r="W37" s="8">
+        <f t="shared" ref="W37:AE37" si="272">W20/W10</f>
+        <v>0.24166678919586537</v>
+      </c>
+      <c r="X37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.22963335007533903</v>
+      </c>
+      <c r="Y37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.20132576854049672</v>
+      </c>
+      <c r="Z37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.17915001051967178</v>
+      </c>
+      <c r="AA37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.21567054035851949</v>
+      </c>
+      <c r="AB37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.2462066377137955</v>
+      </c>
+      <c r="AC37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.25672486406842865</v>
+      </c>
+      <c r="AD37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.23968253968253969</v>
+      </c>
+      <c r="AE37" s="8">
+        <f t="shared" si="272"/>
+        <v>0.29379555246526529</v>
+      </c>
+      <c r="AF37" s="8">
+        <f t="shared" ref="AF37:AH37" si="273">AF20/AF10</f>
+        <v>0.27871657501593072</v>
+      </c>
+      <c r="AG37" s="8">
+        <f t="shared" si="273"/>
+        <v>0.29796755336022113</v>
+      </c>
+      <c r="AH37" s="8">
+        <f t="shared" si="273"/>
+        <v>0.27507282132083882</v>
+      </c>
+      <c r="AI37" s="8">
+        <f t="shared" ref="AI37:AL37" si="274">AI20/AI10</f>
+        <v>0.38278254316554733</v>
+      </c>
+      <c r="AJ37" s="8">
+        <f t="shared" si="274"/>
+        <v>0.29240469573153027</v>
+      </c>
+      <c r="AK37" s="8">
+        <f t="shared" si="274"/>
+        <v>0.34177202821800556</v>
+      </c>
+      <c r="AL37" s="8">
+        <f t="shared" si="274"/>
+        <v>0.30269353761816076</v>
+      </c>
+      <c r="AM37" s="8"/>
+      <c r="AN37" s="8"/>
+      <c r="AO37" s="8"/>
+      <c r="AP37" s="8"/>
+      <c r="AR37" s="8">
+        <f t="shared" ref="AR37:BE37" si="275">AR20/AR10</f>
+        <v>0.23028240222454949</v>
+      </c>
+      <c r="AS37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.26171072731126527</v>
+      </c>
+      <c r="AT37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.22418554650092365</v>
+      </c>
+      <c r="AU37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.22209864841913798</v>
+      </c>
+      <c r="AV37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.30046480875927528</v>
+      </c>
+      <c r="AW37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.21203807153261961</v>
+      </c>
+      <c r="AX37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.24006649446638517</v>
+      </c>
+      <c r="AY37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.28603671811164</v>
+      </c>
+      <c r="AZ37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.32809877965226542</v>
+      </c>
+      <c r="BA37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.28684176788388771</v>
+      </c>
+      <c r="BB37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.29014295736460743</v>
+      </c>
+      <c r="BC37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.29302292997840401</v>
+      </c>
+      <c r="BD37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.2947481284184072</v>
+      </c>
+      <c r="BE37" s="8">
+        <f t="shared" si="275"/>
+        <v>0.29614208440053641</v>
+      </c>
+      <c r="BF37" s="8">
+        <f t="shared" ref="BF37:BJ37" si="276">BF20/BF10</f>
+        <v>0.29697130707551478</v>
+      </c>
+      <c r="BG37" s="8">
         <f t="shared" si="276"/>
-        <v>0.24240241970329829</v>
-      </c>
-      <c r="F37" s="8">
+        <v>0.29725931579504794</v>
+      </c>
+      <c r="BH37" s="8">
         <f t="shared" si="276"/>
-        <v>-9.6518987341772153E-2</v>
-      </c>
-      <c r="G37" s="8">
+        <v>0.29650993562711842</v>
+      </c>
+      <c r="BI37" s="8">
         <f t="shared" si="276"/>
-        <v>0.30183651191164196</v>
-      </c>
-      <c r="H37" s="8">
+        <v>0.29576625726646077</v>
+      </c>
+      <c r="BJ37" s="8">
         <f t="shared" si="276"/>
-        <v>0.25311571791652632</v>
-      </c>
-      <c r="I37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.2724362774155305</v>
-      </c>
-      <c r="J37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.22782360729198492</v>
-      </c>
-      <c r="K37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.18319161231734502</v>
-      </c>
-      <c r="L37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.25541803615447822</v>
-      </c>
-      <c r="M37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.17452282772414135</v>
-      </c>
-      <c r="N37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.23160065111231687</v>
-      </c>
-      <c r="O37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.16608761145800433</v>
-      </c>
-      <c r="P37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.1817113612032274</v>
-      </c>
-      <c r="Q37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.24943148593333767</v>
-      </c>
-      <c r="R37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.26761924847973567</v>
-      </c>
-      <c r="S37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="T37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.32414940159814876</v>
-      </c>
-      <c r="U37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.29079517184188702</v>
-      </c>
-      <c r="V37" s="8">
-        <f t="shared" si="276"/>
-        <v>0.2740391636242947</v>
-      </c>
-      <c r="W37" s="8">
-        <f t="shared" ref="W37:AE37" si="277">W20/W10</f>
-        <v>0.24166678919586537</v>
-      </c>
-      <c r="X37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.22963335007533903</v>
-      </c>
-      <c r="Y37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.20132576854049672</v>
-      </c>
-      <c r="Z37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.17915001051967178</v>
-      </c>
-      <c r="AA37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.21567054035851949</v>
-      </c>
-      <c r="AB37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.2462066377137955</v>
-      </c>
-      <c r="AC37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.25672486406842865</v>
-      </c>
-      <c r="AD37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.23968253968253969</v>
-      </c>
-      <c r="AE37" s="8">
-        <f t="shared" si="277"/>
-        <v>0.29379555246526529</v>
-      </c>
-      <c r="AF37" s="8">
-        <f t="shared" ref="AF37:AH37" si="278">AF20/AF10</f>
-        <v>0.27871657501593072</v>
-      </c>
-      <c r="AG37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.29796755336022113</v>
-      </c>
-      <c r="AH37" s="8">
-        <f t="shared" si="278"/>
-        <v>0.27507282132083882</v>
-      </c>
-      <c r="AI37" s="8">
-        <f t="shared" ref="AI37:AL37" si="279">AI20/AI10</f>
-        <v>0.38278254316554733</v>
-      </c>
-      <c r="AJ37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.29240469573153027</v>
-      </c>
-      <c r="AK37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.34177202821800556</v>
-      </c>
-      <c r="AL37" s="8">
-        <f t="shared" si="279"/>
-        <v>0.28052718825244599</v>
-      </c>
-      <c r="AN37" s="8">
-        <f t="shared" ref="AN37:BA37" si="280">AN20/AN10</f>
-        <v>0.23028240222454949</v>
-      </c>
-      <c r="AO37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.26171072731126527</v>
-      </c>
-      <c r="AP37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.22418554650092365</v>
-      </c>
-      <c r="AQ37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.22209864841913798</v>
-      </c>
-      <c r="AR37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.30046480875927528</v>
-      </c>
-      <c r="AS37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.21203807153261961</v>
-      </c>
-      <c r="AT37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.24006649446638517</v>
-      </c>
-      <c r="AU37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.28603671811164</v>
-      </c>
-      <c r="AV37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.32221733544930814</v>
-      </c>
-      <c r="AW37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.28755433479868059</v>
-      </c>
-      <c r="AX37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.29070908855078209</v>
-      </c>
-      <c r="AY37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.29354757870763037</v>
-      </c>
-      <c r="AZ37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.29526826601498057</v>
-      </c>
-      <c r="BA37" s="8">
-        <f t="shared" si="280"/>
-        <v>0.29664064290171399</v>
-      </c>
-      <c r="BB37" s="8">
-        <f t="shared" ref="BB37:BF37" si="281">BB20/BB10</f>
-        <v>0.29745052835951458</v>
-      </c>
-      <c r="BC37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.29773306972476565</v>
-      </c>
-      <c r="BD37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.29698862216162819</v>
-      </c>
-      <c r="BE37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.29624999896132798</v>
-      </c>
-      <c r="BF37" s="8">
-        <f t="shared" si="281"/>
-        <v>0.29551738660094518</v>
-      </c>
-      <c r="BH37" t="s">
+        <v>0.29502846502239904</v>
+      </c>
+      <c r="BL37" t="s">
         <v>49</v>
       </c>
-      <c r="BI37" s="2">
-        <f>BI36/BA21</f>
-        <v>252.23502655848986</v>
+      <c r="BM37" s="2">
+        <f>BM36/BE21</f>
+        <v>257.72014639674632</v>
       </c>
     </row>
-    <row r="38" spans="2:61" x14ac:dyDescent="0.3">
-      <c r="BH38" t="s">
+    <row r="38" spans="2:65" x14ac:dyDescent="0.3">
+      <c r="BL38" t="s">
         <v>50</v>
       </c>
-      <c r="BI38" s="2">
+      <c r="BM38" s="2">
         <f>Main!D3</f>
-        <v>296.3</v>
+        <v>329.3</v>
       </c>
     </row>
-    <row r="39" spans="2:61" x14ac:dyDescent="0.3">
-      <c r="BH39" s="6" t="s">
+    <row r="39" spans="2:65" x14ac:dyDescent="0.3">
+      <c r="BL39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BI39" s="10">
-        <f>BI37/BI38-1</f>
-        <v>-0.14871742639726682</v>
+      <c r="BM39" s="10">
+        <f>BM37/BM38-1</f>
+        <v>-0.2173697345984017</v>
       </c>
     </row>
-    <row r="40" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>90</v>
       </c>
       <c r="AG40" s="1">
         <v>181269</v>
+      </c>
+      <c r="AH40" s="1">
+        <v>183323</v>
       </c>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1">
         <v>190167</v>
       </c>
-      <c r="BH40" t="s">
+      <c r="AL40" s="1">
+        <v>190820</v>
+      </c>
+      <c r="BL40" t="s">
         <v>52</v>
       </c>
-      <c r="BI40" s="5" t="s">
-        <v>92</v>
+      <c r="BM40" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
